--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\LandingPage\Landing_MNM\documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487C0164-2099-4D1E-A564-4BE99075A98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB94B61-3610-445B-B71D-A872D03EB1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -727,58 +727,6 @@
   <dxfs count="76">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -912,6 +860,32 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1471,6 +1445,32 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2577,7 +2577,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4333,7 +4333,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6063,7 +6063,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7785,7 +7785,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11963,7 +11963,7 @@
     <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11972,42 +11972,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U4" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U4" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
   <autoFilter ref="A2:U4" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="27">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="26">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 3'!G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12016,17 +12016,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12296,14 +12296,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12333,7 +12333,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -12555,7 +12555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -12666,7 +12666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -12796,25 +12796,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -12831,7 +12831,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -12930,7 +12930,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -12982,7 +12982,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13034,7 +13034,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13086,7 +13086,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13138,7 +13138,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13190,7 +13190,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13242,7 +13242,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13346,7 +13346,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13423,28 +13423,28 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>58</v>
@@ -13462,7 +13462,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13561,7 +13561,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13638,31 +13638,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" customWidth="1"/>
+    <col min="21" max="21" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E1" s="28" t="s">
         <v>59</v>
       </c>
@@ -13683,7 +13683,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13818,7 +13818,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13905,15 +13905,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
@@ -13927,817 +13927,817 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="27"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
       <c r="D4" s="27"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="26"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="27"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="26"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="27"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="26"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="27"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="26"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="27"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="26"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="27"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="27"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="27"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="26"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="27"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="27"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="26"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="27"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="27"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="27"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="27"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="27"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="26"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="38"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="26"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="38"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="26"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="38"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="26"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="38"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="38"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="38"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="26"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="38"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="38"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="38"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="26"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="27"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="26"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="38"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="26"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="38"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="38"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="26"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="38"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="26"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="38"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="26"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="26"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="38"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="26"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="38"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="26"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="38"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="26"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="38"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="26"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="38"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="26"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="38"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="26"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="38"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="26"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="38"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="26"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="38"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="26"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="38"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="26"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="38"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="26"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="38"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="26"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="38"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="26"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="38"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="38"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="26"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="38"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="26"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="38"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="38"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="26"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="38"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="26"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="38"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="26"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="38"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="38"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
       <c r="D58" s="38"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="38"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="38"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="26"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
       <c r="D61" s="38"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="26"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
       <c r="D62" s="38"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="26"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
       <c r="D63" s="38"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="26"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
       <c r="D64" s="38"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="26"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="38"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="26"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="38"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="26"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="38"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="26"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
       <c r="D68" s="38"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="26"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
       <c r="D69" s="38"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="26"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="38"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="26"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="38"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="26"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
       <c r="D72" s="38"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="26"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="38"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="26"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="38"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="26"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="38"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="26"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="38"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="26"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="38"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="26"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="38"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="26"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="D79" s="38"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="26"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="38"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="26"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="38"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="26"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="38"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="26"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="38"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="26"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="38"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="26"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="38"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="26"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="38"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="26"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="38"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="26"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="38"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="26"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="D89" s="38"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="26"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="D90" s="38"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="26"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="D91" s="38"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="26"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="38"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="26"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="38"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="26"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="38"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="26"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="D95" s="38"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="26"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="38"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="26"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="38"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="26"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="38"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="26"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="D99" s="38"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="26"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="38"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="26"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="38"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="26"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="D102" s="38"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="26"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="38"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="26"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="D104" s="38"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="26"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
       <c r="D105" s="38"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="26"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="38"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="26"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="D107" s="38"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="26"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="38"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="26"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
       <c r="D109" s="38"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="26"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="38"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="26"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="D111" s="38"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="26"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
       <c r="D112" s="38"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="26"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
       <c r="D113" s="38"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="26"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
       <c r="D114" s="38"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="26"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
       <c r="D115" s="38"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="26"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
       <c r="D116" s="38"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="26"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
       <c r="D117" s="38"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="26"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="38"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="26"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="D119" s="38"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="26"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
       <c r="D120" s="38"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="26"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
       <c r="D121" s="38"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="26"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
       <c r="D122" s="38"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="26"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
       <c r="D123" s="38"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="26"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
       <c r="D124" s="38"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="26"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="D125" s="38"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="26"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="38"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="26"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="D127" s="38"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="26"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
       <c r="D128" s="38"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="26"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="38"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="26"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="38"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="26"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="D131" s="38"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="26"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
       <c r="D132" s="38"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="26"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
       <c r="D133" s="38"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="26"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="38"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="26"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="38"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="26"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
       <c r="D136" s="38"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="26"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
       <c r="D137" s="38"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="26"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29823"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\LandingPage\Landing_MNM\documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB94B61-3610-445B-B71D-A872D03EB1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88ADCEB-54F8-4DF3-A6BE-659BC915F320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -35,6 +35,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'NIVEL 3'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -90,7 +91,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +100,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +109,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -139,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="99">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -475,6 +476,75 @@
   <si>
     <t>Jose Alejandro Peña Angulo</t>
   </si>
+  <si>
+    <t>Sarath Milena Valencia Agudelo</t>
+  </si>
+  <si>
+    <t>Tomas Sossa Ayala</t>
+  </si>
+  <si>
+    <t>Joel Zuluaga Charis</t>
+  </si>
+  <si>
+    <t>Thiago Mendoza Cervantes</t>
+  </si>
+  <si>
+    <t>Maria Angel Verbel Gonzalez</t>
+  </si>
+  <si>
+    <t>Abraham Peñates Ramos</t>
+  </si>
+  <si>
+    <t>Alanna Sofía Barreiro Garcés</t>
+  </si>
+  <si>
+    <t>Julio Cáceres flores</t>
+  </si>
+  <si>
+    <t>Martin Laureano Hernández Ensuncho</t>
+  </si>
+  <si>
+    <t>Felipe Barreiro franco</t>
+  </si>
+  <si>
+    <t>Edinson Herrera de Oro</t>
+  </si>
+  <si>
+    <t>Esteban Sossa Uparela</t>
+  </si>
+  <si>
+    <t>Gabriel Hoyos Ruiz</t>
+  </si>
+  <si>
+    <t>Jhonatan Steven Cortez Bolivar</t>
+  </si>
+  <si>
+    <t>Juan Luis Guerra Viloria</t>
+  </si>
+  <si>
+    <t>Kaylen Jireth Núñez Hernández</t>
+  </si>
+  <si>
+    <t>Laura Andrea Montes Lopez</t>
+  </si>
+  <si>
+    <t>Lisbeth Arrieta Espejo</t>
+  </si>
+  <si>
+    <t>MAURICIO JOSE ROSSO PINTO</t>
+  </si>
+  <si>
+    <t>Nicolas Jaraba Mercado</t>
+  </si>
+  <si>
+    <t>PILAR TERESA GONZALEZ ACOSTA</t>
+  </si>
+  <si>
+    <t>Susanna Pinzon Pajaro</t>
+  </si>
+  <si>
+    <t>EQUIPO</t>
+  </si>
 </sst>
 </file>
 
@@ -606,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -720,28 +790,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -753,112 +848,19 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
         <patternFill patternType="none">
-          <fgColor indexed="64"/>
+          <fgColor theme="0" tint="-0.14999847407452621"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -886,32 +888,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2289,6 +2265,142 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2577,7 +2689,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2808,7 +2920,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3011,7 +3123,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3214,7 +3326,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3436,7 +3548,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -3617,7 +3729,7 @@
                         <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -4333,7 +4445,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5110,7 +5222,7 @@
                         <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -5278,7 +5390,7 @@
                         <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -5451,7 +5563,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -5624,7 +5736,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -5856,7 +5968,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -6063,7 +6175,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6299,7 +6411,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -6485,7 +6597,7 @@
                         <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -6831,7 +6943,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7177,7 +7289,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7578,7 +7690,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -7785,7 +7897,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11895,37 +12007,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O12" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
-  <autoFilter ref="A2:O12" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O12">
-    <sortCondition ref="D3:D12"/>
-    <sortCondition ref="A3:A12"/>
-    <sortCondition ref="F3:F12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O25" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
+  <autoFilter ref="A2:O25" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O25">
+    <sortCondition ref="D3:D25"/>
+    <sortCondition ref="A3:A25"/>
+    <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="61">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="60">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="59">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="47">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11934,36 +12046,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O4" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="A2:O4" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O11" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A2:O11" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O11">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="44">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11972,43 +12084,43 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U4" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
-  <autoFilter ref="A2:U4" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U5" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U5" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
-      <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 3'!G3:S3),"-")</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
-      <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"-")</calculatedColumnFormula>
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="1">
+      <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12016,17 +12128,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12296,14 +12408,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12333,7 +12445,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12370,17 +12482,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C3" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A3)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D3" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
@@ -12388,7 +12500,7 @@
       </c>
       <c r="E3" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A3)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
@@ -12396,7 +12508,7 @@
       </c>
       <c r="G3" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -12404,10 +12516,10 @@
       </c>
       <c r="I3" s="17">
         <f>COUNTIF(EQUIPO!$C:$C,REPORTE!A3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12444,7 +12556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12481,7 +12593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12518,7 +12630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -12555,7 +12667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -12592,7 +12704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -12629,7 +12741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -12666,7 +12778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -12703,7 +12815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -12740,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -12795,26 +12907,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -12831,7 +12943,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -12878,7 +12990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -12930,7 +13042,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -12982,7 +13094,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13034,7 +13146,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13086,7 +13198,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13138,7 +13250,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13190,7 +13302,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13242,7 +13354,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13294,7 +13406,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13346,7 +13458,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13395,6 +13507,670 @@
       </c>
       <c r="O12" s="18" t="str" cm="1">
         <f t="array" ref="O12">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B13" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C13" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D13" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="43">
+        <v>1035017030</v>
+      </c>
+      <c r="G13" s="44">
+        <v>5</v>
+      </c>
+      <c r="H13" s="44">
+        <v>5</v>
+      </c>
+      <c r="I13" s="44">
+        <v>4</v>
+      </c>
+      <c r="J13" s="44">
+        <v>2</v>
+      </c>
+      <c r="K13" s="44">
+        <v>3</v>
+      </c>
+      <c r="L13" s="44">
+        <v>2</v>
+      </c>
+      <c r="M13" s="44">
+        <v>5</v>
+      </c>
+      <c r="N13" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G13:M13),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O13" s="45" t="str" cm="1">
+        <f t="array" ref="O13">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B14" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C14" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D14" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="43">
+        <v>1062540875</v>
+      </c>
+      <c r="G14" s="44">
+        <v>5</v>
+      </c>
+      <c r="H14" s="44">
+        <v>4</v>
+      </c>
+      <c r="I14" s="44">
+        <v>3</v>
+      </c>
+      <c r="J14" s="44">
+        <v>2</v>
+      </c>
+      <c r="K14" s="44">
+        <v>2</v>
+      </c>
+      <c r="L14" s="44">
+        <v>2</v>
+      </c>
+      <c r="M14" s="44">
+        <v>3</v>
+      </c>
+      <c r="N14" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G14:M14),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O14" s="45" t="str" cm="1">
+        <f t="array" ref="O14">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B15" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C15" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D15" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="43">
+        <v>1062546526</v>
+      </c>
+      <c r="G15" s="44">
+        <v>5</v>
+      </c>
+      <c r="H15" s="44">
+        <v>3</v>
+      </c>
+      <c r="I15" s="44">
+        <v>3</v>
+      </c>
+      <c r="J15" s="44">
+        <v>3</v>
+      </c>
+      <c r="K15" s="44">
+        <v>2</v>
+      </c>
+      <c r="L15" s="44">
+        <v>2</v>
+      </c>
+      <c r="M15" s="44">
+        <v>4</v>
+      </c>
+      <c r="N15" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G15:M15),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O15" s="45" t="str" cm="1">
+        <f t="array" ref="O15">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B16" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C16" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D16" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="43">
+        <v>1062966144</v>
+      </c>
+      <c r="G16" s="44">
+        <v>5</v>
+      </c>
+      <c r="H16" s="44">
+        <v>5</v>
+      </c>
+      <c r="I16" s="44">
+        <v>4</v>
+      </c>
+      <c r="J16" s="44">
+        <v>4</v>
+      </c>
+      <c r="K16" s="44">
+        <v>3</v>
+      </c>
+      <c r="L16" s="44">
+        <v>3</v>
+      </c>
+      <c r="M16" s="44">
+        <v>5</v>
+      </c>
+      <c r="N16" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G16:M16),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O16" s="45" t="str" cm="1">
+        <f t="array" ref="O16">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B17" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C17" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D17" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="43">
+        <v>1067859838</v>
+      </c>
+      <c r="G17" s="44">
+        <v>0</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G17:M17),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="45" t="str" cm="1">
+        <f t="array" ref="O17">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B18" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C18" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D18" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="43">
+        <v>1067945529</v>
+      </c>
+      <c r="G18" s="44">
+        <v>5</v>
+      </c>
+      <c r="H18" s="44">
+        <v>5</v>
+      </c>
+      <c r="I18" s="44">
+        <v>4</v>
+      </c>
+      <c r="J18" s="44">
+        <v>4</v>
+      </c>
+      <c r="K18" s="44">
+        <v>4</v>
+      </c>
+      <c r="L18" s="44">
+        <v>4</v>
+      </c>
+      <c r="M18" s="44">
+        <v>5</v>
+      </c>
+      <c r="N18" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G18:M18),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O18" s="45" t="str" cm="1">
+        <f t="array" ref="O18">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B19" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C19" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D19" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="43">
+        <v>1067956606</v>
+      </c>
+      <c r="G19" s="44">
+        <v>5</v>
+      </c>
+      <c r="H19" s="44">
+        <v>5</v>
+      </c>
+      <c r="I19" s="44">
+        <v>5</v>
+      </c>
+      <c r="J19" s="44">
+        <v>4</v>
+      </c>
+      <c r="K19" s="44">
+        <v>4</v>
+      </c>
+      <c r="L19" s="44">
+        <v>4</v>
+      </c>
+      <c r="M19" s="44">
+        <v>5</v>
+      </c>
+      <c r="N19" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G19:M19),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O19" s="45" t="str" cm="1">
+        <f t="array" ref="O19">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B20" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C20" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D20" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="43">
+        <v>1068439110</v>
+      </c>
+      <c r="G20" s="44">
+        <v>5</v>
+      </c>
+      <c r="H20" s="44">
+        <v>5</v>
+      </c>
+      <c r="I20" s="44">
+        <v>4</v>
+      </c>
+      <c r="J20" s="44">
+        <v>4</v>
+      </c>
+      <c r="K20" s="44">
+        <v>3</v>
+      </c>
+      <c r="L20" s="44">
+        <v>3</v>
+      </c>
+      <c r="M20" s="44">
+        <v>5</v>
+      </c>
+      <c r="N20" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G20:M20),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O20" s="45" t="str" cm="1">
+        <f t="array" ref="O20">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B21" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C21" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D21" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="43">
+        <v>1068443767</v>
+      </c>
+      <c r="G21" s="44">
+        <v>5</v>
+      </c>
+      <c r="H21" s="44">
+        <v>4</v>
+      </c>
+      <c r="I21" s="44">
+        <v>1</v>
+      </c>
+      <c r="J21" s="44">
+        <v>1</v>
+      </c>
+      <c r="K21" s="44">
+        <v>1</v>
+      </c>
+      <c r="L21" s="44">
+        <v>1</v>
+      </c>
+      <c r="M21" s="44">
+        <v>5</v>
+      </c>
+      <c r="N21" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G21:M21),"-")</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O21" s="45" t="str" cm="1">
+        <f t="array" ref="O21">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B22" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C22" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D22" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="43">
+        <v>1073824962</v>
+      </c>
+      <c r="G22" s="44">
+        <v>5</v>
+      </c>
+      <c r="H22" s="44">
+        <v>5</v>
+      </c>
+      <c r="I22" s="44">
+        <v>4</v>
+      </c>
+      <c r="J22" s="44">
+        <v>4</v>
+      </c>
+      <c r="K22" s="44">
+        <v>4</v>
+      </c>
+      <c r="L22" s="44">
+        <v>3</v>
+      </c>
+      <c r="M22" s="44">
+        <v>5</v>
+      </c>
+      <c r="N22" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G22:M22),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O22" s="45" t="str" cm="1">
+        <f t="array" ref="O22">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B23" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C23" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D23" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="43">
+        <v>1126253349</v>
+      </c>
+      <c r="G23" s="44">
+        <v>5</v>
+      </c>
+      <c r="H23" s="44">
+        <v>5</v>
+      </c>
+      <c r="I23" s="44">
+        <v>4</v>
+      </c>
+      <c r="J23" s="44">
+        <v>4</v>
+      </c>
+      <c r="K23" s="44">
+        <v>4</v>
+      </c>
+      <c r="L23" s="44">
+        <v>4</v>
+      </c>
+      <c r="M23" s="44">
+        <v>5</v>
+      </c>
+      <c r="N23" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G23:M23),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O23" s="45" t="str" cm="1">
+        <f t="array" ref="O23">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B24" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C24" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D24" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="43">
+        <v>1233346601</v>
+      </c>
+      <c r="G24" s="44">
+        <v>5</v>
+      </c>
+      <c r="H24" s="44">
+        <v>4</v>
+      </c>
+      <c r="I24" s="44">
+        <v>3</v>
+      </c>
+      <c r="J24" s="44">
+        <v>3</v>
+      </c>
+      <c r="K24" s="44">
+        <v>2</v>
+      </c>
+      <c r="L24" s="44">
+        <v>2</v>
+      </c>
+      <c r="M24" s="44">
+        <v>5</v>
+      </c>
+      <c r="N24" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G24:M24),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O24" s="45" t="str" cm="1">
+        <f t="array" ref="O24">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="39">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B25" s="40" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C25" s="40" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D25" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="44">
+        <v>5</v>
+      </c>
+      <c r="H25" s="44">
+        <v>5</v>
+      </c>
+      <c r="I25" s="44">
+        <v>5</v>
+      </c>
+      <c r="J25" s="44">
+        <v>4</v>
+      </c>
+      <c r="K25" s="44">
+        <v>4</v>
+      </c>
+      <c r="L25" s="44">
+        <v>4</v>
+      </c>
+      <c r="M25" s="44">
+        <v>5</v>
+      </c>
+      <c r="N25" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G25:M25),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O25" s="45" t="str" cm="1">
+        <f t="array" ref="O25">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -13422,29 +14198,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>58</v>
@@ -13462,7 +14238,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13509,7 +14285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13561,7 +14337,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13610,6 +14386,370 @@
       </c>
       <c r="O4" s="18" t="str" cm="1">
         <f t="array" ref="O4">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C5" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D5" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="44">
+        <v>1027663882</v>
+      </c>
+      <c r="G5" s="44">
+        <v>4</v>
+      </c>
+      <c r="H5" s="44">
+        <v>4</v>
+      </c>
+      <c r="I5" s="44">
+        <v>4</v>
+      </c>
+      <c r="J5" s="44">
+        <v>4</v>
+      </c>
+      <c r="K5" s="44">
+        <v>3</v>
+      </c>
+      <c r="L5" s="44">
+        <v>5</v>
+      </c>
+      <c r="M5" s="44">
+        <v>3</v>
+      </c>
+      <c r="N5" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G5:M5),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O5" s="48" t="str" cm="1">
+        <f t="array" ref="O5">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C6" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D6" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="44">
+        <v>1035003918</v>
+      </c>
+      <c r="G6" s="44">
+        <v>4</v>
+      </c>
+      <c r="H6" s="44">
+        <v>4</v>
+      </c>
+      <c r="I6" s="44">
+        <v>4</v>
+      </c>
+      <c r="J6" s="44">
+        <v>4</v>
+      </c>
+      <c r="K6" s="44">
+        <v>4</v>
+      </c>
+      <c r="L6" s="44">
+        <v>4</v>
+      </c>
+      <c r="M6" s="44">
+        <v>2</v>
+      </c>
+      <c r="N6" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G6:M6),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O6" s="48" t="str" cm="1">
+        <f t="array" ref="O6">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B7" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C7" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D7" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="44">
+        <v>1062981643</v>
+      </c>
+      <c r="G7" s="44">
+        <v>4</v>
+      </c>
+      <c r="H7" s="44">
+        <v>5</v>
+      </c>
+      <c r="I7" s="44">
+        <v>2</v>
+      </c>
+      <c r="J7" s="44">
+        <v>3</v>
+      </c>
+      <c r="K7" s="44">
+        <v>3</v>
+      </c>
+      <c r="L7" s="44">
+        <v>4</v>
+      </c>
+      <c r="M7" s="44">
+        <v>2</v>
+      </c>
+      <c r="N7" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G7:M7),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O7" s="48" t="str" cm="1">
+        <f t="array" ref="O7">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C8" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D8" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="44">
+        <v>1073817245</v>
+      </c>
+      <c r="G8" s="44">
+        <v>4</v>
+      </c>
+      <c r="H8" s="44">
+        <v>4</v>
+      </c>
+      <c r="I8" s="44">
+        <v>2</v>
+      </c>
+      <c r="J8" s="44">
+        <v>3</v>
+      </c>
+      <c r="K8" s="44">
+        <v>2</v>
+      </c>
+      <c r="L8" s="44">
+        <v>4</v>
+      </c>
+      <c r="M8" s="44">
+        <v>2</v>
+      </c>
+      <c r="N8" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G8:M8),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O8" s="48" t="str" cm="1">
+        <f t="array" ref="O8">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C9" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D9" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="44">
+        <v>1104267144</v>
+      </c>
+      <c r="G9" s="44">
+        <v>4</v>
+      </c>
+      <c r="H9" s="44">
+        <v>4</v>
+      </c>
+      <c r="I9" s="44">
+        <v>3</v>
+      </c>
+      <c r="J9" s="44">
+        <v>3</v>
+      </c>
+      <c r="K9" s="44">
+        <v>5</v>
+      </c>
+      <c r="L9" s="44">
+        <v>4</v>
+      </c>
+      <c r="M9" s="44">
+        <v>3</v>
+      </c>
+      <c r="N9" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G9:M9),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O9" s="48" t="str" cm="1">
+        <f t="array" ref="O9">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B10" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C10" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D10" s="41">
+        <v>46080</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="44">
+        <v>1138032549</v>
+      </c>
+      <c r="G10" s="44">
+        <v>4</v>
+      </c>
+      <c r="H10" s="44">
+        <v>5</v>
+      </c>
+      <c r="I10" s="44">
+        <v>2</v>
+      </c>
+      <c r="J10" s="44">
+        <v>3</v>
+      </c>
+      <c r="K10" s="44">
+        <v>5</v>
+      </c>
+      <c r="L10" s="44">
+        <v>4</v>
+      </c>
+      <c r="M10" s="44">
+        <v>5</v>
+      </c>
+      <c r="N10" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G10:M10),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O10" s="48" t="str" cm="1">
+        <f t="array" ref="O10">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="44">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B11" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C11" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D11" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="44">
+        <v>1140444971</v>
+      </c>
+      <c r="G11" s="44">
+        <v>5</v>
+      </c>
+      <c r="H11" s="44">
+        <v>4</v>
+      </c>
+      <c r="I11" s="44">
+        <v>4</v>
+      </c>
+      <c r="J11" s="44">
+        <v>4</v>
+      </c>
+      <c r="K11" s="44">
+        <v>3</v>
+      </c>
+      <c r="L11" s="44">
+        <v>5</v>
+      </c>
+      <c r="M11" s="44">
+        <v>2</v>
+      </c>
+      <c r="N11" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G11:M11),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O11" s="48" t="str" cm="1">
+        <f t="array" ref="O11">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -13637,32 +14777,32 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5703125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" customWidth="1"/>
-    <col min="21" max="21" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E1" s="28" t="s">
         <v>59</v>
       </c>
@@ -13683,7 +14823,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13748,7 +14888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13810,15 +14950,15 @@
         <v>5</v>
       </c>
       <c r="T3" s="24">
-        <f>IFERROR(AVERAGE('NIVEL 3'!G3:S3),"-")</f>
+        <f>IFERROR(AVERAGE(G3:S3),"-")</f>
         <v>4.9230769230769234</v>
       </c>
       <c r="U3" s="32" t="str" cm="1">
-        <f t="array" ref="U3">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"-")</f>
+        <f t="array" ref="U3">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13880,12 +15020,82 @@
         <v>5</v>
       </c>
       <c r="T4" s="24">
-        <f>IFERROR(AVERAGE('NIVEL 3'!G4:S4),"-")</f>
+        <f t="shared" ref="T4:T5" si="0">IFERROR(AVERAGE(G4:S4),"-")</f>
         <v>4.9230769230769234</v>
       </c>
       <c r="U4" s="32" t="str" cm="1">
-        <f t="array" ref="U4">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"-")</f>
+        <f t="array" ref="U4">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>CAMBIA A EQUIPO</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="49">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="40" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C5" s="50" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>febrero</v>
+      </c>
+      <c r="D5" s="41">
+        <v>46081</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="52">
+        <v>1062539643</v>
+      </c>
+      <c r="G5" s="52">
+        <v>4</v>
+      </c>
+      <c r="H5" s="52">
+        <v>4</v>
+      </c>
+      <c r="I5" s="52">
+        <v>5</v>
+      </c>
+      <c r="J5" s="52">
+        <v>5</v>
+      </c>
+      <c r="K5" s="52">
+        <v>4</v>
+      </c>
+      <c r="L5" s="52">
+        <v>3</v>
+      </c>
+      <c r="M5" s="52">
+        <v>5</v>
+      </c>
+      <c r="N5" s="52">
+        <v>4</v>
+      </c>
+      <c r="O5" s="52">
+        <v>4</v>
+      </c>
+      <c r="P5" s="52">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="52">
+        <v>3</v>
+      </c>
+      <c r="R5" s="52">
+        <v>3</v>
+      </c>
+      <c r="S5" s="52">
+        <v>4</v>
+      </c>
+      <c r="T5" s="24">
+        <f t="shared" si="0"/>
+        <v>4.0769230769230766</v>
+      </c>
+      <c r="U5" s="32" t="str" cm="1">
+        <f t="array" ref="U5">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
@@ -13893,6 +15103,9 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="T4:T5" formulaRange="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -13905,15 +15118,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
@@ -13927,817 +15140,901 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="26"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="27"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="27"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="26"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="27"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="26"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="27"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="26"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="27"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="27"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="26"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="27"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="26"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="27"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="26"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="27"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="26"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="27"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="26"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="27"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="26"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="27"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="27"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="27"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="27"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="27"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="26"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="38"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="26"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="38"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="26"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="38"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="38"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="38"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="38"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="26"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="38"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="26"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="38"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="26"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="38"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="26"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="27"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="26"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="38"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="26"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="38"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="26"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="38"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="26"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="38"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="26"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="38"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="26"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="26"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="38"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="26"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="38"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="26"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="38"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="26"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="38"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="26"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="38"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="26"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="38"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="26"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="38"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="26"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="38"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="26"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="38"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="26"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="38"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="26"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="38"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="26"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="38"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="26"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="38"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="26"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="38"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="38"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="38"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="26"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="38"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="26"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="38"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="26"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="38"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="26"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="38"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="26"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="38"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="26"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="38"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="26"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
       <c r="D58" s="38"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="26"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="38"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="26"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="38"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="26"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
       <c r="D61" s="38"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="26"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
       <c r="D62" s="38"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="26"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
       <c r="D63" s="38"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="26"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
       <c r="D64" s="38"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="26"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="38"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="26"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="38"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="26"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="38"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="26"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
       <c r="D68" s="38"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="26"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
       <c r="D69" s="38"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="26"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="38"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="26"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="38"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="26"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
       <c r="D72" s="38"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="26"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="38"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="26"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="38"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="26"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="38"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="26"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="38"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="26"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="38"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="26"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="38"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="26"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="D79" s="38"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="26"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="38"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="26"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="38"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="38"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="26"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="38"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="26"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="38"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="26"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="38"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="26"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="38"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="26"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="38"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="26"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="38"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="D89" s="38"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="26"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="D90" s="38"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="26"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="D91" s="38"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="26"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="38"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="26"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="38"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="26"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="38"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="D95" s="38"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="26"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="38"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="26"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="38"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="26"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="38"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="26"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="D99" s="38"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="26"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="38"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="26"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="38"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="26"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="D102" s="38"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="26"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="38"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="26"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="D104" s="38"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="26"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
       <c r="D105" s="38"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="26"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="38"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="26"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="D107" s="38"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="38"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="26"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
       <c r="D109" s="38"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="26"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="38"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="26"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="D111" s="38"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="26"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
       <c r="D112" s="38"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="26"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
       <c r="D113" s="38"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="26"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
       <c r="D114" s="38"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="26"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
       <c r="D115" s="38"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="26"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
       <c r="D116" s="38"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="26"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
       <c r="D117" s="38"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="26"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="38"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="26"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="D119" s="38"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="26"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
       <c r="D120" s="38"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="26"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
       <c r="D121" s="38"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="26"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
       <c r="D122" s="38"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="26"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
       <c r="D123" s="38"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="26"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
       <c r="D124" s="38"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="26"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="D125" s="38"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="26"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="38"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="26"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="D127" s="38"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="26"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
       <c r="D128" s="38"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="26"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="38"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="26"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="38"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="26"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="D131" s="38"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="26"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
       <c r="D132" s="38"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="26"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
       <c r="D133" s="38"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="26"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="38"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="26"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="38"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="26"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
       <c r="D136" s="38"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="26"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
       <c r="D137" s="38"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="26"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29823"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29826"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88ADCEB-54F8-4DF3-A6BE-659BC915F320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9CFC01-7335-42B3-A99B-141667404703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -35,7 +35,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'NIVEL 3'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
@@ -676,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -790,53 +789,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -862,32 +848,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2265,142 +2225,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2673,6 +2497,142 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3897,7 +3857,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -4676,7 +4636,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -6770,7 +6730,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0</c:v>
@@ -11963,7 +11923,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11976,29 +11936,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="66">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="65">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="64">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="63">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="62">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="61">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="60">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="59">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12116,10 +12076,10 @@
     <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
     <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
     <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="0">
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="1">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12128,17 +12088,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12496,7 +12456,7 @@
       </c>
       <c r="D3" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A3)</f>
@@ -13511,665 +13471,677 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="39">
+      <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B13" s="40" t="str">
+      <c r="B13" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C13" s="40" t="str">
+      <c r="C13" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="3">
         <v>46080</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="1">
         <v>1035017030</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="1">
         <v>5</v>
       </c>
-      <c r="H13" s="44">
+      <c r="H13" s="1">
         <v>5</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="1">
         <v>4</v>
       </c>
-      <c r="J13" s="44">
+      <c r="J13" s="1">
         <v>2</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="1">
         <v>3</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="1">
         <v>2</v>
       </c>
-      <c r="M13" s="44">
+      <c r="M13" s="1">
         <v>5</v>
       </c>
       <c r="N13" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G13:M13),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O13" s="45" t="str" cm="1">
+      <c r="O13" s="18" t="str" cm="1">
         <f t="array" ref="O13">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="39">
+      <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B14" s="40" t="str">
+      <c r="B14" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C14" s="40" t="str">
+      <c r="C14" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="3">
         <v>46080</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="1">
         <v>1062540875</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="1">
         <v>5</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="1">
         <v>4</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="1">
         <v>3</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J14" s="1">
         <v>2</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="1">
         <v>2</v>
       </c>
-      <c r="L14" s="44">
+      <c r="L14" s="1">
         <v>2</v>
       </c>
-      <c r="M14" s="44">
+      <c r="M14" s="1">
         <v>3</v>
       </c>
       <c r="N14" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G14:M14),"-")</f>
         <v>3</v>
       </c>
-      <c r="O14" s="45" t="str" cm="1">
+      <c r="O14" s="18" t="str" cm="1">
         <f t="array" ref="O14">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="39">
+      <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B15" s="40" t="str">
+      <c r="B15" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C15" s="40" t="str">
+      <c r="C15" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="3">
         <v>46080</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="1">
         <v>1062546526</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="1">
         <v>5</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="1">
         <v>3</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="1">
         <v>3</v>
       </c>
-      <c r="J15" s="44">
+      <c r="J15" s="1">
         <v>3</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="1">
         <v>2</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="44">
+      <c r="M15" s="1">
         <v>4</v>
       </c>
       <c r="N15" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G15:M15),"-")</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O15" s="45" t="str" cm="1">
+      <c r="O15" s="18" t="str" cm="1">
         <f t="array" ref="O15">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="39">
+      <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B16" s="40" t="str">
+      <c r="B16" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C16" s="40" t="str">
+      <c r="C16" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="3">
         <v>46080</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="1">
         <v>1062966144</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="1">
         <v>5</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
-      <c r="J16" s="44">
+      <c r="J16" s="1">
         <v>4</v>
       </c>
-      <c r="K16" s="44">
+      <c r="K16" s="1">
         <v>3</v>
       </c>
-      <c r="L16" s="44">
+      <c r="L16" s="1">
         <v>3</v>
       </c>
-      <c r="M16" s="44">
+      <c r="M16" s="1">
         <v>5</v>
       </c>
       <c r="N16" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G16:M16),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O16" s="45" t="str" cm="1">
+      <c r="O16" s="18" t="str" cm="1">
         <f t="array" ref="O16">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="39">
+      <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B17" s="40" t="str">
+      <c r="B17" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C17" s="40" t="str">
+      <c r="C17" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="3">
         <v>46080</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G17" s="44">
-        <v>0</v>
-      </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>5</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
+        <v>4</v>
+      </c>
       <c r="N17" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G17:M17),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="45" t="str" cm="1">
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O17" s="18" t="str" cm="1">
         <f t="array" ref="O17">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>-</v>
+        <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="39">
+      <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B18" s="40" t="str">
+      <c r="B18" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C18" s="40" t="str">
+      <c r="C18" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="3">
         <v>46080</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="1">
         <v>1067945529</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="1">
         <v>5</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="1">
         <v>5</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="1">
         <v>4</v>
       </c>
-      <c r="J18" s="44">
+      <c r="J18" s="1">
         <v>4</v>
       </c>
-      <c r="K18" s="44">
+      <c r="K18" s="1">
         <v>4</v>
       </c>
-      <c r="L18" s="44">
+      <c r="L18" s="1">
         <v>4</v>
       </c>
-      <c r="M18" s="44">
+      <c r="M18" s="1">
         <v>5</v>
       </c>
       <c r="N18" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G18:M18),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O18" s="45" t="str" cm="1">
+      <c r="O18" s="18" t="str" cm="1">
         <f t="array" ref="O18">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="39">
+      <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B19" s="40" t="str">
+      <c r="B19" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C19" s="40" t="str">
+      <c r="C19" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="3">
         <v>46080</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="1">
         <v>1067956606</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="1">
         <v>5</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="1">
         <v>5</v>
       </c>
-      <c r="J19" s="44">
+      <c r="J19" s="1">
         <v>4</v>
       </c>
-      <c r="K19" s="44">
+      <c r="K19" s="1">
         <v>4</v>
       </c>
-      <c r="L19" s="44">
+      <c r="L19" s="1">
         <v>4</v>
       </c>
-      <c r="M19" s="44">
+      <c r="M19" s="1">
         <v>5</v>
       </c>
       <c r="N19" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G19:M19),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O19" s="45" t="str" cm="1">
+      <c r="O19" s="18" t="str" cm="1">
         <f t="array" ref="O19">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="39">
+      <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B20" s="40" t="str">
+      <c r="B20" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C20" s="40" t="str">
+      <c r="C20" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="3">
         <v>46080</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="1">
         <v>1068439110</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="1">
         <v>5</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="1">
         <v>4</v>
       </c>
-      <c r="J20" s="44">
+      <c r="J20" s="1">
         <v>4</v>
       </c>
-      <c r="K20" s="44">
+      <c r="K20" s="1">
         <v>3</v>
       </c>
-      <c r="L20" s="44">
+      <c r="L20" s="1">
         <v>3</v>
       </c>
-      <c r="M20" s="44">
+      <c r="M20" s="1">
         <v>5</v>
       </c>
       <c r="N20" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G20:M20),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O20" s="45" t="str" cm="1">
+      <c r="O20" s="18" t="str" cm="1">
         <f t="array" ref="O20">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="39">
+      <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B21" s="40" t="str">
+      <c r="B21" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C21" s="40" t="str">
+      <c r="C21" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="3">
         <v>46080</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="E21" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="1">
         <v>1068443767</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="1">
         <v>5</v>
       </c>
-      <c r="H21" s="44">
+      <c r="H21" s="1">
         <v>4</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="1">
         <v>1</v>
       </c>
-      <c r="J21" s="44">
+      <c r="J21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="44">
+      <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="44">
+      <c r="L21" s="1">
         <v>1</v>
       </c>
-      <c r="M21" s="44">
+      <c r="M21" s="1">
         <v>5</v>
       </c>
       <c r="N21" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G21:M21),"-")</f>
         <v>2.5714285714285716</v>
       </c>
-      <c r="O21" s="45" t="str" cm="1">
+      <c r="O21" s="18" t="str" cm="1">
         <f t="array" ref="O21">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="39">
+      <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B22" s="40" t="str">
+      <c r="B22" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C22" s="40" t="str">
+      <c r="C22" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="3">
         <v>46080</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="1">
         <v>1073824962</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="1">
         <v>5</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="1">
         <v>4</v>
       </c>
-      <c r="J22" s="44">
+      <c r="J22" s="1">
         <v>4</v>
       </c>
-      <c r="K22" s="44">
+      <c r="K22" s="1">
         <v>4</v>
       </c>
-      <c r="L22" s="44">
+      <c r="L22" s="1">
         <v>3</v>
       </c>
-      <c r="M22" s="44">
+      <c r="M22" s="1">
         <v>5</v>
       </c>
       <c r="N22" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G22:M22),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O22" s="45" t="str" cm="1">
+      <c r="O22" s="18" t="str" cm="1">
         <f t="array" ref="O22">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="39">
+      <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B23" s="40" t="str">
+      <c r="B23" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C23" s="40" t="str">
+      <c r="C23" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="3">
         <v>46080</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="1">
         <v>1126253349</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="1">
         <v>5</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="1">
         <v>5</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="1">
         <v>4</v>
       </c>
-      <c r="J23" s="44">
+      <c r="J23" s="1">
         <v>4</v>
       </c>
-      <c r="K23" s="44">
+      <c r="K23" s="1">
         <v>4</v>
       </c>
-      <c r="L23" s="44">
+      <c r="L23" s="1">
         <v>4</v>
       </c>
-      <c r="M23" s="44">
+      <c r="M23" s="1">
         <v>5</v>
       </c>
       <c r="N23" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G23:M23),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O23" s="45" t="str" cm="1">
+      <c r="O23" s="18" t="str" cm="1">
         <f t="array" ref="O23">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="39">
+      <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B24" s="40" t="str">
+      <c r="B24" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C24" s="40" t="str">
+      <c r="C24" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="3">
         <v>46080</v>
       </c>
-      <c r="E24" s="42" t="s">
+      <c r="E24" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="1">
         <v>1233346601</v>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="1">
         <v>5</v>
       </c>
-      <c r="H24" s="44">
+      <c r="H24" s="1">
         <v>4</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="1">
         <v>3</v>
       </c>
-      <c r="J24" s="44">
+      <c r="J24" s="1">
         <v>3</v>
       </c>
-      <c r="K24" s="44">
+      <c r="K24" s="1">
         <v>2</v>
       </c>
-      <c r="L24" s="44">
+      <c r="L24" s="1">
         <v>2</v>
       </c>
-      <c r="M24" s="44">
+      <c r="M24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G24:M24),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O24" s="45" t="str" cm="1">
+      <c r="O24" s="18" t="str" cm="1">
         <f t="array" ref="O24">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="39">
+      <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B25" s="40" t="str">
+      <c r="B25" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C25" s="40" t="str">
+      <c r="C25" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="3">
         <v>46080</v>
       </c>
-      <c r="E25" s="42" t="s">
+      <c r="E25" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="1">
         <v>5</v>
       </c>
-      <c r="H25" s="44">
+      <c r="H25" s="1">
         <v>5</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="1">
         <v>5</v>
       </c>
-      <c r="J25" s="44">
+      <c r="J25" s="1">
         <v>4</v>
       </c>
-      <c r="K25" s="44">
+      <c r="K25" s="1">
         <v>4</v>
       </c>
-      <c r="L25" s="44">
+      <c r="L25" s="1">
         <v>4</v>
       </c>
-      <c r="M25" s="44">
+      <c r="M25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G25:M25),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O25" s="45" t="str" cm="1">
+      <c r="O25" s="18" t="str" cm="1">
         <f t="array" ref="O25">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
@@ -14390,365 +14362,365 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="44">
+      <c r="A5" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B5" s="47" t="str">
+      <c r="B5" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C5" s="47" t="str">
+      <c r="C5" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="3">
         <v>46081</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="1">
         <v>4</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="1">
         <v>4</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="1">
         <v>4</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="1">
         <v>5</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="1">
         <v>3</v>
       </c>
       <c r="N5" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G5:M5),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O5" s="48" t="str" cm="1">
+      <c r="O5" s="18" t="str" cm="1">
         <f t="array" ref="O5">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="44">
+      <c r="A6" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B6" s="47" t="str">
+      <c r="B6" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C6" s="47" t="str">
+      <c r="C6" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="3">
         <v>46081</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="1">
         <v>1035003918</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="1">
         <v>4</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="1">
         <v>4</v>
       </c>
-      <c r="J6" s="44">
+      <c r="J6" s="1">
         <v>4</v>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="1">
         <v>4</v>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="1">
         <v>2</v>
       </c>
       <c r="N6" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G6:M6),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O6" s="48" t="str" cm="1">
+      <c r="O6" s="18" t="str" cm="1">
         <f t="array" ref="O6">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="44">
+      <c r="A7" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B7" s="47" t="str">
+      <c r="B7" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C7" s="47" t="str">
+      <c r="C7" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="3">
         <v>46081</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="1">
         <v>1062981643</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="J7" s="44">
+      <c r="J7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="1">
         <v>3</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="M7" s="44">
+      <c r="M7" s="1">
         <v>2</v>
       </c>
       <c r="N7" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G7:M7),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O7" s="48" t="str" cm="1">
+      <c r="O7" s="18" t="str" cm="1">
         <f t="array" ref="O7">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="44">
+      <c r="A8" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B8" s="47" t="str">
+      <c r="B8" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C8" s="47" t="str">
+      <c r="C8" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="3">
         <v>46081</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="1">
         <v>4</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="1">
         <v>4</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="J8" s="44">
+      <c r="J8" s="1">
         <v>3</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="1">
         <v>2</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="1">
         <v>4</v>
       </c>
-      <c r="M8" s="44">
+      <c r="M8" s="1">
         <v>2</v>
       </c>
       <c r="N8" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G8:M8),"-")</f>
         <v>3</v>
       </c>
-      <c r="O8" s="48" t="str" cm="1">
+      <c r="O8" s="18" t="str" cm="1">
         <f t="array" ref="O8">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="44">
+      <c r="A9" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B9" s="47" t="str">
+      <c r="B9" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C9" s="47" t="str">
+      <c r="C9" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="3">
         <v>46081</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="1">
         <v>1104267144</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="1">
         <v>4</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="1">
         <v>3</v>
       </c>
-      <c r="J9" s="44">
+      <c r="J9" s="1">
         <v>3</v>
       </c>
-      <c r="K9" s="44">
+      <c r="K9" s="1">
         <v>5</v>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="1">
         <v>4</v>
       </c>
-      <c r="M9" s="44">
+      <c r="M9" s="1">
         <v>3</v>
       </c>
       <c r="N9" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G9:M9),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O9" s="48" t="str" cm="1">
+      <c r="O9" s="18" t="str" cm="1">
         <f t="array" ref="O9">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="44">
+      <c r="A10" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B10" s="47" t="str">
+      <c r="B10" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C10" s="47" t="str">
+      <c r="C10" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="3">
         <v>46080</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="J10" s="44">
+      <c r="J10" s="1">
         <v>3</v>
       </c>
-      <c r="K10" s="44">
+      <c r="K10" s="1">
         <v>5</v>
       </c>
-      <c r="L10" s="44">
+      <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="44">
+      <c r="M10" s="1">
         <v>5</v>
       </c>
       <c r="N10" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G10:M10),"-")</f>
         <v>4</v>
       </c>
-      <c r="O10" s="48" t="str" cm="1">
+      <c r="O10" s="18" t="str" cm="1">
         <f t="array" ref="O10">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="44">
+      <c r="A11" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B11" s="47" t="str">
+      <c r="B11" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C11" s="47" t="str">
+      <c r="C11" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="3">
         <v>46081</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="1">
         <v>5</v>
       </c>
-      <c r="H11" s="44">
+      <c r="H11" s="1">
         <v>4</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="1">
         <v>4</v>
       </c>
-      <c r="J11" s="44">
+      <c r="J11" s="1">
         <v>4</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="1">
         <v>3</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="1">
         <v>5</v>
       </c>
-      <c r="M11" s="44">
+      <c r="M11" s="1">
         <v>2</v>
       </c>
       <c r="N11" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G11:M11),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O11" s="48" t="str" cm="1">
+      <c r="O11" s="18" t="str" cm="1">
         <f t="array" ref="O11">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
@@ -15029,64 +15001,64 @@
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="49">
+      <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
       </c>
-      <c r="B5" s="40" t="str">
+      <c r="B5" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C5" s="50" t="str">
+      <c r="C5" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>febrero</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="3">
         <v>46081</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="52">
+      <c r="F5" s="23">
         <v>1062539643</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="23">
         <v>4</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="23">
         <v>4</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="23">
         <v>5</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="23">
         <v>5</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="23">
         <v>4</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="23">
         <v>3</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="23">
         <v>5</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="23">
         <v>4</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="23">
         <v>4</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="23">
         <v>5</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="23">
         <v>3</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="23">
         <v>3</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="23">
         <v>4</v>
       </c>
       <c r="T5" s="24">

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29826"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9CFC01-7335-42B3-A99B-141667404703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4CE410-6785-43C7-B549-86AAE1EF8F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="115">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -544,6 +544,54 @@
   <si>
     <t>EQUIPO</t>
   </si>
+  <si>
+    <t>Eduardo Luis Diaz Olivo</t>
+  </si>
+  <si>
+    <t>Laura Ruiz Palomo</t>
+  </si>
+  <si>
+    <t>Miguel Castro Montes</t>
+  </si>
+  <si>
+    <t>Dario Restrepo Rojas</t>
+  </si>
+  <si>
+    <t>Saray Bastidas Pelaez</t>
+  </si>
+  <si>
+    <t>Santiago Peñates Ramos</t>
+  </si>
+  <si>
+    <t>Joel Jaraba Rosario</t>
+  </si>
+  <si>
+    <t>Angie Tatiana Patiño Segura</t>
+  </si>
+  <si>
+    <t>Evangely Bravo Padilla</t>
+  </si>
+  <si>
+    <t>Valeria Martinez Valero</t>
+  </si>
+  <si>
+    <t>Maria Carolina Tannus</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Cogollo Cogollo</t>
+  </si>
+  <si>
+    <t>Elias Vergara Villalba</t>
+  </si>
+  <si>
+    <t>Ever Junior Polo Lozano</t>
+  </si>
+  <si>
+    <t>Sara Lucia Movilla Villalba</t>
+  </si>
+  <si>
+    <t>Valeria Guerra Machado</t>
+  </si>
 </sst>
 </file>
 
@@ -675,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -792,11 +840,640 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1425,32 +2102,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor theme="0" tint="-0.14999847407452621"/>
@@ -1816,425 +2467,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -2497,142 +2729,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2883,7 +2979,7 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3086,7 +3182,7 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3289,7 +3385,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3692,7 +3788,7 @@
                         <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>34</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -3860,7 +3956,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -4639,7 +4735,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -5185,7 +5281,7 @@
                         <c:v>35</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>34</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -5353,7 +5449,7 @@
                         <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -5526,7 +5622,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -5699,7 +5795,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -6374,7 +6470,7 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -6560,7 +6656,7 @@
                         <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -6733,7 +6829,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -6906,7 +7002,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -7252,7 +7348,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>0</c:v>
+                        <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>0</c:v>
@@ -11923,7 +12019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -11936,29 +12032,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="66">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="65">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="64">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="63">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="62">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="61">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="60">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="59">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11967,37 +12063,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O25" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
-  <autoFilter ref="A2:O25" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O46" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A2:O46" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O46">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="15">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="14">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="13">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12006,36 +12102,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O11" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A2:O11" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O23" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+  <autoFilter ref="A2:O23" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O23">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="62">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="61">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="60">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="49">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12044,42 +12140,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U5" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A2:U5" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U6" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
+  <autoFilter ref="A2:U6" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="45">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="44">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="43">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="26">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="25">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12088,17 +12184,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="73"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12485,19 +12581,19 @@
       </c>
       <c r="B4" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C4" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A4)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D4" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A4)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
@@ -12505,7 +12601,7 @@
       </c>
       <c r="G4" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -12867,7 +12963,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -14143,6 +14239,1098 @@
       </c>
       <c r="O25" s="18" t="str" cm="1">
         <f t="array" ref="O25">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B26" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C26" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D26" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="44">
+        <v>1003027198</v>
+      </c>
+      <c r="G26" s="45">
+        <v>5</v>
+      </c>
+      <c r="H26" s="45">
+        <v>5</v>
+      </c>
+      <c r="I26" s="45">
+        <v>4</v>
+      </c>
+      <c r="J26" s="45">
+        <v>4</v>
+      </c>
+      <c r="K26" s="45">
+        <v>4</v>
+      </c>
+      <c r="L26" s="45">
+        <v>4</v>
+      </c>
+      <c r="M26" s="45">
+        <v>5</v>
+      </c>
+      <c r="N26" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G26:M26),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O26" s="46" t="str" cm="1">
+        <f t="array" ref="O26">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B27" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C27" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D27" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="44">
+        <v>1035017030</v>
+      </c>
+      <c r="G27" s="45">
+        <v>5</v>
+      </c>
+      <c r="H27" s="45">
+        <v>5</v>
+      </c>
+      <c r="I27" s="45">
+        <v>5</v>
+      </c>
+      <c r="J27" s="45">
+        <v>3</v>
+      </c>
+      <c r="K27" s="45">
+        <v>4</v>
+      </c>
+      <c r="L27" s="45">
+        <v>3</v>
+      </c>
+      <c r="M27" s="45">
+        <v>5</v>
+      </c>
+      <c r="N27" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G27:M27),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O27" s="46" t="str" cm="1">
+        <f t="array" ref="O27">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B28" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C28" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D28" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="44">
+        <v>1062424218</v>
+      </c>
+      <c r="G28" s="45">
+        <v>5</v>
+      </c>
+      <c r="H28" s="45">
+        <v>5</v>
+      </c>
+      <c r="I28" s="45">
+        <v>5</v>
+      </c>
+      <c r="J28" s="45">
+        <v>4</v>
+      </c>
+      <c r="K28" s="45">
+        <v>4</v>
+      </c>
+      <c r="L28" s="45">
+        <v>4</v>
+      </c>
+      <c r="M28" s="45">
+        <v>5</v>
+      </c>
+      <c r="N28" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G28:M28),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O28" s="46" t="str" cm="1">
+        <f t="array" ref="O28">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B29" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C29" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D29" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="44">
+        <v>1062436143</v>
+      </c>
+      <c r="G29" s="45">
+        <v>5</v>
+      </c>
+      <c r="H29" s="45">
+        <v>5</v>
+      </c>
+      <c r="I29" s="45">
+        <v>3</v>
+      </c>
+      <c r="J29" s="45">
+        <v>3</v>
+      </c>
+      <c r="K29" s="45">
+        <v>2</v>
+      </c>
+      <c r="L29" s="45">
+        <v>2</v>
+      </c>
+      <c r="M29" s="45">
+        <v>5</v>
+      </c>
+      <c r="N29" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G29:M29),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O29" s="46" t="str" cm="1">
+        <f t="array" ref="O29">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B30" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C30" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D30" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="44">
+        <v>1062444411</v>
+      </c>
+      <c r="G30" s="45">
+        <v>5</v>
+      </c>
+      <c r="H30" s="45">
+        <v>5</v>
+      </c>
+      <c r="I30" s="45">
+        <v>5</v>
+      </c>
+      <c r="J30" s="45">
+        <v>5</v>
+      </c>
+      <c r="K30" s="45">
+        <v>5</v>
+      </c>
+      <c r="L30" s="45">
+        <v>5</v>
+      </c>
+      <c r="M30" s="45">
+        <v>5</v>
+      </c>
+      <c r="N30" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G30:M30),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O30" s="46" t="str" cm="1">
+        <f t="array" ref="O30">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B31" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C31" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D31" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="44">
+        <v>1062540875</v>
+      </c>
+      <c r="G31" s="45">
+        <v>5</v>
+      </c>
+      <c r="H31" s="45">
+        <v>5</v>
+      </c>
+      <c r="I31" s="45">
+        <v>3</v>
+      </c>
+      <c r="J31" s="45">
+        <v>3</v>
+      </c>
+      <c r="K31" s="45">
+        <v>3</v>
+      </c>
+      <c r="L31" s="45">
+        <v>2</v>
+      </c>
+      <c r="M31" s="45">
+        <v>4</v>
+      </c>
+      <c r="N31" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G31:M31),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O31" s="46" t="str" cm="1">
+        <f t="array" ref="O31">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B32" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C32" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D32" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="44">
+        <v>1062544508</v>
+      </c>
+      <c r="G32" s="45">
+        <v>5</v>
+      </c>
+      <c r="H32" s="45">
+        <v>5</v>
+      </c>
+      <c r="I32" s="45">
+        <v>5</v>
+      </c>
+      <c r="J32" s="45">
+        <v>4</v>
+      </c>
+      <c r="K32" s="45">
+        <v>4</v>
+      </c>
+      <c r="L32" s="45">
+        <v>4</v>
+      </c>
+      <c r="M32" s="45">
+        <v>5</v>
+      </c>
+      <c r="N32" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G32:M32),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O32" s="46" t="str" cm="1">
+        <f t="array" ref="O32">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B33" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C33" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D33" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="44">
+        <v>1062546526</v>
+      </c>
+      <c r="G33" s="45">
+        <v>5</v>
+      </c>
+      <c r="H33" s="45">
+        <v>5</v>
+      </c>
+      <c r="I33" s="45">
+        <v>3</v>
+      </c>
+      <c r="J33" s="45">
+        <v>3</v>
+      </c>
+      <c r="K33" s="45">
+        <v>3</v>
+      </c>
+      <c r="L33" s="45">
+        <v>2</v>
+      </c>
+      <c r="M33" s="45">
+        <v>5</v>
+      </c>
+      <c r="N33" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G33:M33),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O33" s="46" t="str" cm="1">
+        <f t="array" ref="O33">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B34" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C34" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D34" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="44">
+        <v>1062966144</v>
+      </c>
+      <c r="G34" s="45">
+        <v>5</v>
+      </c>
+      <c r="H34" s="45">
+        <v>5</v>
+      </c>
+      <c r="I34" s="45">
+        <v>5</v>
+      </c>
+      <c r="J34" s="45">
+        <v>4</v>
+      </c>
+      <c r="K34" s="45">
+        <v>4</v>
+      </c>
+      <c r="L34" s="45">
+        <v>4</v>
+      </c>
+      <c r="M34" s="45">
+        <v>5</v>
+      </c>
+      <c r="N34" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G34:M34),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O34" s="46" t="str" cm="1">
+        <f t="array" ref="O34">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B35" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C35" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D35" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="44">
+        <v>1067940515</v>
+      </c>
+      <c r="G35" s="45">
+        <v>5</v>
+      </c>
+      <c r="H35" s="45">
+        <v>5</v>
+      </c>
+      <c r="I35" s="45">
+        <v>4</v>
+      </c>
+      <c r="J35" s="45">
+        <v>3</v>
+      </c>
+      <c r="K35" s="45">
+        <v>4</v>
+      </c>
+      <c r="L35" s="45">
+        <v>3</v>
+      </c>
+      <c r="M35" s="45">
+        <v>5</v>
+      </c>
+      <c r="N35" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G35:M35),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O35" s="46" t="str" cm="1">
+        <f t="array" ref="O35">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B36" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C36" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D36" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="44">
+        <v>1067945529</v>
+      </c>
+      <c r="G36" s="45">
+        <v>5</v>
+      </c>
+      <c r="H36" s="45">
+        <v>5</v>
+      </c>
+      <c r="I36" s="45">
+        <v>5</v>
+      </c>
+      <c r="J36" s="45">
+        <v>4</v>
+      </c>
+      <c r="K36" s="45">
+        <v>4</v>
+      </c>
+      <c r="L36" s="45">
+        <v>4</v>
+      </c>
+      <c r="M36" s="45">
+        <v>5</v>
+      </c>
+      <c r="N36" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G36:M36),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O36" s="46" t="str" cm="1">
+        <f t="array" ref="O36">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B37" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C37" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D37" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="44">
+        <v>1067956606</v>
+      </c>
+      <c r="G37" s="45">
+        <v>5</v>
+      </c>
+      <c r="H37" s="45">
+        <v>5</v>
+      </c>
+      <c r="I37" s="45">
+        <v>5</v>
+      </c>
+      <c r="J37" s="45">
+        <v>5</v>
+      </c>
+      <c r="K37" s="45">
+        <v>5</v>
+      </c>
+      <c r="L37" s="45">
+        <v>5</v>
+      </c>
+      <c r="M37" s="45">
+        <v>5</v>
+      </c>
+      <c r="N37" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G37:M37),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O37" s="46" t="str" cm="1">
+        <f t="array" ref="O37">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B38" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C38" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D38" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E38" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F38" s="44">
+        <v>1068441879</v>
+      </c>
+      <c r="G38" s="45">
+        <v>5</v>
+      </c>
+      <c r="H38" s="45">
+        <v>3</v>
+      </c>
+      <c r="I38" s="45">
+        <v>2</v>
+      </c>
+      <c r="J38" s="45">
+        <v>3</v>
+      </c>
+      <c r="K38" s="45">
+        <v>2</v>
+      </c>
+      <c r="L38" s="45">
+        <v>2</v>
+      </c>
+      <c r="M38" s="45">
+        <v>4</v>
+      </c>
+      <c r="N38" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G38:M38),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O38" s="46" t="str" cm="1">
+        <f t="array" ref="O38">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B39" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C39" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D39" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="44">
+        <v>1068442748</v>
+      </c>
+      <c r="G39" s="45">
+        <v>5</v>
+      </c>
+      <c r="H39" s="45">
+        <v>1</v>
+      </c>
+      <c r="I39" s="45">
+        <v>2</v>
+      </c>
+      <c r="J39" s="45">
+        <v>1</v>
+      </c>
+      <c r="K39" s="45">
+        <v>1</v>
+      </c>
+      <c r="L39" s="45">
+        <v>1</v>
+      </c>
+      <c r="M39" s="45">
+        <v>1</v>
+      </c>
+      <c r="N39" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G39:M39),"-")</f>
+        <v>1.7142857142857142</v>
+      </c>
+      <c r="O39" s="46" t="str" cm="1">
+        <f t="array" ref="O39">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B40" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C40" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D40" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="44">
+        <v>1068443767</v>
+      </c>
+      <c r="G40" s="45">
+        <v>5</v>
+      </c>
+      <c r="H40" s="45">
+        <v>3</v>
+      </c>
+      <c r="I40" s="45">
+        <v>2</v>
+      </c>
+      <c r="J40" s="45">
+        <v>2</v>
+      </c>
+      <c r="K40" s="45">
+        <v>2</v>
+      </c>
+      <c r="L40" s="45">
+        <v>2</v>
+      </c>
+      <c r="M40" s="45">
+        <v>5</v>
+      </c>
+      <c r="N40" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G40:M40),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O40" s="46" t="str" cm="1">
+        <f t="array" ref="O40">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B41" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C41" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D41" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="44">
+        <v>1073824962</v>
+      </c>
+      <c r="G41" s="45">
+        <v>5</v>
+      </c>
+      <c r="H41" s="45">
+        <v>5</v>
+      </c>
+      <c r="I41" s="45">
+        <v>5</v>
+      </c>
+      <c r="J41" s="45">
+        <v>4</v>
+      </c>
+      <c r="K41" s="45">
+        <v>5</v>
+      </c>
+      <c r="L41" s="45">
+        <v>4</v>
+      </c>
+      <c r="M41" s="45">
+        <v>5</v>
+      </c>
+      <c r="N41" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G41:M41),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O41" s="46" t="str" cm="1">
+        <f t="array" ref="O41">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B42" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C42" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D42" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E42" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="44">
+        <v>1126253349</v>
+      </c>
+      <c r="G42" s="45">
+        <v>5</v>
+      </c>
+      <c r="H42" s="45">
+        <v>5</v>
+      </c>
+      <c r="I42" s="45">
+        <v>4</v>
+      </c>
+      <c r="J42" s="45">
+        <v>4</v>
+      </c>
+      <c r="K42" s="45">
+        <v>4</v>
+      </c>
+      <c r="L42" s="45">
+        <v>5</v>
+      </c>
+      <c r="M42" s="45">
+        <v>5</v>
+      </c>
+      <c r="N42" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G42:M42),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O42" s="46" t="str" cm="1">
+        <f t="array" ref="O42">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B43" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C43" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D43" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="44">
+        <v>1137975856</v>
+      </c>
+      <c r="G43" s="45">
+        <v>5</v>
+      </c>
+      <c r="H43" s="45">
+        <v>5</v>
+      </c>
+      <c r="I43" s="45">
+        <v>5</v>
+      </c>
+      <c r="J43" s="45">
+        <v>4</v>
+      </c>
+      <c r="K43" s="45">
+        <v>4</v>
+      </c>
+      <c r="L43" s="45">
+        <v>4</v>
+      </c>
+      <c r="M43" s="45">
+        <v>5</v>
+      </c>
+      <c r="N43" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G43:M43),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O43" s="46" t="str" cm="1">
+        <f t="array" ref="O43">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B44" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C44" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D44" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="44">
+        <v>1138030749</v>
+      </c>
+      <c r="G44" s="45">
+        <v>5</v>
+      </c>
+      <c r="H44" s="45">
+        <v>5</v>
+      </c>
+      <c r="I44" s="45">
+        <v>4</v>
+      </c>
+      <c r="J44" s="45">
+        <v>4</v>
+      </c>
+      <c r="K44" s="45">
+        <v>4</v>
+      </c>
+      <c r="L44" s="45">
+        <v>4</v>
+      </c>
+      <c r="M44" s="45">
+        <v>5</v>
+      </c>
+      <c r="N44" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G44:M44),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O44" s="46" t="str" cm="1">
+        <f t="array" ref="O44">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B45" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C45" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D45" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="44">
+        <v>1138031920</v>
+      </c>
+      <c r="G45" s="45">
+        <v>5</v>
+      </c>
+      <c r="H45" s="45">
+        <v>5</v>
+      </c>
+      <c r="I45" s="45">
+        <v>5</v>
+      </c>
+      <c r="J45" s="45">
+        <v>4</v>
+      </c>
+      <c r="K45" s="45">
+        <v>5</v>
+      </c>
+      <c r="L45" s="45">
+        <v>4</v>
+      </c>
+      <c r="M45" s="45">
+        <v>5</v>
+      </c>
+      <c r="N45" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G45:M45),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O45" s="46" t="str" cm="1">
+        <f t="array" ref="O45">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B46" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C46" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D46" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" s="44">
+        <v>1233348383</v>
+      </c>
+      <c r="G46" s="45">
+        <v>5</v>
+      </c>
+      <c r="H46" s="45">
+        <v>2</v>
+      </c>
+      <c r="I46" s="45">
+        <v>2</v>
+      </c>
+      <c r="J46" s="45">
+        <v>2</v>
+      </c>
+      <c r="K46" s="45">
+        <v>2</v>
+      </c>
+      <c r="L46" s="45">
+        <v>2</v>
+      </c>
+      <c r="M46" s="45">
+        <v>4</v>
+      </c>
+      <c r="N46" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G46:M46),"-")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="O46" s="46" t="str" cm="1">
+        <f t="array" ref="O46">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -14170,7 +15358,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -14725,6 +15913,630 @@
         <v>-</v>
       </c>
     </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B12" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C12" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D12" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="45">
+        <v>1027663882</v>
+      </c>
+      <c r="G12" s="45">
+        <v>4</v>
+      </c>
+      <c r="H12" s="45">
+        <v>4</v>
+      </c>
+      <c r="I12" s="45">
+        <v>4</v>
+      </c>
+      <c r="J12" s="45">
+        <v>4</v>
+      </c>
+      <c r="K12" s="45">
+        <v>3</v>
+      </c>
+      <c r="L12" s="45">
+        <v>5</v>
+      </c>
+      <c r="M12" s="45">
+        <v>3</v>
+      </c>
+      <c r="N12" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G12:M12),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O12" s="48" t="str" cm="1">
+        <f t="array" ref="O12">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B13" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C13" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D13" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="45">
+        <v>1035003918</v>
+      </c>
+      <c r="G13" s="45">
+        <v>5</v>
+      </c>
+      <c r="H13" s="45">
+        <v>4</v>
+      </c>
+      <c r="I13" s="45">
+        <v>4</v>
+      </c>
+      <c r="J13" s="45">
+        <v>4</v>
+      </c>
+      <c r="K13" s="45">
+        <v>4</v>
+      </c>
+      <c r="L13" s="45">
+        <v>5</v>
+      </c>
+      <c r="M13" s="45">
+        <v>2</v>
+      </c>
+      <c r="N13" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G13:M13),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O13" s="48" t="str" cm="1">
+        <f t="array" ref="O13">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B14" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C14" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D14" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="45">
+        <v>1062980565</v>
+      </c>
+      <c r="G14" s="45">
+        <v>4</v>
+      </c>
+      <c r="H14" s="45">
+        <v>4</v>
+      </c>
+      <c r="I14" s="45">
+        <v>2</v>
+      </c>
+      <c r="J14" s="45">
+        <v>3</v>
+      </c>
+      <c r="K14" s="45">
+        <v>3</v>
+      </c>
+      <c r="L14" s="45">
+        <v>5</v>
+      </c>
+      <c r="M14" s="45">
+        <v>2</v>
+      </c>
+      <c r="N14" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G14:M14),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O14" s="48" t="str" cm="1">
+        <f t="array" ref="O14">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B15" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C15" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D15" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="45">
+        <v>1062981643</v>
+      </c>
+      <c r="G15" s="45">
+        <v>4</v>
+      </c>
+      <c r="H15" s="45">
+        <v>5</v>
+      </c>
+      <c r="I15" s="45">
+        <v>2</v>
+      </c>
+      <c r="J15" s="45">
+        <v>3</v>
+      </c>
+      <c r="K15" s="45">
+        <v>3</v>
+      </c>
+      <c r="L15" s="45">
+        <v>4</v>
+      </c>
+      <c r="M15" s="45">
+        <v>2</v>
+      </c>
+      <c r="N15" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G15:M15),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O15" s="48" t="str" cm="1">
+        <f t="array" ref="O15">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B16" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C16" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D16" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="45">
+        <v>1066747786</v>
+      </c>
+      <c r="G16" s="45">
+        <v>5</v>
+      </c>
+      <c r="H16" s="45">
+        <v>4</v>
+      </c>
+      <c r="I16" s="45">
+        <v>4</v>
+      </c>
+      <c r="J16" s="45">
+        <v>4</v>
+      </c>
+      <c r="K16" s="45">
+        <v>4</v>
+      </c>
+      <c r="L16" s="45">
+        <v>5</v>
+      </c>
+      <c r="M16" s="45">
+        <v>2</v>
+      </c>
+      <c r="N16" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G16:M16),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O16" s="48" t="str" cm="1">
+        <f t="array" ref="O16">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B17" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C17" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D17" s="42">
+        <v>46111</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="45">
+        <v>1067859838</v>
+      </c>
+      <c r="G17" s="45">
+        <v>4</v>
+      </c>
+      <c r="H17" s="45">
+        <v>4</v>
+      </c>
+      <c r="I17" s="45">
+        <v>2</v>
+      </c>
+      <c r="J17" s="45">
+        <v>4</v>
+      </c>
+      <c r="K17" s="45">
+        <v>4</v>
+      </c>
+      <c r="L17" s="45">
+        <v>5</v>
+      </c>
+      <c r="M17" s="45">
+        <v>1</v>
+      </c>
+      <c r="N17" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G17:M17),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O17" s="48" t="str" cm="1">
+        <f t="array" ref="O17">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B18" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C18" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D18" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="45">
+        <v>1068439668</v>
+      </c>
+      <c r="G18" s="45">
+        <v>5</v>
+      </c>
+      <c r="H18" s="45">
+        <v>5</v>
+      </c>
+      <c r="I18" s="45">
+        <v>4</v>
+      </c>
+      <c r="J18" s="45">
+        <v>4</v>
+      </c>
+      <c r="K18" s="45">
+        <v>3</v>
+      </c>
+      <c r="L18" s="45">
+        <v>5</v>
+      </c>
+      <c r="M18" s="45">
+        <v>3</v>
+      </c>
+      <c r="N18" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G18:M18),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O18" s="48" t="str" cm="1">
+        <f t="array" ref="O18">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B19" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C19" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D19" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="45">
+        <v>1073817245</v>
+      </c>
+      <c r="G19" s="45">
+        <v>5</v>
+      </c>
+      <c r="H19" s="45">
+        <v>4</v>
+      </c>
+      <c r="I19" s="45">
+        <v>2</v>
+      </c>
+      <c r="J19" s="45">
+        <v>3</v>
+      </c>
+      <c r="K19" s="45">
+        <v>2</v>
+      </c>
+      <c r="L19" s="45">
+        <v>5</v>
+      </c>
+      <c r="M19" s="45">
+        <v>2</v>
+      </c>
+      <c r="N19" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G19:M19),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O19" s="48" t="str" cm="1">
+        <f t="array" ref="O19">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B20" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C20" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D20" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="45">
+        <v>1104267144</v>
+      </c>
+      <c r="G20" s="45">
+        <v>4</v>
+      </c>
+      <c r="H20" s="45">
+        <v>4</v>
+      </c>
+      <c r="I20" s="45">
+        <v>3</v>
+      </c>
+      <c r="J20" s="45">
+        <v>3</v>
+      </c>
+      <c r="K20" s="45">
+        <v>5</v>
+      </c>
+      <c r="L20" s="45">
+        <v>4</v>
+      </c>
+      <c r="M20" s="45">
+        <v>3</v>
+      </c>
+      <c r="N20" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G20:M20),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O20" s="48" t="str" cm="1">
+        <f t="array" ref="O20">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B21" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C21" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D21" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="45">
+        <v>1138031207</v>
+      </c>
+      <c r="G21" s="45">
+        <v>5</v>
+      </c>
+      <c r="H21" s="45">
+        <v>4</v>
+      </c>
+      <c r="I21" s="45">
+        <v>3</v>
+      </c>
+      <c r="J21" s="45">
+        <v>3</v>
+      </c>
+      <c r="K21" s="45">
+        <v>3</v>
+      </c>
+      <c r="L21" s="45">
+        <v>5</v>
+      </c>
+      <c r="M21" s="45">
+        <v>3</v>
+      </c>
+      <c r="N21" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G21:M21),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O21" s="48" t="str" cm="1">
+        <f t="array" ref="O21">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B22" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C22" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D22" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="45">
+        <v>1138032549</v>
+      </c>
+      <c r="G22" s="45">
+        <v>4</v>
+      </c>
+      <c r="H22" s="45">
+        <v>5</v>
+      </c>
+      <c r="I22" s="45">
+        <v>3</v>
+      </c>
+      <c r="J22" s="45">
+        <v>3</v>
+      </c>
+      <c r="K22" s="45">
+        <v>5</v>
+      </c>
+      <c r="L22" s="45">
+        <v>5</v>
+      </c>
+      <c r="M22" s="45">
+        <v>5</v>
+      </c>
+      <c r="N22" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G22:M22),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O22" s="48" t="str" cm="1">
+        <f t="array" ref="O22">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B23" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C23" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D23" s="42">
+        <v>46110</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="45">
+        <v>1140444971</v>
+      </c>
+      <c r="G23" s="45">
+        <v>5</v>
+      </c>
+      <c r="H23" s="45">
+        <v>4</v>
+      </c>
+      <c r="I23" s="45">
+        <v>4</v>
+      </c>
+      <c r="J23" s="45">
+        <v>4</v>
+      </c>
+      <c r="K23" s="45">
+        <v>3</v>
+      </c>
+      <c r="L23" s="45">
+        <v>5</v>
+      </c>
+      <c r="M23" s="45">
+        <v>3</v>
+      </c>
+      <c r="N23" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G23:M23),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O23" s="48" t="str" cm="1">
+        <f t="array" ref="O23">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -14749,7 +16561,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -15067,6 +16879,76 @@
       </c>
       <c r="U5" s="32" t="str" cm="1">
         <f t="array" ref="U5">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="49">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C6" s="50" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>marzo</v>
+      </c>
+      <c r="D6" s="51">
+        <v>46110</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="53">
+        <v>1062539643</v>
+      </c>
+      <c r="G6" s="53">
+        <v>4</v>
+      </c>
+      <c r="H6" s="53">
+        <v>4</v>
+      </c>
+      <c r="I6" s="53">
+        <v>5</v>
+      </c>
+      <c r="J6" s="53">
+        <v>5</v>
+      </c>
+      <c r="K6" s="53">
+        <v>4</v>
+      </c>
+      <c r="L6" s="53">
+        <v>3</v>
+      </c>
+      <c r="M6" s="53">
+        <v>5</v>
+      </c>
+      <c r="N6" s="53">
+        <v>4</v>
+      </c>
+      <c r="O6" s="53">
+        <v>4</v>
+      </c>
+      <c r="P6" s="53">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="53">
+        <v>3</v>
+      </c>
+      <c r="R6" s="53">
+        <v>3</v>
+      </c>
+      <c r="S6" s="53">
+        <v>4</v>
+      </c>
+      <c r="T6" s="54">
+        <f>IFERROR(AVERAGE(G6:S6),"-")</f>
+        <v>4.0769230769230766</v>
+      </c>
+      <c r="U6" s="55" t="str" cm="1">
+        <f t="array" ref="U6">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4CE410-6785-43C7-B549-86AAE1EF8F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D08E74B-500F-4062-8E2A-DD842FC0A1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -592,6 +592,66 @@
   <si>
     <t>Valeria Guerra Machado</t>
   </si>
+  <si>
+    <t>Maria Virginia Ortiz Cuadrado</t>
+  </si>
+  <si>
+    <t>Matias Gabriel Núñez Salgado</t>
+  </si>
+  <si>
+    <t>katty Saenz Solano</t>
+  </si>
+  <si>
+    <t>Maria Victoria Velasquez</t>
+  </si>
+  <si>
+    <t>Risa Kikuchi</t>
+  </si>
+  <si>
+    <t>Carlos Vizcanio Diaz</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Simanca Urueta</t>
+  </si>
+  <si>
+    <t>William Yepes Suarez</t>
+  </si>
+  <si>
+    <t>Maria Jose Paternina Doria</t>
+  </si>
+  <si>
+    <t>Francisco Barreiro</t>
+  </si>
+  <si>
+    <t>Any Sofia Rodriguez López</t>
+  </si>
+  <si>
+    <t>Dylan Espinosa</t>
+  </si>
+  <si>
+    <t>Andrea Molina</t>
+  </si>
+  <si>
+    <t>DAIRO LUIS ORTEGA BRACAMONTE</t>
+  </si>
+  <si>
+    <t>Mariana Mendieta Martinez</t>
+  </si>
+  <si>
+    <t>Yina lopez</t>
+  </si>
+  <si>
+    <t>Elias lopez arteaga</t>
+  </si>
+  <si>
+    <t>Ruth Elena LOpez Arteaga</t>
+  </si>
+  <si>
+    <t>Keysi julieth Montiel Mestra</t>
+  </si>
+  <si>
+    <t>Jaime Andres Forero Marquez</t>
+  </si>
 </sst>
 </file>
 
@@ -723,7 +783,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -846,6 +906,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -858,8 +921,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -908,6 +971,32 @@
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -936,7 +1025,376 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -960,8 +1418,9 @@
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1473,6 +1932,280 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2059,676 +2792,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2982,7 +3045,7 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -3185,7 +3248,7 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -3388,7 +3451,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -3791,7 +3854,7 @@
                         <c:v>34</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>45</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -3959,7 +4022,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -4738,7 +4801,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -5284,7 +5347,7 @@
                         <c:v>34</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>45</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -5452,7 +5515,7 @@
                         <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>31</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -5625,7 +5688,7 @@
                         <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -5798,7 +5861,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -6473,7 +6536,7 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -6659,7 +6722,7 @@
                         <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>31</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -6832,7 +6895,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -7005,7 +7068,7 @@
                         <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -7351,7 +7414,7 @@
                         <c:v>1</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>0</c:v>
@@ -12019,7 +12082,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -12032,29 +12095,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="48">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="47">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="46">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="45">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="44">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="43">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="42">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="41">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12063,37 +12126,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O46" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A2:O46" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O77" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
+  <autoFilter ref="A2:O77" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O77">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="15">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="31">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="30">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="13">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="29">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="18">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="2">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="17">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12102,36 +12165,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O23" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
-  <autoFilter ref="A2:O23" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O35" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:O35" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O35">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="60">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="49">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12140,42 +12203,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U6" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
-  <autoFilter ref="A2:U6" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U8" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74" tableBorderDxfId="73">
+  <autoFilter ref="A2:U8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="45">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="72">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="44">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="71">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="70">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="26">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="60"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="59"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="56"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="55"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="54"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="53">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="25">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="52">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12184,17 +12247,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="22"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12618,19 +12681,19 @@
       </c>
       <c r="B5" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C5" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A5)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D5" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A5)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
@@ -12638,7 +12701,7 @@
       </c>
       <c r="G5" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -12963,7 +13026,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -14243,1094 +14306,2706 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="40">
+      <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B26" s="41" t="str">
+      <c r="B26" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C26" s="41" t="str">
+      <c r="C26" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D26" s="42">
+      <c r="D26" s="3">
         <v>46111</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="44">
+      <c r="F26" s="1">
         <v>1003027198</v>
       </c>
-      <c r="G26" s="45">
-        <v>5</v>
-      </c>
-      <c r="H26" s="45">
-        <v>5</v>
-      </c>
-      <c r="I26" s="45">
-        <v>4</v>
-      </c>
-      <c r="J26" s="45">
-        <v>4</v>
-      </c>
-      <c r="K26" s="45">
-        <v>4</v>
-      </c>
-      <c r="L26" s="45">
-        <v>4</v>
-      </c>
-      <c r="M26" s="45">
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+      <c r="I26" s="1">
+        <v>4</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>4</v>
+      </c>
+      <c r="L26" s="1">
+        <v>4</v>
+      </c>
+      <c r="M26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G26:M26),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O26" s="46" t="str" cm="1">
+      <c r="O26" s="18" t="str" cm="1">
         <f t="array" ref="O26">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="40">
+      <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B27" s="41" t="str">
+      <c r="B27" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C27" s="41" t="str">
+      <c r="C27" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="3">
         <v>46111</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="E27" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="1">
         <v>1035017030</v>
       </c>
-      <c r="G27" s="45">
-        <v>5</v>
-      </c>
-      <c r="H27" s="45">
-        <v>5</v>
-      </c>
-      <c r="I27" s="45">
-        <v>5</v>
-      </c>
-      <c r="J27" s="45">
+      <c r="G27" s="1">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
         <v>3</v>
       </c>
-      <c r="K27" s="45">
-        <v>4</v>
-      </c>
-      <c r="L27" s="45">
+      <c r="K27" s="1">
+        <v>4</v>
+      </c>
+      <c r="L27" s="1">
         <v>3</v>
       </c>
-      <c r="M27" s="45">
+      <c r="M27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G27:M27),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O27" s="46" t="str" cm="1">
+      <c r="O27" s="18" t="str" cm="1">
         <f t="array" ref="O27">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
+      <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B28" s="41" t="str">
+      <c r="B28" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C28" s="41" t="str">
+      <c r="C28" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="3">
         <v>46111</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="E28" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="1">
         <v>1062424218</v>
       </c>
-      <c r="G28" s="45">
-        <v>5</v>
-      </c>
-      <c r="H28" s="45">
-        <v>5</v>
-      </c>
-      <c r="I28" s="45">
-        <v>5</v>
-      </c>
-      <c r="J28" s="45">
-        <v>4</v>
-      </c>
-      <c r="K28" s="45">
-        <v>4</v>
-      </c>
-      <c r="L28" s="45">
-        <v>4</v>
-      </c>
-      <c r="M28" s="45">
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4</v>
+      </c>
+      <c r="K28" s="1">
+        <v>4</v>
+      </c>
+      <c r="L28" s="1">
+        <v>4</v>
+      </c>
+      <c r="M28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G28:M28),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O28" s="46" t="str" cm="1">
+      <c r="O28" s="18" t="str" cm="1">
         <f t="array" ref="O28">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="40">
+      <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B29" s="41" t="str">
+      <c r="B29" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C29" s="41" t="str">
+      <c r="C29" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="3">
         <v>46111</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="1">
         <v>1062436143</v>
       </c>
-      <c r="G29" s="45">
-        <v>5</v>
-      </c>
-      <c r="H29" s="45">
-        <v>5</v>
-      </c>
-      <c r="I29" s="45">
+      <c r="G29" s="1">
+        <v>5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>5</v>
+      </c>
+      <c r="I29" s="1">
         <v>3</v>
       </c>
-      <c r="J29" s="45">
+      <c r="J29" s="1">
         <v>3</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="1">
         <v>2</v>
       </c>
-      <c r="L29" s="45">
+      <c r="L29" s="1">
         <v>2</v>
       </c>
-      <c r="M29" s="45">
+      <c r="M29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G29:M29),"-")</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O29" s="46" t="str" cm="1">
+      <c r="O29" s="18" t="str" cm="1">
         <f t="array" ref="O29">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="40">
+      <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B30" s="41" t="str">
+      <c r="B30" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C30" s="41" t="str">
+      <c r="C30" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="3">
         <v>46111</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="1">
         <v>1062444411</v>
       </c>
-      <c r="G30" s="45">
-        <v>5</v>
-      </c>
-      <c r="H30" s="45">
-        <v>5</v>
-      </c>
-      <c r="I30" s="45">
-        <v>5</v>
-      </c>
-      <c r="J30" s="45">
-        <v>5</v>
-      </c>
-      <c r="K30" s="45">
-        <v>5</v>
-      </c>
-      <c r="L30" s="45">
-        <v>5</v>
-      </c>
-      <c r="M30" s="45">
+      <c r="G30" s="1">
+        <v>5</v>
+      </c>
+      <c r="H30" s="1">
+        <v>5</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5</v>
+      </c>
+      <c r="K30" s="1">
+        <v>5</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G30:M30),"-")</f>
         <v>5</v>
       </c>
-      <c r="O30" s="46" t="str" cm="1">
+      <c r="O30" s="18" t="str" cm="1">
         <f t="array" ref="O30">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="40">
+      <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B31" s="41" t="str">
+      <c r="B31" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C31" s="41" t="str">
+      <c r="C31" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="3">
         <v>46111</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="E31" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="1">
         <v>1062540875</v>
       </c>
-      <c r="G31" s="45">
-        <v>5</v>
-      </c>
-      <c r="H31" s="45">
-        <v>5</v>
-      </c>
-      <c r="I31" s="45">
+      <c r="G31" s="1">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>5</v>
+      </c>
+      <c r="I31" s="1">
         <v>3</v>
       </c>
-      <c r="J31" s="45">
+      <c r="J31" s="1">
         <v>3</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="1">
         <v>3</v>
       </c>
-      <c r="L31" s="45">
+      <c r="L31" s="1">
         <v>2</v>
       </c>
-      <c r="M31" s="45">
+      <c r="M31" s="1">
         <v>4</v>
       </c>
       <c r="N31" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G31:M31),"-")</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O31" s="46" t="str" cm="1">
+      <c r="O31" s="18" t="str" cm="1">
         <f t="array" ref="O31">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="40">
+      <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B32" s="41" t="str">
+      <c r="B32" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C32" s="41" t="str">
+      <c r="C32" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D32" s="42">
+      <c r="D32" s="3">
         <v>46111</v>
       </c>
-      <c r="E32" s="43" t="s">
+      <c r="E32" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G32" s="45">
-        <v>5</v>
-      </c>
-      <c r="H32" s="45">
-        <v>5</v>
-      </c>
-      <c r="I32" s="45">
-        <v>5</v>
-      </c>
-      <c r="J32" s="45">
-        <v>4</v>
-      </c>
-      <c r="K32" s="45">
-        <v>4</v>
-      </c>
-      <c r="L32" s="45">
-        <v>4</v>
-      </c>
-      <c r="M32" s="45">
+      <c r="G32" s="1">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4</v>
+      </c>
+      <c r="K32" s="1">
+        <v>4</v>
+      </c>
+      <c r="L32" s="1">
+        <v>4</v>
+      </c>
+      <c r="M32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G32:M32),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O32" s="46" t="str" cm="1">
+      <c r="O32" s="18" t="str" cm="1">
         <f t="array" ref="O32">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="40">
+      <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B33" s="41" t="str">
+      <c r="B33" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C33" s="41" t="str">
+      <c r="C33" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D33" s="42">
+      <c r="D33" s="3">
         <v>46111</v>
       </c>
-      <c r="E33" s="43" t="s">
+      <c r="E33" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="44">
+      <c r="F33" s="1">
         <v>1062546526</v>
       </c>
-      <c r="G33" s="45">
-        <v>5</v>
-      </c>
-      <c r="H33" s="45">
-        <v>5</v>
-      </c>
-      <c r="I33" s="45">
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>5</v>
+      </c>
+      <c r="I33" s="1">
         <v>3</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="1">
         <v>3</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="1">
         <v>3</v>
       </c>
-      <c r="L33" s="45">
+      <c r="L33" s="1">
         <v>2</v>
       </c>
-      <c r="M33" s="45">
+      <c r="M33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G33:M33),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O33" s="46" t="str" cm="1">
+      <c r="O33" s="18" t="str" cm="1">
         <f t="array" ref="O33">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="40">
+      <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B34" s="41" t="str">
+      <c r="B34" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C34" s="41" t="str">
+      <c r="C34" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D34" s="42">
+      <c r="D34" s="3">
         <v>46111</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="E34" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="44">
+      <c r="F34" s="1">
         <v>1062966144</v>
       </c>
-      <c r="G34" s="45">
-        <v>5</v>
-      </c>
-      <c r="H34" s="45">
-        <v>5</v>
-      </c>
-      <c r="I34" s="45">
-        <v>5</v>
-      </c>
-      <c r="J34" s="45">
-        <v>4</v>
-      </c>
-      <c r="K34" s="45">
-        <v>4</v>
-      </c>
-      <c r="L34" s="45">
-        <v>4</v>
-      </c>
-      <c r="M34" s="45">
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4</v>
+      </c>
+      <c r="K34" s="1">
+        <v>4</v>
+      </c>
+      <c r="L34" s="1">
+        <v>4</v>
+      </c>
+      <c r="M34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G34:M34),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O34" s="46" t="str" cm="1">
+      <c r="O34" s="18" t="str" cm="1">
         <f t="array" ref="O34">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="40">
+      <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B35" s="41" t="str">
+      <c r="B35" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C35" s="41" t="str">
+      <c r="C35" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="3">
         <v>46111</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="1">
         <v>1067940515</v>
       </c>
-      <c r="G35" s="45">
-        <v>5</v>
-      </c>
-      <c r="H35" s="45">
-        <v>5</v>
-      </c>
-      <c r="I35" s="45">
-        <v>4</v>
-      </c>
-      <c r="J35" s="45">
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5</v>
+      </c>
+      <c r="I35" s="1">
+        <v>4</v>
+      </c>
+      <c r="J35" s="1">
         <v>3</v>
       </c>
-      <c r="K35" s="45">
-        <v>4</v>
-      </c>
-      <c r="L35" s="45">
+      <c r="K35" s="1">
+        <v>4</v>
+      </c>
+      <c r="L35" s="1">
         <v>3</v>
       </c>
-      <c r="M35" s="45">
+      <c r="M35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G35:M35),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O35" s="46" t="str" cm="1">
+      <c r="O35" s="18" t="str" cm="1">
         <f t="array" ref="O35">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="40">
+      <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B36" s="41" t="str">
+      <c r="B36" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C36" s="41" t="str">
+      <c r="C36" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="3">
         <v>46111</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="E36" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="1">
         <v>1067945529</v>
       </c>
-      <c r="G36" s="45">
-        <v>5</v>
-      </c>
-      <c r="H36" s="45">
-        <v>5</v>
-      </c>
-      <c r="I36" s="45">
-        <v>5</v>
-      </c>
-      <c r="J36" s="45">
-        <v>4</v>
-      </c>
-      <c r="K36" s="45">
-        <v>4</v>
-      </c>
-      <c r="L36" s="45">
-        <v>4</v>
-      </c>
-      <c r="M36" s="45">
+      <c r="G36" s="1">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1">
+        <v>5</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>4</v>
+      </c>
+      <c r="K36" s="1">
+        <v>4</v>
+      </c>
+      <c r="L36" s="1">
+        <v>4</v>
+      </c>
+      <c r="M36" s="1">
         <v>5</v>
       </c>
       <c r="N36" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G36:M36),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O36" s="46" t="str" cm="1">
+      <c r="O36" s="18" t="str" cm="1">
         <f t="array" ref="O36">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="40">
+      <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B37" s="41" t="str">
+      <c r="B37" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C37" s="41" t="str">
+      <c r="C37" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="3">
         <v>46111</v>
       </c>
-      <c r="E37" s="43" t="s">
+      <c r="E37" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="1">
         <v>1067956606</v>
       </c>
-      <c r="G37" s="45">
-        <v>5</v>
-      </c>
-      <c r="H37" s="45">
-        <v>5</v>
-      </c>
-      <c r="I37" s="45">
-        <v>5</v>
-      </c>
-      <c r="J37" s="45">
-        <v>5</v>
-      </c>
-      <c r="K37" s="45">
-        <v>5</v>
-      </c>
-      <c r="L37" s="45">
-        <v>5</v>
-      </c>
-      <c r="M37" s="45">
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5</v>
+      </c>
+      <c r="K37" s="1">
+        <v>5</v>
+      </c>
+      <c r="L37" s="1">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1">
         <v>5</v>
       </c>
       <c r="N37" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G37:M37),"-")</f>
         <v>5</v>
       </c>
-      <c r="O37" s="46" t="str" cm="1">
+      <c r="O37" s="18" t="str" cm="1">
         <f t="array" ref="O37">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="40">
+      <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B38" s="41" t="str">
+      <c r="B38" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C38" s="41" t="str">
+      <c r="C38" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D38" s="42">
+      <c r="D38" s="3">
         <v>46111</v>
       </c>
-      <c r="E38" s="43" t="s">
+      <c r="E38" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="1">
         <v>1068441879</v>
       </c>
-      <c r="G38" s="45">
-        <v>5</v>
-      </c>
-      <c r="H38" s="45">
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1">
         <v>3</v>
       </c>
-      <c r="I38" s="45">
+      <c r="I38" s="1">
         <v>2</v>
       </c>
-      <c r="J38" s="45">
+      <c r="J38" s="1">
         <v>3</v>
       </c>
-      <c r="K38" s="45">
+      <c r="K38" s="1">
         <v>2</v>
       </c>
-      <c r="L38" s="45">
+      <c r="L38" s="1">
         <v>2</v>
       </c>
-      <c r="M38" s="45">
+      <c r="M38" s="1">
         <v>4</v>
       </c>
       <c r="N38" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G38:M38),"-")</f>
         <v>3</v>
       </c>
-      <c r="O38" s="46" t="str" cm="1">
+      <c r="O38" s="18" t="str" cm="1">
         <f t="array" ref="O38">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="40">
+      <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B39" s="41" t="str">
+      <c r="B39" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C39" s="41" t="str">
+      <c r="C39" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D39" s="42">
+      <c r="D39" s="3">
         <v>46111</v>
       </c>
-      <c r="E39" s="43" t="s">
+      <c r="E39" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F39" s="44">
+      <c r="F39" s="1">
         <v>1068442748</v>
       </c>
-      <c r="G39" s="45">
-        <v>5</v>
-      </c>
-      <c r="H39" s="45">
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1">
         <v>1</v>
       </c>
-      <c r="I39" s="45">
+      <c r="I39" s="1">
         <v>2</v>
       </c>
-      <c r="J39" s="45">
+      <c r="J39" s="1">
         <v>1</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="1">
         <v>1</v>
       </c>
-      <c r="L39" s="45">
+      <c r="L39" s="1">
         <v>1</v>
       </c>
-      <c r="M39" s="45">
+      <c r="M39" s="1">
         <v>1</v>
       </c>
       <c r="N39" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G39:M39),"-")</f>
         <v>1.7142857142857142</v>
       </c>
-      <c r="O39" s="46" t="str" cm="1">
+      <c r="O39" s="18" t="str" cm="1">
         <f t="array" ref="O39">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="40">
+      <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B40" s="41" t="str">
+      <c r="B40" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C40" s="41" t="str">
+      <c r="C40" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D40" s="3">
         <v>46111</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="E40" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F40" s="44">
+      <c r="F40" s="1">
         <v>1068443767</v>
       </c>
-      <c r="G40" s="45">
-        <v>5</v>
-      </c>
-      <c r="H40" s="45">
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
         <v>3</v>
       </c>
-      <c r="I40" s="45">
+      <c r="I40" s="1">
         <v>2</v>
       </c>
-      <c r="J40" s="45">
+      <c r="J40" s="1">
         <v>2</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="1">
         <v>2</v>
       </c>
-      <c r="L40" s="45">
+      <c r="L40" s="1">
         <v>2</v>
       </c>
-      <c r="M40" s="45">
+      <c r="M40" s="1">
         <v>5</v>
       </c>
       <c r="N40" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G40:M40),"-")</f>
         <v>3</v>
       </c>
-      <c r="O40" s="46" t="str" cm="1">
+      <c r="O40" s="18" t="str" cm="1">
         <f t="array" ref="O40">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="40">
+      <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B41" s="41" t="str">
+      <c r="B41" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C41" s="41" t="str">
+      <c r="C41" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D41" s="42">
+      <c r="D41" s="3">
         <v>46111</v>
       </c>
-      <c r="E41" s="43" t="s">
+      <c r="E41" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F41" s="44">
+      <c r="F41" s="1">
         <v>1073824962</v>
       </c>
-      <c r="G41" s="45">
-        <v>5</v>
-      </c>
-      <c r="H41" s="45">
-        <v>5</v>
-      </c>
-      <c r="I41" s="45">
-        <v>5</v>
-      </c>
-      <c r="J41" s="45">
-        <v>4</v>
-      </c>
-      <c r="K41" s="45">
-        <v>5</v>
-      </c>
-      <c r="L41" s="45">
-        <v>4</v>
-      </c>
-      <c r="M41" s="45">
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>5</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1">
+        <v>5</v>
+      </c>
+      <c r="L41" s="1">
+        <v>4</v>
+      </c>
+      <c r="M41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G41:M41),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O41" s="46" t="str" cm="1">
+      <c r="O41" s="18" t="str" cm="1">
         <f t="array" ref="O41">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="40">
+      <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B42" s="41" t="str">
+      <c r="B42" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C42" s="41" t="str">
+      <c r="C42" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D42" s="42">
+      <c r="D42" s="3">
         <v>46111</v>
       </c>
-      <c r="E42" s="43" t="s">
+      <c r="E42" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="44">
+      <c r="F42" s="1">
         <v>1126253349</v>
       </c>
-      <c r="G42" s="45">
-        <v>5</v>
-      </c>
-      <c r="H42" s="45">
-        <v>5</v>
-      </c>
-      <c r="I42" s="45">
-        <v>4</v>
-      </c>
-      <c r="J42" s="45">
-        <v>4</v>
-      </c>
-      <c r="K42" s="45">
-        <v>4</v>
-      </c>
-      <c r="L42" s="45">
-        <v>5</v>
-      </c>
-      <c r="M42" s="45">
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>5</v>
+      </c>
+      <c r="I42" s="1">
+        <v>4</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="1">
+        <v>4</v>
+      </c>
+      <c r="L42" s="1">
+        <v>5</v>
+      </c>
+      <c r="M42" s="1">
         <v>5</v>
       </c>
       <c r="N42" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G42:M42),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O42" s="46" t="str" cm="1">
+      <c r="O42" s="18" t="str" cm="1">
         <f t="array" ref="O42">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="40">
+      <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B43" s="41" t="str">
+      <c r="B43" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C43" s="41" t="str">
+      <c r="C43" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D43" s="42">
+      <c r="D43" s="3">
         <v>46111</v>
       </c>
-      <c r="E43" s="43" t="s">
+      <c r="E43" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="44">
+      <c r="F43" s="1">
         <v>1137975856</v>
       </c>
-      <c r="G43" s="45">
-        <v>5</v>
-      </c>
-      <c r="H43" s="45">
-        <v>5</v>
-      </c>
-      <c r="I43" s="45">
-        <v>5</v>
-      </c>
-      <c r="J43" s="45">
-        <v>4</v>
-      </c>
-      <c r="K43" s="45">
-        <v>4</v>
-      </c>
-      <c r="L43" s="45">
-        <v>4</v>
-      </c>
-      <c r="M43" s="45">
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1">
+        <v>5</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" s="1">
+        <v>4</v>
+      </c>
+      <c r="L43" s="1">
+        <v>4</v>
+      </c>
+      <c r="M43" s="1">
         <v>5</v>
       </c>
       <c r="N43" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G43:M43),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O43" s="46" t="str" cm="1">
+      <c r="O43" s="18" t="str" cm="1">
         <f t="array" ref="O43">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="40">
+      <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B44" s="41" t="str">
+      <c r="B44" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C44" s="41" t="str">
+      <c r="C44" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D44" s="42">
+      <c r="D44" s="3">
         <v>46111</v>
       </c>
-      <c r="E44" s="43" t="s">
+      <c r="E44" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F44" s="44">
+      <c r="F44" s="1">
         <v>1138030749</v>
       </c>
-      <c r="G44" s="45">
-        <v>5</v>
-      </c>
-      <c r="H44" s="45">
-        <v>5</v>
-      </c>
-      <c r="I44" s="45">
-        <v>4</v>
-      </c>
-      <c r="J44" s="45">
-        <v>4</v>
-      </c>
-      <c r="K44" s="45">
-        <v>4</v>
-      </c>
-      <c r="L44" s="45">
-        <v>4</v>
-      </c>
-      <c r="M44" s="45">
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>5</v>
+      </c>
+      <c r="I44" s="1">
+        <v>4</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="1">
+        <v>4</v>
+      </c>
+      <c r="L44" s="1">
+        <v>4</v>
+      </c>
+      <c r="M44" s="1">
         <v>5</v>
       </c>
       <c r="N44" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G44:M44),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O44" s="46" t="str" cm="1">
+      <c r="O44" s="18" t="str" cm="1">
         <f t="array" ref="O44">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="40">
+      <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B45" s="41" t="str">
+      <c r="B45" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C45" s="41" t="str">
+      <c r="C45" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D45" s="42">
+      <c r="D45" s="3">
         <v>46111</v>
       </c>
-      <c r="E45" s="43" t="s">
+      <c r="E45" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="44">
+      <c r="F45" s="1">
         <v>1138031920</v>
       </c>
-      <c r="G45" s="45">
-        <v>5</v>
-      </c>
-      <c r="H45" s="45">
-        <v>5</v>
-      </c>
-      <c r="I45" s="45">
-        <v>5</v>
-      </c>
-      <c r="J45" s="45">
-        <v>4</v>
-      </c>
-      <c r="K45" s="45">
-        <v>5</v>
-      </c>
-      <c r="L45" s="45">
-        <v>4</v>
-      </c>
-      <c r="M45" s="45">
+      <c r="G45" s="1">
+        <v>5</v>
+      </c>
+      <c r="H45" s="1">
+        <v>5</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+      <c r="K45" s="1">
+        <v>5</v>
+      </c>
+      <c r="L45" s="1">
+        <v>4</v>
+      </c>
+      <c r="M45" s="1">
         <v>5</v>
       </c>
       <c r="N45" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G45:M45),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O45" s="46" t="str" cm="1">
+      <c r="O45" s="18" t="str" cm="1">
         <f t="array" ref="O45">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="40">
+      <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B46" s="41" t="str">
+      <c r="B46" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C46" s="41" t="str">
+      <c r="C46" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D46" s="42">
+      <c r="D46" s="3">
         <v>46111</v>
       </c>
-      <c r="E46" s="43" t="s">
+      <c r="E46" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F46" s="44">
+      <c r="F46" s="1">
         <v>1233348383</v>
       </c>
-      <c r="G46" s="45">
-        <v>5</v>
-      </c>
-      <c r="H46" s="45">
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1">
         <v>2</v>
       </c>
-      <c r="I46" s="45">
+      <c r="I46" s="1">
         <v>2</v>
       </c>
-      <c r="J46" s="45">
+      <c r="J46" s="1">
         <v>2</v>
       </c>
-      <c r="K46" s="45">
+      <c r="K46" s="1">
         <v>2</v>
       </c>
-      <c r="L46" s="45">
+      <c r="L46" s="1">
         <v>2</v>
       </c>
-      <c r="M46" s="45">
+      <c r="M46" s="1">
         <v>4</v>
       </c>
       <c r="N46" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G46:M46),"-")</f>
         <v>2.7142857142857144</v>
       </c>
-      <c r="O46" s="46" t="str" cm="1">
+      <c r="O46" s="18" t="str" cm="1">
         <f t="array" ref="O46">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B47" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C47" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D47" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E47" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="45">
+        <v>8203609</v>
+      </c>
+      <c r="G47" s="46">
+        <v>5</v>
+      </c>
+      <c r="H47" s="46">
+        <v>5</v>
+      </c>
+      <c r="I47" s="46">
+        <v>5</v>
+      </c>
+      <c r="J47" s="46">
+        <v>5</v>
+      </c>
+      <c r="K47" s="46">
+        <v>5</v>
+      </c>
+      <c r="L47" s="46">
+        <v>5</v>
+      </c>
+      <c r="M47" s="46">
+        <v>5</v>
+      </c>
+      <c r="N47" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G47:M47),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O47" s="42" t="str" cm="1">
+        <f t="array" ref="O47">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B48" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C48" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D48" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E48" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="45">
+        <v>10784668</v>
+      </c>
+      <c r="G48" s="46">
+        <v>5</v>
+      </c>
+      <c r="H48" s="46">
+        <v>5</v>
+      </c>
+      <c r="I48" s="46">
+        <v>4</v>
+      </c>
+      <c r="J48" s="46">
+        <v>3</v>
+      </c>
+      <c r="K48" s="46">
+        <v>3</v>
+      </c>
+      <c r="L48" s="46">
+        <v>3</v>
+      </c>
+      <c r="M48" s="46">
+        <v>5</v>
+      </c>
+      <c r="N48" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G48:M48),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O48" s="42" t="str" cm="1">
+        <f t="array" ref="O48">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B49" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C49" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D49" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E49" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" s="45">
+        <v>34882674</v>
+      </c>
+      <c r="G49" s="46">
+        <v>5</v>
+      </c>
+      <c r="H49" s="46">
+        <v>2</v>
+      </c>
+      <c r="I49" s="46">
+        <v>2</v>
+      </c>
+      <c r="J49" s="46">
+        <v>2</v>
+      </c>
+      <c r="K49" s="46">
+        <v>2</v>
+      </c>
+      <c r="L49" s="46">
+        <v>2</v>
+      </c>
+      <c r="M49" s="46">
+        <v>1</v>
+      </c>
+      <c r="N49" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G49:M49),"-")</f>
+        <v>2.2857142857142856</v>
+      </c>
+      <c r="O49" s="42" t="str" cm="1">
+        <f t="array" ref="O49">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B50" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C50" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D50" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E50" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="45">
+        <v>50906315</v>
+      </c>
+      <c r="G50" s="46">
+        <v>5</v>
+      </c>
+      <c r="H50" s="46">
+        <v>2</v>
+      </c>
+      <c r="I50" s="46">
+        <v>2</v>
+      </c>
+      <c r="J50" s="46">
+        <v>1</v>
+      </c>
+      <c r="K50" s="46">
+        <v>1</v>
+      </c>
+      <c r="L50" s="46">
+        <v>1</v>
+      </c>
+      <c r="M50" s="46">
+        <v>1</v>
+      </c>
+      <c r="N50" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G50:M50),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O50" s="42" t="str" cm="1">
+        <f t="array" ref="O50">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B51" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C51" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D51" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E51" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="F51" s="45">
+        <v>78713979</v>
+      </c>
+      <c r="G51" s="46">
+        <v>5</v>
+      </c>
+      <c r="H51" s="46">
+        <v>3</v>
+      </c>
+      <c r="I51" s="46">
+        <v>3</v>
+      </c>
+      <c r="J51" s="46">
+        <v>3</v>
+      </c>
+      <c r="K51" s="46">
+        <v>1</v>
+      </c>
+      <c r="L51" s="46">
+        <v>1</v>
+      </c>
+      <c r="M51" s="46">
+        <v>1</v>
+      </c>
+      <c r="N51" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G51:M51),"-")</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O51" s="42" t="str" cm="1">
+        <f t="array" ref="O51">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B52" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C52" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D52" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E52" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F52" s="45">
+        <v>1003027198</v>
+      </c>
+      <c r="G52" s="46">
+        <v>5</v>
+      </c>
+      <c r="H52" s="46">
+        <v>5</v>
+      </c>
+      <c r="I52" s="46">
+        <v>5</v>
+      </c>
+      <c r="J52" s="46">
+        <v>5</v>
+      </c>
+      <c r="K52" s="46">
+        <v>5</v>
+      </c>
+      <c r="L52" s="46">
+        <v>5</v>
+      </c>
+      <c r="M52" s="46">
+        <v>5</v>
+      </c>
+      <c r="N52" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G52:M52),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O52" s="42" t="str" cm="1">
+        <f t="array" ref="O52">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B53" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C53" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D53" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E53" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="45">
+        <v>1003405136</v>
+      </c>
+      <c r="G53" s="46">
+        <v>5</v>
+      </c>
+      <c r="H53" s="46">
+        <v>4</v>
+      </c>
+      <c r="I53" s="46">
+        <v>4</v>
+      </c>
+      <c r="J53" s="46">
+        <v>3</v>
+      </c>
+      <c r="K53" s="46">
+        <v>3</v>
+      </c>
+      <c r="L53" s="46">
+        <v>2</v>
+      </c>
+      <c r="M53" s="46">
+        <v>3</v>
+      </c>
+      <c r="N53" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G53:M53),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O53" s="42" t="str" cm="1">
+        <f t="array" ref="O53">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B54" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C54" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D54" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E54" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="45">
+        <v>1003435656</v>
+      </c>
+      <c r="G54" s="46">
+        <v>5</v>
+      </c>
+      <c r="H54" s="46">
+        <v>5</v>
+      </c>
+      <c r="I54" s="46">
+        <v>5</v>
+      </c>
+      <c r="J54" s="46">
+        <v>5</v>
+      </c>
+      <c r="K54" s="46">
+        <v>5</v>
+      </c>
+      <c r="L54" s="46">
+        <v>5</v>
+      </c>
+      <c r="M54" s="46">
+        <v>5</v>
+      </c>
+      <c r="N54" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G54:M54),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O54" s="42" t="str" cm="1">
+        <f t="array" ref="O54">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B55" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C55" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D55" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E55" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="45">
+        <v>1003561480</v>
+      </c>
+      <c r="G55" s="46">
+        <v>5</v>
+      </c>
+      <c r="H55" s="46">
+        <v>1</v>
+      </c>
+      <c r="I55" s="46">
+        <v>2</v>
+      </c>
+      <c r="J55" s="46">
+        <v>1</v>
+      </c>
+      <c r="K55" s="46">
+        <v>1</v>
+      </c>
+      <c r="L55" s="46">
+        <v>1</v>
+      </c>
+      <c r="M55" s="46">
+        <v>2</v>
+      </c>
+      <c r="N55" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G55:M55),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O55" s="42" t="str" cm="1">
+        <f t="array" ref="O55">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B56" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C56" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D56" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E56" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56" s="45">
+        <v>1025564047</v>
+      </c>
+      <c r="G56" s="46">
+        <v>5</v>
+      </c>
+      <c r="H56" s="46">
+        <v>5</v>
+      </c>
+      <c r="I56" s="46">
+        <v>2</v>
+      </c>
+      <c r="J56" s="46">
+        <v>2</v>
+      </c>
+      <c r="K56" s="46">
+        <v>2</v>
+      </c>
+      <c r="L56" s="46">
+        <v>2</v>
+      </c>
+      <c r="M56" s="46">
+        <v>5</v>
+      </c>
+      <c r="N56" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G56:M56),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O56" s="42" t="str" cm="1">
+        <f t="array" ref="O56">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B57" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C57" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D57" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E57" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="45">
+        <v>1033205387</v>
+      </c>
+      <c r="G57" s="46">
+        <v>4</v>
+      </c>
+      <c r="H57" s="46">
+        <v>2</v>
+      </c>
+      <c r="I57" s="46">
+        <v>1</v>
+      </c>
+      <c r="J57" s="46">
+        <v>1</v>
+      </c>
+      <c r="K57" s="46">
+        <v>1</v>
+      </c>
+      <c r="L57" s="46">
+        <v>1</v>
+      </c>
+      <c r="M57" s="46">
+        <v>3</v>
+      </c>
+      <c r="N57" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G57:M57),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O57" s="42" t="str" cm="1">
+        <f t="array" ref="O57">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B58" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C58" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D58" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E58" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" s="45">
+        <v>1035017030</v>
+      </c>
+      <c r="G58" s="46">
+        <v>5</v>
+      </c>
+      <c r="H58" s="46">
+        <v>5</v>
+      </c>
+      <c r="I58" s="46">
+        <v>5</v>
+      </c>
+      <c r="J58" s="46">
+        <v>3</v>
+      </c>
+      <c r="K58" s="46">
+        <v>5</v>
+      </c>
+      <c r="L58" s="46">
+        <v>3</v>
+      </c>
+      <c r="M58" s="46">
+        <v>5</v>
+      </c>
+      <c r="N58" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G58:M58),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O58" s="42" t="str" cm="1">
+        <f t="array" ref="O58">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B59" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C59" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D59" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E59" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="45">
+        <v>1037236492</v>
+      </c>
+      <c r="G59" s="46">
+        <v>5</v>
+      </c>
+      <c r="H59" s="46">
+        <v>5</v>
+      </c>
+      <c r="I59" s="46">
+        <v>4</v>
+      </c>
+      <c r="J59" s="46">
+        <v>3</v>
+      </c>
+      <c r="K59" s="46">
+        <v>3</v>
+      </c>
+      <c r="L59" s="46">
+        <v>2</v>
+      </c>
+      <c r="M59" s="46">
+        <v>4</v>
+      </c>
+      <c r="N59" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G59:M59),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O59" s="42" t="str" cm="1">
+        <f t="array" ref="O59">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B60" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C60" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D60" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E60" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="F60" s="45">
+        <v>1062438398</v>
+      </c>
+      <c r="G60" s="46">
+        <v>5</v>
+      </c>
+      <c r="H60" s="46">
+        <v>5</v>
+      </c>
+      <c r="I60" s="46">
+        <v>4</v>
+      </c>
+      <c r="J60" s="46">
+        <v>4</v>
+      </c>
+      <c r="K60" s="46">
+        <v>4</v>
+      </c>
+      <c r="L60" s="46">
+        <v>4</v>
+      </c>
+      <c r="M60" s="46">
+        <v>5</v>
+      </c>
+      <c r="N60" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G60:M60),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O60" s="42" t="str" cm="1">
+        <f t="array" ref="O60">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B61" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C61" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D61" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E61" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61" s="45">
+        <v>1062540875</v>
+      </c>
+      <c r="G61" s="46">
+        <v>5</v>
+      </c>
+      <c r="H61" s="46">
+        <v>5</v>
+      </c>
+      <c r="I61" s="46">
+        <v>4</v>
+      </c>
+      <c r="J61" s="46">
+        <v>3</v>
+      </c>
+      <c r="K61" s="46">
+        <v>4</v>
+      </c>
+      <c r="L61" s="46">
+        <v>2</v>
+      </c>
+      <c r="M61" s="46">
+        <v>5</v>
+      </c>
+      <c r="N61" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G61:M61),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O61" s="42" t="str" cm="1">
+        <f t="array" ref="O61">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B62" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C62" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D62" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E62" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="F62" s="45">
+        <v>1062544508</v>
+      </c>
+      <c r="G62" s="46">
+        <v>5</v>
+      </c>
+      <c r="H62" s="46">
+        <v>5</v>
+      </c>
+      <c r="I62" s="46">
+        <v>5</v>
+      </c>
+      <c r="J62" s="46">
+        <v>5</v>
+      </c>
+      <c r="K62" s="46">
+        <v>5</v>
+      </c>
+      <c r="L62" s="46">
+        <v>5</v>
+      </c>
+      <c r="M62" s="46">
+        <v>5</v>
+      </c>
+      <c r="N62" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G62:M62),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O62" s="42" t="str" cm="1">
+        <f t="array" ref="O62">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B63" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C63" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D63" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E63" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63" s="45">
+        <v>1062546526</v>
+      </c>
+      <c r="G63" s="46">
+        <v>5</v>
+      </c>
+      <c r="H63" s="46">
+        <v>5</v>
+      </c>
+      <c r="I63" s="46">
+        <v>4</v>
+      </c>
+      <c r="J63" s="46">
+        <v>3</v>
+      </c>
+      <c r="K63" s="46">
+        <v>2</v>
+      </c>
+      <c r="L63" s="46">
+        <v>2</v>
+      </c>
+      <c r="M63" s="46">
+        <v>5</v>
+      </c>
+      <c r="N63" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G63:M63),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O63" s="42" t="str" cm="1">
+        <f t="array" ref="O63">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B64" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C64" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D64" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E64" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F64" s="45">
+        <v>1062966144</v>
+      </c>
+      <c r="G64" s="46">
+        <v>5</v>
+      </c>
+      <c r="H64" s="46">
+        <v>5</v>
+      </c>
+      <c r="I64" s="46">
+        <v>5</v>
+      </c>
+      <c r="J64" s="46">
+        <v>5</v>
+      </c>
+      <c r="K64" s="46">
+        <v>5</v>
+      </c>
+      <c r="L64" s="46">
+        <v>5</v>
+      </c>
+      <c r="M64" s="46">
+        <v>5</v>
+      </c>
+      <c r="N64" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G64:M64),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O64" s="42" t="str" cm="1">
+        <f t="array" ref="O64">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B65" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C65" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D65" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E65" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" s="45">
+        <v>1063077486</v>
+      </c>
+      <c r="G65" s="46">
+        <v>5</v>
+      </c>
+      <c r="H65" s="46">
+        <v>5</v>
+      </c>
+      <c r="I65" s="46">
+        <v>5</v>
+      </c>
+      <c r="J65" s="46">
+        <v>5</v>
+      </c>
+      <c r="K65" s="46">
+        <v>5</v>
+      </c>
+      <c r="L65" s="46">
+        <v>5</v>
+      </c>
+      <c r="M65" s="46">
+        <v>1</v>
+      </c>
+      <c r="N65" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G65:M65),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O65" s="42" t="str" cm="1">
+        <f t="array" ref="O65">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B66" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C66" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D66" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E66" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F66" s="45">
+        <v>1067860876</v>
+      </c>
+      <c r="G66" s="46">
+        <v>5</v>
+      </c>
+      <c r="H66" s="46">
+        <v>5</v>
+      </c>
+      <c r="I66" s="46">
+        <v>4</v>
+      </c>
+      <c r="J66" s="46">
+        <v>4</v>
+      </c>
+      <c r="K66" s="46">
+        <v>4</v>
+      </c>
+      <c r="L66" s="46">
+        <v>4</v>
+      </c>
+      <c r="M66" s="46">
+        <v>5</v>
+      </c>
+      <c r="N66" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G66:M66),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O66" s="42" t="str" cm="1">
+        <f t="array" ref="O66">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B67" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C67" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D67" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E67" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="45">
+        <v>1067945529</v>
+      </c>
+      <c r="G67" s="46">
+        <v>5</v>
+      </c>
+      <c r="H67" s="46">
+        <v>5</v>
+      </c>
+      <c r="I67" s="46">
+        <v>5</v>
+      </c>
+      <c r="J67" s="46">
+        <v>5</v>
+      </c>
+      <c r="K67" s="46">
+        <v>5</v>
+      </c>
+      <c r="L67" s="46">
+        <v>5</v>
+      </c>
+      <c r="M67" s="46">
+        <v>5</v>
+      </c>
+      <c r="N67" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G67:M67),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O67" s="42" t="str" cm="1">
+        <f t="array" ref="O67">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B68" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C68" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D68" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E68" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68" s="45">
+        <v>1067958657</v>
+      </c>
+      <c r="G68" s="46">
+        <v>5</v>
+      </c>
+      <c r="H68" s="46">
+        <v>2</v>
+      </c>
+      <c r="I68" s="46">
+        <v>2</v>
+      </c>
+      <c r="J68" s="46">
+        <v>2</v>
+      </c>
+      <c r="K68" s="46">
+        <v>2</v>
+      </c>
+      <c r="L68" s="46">
+        <v>2</v>
+      </c>
+      <c r="M68" s="46">
+        <v>2</v>
+      </c>
+      <c r="N68" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G68:M68),"-")</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O68" s="42" t="str" cm="1">
+        <f t="array" ref="O68">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B69" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C69" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D69" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E69" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" s="45">
+        <v>1068441879</v>
+      </c>
+      <c r="G69" s="46">
+        <v>5</v>
+      </c>
+      <c r="H69" s="46">
+        <v>4</v>
+      </c>
+      <c r="I69" s="46">
+        <v>3</v>
+      </c>
+      <c r="J69" s="46">
+        <v>3</v>
+      </c>
+      <c r="K69" s="46">
+        <v>2</v>
+      </c>
+      <c r="L69" s="46">
+        <v>2</v>
+      </c>
+      <c r="M69" s="46">
+        <v>5</v>
+      </c>
+      <c r="N69" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G69:M69),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O69" s="42" t="str" cm="1">
+        <f t="array" ref="O69">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B70" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C70" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D70" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E70" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="45">
+        <v>1068442748</v>
+      </c>
+      <c r="G70" s="46">
+        <v>5</v>
+      </c>
+      <c r="H70" s="46">
+        <v>2</v>
+      </c>
+      <c r="I70" s="46">
+        <v>2</v>
+      </c>
+      <c r="J70" s="46">
+        <v>1</v>
+      </c>
+      <c r="K70" s="46">
+        <v>1</v>
+      </c>
+      <c r="L70" s="46">
+        <v>1</v>
+      </c>
+      <c r="M70" s="46">
+        <v>1</v>
+      </c>
+      <c r="N70" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G70:M70),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O70" s="42" t="str" cm="1">
+        <f t="array" ref="O70">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B71" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C71" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D71" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E71" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F71" s="45">
+        <v>1068443767</v>
+      </c>
+      <c r="G71" s="46">
+        <v>5</v>
+      </c>
+      <c r="H71" s="46">
+        <v>3</v>
+      </c>
+      <c r="I71" s="46">
+        <v>2</v>
+      </c>
+      <c r="J71" s="46">
+        <v>2</v>
+      </c>
+      <c r="K71" s="46">
+        <v>2</v>
+      </c>
+      <c r="L71" s="46">
+        <v>2</v>
+      </c>
+      <c r="M71" s="46">
+        <v>5</v>
+      </c>
+      <c r="N71" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G71:M71),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O71" s="42" t="str" cm="1">
+        <f t="array" ref="O71">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B72" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C72" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D72" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E72" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" s="45">
+        <v>1068580241</v>
+      </c>
+      <c r="G72" s="46">
+        <v>5</v>
+      </c>
+      <c r="H72" s="46">
+        <v>5</v>
+      </c>
+      <c r="I72" s="46">
+        <v>4</v>
+      </c>
+      <c r="J72" s="46">
+        <v>3</v>
+      </c>
+      <c r="K72" s="46">
+        <v>4</v>
+      </c>
+      <c r="L72" s="46">
+        <v>3</v>
+      </c>
+      <c r="M72" s="46">
+        <v>4</v>
+      </c>
+      <c r="N72" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G72:M72),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O72" s="42" t="str" cm="1">
+        <f t="array" ref="O72">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B73" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C73" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D73" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E73" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="F73" s="45">
+        <v>1103755851</v>
+      </c>
+      <c r="G73" s="46">
+        <v>5</v>
+      </c>
+      <c r="H73" s="46">
+        <v>4</v>
+      </c>
+      <c r="I73" s="46">
+        <v>4</v>
+      </c>
+      <c r="J73" s="46">
+        <v>3</v>
+      </c>
+      <c r="K73" s="46">
+        <v>2</v>
+      </c>
+      <c r="L73" s="46">
+        <v>2</v>
+      </c>
+      <c r="M73" s="46">
+        <v>4</v>
+      </c>
+      <c r="N73" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G73:M73),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O73" s="42" t="str" cm="1">
+        <f t="array" ref="O73">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B74" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C74" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D74" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E74" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="F74" s="45">
+        <v>1137975856</v>
+      </c>
+      <c r="G74" s="46">
+        <v>5</v>
+      </c>
+      <c r="H74" s="46">
+        <v>5</v>
+      </c>
+      <c r="I74" s="46">
+        <v>5</v>
+      </c>
+      <c r="J74" s="46">
+        <v>5</v>
+      </c>
+      <c r="K74" s="46">
+        <v>5</v>
+      </c>
+      <c r="L74" s="46">
+        <v>5</v>
+      </c>
+      <c r="M74" s="46">
+        <v>5</v>
+      </c>
+      <c r="N74" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G74:M74),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O74" s="42" t="str" cm="1">
+        <f t="array" ref="O74">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B75" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C75" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D75" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E75" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="45">
+        <v>1138030749</v>
+      </c>
+      <c r="G75" s="46">
+        <v>5</v>
+      </c>
+      <c r="H75" s="46">
+        <v>5</v>
+      </c>
+      <c r="I75" s="46">
+        <v>4</v>
+      </c>
+      <c r="J75" s="46">
+        <v>4</v>
+      </c>
+      <c r="K75" s="46">
+        <v>4</v>
+      </c>
+      <c r="L75" s="46">
+        <v>4</v>
+      </c>
+      <c r="M75" s="46">
+        <v>5</v>
+      </c>
+      <c r="N75" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G75:M75),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O75" s="42" t="str" cm="1">
+        <f t="array" ref="O75">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B76" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C76" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D76" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E76" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F76" s="45">
+        <v>1233348383</v>
+      </c>
+      <c r="G76" s="46">
+        <v>5</v>
+      </c>
+      <c r="H76" s="46">
+        <v>4</v>
+      </c>
+      <c r="I76" s="46">
+        <v>3</v>
+      </c>
+      <c r="J76" s="46">
+        <v>3</v>
+      </c>
+      <c r="K76" s="46">
+        <v>2</v>
+      </c>
+      <c r="L76" s="46">
+        <v>2</v>
+      </c>
+      <c r="M76" s="46">
+        <v>4</v>
+      </c>
+      <c r="N76" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G76:M76),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O76" s="42" t="str" cm="1">
+        <f t="array" ref="O76">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B77" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C77" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D77" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E77" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F77" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G77" s="46">
+        <v>5</v>
+      </c>
+      <c r="H77" s="46">
+        <v>5</v>
+      </c>
+      <c r="I77" s="46">
+        <v>5</v>
+      </c>
+      <c r="J77" s="46">
+        <v>3</v>
+      </c>
+      <c r="K77" s="46">
+        <v>5</v>
+      </c>
+      <c r="L77" s="46">
+        <v>3</v>
+      </c>
+      <c r="M77" s="46">
+        <v>5</v>
+      </c>
+      <c r="N77" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G77:M77),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O77" s="42" t="str" cm="1">
+        <f t="array" ref="O77">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -15358,7 +17033,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -15914,626 +17589,1250 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="45">
+      <c r="A12" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B12" s="47" t="str">
+      <c r="B12" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C12" s="47" t="str">
+      <c r="C12" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="3">
         <v>46110</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G12" s="45">
-        <v>4</v>
-      </c>
-      <c r="H12" s="45">
-        <v>4</v>
-      </c>
-      <c r="I12" s="45">
-        <v>4</v>
-      </c>
-      <c r="J12" s="45">
-        <v>4</v>
-      </c>
-      <c r="K12" s="45">
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4</v>
+      </c>
+      <c r="K12" s="1">
         <v>3</v>
       </c>
-      <c r="L12" s="45">
-        <v>5</v>
-      </c>
-      <c r="M12" s="45">
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>3</v>
       </c>
       <c r="N12" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G12:M12),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O12" s="48" t="str" cm="1">
+      <c r="O12" s="18" t="str" cm="1">
         <f t="array" ref="O12">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="45">
+      <c r="A13" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B13" s="47" t="str">
+      <c r="B13" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C13" s="47" t="str">
+      <c r="C13" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="3">
         <v>46110</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="1">
         <v>1035003918</v>
       </c>
-      <c r="G13" s="45">
-        <v>5</v>
-      </c>
-      <c r="H13" s="45">
-        <v>4</v>
-      </c>
-      <c r="I13" s="45">
-        <v>4</v>
-      </c>
-      <c r="J13" s="45">
-        <v>4</v>
-      </c>
-      <c r="K13" s="45">
-        <v>4</v>
-      </c>
-      <c r="L13" s="45">
-        <v>5</v>
-      </c>
-      <c r="M13" s="45">
+      <c r="G13" s="1">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
         <v>2</v>
       </c>
       <c r="N13" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G13:M13),"-")</f>
         <v>4</v>
       </c>
-      <c r="O13" s="48" t="str" cm="1">
+      <c r="O13" s="18" t="str" cm="1">
         <f t="array" ref="O13">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
+      <c r="A14" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B14" s="47" t="str">
+      <c r="B14" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C14" s="47" t="str">
+      <c r="C14" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="3">
         <v>46110</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="1">
         <v>1062980565</v>
       </c>
-      <c r="G14" s="45">
-        <v>4</v>
-      </c>
-      <c r="H14" s="45">
-        <v>4</v>
-      </c>
-      <c r="I14" s="45">
+      <c r="G14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4</v>
+      </c>
+      <c r="I14" s="1">
         <v>2</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="1">
         <v>3</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="1">
         <v>3</v>
       </c>
-      <c r="L14" s="45">
-        <v>5</v>
-      </c>
-      <c r="M14" s="45">
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1">
         <v>2</v>
       </c>
       <c r="N14" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G14:M14),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O14" s="48" t="str" cm="1">
+      <c r="O14" s="18" t="str" cm="1">
         <f t="array" ref="O14">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="45">
+      <c r="A15" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B15" s="47" t="str">
+      <c r="B15" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C15" s="47" t="str">
+      <c r="C15" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="3">
         <v>46110</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="1">
         <v>1062981643</v>
       </c>
-      <c r="G15" s="45">
-        <v>4</v>
-      </c>
-      <c r="H15" s="45">
-        <v>5</v>
-      </c>
-      <c r="I15" s="45">
+      <c r="G15" s="1">
+        <v>4</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5</v>
+      </c>
+      <c r="I15" s="1">
         <v>2</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="1">
         <v>3</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="1">
         <v>3</v>
       </c>
-      <c r="L15" s="45">
-        <v>4</v>
-      </c>
-      <c r="M15" s="45">
+      <c r="L15" s="1">
+        <v>4</v>
+      </c>
+      <c r="M15" s="1">
         <v>2</v>
       </c>
       <c r="N15" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G15:M15),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O15" s="48" t="str" cm="1">
+      <c r="O15" s="18" t="str" cm="1">
         <f t="array" ref="O15">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="45">
+      <c r="A16" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B16" s="47" t="str">
+      <c r="B16" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C16" s="47" t="str">
+      <c r="C16" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="3">
         <v>46110</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="1">
         <v>1066747786</v>
       </c>
-      <c r="G16" s="45">
-        <v>5</v>
-      </c>
-      <c r="H16" s="45">
-        <v>4</v>
-      </c>
-      <c r="I16" s="45">
-        <v>4</v>
-      </c>
-      <c r="J16" s="45">
-        <v>4</v>
-      </c>
-      <c r="K16" s="45">
-        <v>4</v>
-      </c>
-      <c r="L16" s="45">
-        <v>5</v>
-      </c>
-      <c r="M16" s="45">
+      <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1">
+        <v>4</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
         <v>2</v>
       </c>
       <c r="N16" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G16:M16),"-")</f>
         <v>4</v>
       </c>
-      <c r="O16" s="48" t="str" cm="1">
+      <c r="O16" s="18" t="str" cm="1">
         <f t="array" ref="O16">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="45">
+      <c r="A17" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B17" s="47" t="str">
+      <c r="B17" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C17" s="47" t="str">
+      <c r="C17" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="3">
         <v>46111</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G17" s="45">
-        <v>4</v>
-      </c>
-      <c r="H17" s="45">
-        <v>4</v>
-      </c>
-      <c r="I17" s="45">
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+      <c r="I17" s="1">
         <v>2</v>
       </c>
-      <c r="J17" s="45">
-        <v>4</v>
-      </c>
-      <c r="K17" s="45">
-        <v>4</v>
-      </c>
-      <c r="L17" s="45">
-        <v>5</v>
-      </c>
-      <c r="M17" s="45">
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1">
+        <v>4</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <v>1</v>
       </c>
       <c r="N17" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G17:M17),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O17" s="48" t="str" cm="1">
+      <c r="O17" s="18" t="str" cm="1">
         <f t="array" ref="O17">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="45">
+      <c r="A18" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B18" s="47" t="str">
+      <c r="B18" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C18" s="47" t="str">
+      <c r="C18" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="3">
         <v>46110</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="1">
         <v>1068439668</v>
       </c>
-      <c r="G18" s="45">
-        <v>5</v>
-      </c>
-      <c r="H18" s="45">
-        <v>5</v>
-      </c>
-      <c r="I18" s="45">
-        <v>4</v>
-      </c>
-      <c r="J18" s="45">
-        <v>4</v>
-      </c>
-      <c r="K18" s="45">
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1">
         <v>3</v>
       </c>
-      <c r="L18" s="45">
-        <v>5</v>
-      </c>
-      <c r="M18" s="45">
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1">
         <v>3</v>
       </c>
       <c r="N18" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G18:M18),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O18" s="48" t="str" cm="1">
+      <c r="O18" s="18" t="str" cm="1">
         <f t="array" ref="O18">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="45">
+      <c r="A19" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B19" s="47" t="str">
+      <c r="B19" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C19" s="47" t="str">
+      <c r="C19" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="3">
         <v>46110</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G19" s="45">
-        <v>5</v>
-      </c>
-      <c r="H19" s="45">
-        <v>4</v>
-      </c>
-      <c r="I19" s="45">
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+      <c r="I19" s="1">
         <v>2</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="1">
         <v>3</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="1">
         <v>2</v>
       </c>
-      <c r="L19" s="45">
-        <v>5</v>
-      </c>
-      <c r="M19" s="45">
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
         <v>2</v>
       </c>
       <c r="N19" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G19:M19),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O19" s="48" t="str" cm="1">
+      <c r="O19" s="18" t="str" cm="1">
         <f t="array" ref="O19">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="45">
+      <c r="A20" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B20" s="47" t="str">
+      <c r="B20" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C20" s="47" t="str">
+      <c r="C20" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="3">
         <v>46110</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="45">
+      <c r="F20" s="1">
         <v>1104267144</v>
       </c>
-      <c r="G20" s="45">
-        <v>4</v>
-      </c>
-      <c r="H20" s="45">
-        <v>4</v>
-      </c>
-      <c r="I20" s="45">
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4</v>
+      </c>
+      <c r="I20" s="1">
         <v>3</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="1">
         <v>3</v>
       </c>
-      <c r="K20" s="45">
-        <v>5</v>
-      </c>
-      <c r="L20" s="45">
-        <v>4</v>
-      </c>
-      <c r="M20" s="45">
+      <c r="K20" s="1">
+        <v>5</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1">
         <v>3</v>
       </c>
       <c r="N20" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G20:M20),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O20" s="48" t="str" cm="1">
+      <c r="O20" s="18" t="str" cm="1">
         <f t="array" ref="O20">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="45">
+      <c r="A21" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B21" s="47" t="str">
+      <c r="B21" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C21" s="47" t="str">
+      <c r="C21" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="3">
         <v>46110</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E21" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="1">
         <v>1138031207</v>
       </c>
-      <c r="G21" s="45">
-        <v>5</v>
-      </c>
-      <c r="H21" s="45">
-        <v>4</v>
-      </c>
-      <c r="I21" s="45">
+      <c r="G21" s="1">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1">
         <v>3</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="1">
         <v>3</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="1">
         <v>3</v>
       </c>
-      <c r="L21" s="45">
-        <v>5</v>
-      </c>
-      <c r="M21" s="45">
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+      <c r="M21" s="1">
         <v>3</v>
       </c>
       <c r="N21" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G21:M21),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O21" s="48" t="str" cm="1">
+      <c r="O21" s="18" t="str" cm="1">
         <f t="array" ref="O21">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="45">
+      <c r="A22" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B22" s="47" t="str">
+      <c r="B22" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C22" s="47" t="str">
+      <c r="C22" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="3">
         <v>46110</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G22" s="45">
-        <v>4</v>
-      </c>
-      <c r="H22" s="45">
-        <v>5</v>
-      </c>
-      <c r="I22" s="45">
+      <c r="G22" s="1">
+        <v>4</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
         <v>3</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="1">
         <v>3</v>
       </c>
-      <c r="K22" s="45">
-        <v>5</v>
-      </c>
-      <c r="L22" s="45">
-        <v>5</v>
-      </c>
-      <c r="M22" s="45">
+      <c r="K22" s="1">
+        <v>5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
         <v>5</v>
       </c>
       <c r="N22" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G22:M22),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O22" s="48" t="str" cm="1">
+      <c r="O22" s="18" t="str" cm="1">
         <f t="array" ref="O22">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="45">
+      <c r="A23" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B23" s="47" t="str">
+      <c r="B23" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C23" s="47" t="str">
+      <c r="C23" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D23" s="42">
+      <c r="D23" s="3">
         <v>46110</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G23" s="45">
-        <v>5</v>
-      </c>
-      <c r="H23" s="45">
-        <v>4</v>
-      </c>
-      <c r="I23" s="45">
-        <v>4</v>
-      </c>
-      <c r="J23" s="45">
-        <v>4</v>
-      </c>
-      <c r="K23" s="45">
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4</v>
+      </c>
+      <c r="K23" s="1">
         <v>3</v>
       </c>
-      <c r="L23" s="45">
-        <v>5</v>
-      </c>
-      <c r="M23" s="45">
+      <c r="L23" s="1">
+        <v>5</v>
+      </c>
+      <c r="M23" s="1">
         <v>3</v>
       </c>
       <c r="N23" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G23:M23),"-")</f>
         <v>4</v>
       </c>
-      <c r="O23" s="48" t="str" cm="1">
+      <c r="O23" s="18" t="str" cm="1">
         <f t="array" ref="O23">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B24" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C24" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D24" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E24" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="46">
+        <v>1027663882</v>
+      </c>
+      <c r="G24" s="46">
+        <v>4</v>
+      </c>
+      <c r="H24" s="46">
+        <v>4</v>
+      </c>
+      <c r="I24" s="46">
+        <v>5</v>
+      </c>
+      <c r="J24" s="46">
+        <v>4</v>
+      </c>
+      <c r="K24" s="46">
+        <v>3</v>
+      </c>
+      <c r="L24" s="46">
+        <v>5</v>
+      </c>
+      <c r="M24" s="46">
+        <v>3</v>
+      </c>
+      <c r="N24" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G24:M24),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O24" s="49" t="str" cm="1">
+        <f t="array" ref="O24">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B25" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C25" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D25" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="46">
+        <v>1062444411</v>
+      </c>
+      <c r="G25" s="46">
+        <v>5</v>
+      </c>
+      <c r="H25" s="46">
+        <v>5</v>
+      </c>
+      <c r="I25" s="46">
+        <v>2</v>
+      </c>
+      <c r="J25" s="46">
+        <v>3</v>
+      </c>
+      <c r="K25" s="46">
+        <v>4</v>
+      </c>
+      <c r="L25" s="46">
+        <v>5</v>
+      </c>
+      <c r="M25" s="46">
+        <v>2</v>
+      </c>
+      <c r="N25" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G25:M25),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O25" s="49" t="str" cm="1">
+        <f t="array" ref="O25">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B26" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C26" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D26" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E26" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="46">
+        <v>1062980565</v>
+      </c>
+      <c r="G26" s="46">
+        <v>4</v>
+      </c>
+      <c r="H26" s="46">
+        <v>4</v>
+      </c>
+      <c r="I26" s="46">
+        <v>3</v>
+      </c>
+      <c r="J26" s="46">
+        <v>3</v>
+      </c>
+      <c r="K26" s="46">
+        <v>3</v>
+      </c>
+      <c r="L26" s="46">
+        <v>5</v>
+      </c>
+      <c r="M26" s="46">
+        <v>2</v>
+      </c>
+      <c r="N26" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G26:M26),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O26" s="49" t="str" cm="1">
+        <f t="array" ref="O26">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B27" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C27" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D27" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="46">
+        <v>1062981643</v>
+      </c>
+      <c r="G27" s="46">
+        <v>4</v>
+      </c>
+      <c r="H27" s="46">
+        <v>5</v>
+      </c>
+      <c r="I27" s="46">
+        <v>2</v>
+      </c>
+      <c r="J27" s="46">
+        <v>3</v>
+      </c>
+      <c r="K27" s="46">
+        <v>3</v>
+      </c>
+      <c r="L27" s="46">
+        <v>5</v>
+      </c>
+      <c r="M27" s="46">
+        <v>2</v>
+      </c>
+      <c r="N27" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G27:M27),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O27" s="49" t="str" cm="1">
+        <f t="array" ref="O27">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B28" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C28" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D28" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E28" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="46">
+        <v>1062986616</v>
+      </c>
+      <c r="G28" s="46">
+        <v>4</v>
+      </c>
+      <c r="H28" s="46">
+        <v>4</v>
+      </c>
+      <c r="I28" s="46">
+        <v>4</v>
+      </c>
+      <c r="J28" s="46">
+        <v>3</v>
+      </c>
+      <c r="K28" s="46">
+        <v>2</v>
+      </c>
+      <c r="L28" s="46">
+        <v>5</v>
+      </c>
+      <c r="M28" s="46">
+        <v>1</v>
+      </c>
+      <c r="N28" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G28:M28),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O28" s="49" t="str" cm="1">
+        <f t="array" ref="O28">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B29" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C29" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D29" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="46">
+        <v>1067859838</v>
+      </c>
+      <c r="G29" s="46">
+        <v>4</v>
+      </c>
+      <c r="H29" s="46">
+        <v>4</v>
+      </c>
+      <c r="I29" s="46">
+        <v>4</v>
+      </c>
+      <c r="J29" s="46">
+        <v>4</v>
+      </c>
+      <c r="K29" s="46">
+        <v>4</v>
+      </c>
+      <c r="L29" s="46">
+        <v>5</v>
+      </c>
+      <c r="M29" s="46">
+        <v>1</v>
+      </c>
+      <c r="N29" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G29:M29),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O29" s="49" t="str" cm="1">
+        <f t="array" ref="O29">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B30" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C30" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D30" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="46">
+        <v>1067956606</v>
+      </c>
+      <c r="G30" s="46">
+        <v>4</v>
+      </c>
+      <c r="H30" s="46">
+        <v>4</v>
+      </c>
+      <c r="I30" s="46">
+        <v>4</v>
+      </c>
+      <c r="J30" s="46">
+        <v>4</v>
+      </c>
+      <c r="K30" s="46">
+        <v>5</v>
+      </c>
+      <c r="L30" s="46">
+        <v>3</v>
+      </c>
+      <c r="M30" s="46">
+        <v>4</v>
+      </c>
+      <c r="N30" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G30:M30),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O30" s="49" t="str" cm="1">
+        <f t="array" ref="O30">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B31" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C31" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D31" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="46">
+        <v>1068439668</v>
+      </c>
+      <c r="G31" s="46">
+        <v>5</v>
+      </c>
+      <c r="H31" s="46">
+        <v>5</v>
+      </c>
+      <c r="I31" s="46">
+        <v>4</v>
+      </c>
+      <c r="J31" s="46">
+        <v>4</v>
+      </c>
+      <c r="K31" s="46">
+        <v>4</v>
+      </c>
+      <c r="L31" s="46">
+        <v>5</v>
+      </c>
+      <c r="M31" s="46">
+        <v>3</v>
+      </c>
+      <c r="N31" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G31:M31),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O31" s="49" t="str" cm="1">
+        <f t="array" ref="O31">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B32" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C32" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D32" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="46">
+        <v>1073817245</v>
+      </c>
+      <c r="G32" s="46">
+        <v>5</v>
+      </c>
+      <c r="H32" s="46">
+        <v>4</v>
+      </c>
+      <c r="I32" s="46">
+        <v>2</v>
+      </c>
+      <c r="J32" s="46">
+        <v>4</v>
+      </c>
+      <c r="K32" s="46">
+        <v>2</v>
+      </c>
+      <c r="L32" s="46">
+        <v>5</v>
+      </c>
+      <c r="M32" s="46">
+        <v>2</v>
+      </c>
+      <c r="N32" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G32:M32),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O32" s="49" t="str" cm="1">
+        <f t="array" ref="O32">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B33" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C33" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D33" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="46">
+        <v>1104267144</v>
+      </c>
+      <c r="G33" s="46">
+        <v>5</v>
+      </c>
+      <c r="H33" s="46">
+        <v>4</v>
+      </c>
+      <c r="I33" s="46">
+        <v>4</v>
+      </c>
+      <c r="J33" s="46">
+        <v>3</v>
+      </c>
+      <c r="K33" s="46">
+        <v>5</v>
+      </c>
+      <c r="L33" s="46">
+        <v>5</v>
+      </c>
+      <c r="M33" s="46">
+        <v>3</v>
+      </c>
+      <c r="N33" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G33:M33),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O33" s="49" t="str" cm="1">
+        <f t="array" ref="O33">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B34" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C34" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D34" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" s="46">
+        <v>1138032549</v>
+      </c>
+      <c r="G34" s="46">
+        <v>5</v>
+      </c>
+      <c r="H34" s="46">
+        <v>5</v>
+      </c>
+      <c r="I34" s="46">
+        <v>3</v>
+      </c>
+      <c r="J34" s="46">
+        <v>3</v>
+      </c>
+      <c r="K34" s="46">
+        <v>5</v>
+      </c>
+      <c r="L34" s="46">
+        <v>5</v>
+      </c>
+      <c r="M34" s="46">
+        <v>5</v>
+      </c>
+      <c r="N34" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G34:M34),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O34" s="49" t="str" cm="1">
+        <f t="array" ref="O34">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="46">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B35" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C35" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D35" s="43">
+        <v>46142</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="46">
+        <v>1140444971</v>
+      </c>
+      <c r="G35" s="46">
+        <v>5</v>
+      </c>
+      <c r="H35" s="46">
+        <v>5</v>
+      </c>
+      <c r="I35" s="46">
+        <v>4</v>
+      </c>
+      <c r="J35" s="46">
+        <v>4</v>
+      </c>
+      <c r="K35" s="46">
+        <v>3</v>
+      </c>
+      <c r="L35" s="46">
+        <v>5</v>
+      </c>
+      <c r="M35" s="46">
+        <v>3</v>
+      </c>
+      <c r="N35" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G35:M35),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O35" s="49" t="str" cm="1">
+        <f t="array" ref="O35">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -16561,7 +18860,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -16883,72 +19182,212 @@
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="49">
+      <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="str">
+      <c r="B6" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C6" s="50" t="str">
+      <c r="C6" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>marzo</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="21">
         <v>46110</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="23">
         <v>1062539643</v>
       </c>
-      <c r="G6" s="53">
-        <v>4</v>
-      </c>
-      <c r="H6" s="53">
-        <v>4</v>
-      </c>
-      <c r="I6" s="53">
-        <v>5</v>
-      </c>
-      <c r="J6" s="53">
-        <v>5</v>
-      </c>
-      <c r="K6" s="53">
-        <v>4</v>
-      </c>
-      <c r="L6" s="53">
+      <c r="G6" s="23">
+        <v>4</v>
+      </c>
+      <c r="H6" s="23">
+        <v>4</v>
+      </c>
+      <c r="I6" s="23">
+        <v>5</v>
+      </c>
+      <c r="J6" s="23">
+        <v>5</v>
+      </c>
+      <c r="K6" s="23">
+        <v>4</v>
+      </c>
+      <c r="L6" s="23">
         <v>3</v>
       </c>
-      <c r="M6" s="53">
-        <v>5</v>
-      </c>
-      <c r="N6" s="53">
-        <v>4</v>
-      </c>
-      <c r="O6" s="53">
-        <v>4</v>
-      </c>
-      <c r="P6" s="53">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="53">
+      <c r="M6" s="23">
+        <v>5</v>
+      </c>
+      <c r="N6" s="23">
+        <v>4</v>
+      </c>
+      <c r="O6" s="23">
+        <v>4</v>
+      </c>
+      <c r="P6" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="23">
         <v>3</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="23">
         <v>3</v>
       </c>
-      <c r="S6" s="53">
-        <v>4</v>
-      </c>
-      <c r="T6" s="54">
+      <c r="S6" s="23">
+        <v>4</v>
+      </c>
+      <c r="T6" s="24">
         <f>IFERROR(AVERAGE(G6:S6),"-")</f>
         <v>4.0769230769230766</v>
       </c>
-      <c r="U6" s="55" t="str" cm="1">
+      <c r="U6" s="32" t="str" cm="1">
         <f t="array" ref="U6">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B7" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C7" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D7" s="52">
+        <v>46142</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="54">
+        <v>1062539643</v>
+      </c>
+      <c r="G7" s="54">
+        <v>5</v>
+      </c>
+      <c r="H7" s="54">
+        <v>4</v>
+      </c>
+      <c r="I7" s="54">
+        <v>5</v>
+      </c>
+      <c r="J7" s="54">
+        <v>5</v>
+      </c>
+      <c r="K7" s="54">
+        <v>4</v>
+      </c>
+      <c r="L7" s="54">
+        <v>3</v>
+      </c>
+      <c r="M7" s="54">
+        <v>5</v>
+      </c>
+      <c r="N7" s="54">
+        <v>4</v>
+      </c>
+      <c r="O7" s="54">
+        <v>4</v>
+      </c>
+      <c r="P7" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>3</v>
+      </c>
+      <c r="R7" s="54">
+        <v>4</v>
+      </c>
+      <c r="S7" s="54">
+        <v>5</v>
+      </c>
+      <c r="T7" s="55">
+        <f t="shared" ref="T7:T8" si="1">IFERROR(AVERAGE(G7:S7),"-")</f>
+        <v>4.3076923076923075</v>
+      </c>
+      <c r="U7" s="56" t="str" cm="1">
+        <f t="array" ref="U7">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>4</v>
+      </c>
+      <c r="B8" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C8" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>abril</v>
+      </c>
+      <c r="D8" s="52">
+        <v>46142</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="54">
+        <v>1067947255</v>
+      </c>
+      <c r="G8" s="54">
+        <v>5</v>
+      </c>
+      <c r="H8" s="54">
+        <v>3</v>
+      </c>
+      <c r="I8" s="54">
+        <v>5</v>
+      </c>
+      <c r="J8" s="54">
+        <v>5</v>
+      </c>
+      <c r="K8" s="54">
+        <v>4</v>
+      </c>
+      <c r="L8" s="54">
+        <v>3</v>
+      </c>
+      <c r="M8" s="54">
+        <v>5</v>
+      </c>
+      <c r="N8" s="54">
+        <v>5</v>
+      </c>
+      <c r="O8" s="54">
+        <v>5</v>
+      </c>
+      <c r="P8" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="54">
+        <v>3</v>
+      </c>
+      <c r="R8" s="54">
+        <v>4</v>
+      </c>
+      <c r="S8" s="54">
+        <v>5</v>
+      </c>
+      <c r="T8" s="55">
+        <f t="shared" si="1"/>
+        <v>4.384615384615385</v>
+      </c>
+      <c r="U8" s="56" t="str" cm="1">
+        <f t="array" ref="U8">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D08E74B-500F-4062-8E2A-DD842FC0A1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF750810-FD4A-4BBB-A0B0-D75513CE40C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -90,7 +90,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +99,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +108,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="149">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -652,6 +652,48 @@
   <si>
     <t>Jaime Andres Forero Marquez</t>
   </si>
+  <si>
+    <t>Mariam Sofia Doria Laza</t>
+  </si>
+  <si>
+    <t>Ana Rodriguez</t>
+  </si>
+  <si>
+    <t>Maria Angel Urango Vasquez</t>
+  </si>
+  <si>
+    <t>Sara Sofia Muñoz Ramirez</t>
+  </si>
+  <si>
+    <t>Mateo Alejandro Vergara Alvarez</t>
+  </si>
+  <si>
+    <t>Maria del Pilar Paternina</t>
+  </si>
+  <si>
+    <t>Maximiliano Pesci Pacheco</t>
+  </si>
+  <si>
+    <t>lercy maria Alvarez garcia</t>
+  </si>
+  <si>
+    <t>Maria del Mar Argumedo</t>
+  </si>
+  <si>
+    <t>Esneider de Jesús Zuluaga Quintero</t>
+  </si>
+  <si>
+    <t>Guadalupe Cortez de Hoyos</t>
+  </si>
+  <si>
+    <t>Jessica marin</t>
+  </si>
+  <si>
+    <t>Maria Jose Villagas De Hoyos</t>
+  </si>
+  <si>
+    <t>Sarah Brieva Rivero</t>
+  </si>
 </sst>
 </file>
 
@@ -783,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -900,13 +942,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -914,21 +959,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -956,6 +986,591 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2207,591 +2822,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3048,7 +3078,7 @@
                   <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3251,7 +3281,7 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3454,7 +3484,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3857,7 +3887,7 @@
                         <c:v>45</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -4025,7 +4055,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -4193,7 +4223,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -4804,7 +4834,7 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5012,7 +5042,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5350,7 +5380,7 @@
                         <c:v>45</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -5518,7 +5548,7 @@
                         <c:v>31</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -5691,7 +5721,7 @@
                         <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -5864,7 +5894,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -6539,7 +6569,7 @@
                   <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -6725,7 +6755,7 @@
                         <c:v>31</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -6898,7 +6928,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -7071,7 +7101,7 @@
                         <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -7244,7 +7274,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -7417,7 +7447,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>0</c:v>
@@ -12082,7 +12112,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -12095,29 +12125,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="46">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="45">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="44">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="43">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="42">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="41">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12126,37 +12156,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O77" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A2:O77" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O102" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
+  <autoFilter ref="A2:O102" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O102">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="31">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="29">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="17">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12165,36 +12195,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O35" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:O35" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O56" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A2:O56" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O56">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12203,42 +12233,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U8" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74" tableBorderDxfId="73">
-  <autoFilter ref="A2:U8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U10" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U10" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="72">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="71">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="70">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="60"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="59"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="56"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="55"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="54"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="53">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="52">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12247,17 +12277,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12718,27 +12748,27 @@
       </c>
       <c r="B6" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C6" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A6)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D6" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A6)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A6)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -13026,7 +13056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
@@ -15398,1614 +15428,2914 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="40">
+      <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B47" s="41" t="str">
+      <c r="B47" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C47" s="41" t="str">
+      <c r="C47" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D47" s="43">
+      <c r="D47" s="3">
         <v>46142</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="45">
+      <c r="F47" s="1">
         <v>8203609</v>
       </c>
-      <c r="G47" s="46">
-        <v>5</v>
-      </c>
-      <c r="H47" s="46">
-        <v>5</v>
-      </c>
-      <c r="I47" s="46">
-        <v>5</v>
-      </c>
-      <c r="J47" s="46">
-        <v>5</v>
-      </c>
-      <c r="K47" s="46">
-        <v>5</v>
-      </c>
-      <c r="L47" s="46">
-        <v>5</v>
-      </c>
-      <c r="M47" s="46">
+      <c r="G47" s="1">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1">
+        <v>5</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>5</v>
+      </c>
+      <c r="K47" s="1">
+        <v>5</v>
+      </c>
+      <c r="L47" s="1">
+        <v>5</v>
+      </c>
+      <c r="M47" s="1">
         <v>5</v>
       </c>
       <c r="N47" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G47:M47),"-")</f>
         <v>5</v>
       </c>
-      <c r="O47" s="42" t="str" cm="1">
+      <c r="O47" s="18" t="str" cm="1">
         <f t="array" ref="O47">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="40">
+      <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B48" s="41" t="str">
+      <c r="B48" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C48" s="41" t="str">
+      <c r="C48" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="3">
         <v>46142</v>
       </c>
-      <c r="E48" s="44" t="s">
+      <c r="E48" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="45">
+      <c r="F48" s="1">
         <v>10784668</v>
       </c>
-      <c r="G48" s="46">
-        <v>5</v>
-      </c>
-      <c r="H48" s="46">
-        <v>5</v>
-      </c>
-      <c r="I48" s="46">
-        <v>4</v>
-      </c>
-      <c r="J48" s="46">
+      <c r="G48" s="1">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5</v>
+      </c>
+      <c r="I48" s="1">
+        <v>4</v>
+      </c>
+      <c r="J48" s="1">
         <v>3</v>
       </c>
-      <c r="K48" s="46">
+      <c r="K48" s="1">
         <v>3</v>
       </c>
-      <c r="L48" s="46">
+      <c r="L48" s="1">
         <v>3</v>
       </c>
-      <c r="M48" s="46">
+      <c r="M48" s="1">
         <v>5</v>
       </c>
       <c r="N48" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G48:M48),"-")</f>
         <v>4</v>
       </c>
-      <c r="O48" s="42" t="str" cm="1">
+      <c r="O48" s="18" t="str" cm="1">
         <f t="array" ref="O48">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="40">
+      <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B49" s="41" t="str">
+      <c r="B49" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C49" s="41" t="str">
+      <c r="C49" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D49" s="43">
+      <c r="D49" s="3">
         <v>46142</v>
       </c>
-      <c r="E49" s="44" t="s">
+      <c r="E49" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F49" s="45">
+      <c r="F49" s="1">
         <v>34882674</v>
       </c>
-      <c r="G49" s="46">
-        <v>5</v>
-      </c>
-      <c r="H49" s="46">
+      <c r="G49" s="1">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1">
         <v>2</v>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="1">
         <v>2</v>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="1">
         <v>2</v>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="1">
         <v>2</v>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="1">
         <v>2</v>
       </c>
-      <c r="M49" s="46">
+      <c r="M49" s="1">
         <v>1</v>
       </c>
       <c r="N49" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G49:M49),"-")</f>
         <v>2.2857142857142856</v>
       </c>
-      <c r="O49" s="42" t="str" cm="1">
+      <c r="O49" s="18" t="str" cm="1">
         <f t="array" ref="O49">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="40">
+      <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B50" s="41" t="str">
+      <c r="B50" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C50" s="41" t="str">
+      <c r="C50" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="3">
         <v>46142</v>
       </c>
-      <c r="E50" s="44" t="s">
+      <c r="E50" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="45">
+      <c r="F50" s="1">
         <v>50906315</v>
       </c>
-      <c r="G50" s="46">
-        <v>5</v>
-      </c>
-      <c r="H50" s="46">
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1">
         <v>2</v>
       </c>
-      <c r="I50" s="46">
+      <c r="I50" s="1">
         <v>2</v>
       </c>
-      <c r="J50" s="46">
+      <c r="J50" s="1">
         <v>1</v>
       </c>
-      <c r="K50" s="46">
+      <c r="K50" s="1">
         <v>1</v>
       </c>
-      <c r="L50" s="46">
+      <c r="L50" s="1">
         <v>1</v>
       </c>
-      <c r="M50" s="46">
+      <c r="M50" s="1">
         <v>1</v>
       </c>
       <c r="N50" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G50:M50),"-")</f>
         <v>1.8571428571428572</v>
       </c>
-      <c r="O50" s="42" t="str" cm="1">
+      <c r="O50" s="18" t="str" cm="1">
         <f t="array" ref="O50">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="40">
+      <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B51" s="41" t="str">
+      <c r="B51" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C51" s="41" t="str">
+      <c r="C51" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="3">
         <v>46142</v>
       </c>
-      <c r="E51" s="44" t="s">
+      <c r="E51" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F51" s="45">
+      <c r="F51" s="1">
         <v>78713979</v>
       </c>
-      <c r="G51" s="46">
-        <v>5</v>
-      </c>
-      <c r="H51" s="46">
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1">
         <v>3</v>
       </c>
-      <c r="I51" s="46">
+      <c r="I51" s="1">
         <v>3</v>
       </c>
-      <c r="J51" s="46">
+      <c r="J51" s="1">
         <v>3</v>
       </c>
-      <c r="K51" s="46">
+      <c r="K51" s="1">
         <v>1</v>
       </c>
-      <c r="L51" s="46">
+      <c r="L51" s="1">
         <v>1</v>
       </c>
-      <c r="M51" s="46">
+      <c r="M51" s="1">
         <v>1</v>
       </c>
       <c r="N51" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G51:M51),"-")</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O51" s="42" t="str" cm="1">
+      <c r="O51" s="18" t="str" cm="1">
         <f t="array" ref="O51">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="40">
+      <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B52" s="41" t="str">
+      <c r="B52" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C52" s="41" t="str">
+      <c r="C52" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D52" s="43">
+      <c r="D52" s="3">
         <v>46142</v>
       </c>
-      <c r="E52" s="44" t="s">
+      <c r="E52" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F52" s="45">
+      <c r="F52" s="1">
         <v>1003027198</v>
       </c>
-      <c r="G52" s="46">
-        <v>5</v>
-      </c>
-      <c r="H52" s="46">
-        <v>5</v>
-      </c>
-      <c r="I52" s="46">
-        <v>5</v>
-      </c>
-      <c r="J52" s="46">
-        <v>5</v>
-      </c>
-      <c r="K52" s="46">
-        <v>5</v>
-      </c>
-      <c r="L52" s="46">
-        <v>5</v>
-      </c>
-      <c r="M52" s="46">
+      <c r="G52" s="1">
+        <v>5</v>
+      </c>
+      <c r="H52" s="1">
+        <v>5</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
+        <v>5</v>
+      </c>
+      <c r="L52" s="1">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1">
         <v>5</v>
       </c>
       <c r="N52" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G52:M52),"-")</f>
         <v>5</v>
       </c>
-      <c r="O52" s="42" t="str" cm="1">
+      <c r="O52" s="18" t="str" cm="1">
         <f t="array" ref="O52">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="40">
+      <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B53" s="41" t="str">
+      <c r="B53" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C53" s="41" t="str">
+      <c r="C53" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D53" s="43">
+      <c r="D53" s="3">
         <v>46142</v>
       </c>
-      <c r="E53" s="44" t="s">
+      <c r="E53" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="45">
+      <c r="F53" s="1">
         <v>1003405136</v>
       </c>
-      <c r="G53" s="46">
-        <v>5</v>
-      </c>
-      <c r="H53" s="46">
-        <v>4</v>
-      </c>
-      <c r="I53" s="46">
-        <v>4</v>
-      </c>
-      <c r="J53" s="46">
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1">
+        <v>4</v>
+      </c>
+      <c r="I53" s="1">
+        <v>4</v>
+      </c>
+      <c r="J53" s="1">
         <v>3</v>
       </c>
-      <c r="K53" s="46">
+      <c r="K53" s="1">
         <v>3</v>
       </c>
-      <c r="L53" s="46">
+      <c r="L53" s="1">
         <v>2</v>
       </c>
-      <c r="M53" s="46">
+      <c r="M53" s="1">
         <v>3</v>
       </c>
       <c r="N53" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G53:M53),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O53" s="42" t="str" cm="1">
+      <c r="O53" s="18" t="str" cm="1">
         <f t="array" ref="O53">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="40">
+      <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B54" s="41" t="str">
+      <c r="B54" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C54" s="41" t="str">
+      <c r="C54" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D54" s="43">
+      <c r="D54" s="3">
         <v>46142</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="E54" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F54" s="45">
+      <c r="F54" s="1">
         <v>1003435656</v>
       </c>
-      <c r="G54" s="46">
-        <v>5</v>
-      </c>
-      <c r="H54" s="46">
-        <v>5</v>
-      </c>
-      <c r="I54" s="46">
-        <v>5</v>
-      </c>
-      <c r="J54" s="46">
-        <v>5</v>
-      </c>
-      <c r="K54" s="46">
-        <v>5</v>
-      </c>
-      <c r="L54" s="46">
-        <v>5</v>
-      </c>
-      <c r="M54" s="46">
+      <c r="G54" s="1">
+        <v>5</v>
+      </c>
+      <c r="H54" s="1">
+        <v>5</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="1">
+        <v>5</v>
+      </c>
+      <c r="L54" s="1">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1">
         <v>5</v>
       </c>
       <c r="N54" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G54:M54),"-")</f>
         <v>5</v>
       </c>
-      <c r="O54" s="42" t="str" cm="1">
+      <c r="O54" s="18" t="str" cm="1">
         <f t="array" ref="O54">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="40">
+      <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B55" s="41" t="str">
+      <c r="B55" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C55" s="41" t="str">
+      <c r="C55" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D55" s="43">
+      <c r="D55" s="3">
         <v>46142</v>
       </c>
-      <c r="E55" s="44" t="s">
+      <c r="E55" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F55" s="45">
+      <c r="F55" s="1">
         <v>1003561480</v>
       </c>
-      <c r="G55" s="46">
-        <v>5</v>
-      </c>
-      <c r="H55" s="46">
+      <c r="G55" s="1">
+        <v>5</v>
+      </c>
+      <c r="H55" s="1">
         <v>1</v>
       </c>
-      <c r="I55" s="46">
+      <c r="I55" s="1">
         <v>2</v>
       </c>
-      <c r="J55" s="46">
+      <c r="J55" s="1">
         <v>1</v>
       </c>
-      <c r="K55" s="46">
+      <c r="K55" s="1">
         <v>1</v>
       </c>
-      <c r="L55" s="46">
+      <c r="L55" s="1">
         <v>1</v>
       </c>
-      <c r="M55" s="46">
+      <c r="M55" s="1">
         <v>2</v>
       </c>
       <c r="N55" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G55:M55),"-")</f>
         <v>1.8571428571428572</v>
       </c>
-      <c r="O55" s="42" t="str" cm="1">
+      <c r="O55" s="18" t="str" cm="1">
         <f t="array" ref="O55">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="40">
+      <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B56" s="41" t="str">
+      <c r="B56" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C56" s="41" t="str">
+      <c r="C56" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D56" s="43">
+      <c r="D56" s="3">
         <v>46142</v>
       </c>
-      <c r="E56" s="44" t="s">
+      <c r="E56" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F56" s="45">
+      <c r="F56" s="1">
         <v>1025564047</v>
       </c>
-      <c r="G56" s="46">
-        <v>5</v>
-      </c>
-      <c r="H56" s="46">
-        <v>5</v>
-      </c>
-      <c r="I56" s="46">
+      <c r="G56" s="1">
+        <v>5</v>
+      </c>
+      <c r="H56" s="1">
+        <v>5</v>
+      </c>
+      <c r="I56" s="1">
         <v>2</v>
       </c>
-      <c r="J56" s="46">
+      <c r="J56" s="1">
         <v>2</v>
       </c>
-      <c r="K56" s="46">
+      <c r="K56" s="1">
         <v>2</v>
       </c>
-      <c r="L56" s="46">
+      <c r="L56" s="1">
         <v>2</v>
       </c>
-      <c r="M56" s="46">
+      <c r="M56" s="1">
         <v>5</v>
       </c>
       <c r="N56" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G56:M56),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O56" s="42" t="str" cm="1">
+      <c r="O56" s="18" t="str" cm="1">
         <f t="array" ref="O56">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="40">
+      <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B57" s="41" t="str">
+      <c r="B57" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C57" s="41" t="str">
+      <c r="C57" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D57" s="43">
+      <c r="D57" s="3">
         <v>46142</v>
       </c>
-      <c r="E57" s="44" t="s">
+      <c r="E57" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="F57" s="45">
+      <c r="F57" s="1">
         <v>1033205387</v>
       </c>
-      <c r="G57" s="46">
-        <v>4</v>
-      </c>
-      <c r="H57" s="46">
+      <c r="G57" s="1">
+        <v>4</v>
+      </c>
+      <c r="H57" s="1">
         <v>2</v>
       </c>
-      <c r="I57" s="46">
+      <c r="I57" s="1">
         <v>1</v>
       </c>
-      <c r="J57" s="46">
+      <c r="J57" s="1">
         <v>1</v>
       </c>
-      <c r="K57" s="46">
+      <c r="K57" s="1">
         <v>1</v>
       </c>
-      <c r="L57" s="46">
+      <c r="L57" s="1">
         <v>1</v>
       </c>
-      <c r="M57" s="46">
+      <c r="M57" s="1">
         <v>3</v>
       </c>
       <c r="N57" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G57:M57),"-")</f>
         <v>1.8571428571428572</v>
       </c>
-      <c r="O57" s="42" t="str" cm="1">
+      <c r="O57" s="18" t="str" cm="1">
         <f t="array" ref="O57">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="40">
+      <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B58" s="41" t="str">
+      <c r="B58" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C58" s="41" t="str">
+      <c r="C58" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D58" s="43">
+      <c r="D58" s="3">
         <v>46142</v>
       </c>
-      <c r="E58" s="44" t="s">
+      <c r="E58" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F58" s="45">
+      <c r="F58" s="1">
         <v>1035017030</v>
       </c>
-      <c r="G58" s="46">
-        <v>5</v>
-      </c>
-      <c r="H58" s="46">
-        <v>5</v>
-      </c>
-      <c r="I58" s="46">
-        <v>5</v>
-      </c>
-      <c r="J58" s="46">
+      <c r="G58" s="1">
+        <v>5</v>
+      </c>
+      <c r="H58" s="1">
+        <v>5</v>
+      </c>
+      <c r="I58" s="1">
+        <v>5</v>
+      </c>
+      <c r="J58" s="1">
         <v>3</v>
       </c>
-      <c r="K58" s="46">
-        <v>5</v>
-      </c>
-      <c r="L58" s="46">
+      <c r="K58" s="1">
+        <v>5</v>
+      </c>
+      <c r="L58" s="1">
         <v>3</v>
       </c>
-      <c r="M58" s="46">
+      <c r="M58" s="1">
         <v>5</v>
       </c>
       <c r="N58" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G58:M58),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O58" s="42" t="str" cm="1">
+      <c r="O58" s="18" t="str" cm="1">
         <f t="array" ref="O58">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" s="40">
+      <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B59" s="41" t="str">
+      <c r="B59" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C59" s="41" t="str">
+      <c r="C59" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D59" s="43">
+      <c r="D59" s="3">
         <v>46142</v>
       </c>
-      <c r="E59" s="44" t="s">
+      <c r="E59" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F59" s="45">
+      <c r="F59" s="1">
         <v>1037236492</v>
       </c>
-      <c r="G59" s="46">
-        <v>5</v>
-      </c>
-      <c r="H59" s="46">
-        <v>5</v>
-      </c>
-      <c r="I59" s="46">
-        <v>4</v>
-      </c>
-      <c r="J59" s="46">
+      <c r="G59" s="1">
+        <v>5</v>
+      </c>
+      <c r="H59" s="1">
+        <v>5</v>
+      </c>
+      <c r="I59" s="1">
+        <v>4</v>
+      </c>
+      <c r="J59" s="1">
         <v>3</v>
       </c>
-      <c r="K59" s="46">
+      <c r="K59" s="1">
         <v>3</v>
       </c>
-      <c r="L59" s="46">
+      <c r="L59" s="1">
         <v>2</v>
       </c>
-      <c r="M59" s="46">
+      <c r="M59" s="1">
         <v>4</v>
       </c>
       <c r="N59" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G59:M59),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O59" s="42" t="str" cm="1">
+      <c r="O59" s="18" t="str" cm="1">
         <f t="array" ref="O59">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" s="40">
+      <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B60" s="41" t="str">
+      <c r="B60" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C60" s="41" t="str">
+      <c r="C60" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D60" s="43">
+      <c r="D60" s="3">
         <v>46142</v>
       </c>
-      <c r="E60" s="44" t="s">
+      <c r="E60" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="45">
+      <c r="F60" s="1">
         <v>1062438398</v>
       </c>
-      <c r="G60" s="46">
-        <v>5</v>
-      </c>
-      <c r="H60" s="46">
-        <v>5</v>
-      </c>
-      <c r="I60" s="46">
-        <v>4</v>
-      </c>
-      <c r="J60" s="46">
-        <v>4</v>
-      </c>
-      <c r="K60" s="46">
-        <v>4</v>
-      </c>
-      <c r="L60" s="46">
-        <v>4</v>
-      </c>
-      <c r="M60" s="46">
+      <c r="G60" s="1">
+        <v>5</v>
+      </c>
+      <c r="H60" s="1">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1">
+        <v>4</v>
+      </c>
+      <c r="J60" s="1">
+        <v>4</v>
+      </c>
+      <c r="K60" s="1">
+        <v>4</v>
+      </c>
+      <c r="L60" s="1">
+        <v>4</v>
+      </c>
+      <c r="M60" s="1">
         <v>5</v>
       </c>
       <c r="N60" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G60:M60),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O60" s="42" t="str" cm="1">
+      <c r="O60" s="18" t="str" cm="1">
         <f t="array" ref="O60">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" s="40">
+      <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B61" s="41" t="str">
+      <c r="B61" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C61" s="41" t="str">
+      <c r="C61" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D61" s="43">
+      <c r="D61" s="3">
         <v>46142</v>
       </c>
-      <c r="E61" s="44" t="s">
+      <c r="E61" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F61" s="45">
+      <c r="F61" s="1">
         <v>1062540875</v>
       </c>
-      <c r="G61" s="46">
-        <v>5</v>
-      </c>
-      <c r="H61" s="46">
-        <v>5</v>
-      </c>
-      <c r="I61" s="46">
-        <v>4</v>
-      </c>
-      <c r="J61" s="46">
+      <c r="G61" s="1">
+        <v>5</v>
+      </c>
+      <c r="H61" s="1">
+        <v>5</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4</v>
+      </c>
+      <c r="J61" s="1">
         <v>3</v>
       </c>
-      <c r="K61" s="46">
-        <v>4</v>
-      </c>
-      <c r="L61" s="46">
+      <c r="K61" s="1">
+        <v>4</v>
+      </c>
+      <c r="L61" s="1">
         <v>2</v>
       </c>
-      <c r="M61" s="46">
+      <c r="M61" s="1">
         <v>5</v>
       </c>
       <c r="N61" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G61:M61),"-")</f>
         <v>4</v>
       </c>
-      <c r="O61" s="42" t="str" cm="1">
+      <c r="O61" s="18" t="str" cm="1">
         <f t="array" ref="O61">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" s="40">
+      <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B62" s="41" t="str">
+      <c r="B62" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C62" s="41" t="str">
+      <c r="C62" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D62" s="43">
+      <c r="D62" s="3">
         <v>46142</v>
       </c>
-      <c r="E62" s="44" t="s">
+      <c r="E62" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F62" s="45">
+      <c r="F62" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G62" s="46">
-        <v>5</v>
-      </c>
-      <c r="H62" s="46">
-        <v>5</v>
-      </c>
-      <c r="I62" s="46">
-        <v>5</v>
-      </c>
-      <c r="J62" s="46">
-        <v>5</v>
-      </c>
-      <c r="K62" s="46">
-        <v>5</v>
-      </c>
-      <c r="L62" s="46">
-        <v>5</v>
-      </c>
-      <c r="M62" s="46">
+      <c r="G62" s="1">
+        <v>5</v>
+      </c>
+      <c r="H62" s="1">
+        <v>5</v>
+      </c>
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>5</v>
+      </c>
+      <c r="L62" s="1">
+        <v>5</v>
+      </c>
+      <c r="M62" s="1">
         <v>5</v>
       </c>
       <c r="N62" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G62:M62),"-")</f>
         <v>5</v>
       </c>
-      <c r="O62" s="42" t="str" cm="1">
+      <c r="O62" s="18" t="str" cm="1">
         <f t="array" ref="O62">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="40">
+      <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B63" s="41" t="str">
+      <c r="B63" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C63" s="41" t="str">
+      <c r="C63" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D63" s="43">
+      <c r="D63" s="3">
         <v>46142</v>
       </c>
-      <c r="E63" s="44" t="s">
+      <c r="E63" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F63" s="45">
+      <c r="F63" s="1">
         <v>1062546526</v>
       </c>
-      <c r="G63" s="46">
-        <v>5</v>
-      </c>
-      <c r="H63" s="46">
-        <v>5</v>
-      </c>
-      <c r="I63" s="46">
-        <v>4</v>
-      </c>
-      <c r="J63" s="46">
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" s="1">
+        <v>5</v>
+      </c>
+      <c r="I63" s="1">
+        <v>4</v>
+      </c>
+      <c r="J63" s="1">
         <v>3</v>
       </c>
-      <c r="K63" s="46">
+      <c r="K63" s="1">
         <v>2</v>
       </c>
-      <c r="L63" s="46">
+      <c r="L63" s="1">
         <v>2</v>
       </c>
-      <c r="M63" s="46">
+      <c r="M63" s="1">
         <v>5</v>
       </c>
       <c r="N63" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G63:M63),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O63" s="42" t="str" cm="1">
+      <c r="O63" s="18" t="str" cm="1">
         <f t="array" ref="O63">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="40">
+      <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B64" s="41" t="str">
+      <c r="B64" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C64" s="41" t="str">
+      <c r="C64" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D64" s="43">
+      <c r="D64" s="3">
         <v>46142</v>
       </c>
-      <c r="E64" s="44" t="s">
+      <c r="E64" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F64" s="45">
+      <c r="F64" s="1">
         <v>1062966144</v>
       </c>
-      <c r="G64" s="46">
-        <v>5</v>
-      </c>
-      <c r="H64" s="46">
-        <v>5</v>
-      </c>
-      <c r="I64" s="46">
-        <v>5</v>
-      </c>
-      <c r="J64" s="46">
-        <v>5</v>
-      </c>
-      <c r="K64" s="46">
-        <v>5</v>
-      </c>
-      <c r="L64" s="46">
-        <v>5</v>
-      </c>
-      <c r="M64" s="46">
+      <c r="G64" s="1">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1">
+        <v>5</v>
+      </c>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>5</v>
+      </c>
+      <c r="L64" s="1">
+        <v>5</v>
+      </c>
+      <c r="M64" s="1">
         <v>5</v>
       </c>
       <c r="N64" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G64:M64),"-")</f>
         <v>5</v>
       </c>
-      <c r="O64" s="42" t="str" cm="1">
+      <c r="O64" s="18" t="str" cm="1">
         <f t="array" ref="O64">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="40">
+      <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B65" s="41" t="str">
+      <c r="B65" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C65" s="41" t="str">
+      <c r="C65" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D65" s="43">
+      <c r="D65" s="3">
         <v>46142</v>
       </c>
-      <c r="E65" s="44" t="s">
+      <c r="E65" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="F65" s="45">
+      <c r="F65" s="1">
         <v>1063077486</v>
       </c>
-      <c r="G65" s="46">
-        <v>5</v>
-      </c>
-      <c r="H65" s="46">
-        <v>5</v>
-      </c>
-      <c r="I65" s="46">
-        <v>5</v>
-      </c>
-      <c r="J65" s="46">
-        <v>5</v>
-      </c>
-      <c r="K65" s="46">
-        <v>5</v>
-      </c>
-      <c r="L65" s="46">
-        <v>5</v>
-      </c>
-      <c r="M65" s="46">
+      <c r="G65" s="1">
+        <v>5</v>
+      </c>
+      <c r="H65" s="1">
+        <v>5</v>
+      </c>
+      <c r="I65" s="1">
+        <v>5</v>
+      </c>
+      <c r="J65" s="1">
+        <v>5</v>
+      </c>
+      <c r="K65" s="1">
+        <v>5</v>
+      </c>
+      <c r="L65" s="1">
+        <v>5</v>
+      </c>
+      <c r="M65" s="1">
         <v>1</v>
       </c>
       <c r="N65" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G65:M65),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O65" s="42" t="str" cm="1">
+      <c r="O65" s="18" t="str" cm="1">
         <f t="array" ref="O65">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="40">
+      <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B66" s="41" t="str">
+      <c r="B66" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C66" s="41" t="str">
+      <c r="C66" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D66" s="43">
+      <c r="D66" s="3">
         <v>46142</v>
       </c>
-      <c r="E66" s="44" t="s">
+      <c r="E66" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F66" s="45">
+      <c r="F66" s="1">
         <v>1067860876</v>
       </c>
-      <c r="G66" s="46">
-        <v>5</v>
-      </c>
-      <c r="H66" s="46">
-        <v>5</v>
-      </c>
-      <c r="I66" s="46">
-        <v>4</v>
-      </c>
-      <c r="J66" s="46">
-        <v>4</v>
-      </c>
-      <c r="K66" s="46">
-        <v>4</v>
-      </c>
-      <c r="L66" s="46">
-        <v>4</v>
-      </c>
-      <c r="M66" s="46">
+      <c r="G66" s="1">
+        <v>5</v>
+      </c>
+      <c r="H66" s="1">
+        <v>5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>4</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1">
+        <v>4</v>
+      </c>
+      <c r="L66" s="1">
+        <v>4</v>
+      </c>
+      <c r="M66" s="1">
         <v>5</v>
       </c>
       <c r="N66" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G66:M66),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O66" s="42" t="str" cm="1">
+      <c r="O66" s="18" t="str" cm="1">
         <f t="array" ref="O66">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="40">
+      <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B67" s="41" t="str">
+      <c r="B67" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C67" s="41" t="str">
+      <c r="C67" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D67" s="43">
+      <c r="D67" s="3">
         <v>46142</v>
       </c>
-      <c r="E67" s="44" t="s">
+      <c r="E67" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="45">
+      <c r="F67" s="1">
         <v>1067945529</v>
       </c>
-      <c r="G67" s="46">
-        <v>5</v>
-      </c>
-      <c r="H67" s="46">
-        <v>5</v>
-      </c>
-      <c r="I67" s="46">
-        <v>5</v>
-      </c>
-      <c r="J67" s="46">
-        <v>5</v>
-      </c>
-      <c r="K67" s="46">
-        <v>5</v>
-      </c>
-      <c r="L67" s="46">
-        <v>5</v>
-      </c>
-      <c r="M67" s="46">
+      <c r="G67" s="1">
+        <v>5</v>
+      </c>
+      <c r="H67" s="1">
+        <v>5</v>
+      </c>
+      <c r="I67" s="1">
+        <v>5</v>
+      </c>
+      <c r="J67" s="1">
+        <v>5</v>
+      </c>
+      <c r="K67" s="1">
+        <v>5</v>
+      </c>
+      <c r="L67" s="1">
+        <v>5</v>
+      </c>
+      <c r="M67" s="1">
         <v>5</v>
       </c>
       <c r="N67" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G67:M67),"-")</f>
         <v>5</v>
       </c>
-      <c r="O67" s="42" t="str" cm="1">
+      <c r="O67" s="18" t="str" cm="1">
         <f t="array" ref="O67">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="40">
+      <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B68" s="41" t="str">
+      <c r="B68" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C68" s="41" t="str">
+      <c r="C68" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D68" s="43">
+      <c r="D68" s="3">
         <v>46142</v>
       </c>
-      <c r="E68" s="44" t="s">
+      <c r="E68" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F68" s="45">
+      <c r="F68" s="1">
         <v>1067958657</v>
       </c>
-      <c r="G68" s="46">
-        <v>5</v>
-      </c>
-      <c r="H68" s="46">
+      <c r="G68" s="1">
+        <v>5</v>
+      </c>
+      <c r="H68" s="1">
         <v>2</v>
       </c>
-      <c r="I68" s="46">
+      <c r="I68" s="1">
         <v>2</v>
       </c>
-      <c r="J68" s="46">
+      <c r="J68" s="1">
         <v>2</v>
       </c>
-      <c r="K68" s="46">
+      <c r="K68" s="1">
         <v>2</v>
       </c>
-      <c r="L68" s="46">
+      <c r="L68" s="1">
         <v>2</v>
       </c>
-      <c r="M68" s="46">
+      <c r="M68" s="1">
         <v>2</v>
       </c>
       <c r="N68" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G68:M68),"-")</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O68" s="42" t="str" cm="1">
+      <c r="O68" s="18" t="str" cm="1">
         <f t="array" ref="O68">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="40">
+      <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B69" s="41" t="str">
+      <c r="B69" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C69" s="41" t="str">
+      <c r="C69" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D69" s="43">
+      <c r="D69" s="3">
         <v>46142</v>
       </c>
-      <c r="E69" s="44" t="s">
+      <c r="E69" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F69" s="45">
+      <c r="F69" s="1">
         <v>1068441879</v>
       </c>
-      <c r="G69" s="46">
-        <v>5</v>
-      </c>
-      <c r="H69" s="46">
-        <v>4</v>
-      </c>
-      <c r="I69" s="46">
+      <c r="G69" s="1">
+        <v>5</v>
+      </c>
+      <c r="H69" s="1">
+        <v>4</v>
+      </c>
+      <c r="I69" s="1">
         <v>3</v>
       </c>
-      <c r="J69" s="46">
+      <c r="J69" s="1">
         <v>3</v>
       </c>
-      <c r="K69" s="46">
+      <c r="K69" s="1">
         <v>2</v>
       </c>
-      <c r="L69" s="46">
+      <c r="L69" s="1">
         <v>2</v>
       </c>
-      <c r="M69" s="46">
+      <c r="M69" s="1">
         <v>5</v>
       </c>
       <c r="N69" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G69:M69),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O69" s="42" t="str" cm="1">
+      <c r="O69" s="18" t="str" cm="1">
         <f t="array" ref="O69">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="40">
+      <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B70" s="41" t="str">
+      <c r="B70" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C70" s="41" t="str">
+      <c r="C70" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D70" s="43">
+      <c r="D70" s="3">
         <v>46142</v>
       </c>
-      <c r="E70" s="44" t="s">
+      <c r="E70" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F70" s="45">
+      <c r="F70" s="1">
         <v>1068442748</v>
       </c>
-      <c r="G70" s="46">
-        <v>5</v>
-      </c>
-      <c r="H70" s="46">
+      <c r="G70" s="1">
+        <v>5</v>
+      </c>
+      <c r="H70" s="1">
         <v>2</v>
       </c>
-      <c r="I70" s="46">
+      <c r="I70" s="1">
         <v>2</v>
       </c>
-      <c r="J70" s="46">
+      <c r="J70" s="1">
         <v>1</v>
       </c>
-      <c r="K70" s="46">
+      <c r="K70" s="1">
         <v>1</v>
       </c>
-      <c r="L70" s="46">
+      <c r="L70" s="1">
         <v>1</v>
       </c>
-      <c r="M70" s="46">
+      <c r="M70" s="1">
         <v>1</v>
       </c>
       <c r="N70" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G70:M70),"-")</f>
         <v>1.8571428571428572</v>
       </c>
-      <c r="O70" s="42" t="str" cm="1">
+      <c r="O70" s="18" t="str" cm="1">
         <f t="array" ref="O70">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="40">
+      <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B71" s="41" t="str">
+      <c r="B71" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C71" s="41" t="str">
+      <c r="C71" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D71" s="43">
+      <c r="D71" s="3">
         <v>46142</v>
       </c>
-      <c r="E71" s="44" t="s">
+      <c r="E71" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F71" s="45">
+      <c r="F71" s="1">
         <v>1068443767</v>
       </c>
-      <c r="G71" s="46">
-        <v>5</v>
-      </c>
-      <c r="H71" s="46">
+      <c r="G71" s="1">
+        <v>5</v>
+      </c>
+      <c r="H71" s="1">
         <v>3</v>
       </c>
-      <c r="I71" s="46">
+      <c r="I71" s="1">
         <v>2</v>
       </c>
-      <c r="J71" s="46">
+      <c r="J71" s="1">
         <v>2</v>
       </c>
-      <c r="K71" s="46">
+      <c r="K71" s="1">
         <v>2</v>
       </c>
-      <c r="L71" s="46">
+      <c r="L71" s="1">
         <v>2</v>
       </c>
-      <c r="M71" s="46">
+      <c r="M71" s="1">
         <v>5</v>
       </c>
       <c r="N71" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G71:M71),"-")</f>
         <v>3</v>
       </c>
-      <c r="O71" s="42" t="str" cm="1">
+      <c r="O71" s="18" t="str" cm="1">
         <f t="array" ref="O71">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="40">
+      <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B72" s="41" t="str">
+      <c r="B72" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C72" s="41" t="str">
+      <c r="C72" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D72" s="43">
+      <c r="D72" s="3">
         <v>46142</v>
       </c>
-      <c r="E72" s="44" t="s">
+      <c r="E72" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="45">
+      <c r="F72" s="1">
         <v>1068580241</v>
       </c>
-      <c r="G72" s="46">
-        <v>5</v>
-      </c>
-      <c r="H72" s="46">
-        <v>5</v>
-      </c>
-      <c r="I72" s="46">
-        <v>4</v>
-      </c>
-      <c r="J72" s="46">
+      <c r="G72" s="1">
+        <v>5</v>
+      </c>
+      <c r="H72" s="1">
+        <v>5</v>
+      </c>
+      <c r="I72" s="1">
+        <v>4</v>
+      </c>
+      <c r="J72" s="1">
         <v>3</v>
       </c>
-      <c r="K72" s="46">
-        <v>4</v>
-      </c>
-      <c r="L72" s="46">
+      <c r="K72" s="1">
+        <v>4</v>
+      </c>
+      <c r="L72" s="1">
         <v>3</v>
       </c>
-      <c r="M72" s="46">
+      <c r="M72" s="1">
         <v>4</v>
       </c>
       <c r="N72" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G72:M72),"-")</f>
         <v>4</v>
       </c>
-      <c r="O72" s="42" t="str" cm="1">
+      <c r="O72" s="18" t="str" cm="1">
         <f t="array" ref="O72">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="40">
+      <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B73" s="41" t="str">
+      <c r="B73" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C73" s="41" t="str">
+      <c r="C73" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D73" s="43">
+      <c r="D73" s="3">
         <v>46142</v>
       </c>
-      <c r="E73" s="44" t="s">
+      <c r="E73" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="F73" s="45">
+      <c r="F73" s="1">
         <v>1103755851</v>
       </c>
-      <c r="G73" s="46">
-        <v>5</v>
-      </c>
-      <c r="H73" s="46">
-        <v>4</v>
-      </c>
-      <c r="I73" s="46">
-        <v>4</v>
-      </c>
-      <c r="J73" s="46">
+      <c r="G73" s="1">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1">
+        <v>4</v>
+      </c>
+      <c r="I73" s="1">
+        <v>4</v>
+      </c>
+      <c r="J73" s="1">
         <v>3</v>
       </c>
-      <c r="K73" s="46">
+      <c r="K73" s="1">
         <v>2</v>
       </c>
-      <c r="L73" s="46">
+      <c r="L73" s="1">
         <v>2</v>
       </c>
-      <c r="M73" s="46">
+      <c r="M73" s="1">
         <v>4</v>
       </c>
       <c r="N73" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G73:M73),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O73" s="42" t="str" cm="1">
+      <c r="O73" s="18" t="str" cm="1">
         <f t="array" ref="O73">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="40">
+      <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B74" s="41" t="str">
+      <c r="B74" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C74" s="41" t="str">
+      <c r="C74" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D74" s="43">
+      <c r="D74" s="3">
         <v>46142</v>
       </c>
-      <c r="E74" s="44" t="s">
+      <c r="E74" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F74" s="45">
+      <c r="F74" s="1">
         <v>1137975856</v>
       </c>
-      <c r="G74" s="46">
-        <v>5</v>
-      </c>
-      <c r="H74" s="46">
-        <v>5</v>
-      </c>
-      <c r="I74" s="46">
-        <v>5</v>
-      </c>
-      <c r="J74" s="46">
-        <v>5</v>
-      </c>
-      <c r="K74" s="46">
-        <v>5</v>
-      </c>
-      <c r="L74" s="46">
-        <v>5</v>
-      </c>
-      <c r="M74" s="46">
+      <c r="G74" s="1">
+        <v>5</v>
+      </c>
+      <c r="H74" s="1">
+        <v>5</v>
+      </c>
+      <c r="I74" s="1">
+        <v>5</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
+        <v>5</v>
+      </c>
+      <c r="L74" s="1">
+        <v>5</v>
+      </c>
+      <c r="M74" s="1">
         <v>5</v>
       </c>
       <c r="N74" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G74:M74),"-")</f>
         <v>5</v>
       </c>
-      <c r="O74" s="42" t="str" cm="1">
+      <c r="O74" s="18" t="str" cm="1">
         <f t="array" ref="O74">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="40">
+      <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B75" s="41" t="str">
+      <c r="B75" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C75" s="41" t="str">
+      <c r="C75" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D75" s="43">
+      <c r="D75" s="3">
         <v>46142</v>
       </c>
-      <c r="E75" s="44" t="s">
+      <c r="E75" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F75" s="45">
+      <c r="F75" s="1">
         <v>1138030749</v>
       </c>
-      <c r="G75" s="46">
-        <v>5</v>
-      </c>
-      <c r="H75" s="46">
-        <v>5</v>
-      </c>
-      <c r="I75" s="46">
-        <v>4</v>
-      </c>
-      <c r="J75" s="46">
-        <v>4</v>
-      </c>
-      <c r="K75" s="46">
-        <v>4</v>
-      </c>
-      <c r="L75" s="46">
-        <v>4</v>
-      </c>
-      <c r="M75" s="46">
+      <c r="G75" s="1">
+        <v>5</v>
+      </c>
+      <c r="H75" s="1">
+        <v>5</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4</v>
+      </c>
+      <c r="K75" s="1">
+        <v>4</v>
+      </c>
+      <c r="L75" s="1">
+        <v>4</v>
+      </c>
+      <c r="M75" s="1">
         <v>5</v>
       </c>
       <c r="N75" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G75:M75),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O75" s="42" t="str" cm="1">
+      <c r="O75" s="18" t="str" cm="1">
         <f t="array" ref="O75">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="40">
+      <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B76" s="41" t="str">
+      <c r="B76" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C76" s="41" t="str">
+      <c r="C76" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D76" s="43">
+      <c r="D76" s="3">
         <v>46142</v>
       </c>
-      <c r="E76" s="44" t="s">
+      <c r="E76" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F76" s="45">
+      <c r="F76" s="1">
         <v>1233348383</v>
       </c>
-      <c r="G76" s="46">
-        <v>5</v>
-      </c>
-      <c r="H76" s="46">
-        <v>4</v>
-      </c>
-      <c r="I76" s="46">
+      <c r="G76" s="1">
+        <v>5</v>
+      </c>
+      <c r="H76" s="1">
+        <v>4</v>
+      </c>
+      <c r="I76" s="1">
         <v>3</v>
       </c>
-      <c r="J76" s="46">
+      <c r="J76" s="1">
         <v>3</v>
       </c>
-      <c r="K76" s="46">
+      <c r="K76" s="1">
         <v>2</v>
       </c>
-      <c r="L76" s="46">
+      <c r="L76" s="1">
         <v>2</v>
       </c>
-      <c r="M76" s="46">
+      <c r="M76" s="1">
         <v>4</v>
       </c>
       <c r="N76" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G76:M76),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O76" s="42" t="str" cm="1">
+      <c r="O76" s="18" t="str" cm="1">
         <f t="array" ref="O76">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="40">
+      <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B77" s="41" t="str">
+      <c r="B77" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C77" s="41" t="str">
+      <c r="C77" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D77" s="43">
+      <c r="D77" s="3">
         <v>46142</v>
       </c>
-      <c r="E77" s="44" t="s">
+      <c r="E77" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F77" s="47" t="s">
+      <c r="F77" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G77" s="46">
-        <v>5</v>
-      </c>
-      <c r="H77" s="46">
-        <v>5</v>
-      </c>
-      <c r="I77" s="46">
-        <v>5</v>
-      </c>
-      <c r="J77" s="46">
+      <c r="G77" s="1">
+        <v>5</v>
+      </c>
+      <c r="H77" s="1">
+        <v>5</v>
+      </c>
+      <c r="I77" s="1">
+        <v>5</v>
+      </c>
+      <c r="J77" s="1">
         <v>3</v>
       </c>
-      <c r="K77" s="46">
-        <v>5</v>
-      </c>
-      <c r="L77" s="46">
+      <c r="K77" s="1">
+        <v>5</v>
+      </c>
+      <c r="L77" s="1">
         <v>3</v>
       </c>
-      <c r="M77" s="46">
+      <c r="M77" s="1">
         <v>5</v>
       </c>
       <c r="N77" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G77:M77),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O77" s="42" t="str" cm="1">
+      <c r="O77" s="18" t="str" cm="1">
         <f t="array" ref="O77">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B78" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C78" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D78" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="F78" s="1">
+        <v>10784668</v>
+      </c>
+      <c r="G78" s="1">
+        <v>5</v>
+      </c>
+      <c r="H78" s="1">
+        <v>5</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4</v>
+      </c>
+      <c r="K78" s="1">
+        <v>4</v>
+      </c>
+      <c r="L78" s="1">
+        <v>3</v>
+      </c>
+      <c r="M78" s="1">
+        <v>5</v>
+      </c>
+      <c r="N78" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G78:M78),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O78" s="18" t="str" cm="1">
+        <f t="array" ref="O78">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B79" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C79" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D79" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F79" s="1">
+        <v>34882674</v>
+      </c>
+      <c r="G79" s="1">
+        <v>5</v>
+      </c>
+      <c r="H79" s="1">
+        <v>4</v>
+      </c>
+      <c r="I79" s="1">
+        <v>4</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
+      </c>
+      <c r="K79" s="1">
+        <v>3</v>
+      </c>
+      <c r="L79" s="1">
+        <v>2</v>
+      </c>
+      <c r="M79" s="1">
+        <v>4</v>
+      </c>
+      <c r="N79" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G79:M79),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O79" s="18" t="str" cm="1">
+        <f t="array" ref="O79">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B80" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C80" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D80" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F80" s="1">
+        <v>50906315</v>
+      </c>
+      <c r="G80" s="1">
+        <v>5</v>
+      </c>
+      <c r="H80" s="1">
+        <v>3</v>
+      </c>
+      <c r="I80" s="1">
+        <v>3</v>
+      </c>
+      <c r="J80" s="1">
+        <v>2</v>
+      </c>
+      <c r="K80" s="1">
+        <v>2</v>
+      </c>
+      <c r="L80" s="1">
+        <v>2</v>
+      </c>
+      <c r="M80" s="1">
+        <v>2</v>
+      </c>
+      <c r="N80" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G80:M80),"-")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="O80" s="18" t="str" cm="1">
+        <f t="array" ref="O80">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B81" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C81" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D81" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F81" s="1">
+        <v>78713979</v>
+      </c>
+      <c r="G81" s="1">
+        <v>5</v>
+      </c>
+      <c r="H81" s="1">
+        <v>4</v>
+      </c>
+      <c r="I81" s="1">
+        <v>4</v>
+      </c>
+      <c r="J81" s="1">
+        <v>3</v>
+      </c>
+      <c r="K81" s="1">
+        <v>2</v>
+      </c>
+      <c r="L81" s="1">
+        <v>2</v>
+      </c>
+      <c r="M81" s="1">
+        <v>5</v>
+      </c>
+      <c r="N81" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G81:M81),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O81" s="18" t="str" cm="1">
+        <f t="array" ref="O81">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B82" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C82" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D82" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1003047136</v>
+      </c>
+      <c r="G82" s="1">
+        <v>5</v>
+      </c>
+      <c r="H82" s="1">
+        <v>4</v>
+      </c>
+      <c r="I82" s="1">
+        <v>4</v>
+      </c>
+      <c r="J82" s="1">
+        <v>2</v>
+      </c>
+      <c r="K82" s="1">
+        <v>2</v>
+      </c>
+      <c r="L82" s="1">
+        <v>2</v>
+      </c>
+      <c r="M82" s="1">
+        <v>2</v>
+      </c>
+      <c r="N82" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G82:M82),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O82" s="18" t="str" cm="1">
+        <f t="array" ref="O82">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B83" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C83" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D83" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1003405136</v>
+      </c>
+      <c r="G83" s="1">
+        <v>5</v>
+      </c>
+      <c r="H83" s="1">
+        <v>5</v>
+      </c>
+      <c r="I83" s="1">
+        <v>4</v>
+      </c>
+      <c r="J83" s="1">
+        <v>3</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4</v>
+      </c>
+      <c r="L83" s="1">
+        <v>3</v>
+      </c>
+      <c r="M83" s="1">
+        <v>5</v>
+      </c>
+      <c r="N83" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G83:M83),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O83" s="18" t="str" cm="1">
+        <f t="array" ref="O83">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B84" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C84" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D84" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1003561480</v>
+      </c>
+      <c r="G84" s="1">
+        <v>5</v>
+      </c>
+      <c r="H84" s="1">
+        <v>4</v>
+      </c>
+      <c r="I84" s="1">
+        <v>4</v>
+      </c>
+      <c r="J84" s="1">
+        <v>3</v>
+      </c>
+      <c r="K84" s="1">
+        <v>2</v>
+      </c>
+      <c r="L84" s="1">
+        <v>2</v>
+      </c>
+      <c r="M84" s="1">
+        <v>4</v>
+      </c>
+      <c r="N84" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G84:M84),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O84" s="18" t="str" cm="1">
+        <f t="array" ref="O84">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B85" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C85" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D85" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1025564047</v>
+      </c>
+      <c r="G85" s="1">
+        <v>5</v>
+      </c>
+      <c r="H85" s="1">
+        <v>5</v>
+      </c>
+      <c r="I85" s="1">
+        <v>4</v>
+      </c>
+      <c r="J85" s="1">
+        <v>4</v>
+      </c>
+      <c r="K85" s="1">
+        <v>4</v>
+      </c>
+      <c r="L85" s="1">
+        <v>3</v>
+      </c>
+      <c r="M85" s="1">
+        <v>5</v>
+      </c>
+      <c r="N85" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G85:M85),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O85" s="18" t="str" cm="1">
+        <f t="array" ref="O85">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B86" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C86" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D86" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1037236492</v>
+      </c>
+      <c r="G86" s="1">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1">
+        <v>5</v>
+      </c>
+      <c r="I86" s="1">
+        <v>4</v>
+      </c>
+      <c r="J86" s="1">
+        <v>3</v>
+      </c>
+      <c r="K86" s="1">
+        <v>4</v>
+      </c>
+      <c r="L86" s="1">
+        <v>3</v>
+      </c>
+      <c r="M86" s="1">
+        <v>5</v>
+      </c>
+      <c r="N86" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G86:M86),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O86" s="18" t="str" cm="1">
+        <f t="array" ref="O86">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B87" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C87" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1062436143</v>
+      </c>
+      <c r="G87" s="1">
+        <v>5</v>
+      </c>
+      <c r="H87" s="1">
+        <v>5</v>
+      </c>
+      <c r="I87" s="1">
+        <v>4</v>
+      </c>
+      <c r="J87" s="1">
+        <v>3</v>
+      </c>
+      <c r="K87" s="1">
+        <v>4</v>
+      </c>
+      <c r="L87" s="1">
+        <v>3</v>
+      </c>
+      <c r="M87" s="1">
+        <v>5</v>
+      </c>
+      <c r="N87" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G87:M87),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O87" s="18" t="str" cm="1">
+        <f t="array" ref="O87">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B88" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C88" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1062438398</v>
+      </c>
+      <c r="G88" s="1">
+        <v>5</v>
+      </c>
+      <c r="H88" s="1">
+        <v>5</v>
+      </c>
+      <c r="I88" s="1">
+        <v>5</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
+        <v>5</v>
+      </c>
+      <c r="L88" s="1">
+        <v>4</v>
+      </c>
+      <c r="M88" s="1">
+        <v>5</v>
+      </c>
+      <c r="N88" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G88:M88),"-")</f>
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O88" s="18" t="str" cm="1">
+        <f t="array" ref="O88">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B89" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C89" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D89" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1062445895</v>
+      </c>
+      <c r="G89" s="1">
+        <v>5</v>
+      </c>
+      <c r="H89" s="1">
+        <v>5</v>
+      </c>
+      <c r="I89" s="1">
+        <v>4</v>
+      </c>
+      <c r="J89" s="1">
+        <v>2</v>
+      </c>
+      <c r="K89" s="1">
+        <v>3</v>
+      </c>
+      <c r="L89" s="1">
+        <v>2</v>
+      </c>
+      <c r="M89" s="1">
+        <v>5</v>
+      </c>
+      <c r="N89" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G89:M89),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O89" s="18" t="str" cm="1">
+        <f t="array" ref="O89">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B90" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C90" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D90" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F90" s="1">
+        <v>1062540875</v>
+      </c>
+      <c r="G90" s="1">
+        <v>5</v>
+      </c>
+      <c r="H90" s="1">
+        <v>5</v>
+      </c>
+      <c r="I90" s="1">
+        <v>4</v>
+      </c>
+      <c r="J90" s="1">
+        <v>2</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4</v>
+      </c>
+      <c r="L90" s="1">
+        <v>2</v>
+      </c>
+      <c r="M90" s="1">
+        <v>5</v>
+      </c>
+      <c r="N90" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G90:M90),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O90" s="18" t="str" cm="1">
+        <f t="array" ref="O90">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B91" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C91" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D91" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1066747137</v>
+      </c>
+      <c r="G91" s="1">
+        <v>5</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5</v>
+      </c>
+      <c r="I91" s="1">
+        <v>5</v>
+      </c>
+      <c r="J91" s="1">
+        <v>4</v>
+      </c>
+      <c r="K91" s="1">
+        <v>4</v>
+      </c>
+      <c r="L91" s="1">
+        <v>4</v>
+      </c>
+      <c r="M91" s="1">
+        <v>5</v>
+      </c>
+      <c r="N91" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G91:M91),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O91" s="18" t="str" cm="1">
+        <f t="array" ref="O91">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B92" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C92" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D92" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1068441879</v>
+      </c>
+      <c r="G92" s="1">
+        <v>5</v>
+      </c>
+      <c r="H92" s="1">
+        <v>5</v>
+      </c>
+      <c r="I92" s="1">
+        <v>4</v>
+      </c>
+      <c r="J92" s="1">
+        <v>3</v>
+      </c>
+      <c r="K92" s="1">
+        <v>3</v>
+      </c>
+      <c r="L92" s="1">
+        <v>2</v>
+      </c>
+      <c r="M92" s="1">
+        <v>5</v>
+      </c>
+      <c r="N92" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G92:M92),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O92" s="18" t="str" cm="1">
+        <f t="array" ref="O92">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B93" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C93" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D93" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1068442748</v>
+      </c>
+      <c r="G93" s="1">
+        <v>5</v>
+      </c>
+      <c r="H93" s="1">
+        <v>2</v>
+      </c>
+      <c r="I93" s="1">
+        <v>2</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+      <c r="K93" s="1">
+        <v>1</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
+        <v>1</v>
+      </c>
+      <c r="N93" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G93:M93),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O93" s="18" t="str" cm="1">
+        <f t="array" ref="O93">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B94" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C94" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D94" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" s="1">
+        <v>1068580241</v>
+      </c>
+      <c r="G94" s="1">
+        <v>5</v>
+      </c>
+      <c r="H94" s="1">
+        <v>5</v>
+      </c>
+      <c r="I94" s="1">
+        <v>5</v>
+      </c>
+      <c r="J94" s="1">
+        <v>4</v>
+      </c>
+      <c r="K94" s="1">
+        <v>5</v>
+      </c>
+      <c r="L94" s="1">
+        <v>4</v>
+      </c>
+      <c r="M94" s="1">
+        <v>5</v>
+      </c>
+      <c r="N94" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G94:M94),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O94" s="18" t="str" cm="1">
+        <f t="array" ref="O94">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B95" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C95" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D95" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1103755851</v>
+      </c>
+      <c r="G95" s="1">
+        <v>5</v>
+      </c>
+      <c r="H95" s="1">
+        <v>5</v>
+      </c>
+      <c r="I95" s="1">
+        <v>4</v>
+      </c>
+      <c r="J95" s="1">
+        <v>3</v>
+      </c>
+      <c r="K95" s="1">
+        <v>4</v>
+      </c>
+      <c r="L95" s="1">
+        <v>3</v>
+      </c>
+      <c r="M95" s="1">
+        <v>5</v>
+      </c>
+      <c r="N95" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G95:M95),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O95" s="18" t="str" cm="1">
+        <f t="array" ref="O95">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B96" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C96" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D96" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F96" s="1">
+        <v>1138031915</v>
+      </c>
+      <c r="G96" s="1">
+        <v>5</v>
+      </c>
+      <c r="H96" s="1">
+        <v>5</v>
+      </c>
+      <c r="I96" s="1">
+        <v>4</v>
+      </c>
+      <c r="J96" s="1">
+        <v>3</v>
+      </c>
+      <c r="K96" s="1">
+        <v>3</v>
+      </c>
+      <c r="L96" s="1">
+        <v>2</v>
+      </c>
+      <c r="M96" s="1">
+        <v>5</v>
+      </c>
+      <c r="N96" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G96:M96),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O96" s="18" t="str" cm="1">
+        <f t="array" ref="O96">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B97" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C97" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D97" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1233040347</v>
+      </c>
+      <c r="G97" s="1">
+        <v>5</v>
+      </c>
+      <c r="H97" s="1">
+        <v>4</v>
+      </c>
+      <c r="I97" s="1">
+        <v>4</v>
+      </c>
+      <c r="J97" s="1">
+        <v>2</v>
+      </c>
+      <c r="K97" s="1">
+        <v>2</v>
+      </c>
+      <c r="L97" s="1">
+        <v>2</v>
+      </c>
+      <c r="M97" s="1">
+        <v>4</v>
+      </c>
+      <c r="N97" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G97:M97),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O97" s="18" t="str" cm="1">
+        <f t="array" ref="O97">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B98" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C98" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D98" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1233348383</v>
+      </c>
+      <c r="G98" s="1">
+        <v>5</v>
+      </c>
+      <c r="H98" s="1">
+        <v>5</v>
+      </c>
+      <c r="I98" s="1">
+        <v>4</v>
+      </c>
+      <c r="J98" s="1">
+        <v>3</v>
+      </c>
+      <c r="K98" s="1">
+        <v>3</v>
+      </c>
+      <c r="L98" s="1">
+        <v>3</v>
+      </c>
+      <c r="M98" s="1">
+        <v>5</v>
+      </c>
+      <c r="N98" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G98:M98),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O98" s="18" t="str" cm="1">
+        <f t="array" ref="O98">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B99" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C99" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D99" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G99" s="1">
+        <v>5</v>
+      </c>
+      <c r="H99" s="1">
+        <v>4</v>
+      </c>
+      <c r="I99" s="1">
+        <v>4</v>
+      </c>
+      <c r="J99" s="1">
+        <v>2</v>
+      </c>
+      <c r="K99" s="1">
+        <v>2</v>
+      </c>
+      <c r="L99" s="1">
+        <v>2</v>
+      </c>
+      <c r="M99" s="1">
+        <v>2</v>
+      </c>
+      <c r="N99" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G99:M99),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O99" s="18" t="str" cm="1">
+        <f t="array" ref="O99">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B100" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C100" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D100" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G100" s="1">
+        <v>5</v>
+      </c>
+      <c r="H100" s="1">
+        <v>5</v>
+      </c>
+      <c r="I100" s="1">
+        <v>5</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
+        <v>5</v>
+      </c>
+      <c r="L100" s="1">
+        <v>4</v>
+      </c>
+      <c r="M100" s="1">
+        <v>5</v>
+      </c>
+      <c r="N100" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G100:M100),"-")</f>
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O100" s="18" t="str" cm="1">
+        <f t="array" ref="O100">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B101" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C101" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D101" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G101" s="1">
+        <v>5</v>
+      </c>
+      <c r="H101" s="1">
+        <v>3</v>
+      </c>
+      <c r="I101" s="1">
+        <v>2</v>
+      </c>
+      <c r="J101" s="1">
+        <v>2</v>
+      </c>
+      <c r="K101" s="1">
+        <v>1</v>
+      </c>
+      <c r="L101" s="1">
+        <v>1</v>
+      </c>
+      <c r="M101" s="1">
+        <v>4</v>
+      </c>
+      <c r="N101" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G101:M101),"-")</f>
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="O101" s="18" t="str" cm="1">
+        <f t="array" ref="O101">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B102" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C102" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D102" s="3">
+        <v>46171</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G102" s="1">
+        <v>5</v>
+      </c>
+      <c r="H102" s="1">
+        <v>5</v>
+      </c>
+      <c r="I102" s="1">
+        <v>4</v>
+      </c>
+      <c r="J102" s="1">
+        <v>3</v>
+      </c>
+      <c r="K102" s="1">
+        <v>4</v>
+      </c>
+      <c r="L102" s="1">
+        <v>3</v>
+      </c>
+      <c r="M102" s="1">
+        <v>5</v>
+      </c>
+      <c r="N102" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G102:M102),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O102" s="18" t="str" cm="1">
+        <f t="array" ref="O102">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -17033,7 +18363,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -18213,626 +19543,1718 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="46">
+      <c r="A24" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B24" s="48" t="str">
+      <c r="B24" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C24" s="48" t="str">
+      <c r="C24" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="3">
         <v>46142</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F24" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G24" s="46">
-        <v>4</v>
-      </c>
-      <c r="H24" s="46">
-        <v>4</v>
-      </c>
-      <c r="I24" s="46">
-        <v>5</v>
-      </c>
-      <c r="J24" s="46">
-        <v>4</v>
-      </c>
-      <c r="K24" s="46">
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4</v>
+      </c>
+      <c r="K24" s="1">
         <v>3</v>
       </c>
-      <c r="L24" s="46">
-        <v>5</v>
-      </c>
-      <c r="M24" s="46">
+      <c r="L24" s="1">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1">
         <v>3</v>
       </c>
       <c r="N24" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G24:M24),"-")</f>
         <v>4</v>
       </c>
-      <c r="O24" s="49" t="str" cm="1">
+      <c r="O24" s="18" t="str" cm="1">
         <f t="array" ref="O24">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="46">
+      <c r="A25" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B25" s="48" t="str">
+      <c r="B25" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C25" s="48" t="str">
+      <c r="C25" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="3">
         <v>46142</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="1">
         <v>1062444411</v>
       </c>
-      <c r="G25" s="46">
-        <v>5</v>
-      </c>
-      <c r="H25" s="46">
-        <v>5</v>
-      </c>
-      <c r="I25" s="46">
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1">
         <v>2</v>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="1">
         <v>3</v>
       </c>
-      <c r="K25" s="46">
-        <v>4</v>
-      </c>
-      <c r="L25" s="46">
-        <v>5</v>
-      </c>
-      <c r="M25" s="46">
+      <c r="K25" s="1">
+        <v>4</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1">
         <v>2</v>
       </c>
       <c r="N25" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G25:M25),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O25" s="49" t="str" cm="1">
+      <c r="O25" s="18" t="str" cm="1">
         <f t="array" ref="O25">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="46">
+      <c r="A26" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B26" s="48" t="str">
+      <c r="B26" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C26" s="48" t="str">
+      <c r="C26" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="3">
         <v>46142</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="1">
         <v>1062980565</v>
       </c>
-      <c r="G26" s="46">
-        <v>4</v>
-      </c>
-      <c r="H26" s="46">
-        <v>4</v>
-      </c>
-      <c r="I26" s="46">
+      <c r="G26" s="1">
+        <v>4</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4</v>
+      </c>
+      <c r="I26" s="1">
         <v>3</v>
       </c>
-      <c r="J26" s="46">
+      <c r="J26" s="1">
         <v>3</v>
       </c>
-      <c r="K26" s="46">
+      <c r="K26" s="1">
         <v>3</v>
       </c>
-      <c r="L26" s="46">
-        <v>5</v>
-      </c>
-      <c r="M26" s="46">
+      <c r="L26" s="1">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
         <v>2</v>
       </c>
       <c r="N26" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G26:M26),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O26" s="49" t="str" cm="1">
+      <c r="O26" s="18" t="str" cm="1">
         <f t="array" ref="O26">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="46">
+      <c r="A27" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B27" s="48" t="str">
+      <c r="B27" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C27" s="48" t="str">
+      <c r="C27" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="3">
         <v>46142</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="46">
+      <c r="F27" s="1">
         <v>1062981643</v>
       </c>
-      <c r="G27" s="46">
-        <v>4</v>
-      </c>
-      <c r="H27" s="46">
-        <v>5</v>
-      </c>
-      <c r="I27" s="46">
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="1">
         <v>2</v>
       </c>
-      <c r="J27" s="46">
+      <c r="J27" s="1">
         <v>3</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="1">
         <v>3</v>
       </c>
-      <c r="L27" s="46">
-        <v>5</v>
-      </c>
-      <c r="M27" s="46">
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="1">
         <v>2</v>
       </c>
       <c r="N27" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G27:M27),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O27" s="49" t="str" cm="1">
+      <c r="O27" s="18" t="str" cm="1">
         <f t="array" ref="O27">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="46">
+      <c r="A28" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B28" s="48" t="str">
+      <c r="B28" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C28" s="48" t="str">
+      <c r="C28" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D28" s="43">
+      <c r="D28" s="3">
         <v>46142</v>
       </c>
-      <c r="E28" s="44" t="s">
+      <c r="E28" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="46">
+      <c r="F28" s="1">
         <v>1062986616</v>
       </c>
-      <c r="G28" s="46">
-        <v>4</v>
-      </c>
-      <c r="H28" s="46">
-        <v>4</v>
-      </c>
-      <c r="I28" s="46">
-        <v>4</v>
-      </c>
-      <c r="J28" s="46">
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28" s="1">
+        <v>4</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4</v>
+      </c>
+      <c r="J28" s="1">
         <v>3</v>
       </c>
-      <c r="K28" s="46">
+      <c r="K28" s="1">
         <v>2</v>
       </c>
-      <c r="L28" s="46">
-        <v>5</v>
-      </c>
-      <c r="M28" s="46">
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
         <v>1</v>
       </c>
       <c r="N28" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G28:M28),"-")</f>
         <v>3.2857142857142856</v>
       </c>
-      <c r="O28" s="49" t="str" cm="1">
+      <c r="O28" s="18" t="str" cm="1">
         <f t="array" ref="O28">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="46">
+      <c r="A29" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B29" s="48" t="str">
+      <c r="B29" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C29" s="48" t="str">
+      <c r="C29" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="3">
         <v>46142</v>
       </c>
-      <c r="E29" s="44" t="s">
+      <c r="E29" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="46">
+      <c r="F29" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G29" s="46">
-        <v>4</v>
-      </c>
-      <c r="H29" s="46">
-        <v>4</v>
-      </c>
-      <c r="I29" s="46">
-        <v>4</v>
-      </c>
-      <c r="J29" s="46">
-        <v>4</v>
-      </c>
-      <c r="K29" s="46">
-        <v>4</v>
-      </c>
-      <c r="L29" s="46">
-        <v>5</v>
-      </c>
-      <c r="M29" s="46">
+      <c r="G29" s="1">
+        <v>4</v>
+      </c>
+      <c r="H29" s="1">
+        <v>4</v>
+      </c>
+      <c r="I29" s="1">
+        <v>4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4</v>
+      </c>
+      <c r="K29" s="1">
+        <v>4</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1">
         <v>1</v>
       </c>
       <c r="N29" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G29:M29),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O29" s="49" t="str" cm="1">
+      <c r="O29" s="18" t="str" cm="1">
         <f t="array" ref="O29">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="46">
+      <c r="A30" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B30" s="48" t="str">
+      <c r="B30" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C30" s="48" t="str">
+      <c r="C30" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="3">
         <v>46142</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="46">
+      <c r="F30" s="1">
         <v>1067956606</v>
       </c>
-      <c r="G30" s="46">
-        <v>4</v>
-      </c>
-      <c r="H30" s="46">
-        <v>4</v>
-      </c>
-      <c r="I30" s="46">
-        <v>4</v>
-      </c>
-      <c r="J30" s="46">
-        <v>4</v>
-      </c>
-      <c r="K30" s="46">
-        <v>5</v>
-      </c>
-      <c r="L30" s="46">
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1">
+        <v>4</v>
+      </c>
+      <c r="I30" s="1">
+        <v>4</v>
+      </c>
+      <c r="J30" s="1">
+        <v>4</v>
+      </c>
+      <c r="K30" s="1">
+        <v>5</v>
+      </c>
+      <c r="L30" s="1">
         <v>3</v>
       </c>
-      <c r="M30" s="46">
+      <c r="M30" s="1">
         <v>4</v>
       </c>
       <c r="N30" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G30:M30),"-")</f>
         <v>4</v>
       </c>
-      <c r="O30" s="49" t="str" cm="1">
+      <c r="O30" s="18" t="str" cm="1">
         <f t="array" ref="O30">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="46">
+      <c r="A31" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B31" s="48" t="str">
+      <c r="B31" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C31" s="48" t="str">
+      <c r="C31" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="3">
         <v>46142</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="46">
+      <c r="F31" s="1">
         <v>1068439668</v>
       </c>
-      <c r="G31" s="46">
-        <v>5</v>
-      </c>
-      <c r="H31" s="46">
-        <v>5</v>
-      </c>
-      <c r="I31" s="46">
-        <v>4</v>
-      </c>
-      <c r="J31" s="46">
-        <v>4</v>
-      </c>
-      <c r="K31" s="46">
-        <v>4</v>
-      </c>
-      <c r="L31" s="46">
-        <v>5</v>
-      </c>
-      <c r="M31" s="46">
+      <c r="G31" s="1">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1">
+        <v>5</v>
+      </c>
+      <c r="I31" s="1">
+        <v>4</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4</v>
+      </c>
+      <c r="K31" s="1">
+        <v>4</v>
+      </c>
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1">
         <v>3</v>
       </c>
       <c r="N31" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G31:M31),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O31" s="49" t="str" cm="1">
+      <c r="O31" s="18" t="str" cm="1">
         <f t="array" ref="O31">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="46">
+      <c r="A32" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B32" s="48" t="str">
+      <c r="B32" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C32" s="48" t="str">
+      <c r="C32" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D32" s="43">
+      <c r="D32" s="3">
         <v>46142</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="46">
+      <c r="F32" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G32" s="46">
-        <v>5</v>
-      </c>
-      <c r="H32" s="46">
-        <v>4</v>
-      </c>
-      <c r="I32" s="46">
+      <c r="G32" s="1">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4</v>
+      </c>
+      <c r="I32" s="1">
         <v>2</v>
       </c>
-      <c r="J32" s="46">
-        <v>4</v>
-      </c>
-      <c r="K32" s="46">
+      <c r="J32" s="1">
+        <v>4</v>
+      </c>
+      <c r="K32" s="1">
         <v>2</v>
       </c>
-      <c r="L32" s="46">
-        <v>5</v>
-      </c>
-      <c r="M32" s="46">
+      <c r="L32" s="1">
+        <v>5</v>
+      </c>
+      <c r="M32" s="1">
         <v>2</v>
       </c>
       <c r="N32" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G32:M32),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O32" s="49" t="str" cm="1">
+      <c r="O32" s="18" t="str" cm="1">
         <f t="array" ref="O32">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="46">
+      <c r="A33" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B33" s="48" t="str">
+      <c r="B33" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C33" s="48" t="str">
+      <c r="C33" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="3">
         <v>46142</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="46">
+      <c r="F33" s="1">
         <v>1104267144</v>
       </c>
-      <c r="G33" s="46">
-        <v>5</v>
-      </c>
-      <c r="H33" s="46">
-        <v>4</v>
-      </c>
-      <c r="I33" s="46">
-        <v>4</v>
-      </c>
-      <c r="J33" s="46">
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>4</v>
+      </c>
+      <c r="I33" s="1">
+        <v>4</v>
+      </c>
+      <c r="J33" s="1">
         <v>3</v>
       </c>
-      <c r="K33" s="46">
-        <v>5</v>
-      </c>
-      <c r="L33" s="46">
-        <v>5</v>
-      </c>
-      <c r="M33" s="46">
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="L33" s="1">
+        <v>5</v>
+      </c>
+      <c r="M33" s="1">
         <v>3</v>
       </c>
       <c r="N33" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G33:M33),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O33" s="49" t="str" cm="1">
+      <c r="O33" s="18" t="str" cm="1">
         <f t="array" ref="O33">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="46">
+      <c r="A34" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B34" s="48" t="str">
+      <c r="B34" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C34" s="48" t="str">
+      <c r="C34" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="3">
         <v>46142</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E34" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F34" s="46">
+      <c r="F34" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G34" s="46">
-        <v>5</v>
-      </c>
-      <c r="H34" s="46">
-        <v>5</v>
-      </c>
-      <c r="I34" s="46">
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1">
+        <v>5</v>
+      </c>
+      <c r="I34" s="1">
         <v>3</v>
       </c>
-      <c r="J34" s="46">
+      <c r="J34" s="1">
         <v>3</v>
       </c>
-      <c r="K34" s="46">
-        <v>5</v>
-      </c>
-      <c r="L34" s="46">
-        <v>5</v>
-      </c>
-      <c r="M34" s="46">
+      <c r="K34" s="1">
+        <v>5</v>
+      </c>
+      <c r="L34" s="1">
+        <v>5</v>
+      </c>
+      <c r="M34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G34:M34),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O34" s="49" t="str" cm="1">
+      <c r="O34" s="18" t="str" cm="1">
         <f t="array" ref="O34">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="46">
+      <c r="A35" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B35" s="48" t="str">
+      <c r="B35" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C35" s="48" t="str">
+      <c r="C35" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="3">
         <v>46142</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="46">
+      <c r="F35" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G35" s="46">
-        <v>5</v>
-      </c>
-      <c r="H35" s="46">
-        <v>5</v>
-      </c>
-      <c r="I35" s="46">
-        <v>4</v>
-      </c>
-      <c r="J35" s="46">
-        <v>4</v>
-      </c>
-      <c r="K35" s="46">
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
+        <v>5</v>
+      </c>
+      <c r="I35" s="1">
+        <v>4</v>
+      </c>
+      <c r="J35" s="1">
+        <v>4</v>
+      </c>
+      <c r="K35" s="1">
         <v>3</v>
       </c>
-      <c r="L35" s="46">
-        <v>5</v>
-      </c>
-      <c r="M35" s="46">
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1">
         <v>3</v>
       </c>
       <c r="N35" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G35:M35),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O35" s="49" t="str" cm="1">
+      <c r="O35" s="18" t="str" cm="1">
         <f t="array" ref="O35">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B36" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C36" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D36" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" s="41">
+        <v>8203609</v>
+      </c>
+      <c r="G36" s="41">
+        <v>5</v>
+      </c>
+      <c r="H36" s="41">
+        <v>4</v>
+      </c>
+      <c r="I36" s="41">
+        <v>5</v>
+      </c>
+      <c r="J36" s="41">
+        <v>3</v>
+      </c>
+      <c r="K36" s="41">
+        <v>4</v>
+      </c>
+      <c r="L36" s="41">
+        <v>5</v>
+      </c>
+      <c r="M36" s="41">
+        <v>4</v>
+      </c>
+      <c r="N36" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G36:M36),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O36" s="43" t="str" cm="1">
+        <f t="array" ref="O36">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B37" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C37" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D37" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="41">
+        <v>1001481017</v>
+      </c>
+      <c r="G37" s="41">
+        <v>4</v>
+      </c>
+      <c r="H37" s="41">
+        <v>3</v>
+      </c>
+      <c r="I37" s="41">
+        <v>2</v>
+      </c>
+      <c r="J37" s="41">
+        <v>3</v>
+      </c>
+      <c r="K37" s="41">
+        <v>4</v>
+      </c>
+      <c r="L37" s="41">
+        <v>4</v>
+      </c>
+      <c r="M37" s="41">
+        <v>2</v>
+      </c>
+      <c r="N37" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G37:M37),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O37" s="43" t="str" cm="1">
+        <f t="array" ref="O37">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B38" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C38" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D38" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="41">
+        <v>1003027198</v>
+      </c>
+      <c r="G38" s="41">
+        <v>5</v>
+      </c>
+      <c r="H38" s="41">
+        <v>4</v>
+      </c>
+      <c r="I38" s="41">
+        <v>3</v>
+      </c>
+      <c r="J38" s="41">
+        <v>5</v>
+      </c>
+      <c r="K38" s="41">
+        <v>4</v>
+      </c>
+      <c r="L38" s="41">
+        <v>5</v>
+      </c>
+      <c r="M38" s="41">
+        <v>2</v>
+      </c>
+      <c r="N38" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G38:M38),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O38" s="43" t="str" cm="1">
+        <f t="array" ref="O38">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B39" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C39" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D39" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" s="41">
+        <v>1003435656</v>
+      </c>
+      <c r="G39" s="41">
+        <v>4</v>
+      </c>
+      <c r="H39" s="41">
+        <v>4</v>
+      </c>
+      <c r="I39" s="41">
+        <v>3</v>
+      </c>
+      <c r="J39" s="41">
+        <v>3</v>
+      </c>
+      <c r="K39" s="41">
+        <v>3</v>
+      </c>
+      <c r="L39" s="41">
+        <v>5</v>
+      </c>
+      <c r="M39" s="41">
+        <v>2</v>
+      </c>
+      <c r="N39" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G39:M39),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O39" s="43" t="str" cm="1">
+        <f t="array" ref="O39">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B40" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C40" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D40" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="41">
+        <v>1027663882</v>
+      </c>
+      <c r="G40" s="41">
+        <v>5</v>
+      </c>
+      <c r="H40" s="41">
+        <v>4</v>
+      </c>
+      <c r="I40" s="41">
+        <v>5</v>
+      </c>
+      <c r="J40" s="41">
+        <v>4</v>
+      </c>
+      <c r="K40" s="41">
+        <v>4</v>
+      </c>
+      <c r="L40" s="41">
+        <v>5</v>
+      </c>
+      <c r="M40" s="41">
+        <v>4</v>
+      </c>
+      <c r="N40" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G40:M40),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O40" s="43" t="str" cm="1">
+        <f t="array" ref="O40">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B41" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C41" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D41" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="41">
+        <v>1029722943</v>
+      </c>
+      <c r="G41" s="41">
+        <v>5</v>
+      </c>
+      <c r="H41" s="41">
+        <v>4</v>
+      </c>
+      <c r="I41" s="41">
+        <v>4</v>
+      </c>
+      <c r="J41" s="41">
+        <v>4</v>
+      </c>
+      <c r="K41" s="41">
+        <v>4</v>
+      </c>
+      <c r="L41" s="41">
+        <v>5</v>
+      </c>
+      <c r="M41" s="41">
+        <v>5</v>
+      </c>
+      <c r="N41" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G41:M41),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O41" s="43" t="str" cm="1">
+        <f t="array" ref="O41">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B42" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C42" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D42" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" s="41">
+        <v>1062444411</v>
+      </c>
+      <c r="G42" s="41">
+        <v>5</v>
+      </c>
+      <c r="H42" s="41">
+        <v>5</v>
+      </c>
+      <c r="I42" s="41">
+        <v>2</v>
+      </c>
+      <c r="J42" s="41">
+        <v>4</v>
+      </c>
+      <c r="K42" s="41">
+        <v>4</v>
+      </c>
+      <c r="L42" s="41">
+        <v>5</v>
+      </c>
+      <c r="M42" s="41">
+        <v>2</v>
+      </c>
+      <c r="N42" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G42:M42),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O42" s="43" t="str" cm="1">
+        <f t="array" ref="O42">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B43" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C43" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D43" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="41">
+        <v>1062544508</v>
+      </c>
+      <c r="G43" s="41">
+        <v>4</v>
+      </c>
+      <c r="H43" s="41">
+        <v>4</v>
+      </c>
+      <c r="I43" s="41">
+        <v>2</v>
+      </c>
+      <c r="J43" s="41">
+        <v>3</v>
+      </c>
+      <c r="K43" s="41">
+        <v>3</v>
+      </c>
+      <c r="L43" s="41">
+        <v>3</v>
+      </c>
+      <c r="M43" s="41">
+        <v>2</v>
+      </c>
+      <c r="N43" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G43:M43),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O43" s="43" t="str" cm="1">
+        <f t="array" ref="O43">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B44" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C44" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D44" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F44" s="41">
+        <v>1062980565</v>
+      </c>
+      <c r="G44" s="41">
+        <v>5</v>
+      </c>
+      <c r="H44" s="41">
+        <v>5</v>
+      </c>
+      <c r="I44" s="41">
+        <v>4</v>
+      </c>
+      <c r="J44" s="41">
+        <v>5</v>
+      </c>
+      <c r="K44" s="41">
+        <v>4</v>
+      </c>
+      <c r="L44" s="41">
+        <v>5</v>
+      </c>
+      <c r="M44" s="41">
+        <v>5</v>
+      </c>
+      <c r="N44" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G44:M44),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O44" s="43" t="str" cm="1">
+        <f t="array" ref="O44">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B45" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C45" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D45" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="41">
+        <v>1062981643</v>
+      </c>
+      <c r="G45" s="41">
+        <v>4</v>
+      </c>
+      <c r="H45" s="41">
+        <v>5</v>
+      </c>
+      <c r="I45" s="41">
+        <v>2</v>
+      </c>
+      <c r="J45" s="41">
+        <v>3</v>
+      </c>
+      <c r="K45" s="41">
+        <v>3</v>
+      </c>
+      <c r="L45" s="41">
+        <v>4</v>
+      </c>
+      <c r="M45" s="41">
+        <v>3</v>
+      </c>
+      <c r="N45" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G45:M45),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O45" s="43" t="str" cm="1">
+        <f t="array" ref="O45">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B46" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C46" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D46" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="F46" s="41">
+        <v>1067859838</v>
+      </c>
+      <c r="G46" s="41">
+        <v>4</v>
+      </c>
+      <c r="H46" s="41">
+        <v>4</v>
+      </c>
+      <c r="I46" s="41">
+        <v>4</v>
+      </c>
+      <c r="J46" s="41">
+        <v>4</v>
+      </c>
+      <c r="K46" s="41">
+        <v>4</v>
+      </c>
+      <c r="L46" s="41">
+        <v>5</v>
+      </c>
+      <c r="M46" s="41">
+        <v>1</v>
+      </c>
+      <c r="N46" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G46:M46),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O46" s="43" t="str" cm="1">
+        <f t="array" ref="O46">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B47" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C47" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D47" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="41">
+        <v>1067945529</v>
+      </c>
+      <c r="G47" s="41">
+        <v>4</v>
+      </c>
+      <c r="H47" s="41">
+        <v>4</v>
+      </c>
+      <c r="I47" s="41">
+        <v>4</v>
+      </c>
+      <c r="J47" s="41">
+        <v>4</v>
+      </c>
+      <c r="K47" s="41">
+        <v>4</v>
+      </c>
+      <c r="L47" s="41">
+        <v>4</v>
+      </c>
+      <c r="M47" s="41">
+        <v>1</v>
+      </c>
+      <c r="N47" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G47:M47),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O47" s="43" t="str" cm="1">
+        <f t="array" ref="O47">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B48" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C48" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D48" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" s="41">
+        <v>1067955099</v>
+      </c>
+      <c r="G48" s="41">
+        <v>5</v>
+      </c>
+      <c r="H48" s="41">
+        <v>5</v>
+      </c>
+      <c r="I48" s="41">
+        <v>3</v>
+      </c>
+      <c r="J48" s="41">
+        <v>4</v>
+      </c>
+      <c r="K48" s="41">
+        <v>4</v>
+      </c>
+      <c r="L48" s="41">
+        <v>5</v>
+      </c>
+      <c r="M48" s="41">
+        <v>3</v>
+      </c>
+      <c r="N48" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G48:M48),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O48" s="43" t="str" cm="1">
+        <f t="array" ref="O48">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B49" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C49" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D49" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49" s="41">
+        <v>1067956606</v>
+      </c>
+      <c r="G49" s="41">
+        <v>0</v>
+      </c>
+      <c r="H49" s="41">
+        <v>0</v>
+      </c>
+      <c r="I49" s="41">
+        <v>0</v>
+      </c>
+      <c r="J49" s="41">
+        <v>0</v>
+      </c>
+      <c r="K49" s="41">
+        <v>0</v>
+      </c>
+      <c r="L49" s="41">
+        <v>0</v>
+      </c>
+      <c r="M49" s="41">
+        <v>0</v>
+      </c>
+      <c r="N49" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G49:M49),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="43" t="str" cm="1">
+        <f t="array" ref="O49">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B50" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C50" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D50" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="F50" s="41">
+        <v>1068439668</v>
+      </c>
+      <c r="G50" s="41">
+        <v>5</v>
+      </c>
+      <c r="H50" s="41">
+        <v>5</v>
+      </c>
+      <c r="I50" s="41">
+        <v>4</v>
+      </c>
+      <c r="J50" s="41">
+        <v>5</v>
+      </c>
+      <c r="K50" s="41">
+        <v>4</v>
+      </c>
+      <c r="L50" s="41">
+        <v>5</v>
+      </c>
+      <c r="M50" s="41">
+        <v>5</v>
+      </c>
+      <c r="N50" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G50:M50),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O50" s="43" t="str" cm="1">
+        <f t="array" ref="O50">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B51" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C51" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D51" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="41">
+        <v>1073817245</v>
+      </c>
+      <c r="G51" s="41">
+        <v>5</v>
+      </c>
+      <c r="H51" s="41">
+        <v>4</v>
+      </c>
+      <c r="I51" s="41">
+        <v>2</v>
+      </c>
+      <c r="J51" s="41">
+        <v>4</v>
+      </c>
+      <c r="K51" s="41">
+        <v>3</v>
+      </c>
+      <c r="L51" s="41">
+        <v>5</v>
+      </c>
+      <c r="M51" s="41">
+        <v>2</v>
+      </c>
+      <c r="N51" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G51:M51),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O51" s="43" t="str" cm="1">
+        <f t="array" ref="O51">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B52" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C52" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D52" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F52" s="41">
+        <v>1137975856</v>
+      </c>
+      <c r="G52" s="41">
+        <v>4</v>
+      </c>
+      <c r="H52" s="41">
+        <v>4</v>
+      </c>
+      <c r="I52" s="41">
+        <v>4</v>
+      </c>
+      <c r="J52" s="41">
+        <v>5</v>
+      </c>
+      <c r="K52" s="41">
+        <v>4</v>
+      </c>
+      <c r="L52" s="41">
+        <v>5</v>
+      </c>
+      <c r="M52" s="41">
+        <v>4</v>
+      </c>
+      <c r="N52" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G52:M52),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O52" s="43" t="str" cm="1">
+        <f t="array" ref="O52">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B53" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C53" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D53" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="41">
+        <v>1138032406</v>
+      </c>
+      <c r="G53" s="41">
+        <v>5</v>
+      </c>
+      <c r="H53" s="41">
+        <v>5</v>
+      </c>
+      <c r="I53" s="41">
+        <v>3</v>
+      </c>
+      <c r="J53" s="41">
+        <v>4</v>
+      </c>
+      <c r="K53" s="41">
+        <v>3</v>
+      </c>
+      <c r="L53" s="41">
+        <v>5</v>
+      </c>
+      <c r="M53" s="41">
+        <v>2</v>
+      </c>
+      <c r="N53" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G53:M53),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O53" s="43" t="str" cm="1">
+        <f t="array" ref="O53">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B54" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C54" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D54" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="41">
+        <v>1138032417</v>
+      </c>
+      <c r="G54" s="41">
+        <v>5</v>
+      </c>
+      <c r="H54" s="41">
+        <v>4</v>
+      </c>
+      <c r="I54" s="41">
+        <v>4</v>
+      </c>
+      <c r="J54" s="41">
+        <v>4</v>
+      </c>
+      <c r="K54" s="41">
+        <v>3</v>
+      </c>
+      <c r="L54" s="41">
+        <v>5</v>
+      </c>
+      <c r="M54" s="41">
+        <v>4</v>
+      </c>
+      <c r="N54" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G54:M54),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O54" s="43" t="str" cm="1">
+        <f t="array" ref="O54">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B55" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C55" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D55" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" s="41">
+        <v>1138032549</v>
+      </c>
+      <c r="G55" s="41">
+        <v>5</v>
+      </c>
+      <c r="H55" s="41">
+        <v>5</v>
+      </c>
+      <c r="I55" s="41">
+        <v>3</v>
+      </c>
+      <c r="J55" s="41">
+        <v>4</v>
+      </c>
+      <c r="K55" s="41">
+        <v>5</v>
+      </c>
+      <c r="L55" s="41">
+        <v>5</v>
+      </c>
+      <c r="M55" s="41">
+        <v>5</v>
+      </c>
+      <c r="N55" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G55:M55),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O55" s="43" t="str" cm="1">
+        <f t="array" ref="O55">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="41">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B56" s="42" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C56" s="42" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D56" s="44">
+        <v>46172</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="41">
+        <v>1140444971</v>
+      </c>
+      <c r="G56" s="41">
+        <v>5</v>
+      </c>
+      <c r="H56" s="41">
+        <v>5</v>
+      </c>
+      <c r="I56" s="41">
+        <v>4</v>
+      </c>
+      <c r="J56" s="41">
+        <v>5</v>
+      </c>
+      <c r="K56" s="41">
+        <v>3</v>
+      </c>
+      <c r="L56" s="41">
+        <v>5</v>
+      </c>
+      <c r="M56" s="41">
+        <v>2</v>
+      </c>
+      <c r="N56" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G56:M56),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O56" s="43" t="str" cm="1">
+        <f t="array" ref="O56">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -18860,7 +21282,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -19252,142 +21674,282 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="50">
+      <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="str">
+      <c r="B7" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C7" s="51" t="str">
+      <c r="C7" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="21">
         <v>46142</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="23">
         <v>1062539643</v>
       </c>
-      <c r="G7" s="54">
-        <v>5</v>
-      </c>
-      <c r="H7" s="54">
-        <v>4</v>
-      </c>
-      <c r="I7" s="54">
-        <v>5</v>
-      </c>
-      <c r="J7" s="54">
-        <v>5</v>
-      </c>
-      <c r="K7" s="54">
-        <v>4</v>
-      </c>
-      <c r="L7" s="54">
+      <c r="G7" s="23">
+        <v>5</v>
+      </c>
+      <c r="H7" s="23">
+        <v>4</v>
+      </c>
+      <c r="I7" s="23">
+        <v>5</v>
+      </c>
+      <c r="J7" s="23">
+        <v>5</v>
+      </c>
+      <c r="K7" s="23">
+        <v>4</v>
+      </c>
+      <c r="L7" s="23">
         <v>3</v>
       </c>
-      <c r="M7" s="54">
-        <v>5</v>
-      </c>
-      <c r="N7" s="54">
-        <v>4</v>
-      </c>
-      <c r="O7" s="54">
-        <v>4</v>
-      </c>
-      <c r="P7" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="54">
+      <c r="M7" s="23">
+        <v>5</v>
+      </c>
+      <c r="N7" s="23">
+        <v>4</v>
+      </c>
+      <c r="O7" s="23">
+        <v>4</v>
+      </c>
+      <c r="P7" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="23">
         <v>3</v>
       </c>
-      <c r="R7" s="54">
-        <v>4</v>
-      </c>
-      <c r="S7" s="54">
-        <v>5</v>
-      </c>
-      <c r="T7" s="55">
+      <c r="R7" s="23">
+        <v>4</v>
+      </c>
+      <c r="S7" s="23">
+        <v>5</v>
+      </c>
+      <c r="T7" s="24">
         <f t="shared" ref="T7:T8" si="1">IFERROR(AVERAGE(G7:S7),"-")</f>
         <v>4.3076923076923075</v>
       </c>
-      <c r="U7" s="56" t="str" cm="1">
+      <c r="U7" s="32" t="str" cm="1">
         <f t="array" ref="U7">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="50">
+      <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
       </c>
-      <c r="B8" s="41" t="str">
+      <c r="B8" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C8" s="51" t="str">
+      <c r="C8" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>abril</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="21">
         <v>46142</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="23">
         <v>1067947255</v>
       </c>
-      <c r="G8" s="54">
-        <v>5</v>
-      </c>
-      <c r="H8" s="54">
+      <c r="G8" s="23">
+        <v>5</v>
+      </c>
+      <c r="H8" s="23">
         <v>3</v>
       </c>
-      <c r="I8" s="54">
-        <v>5</v>
-      </c>
-      <c r="J8" s="54">
-        <v>5</v>
-      </c>
-      <c r="K8" s="54">
-        <v>4</v>
-      </c>
-      <c r="L8" s="54">
+      <c r="I8" s="23">
+        <v>5</v>
+      </c>
+      <c r="J8" s="23">
+        <v>5</v>
+      </c>
+      <c r="K8" s="23">
+        <v>4</v>
+      </c>
+      <c r="L8" s="23">
         <v>3</v>
       </c>
-      <c r="M8" s="54">
-        <v>5</v>
-      </c>
-      <c r="N8" s="54">
-        <v>5</v>
-      </c>
-      <c r="O8" s="54">
-        <v>5</v>
-      </c>
-      <c r="P8" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="54">
+      <c r="M8" s="23">
+        <v>5</v>
+      </c>
+      <c r="N8" s="23">
+        <v>5</v>
+      </c>
+      <c r="O8" s="23">
+        <v>5</v>
+      </c>
+      <c r="P8" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="23">
         <v>3</v>
       </c>
-      <c r="R8" s="54">
-        <v>4</v>
-      </c>
-      <c r="S8" s="54">
-        <v>5</v>
-      </c>
-      <c r="T8" s="55">
+      <c r="R8" s="23">
+        <v>4</v>
+      </c>
+      <c r="S8" s="23">
+        <v>5</v>
+      </c>
+      <c r="T8" s="24">
         <f t="shared" si="1"/>
         <v>4.384615384615385</v>
       </c>
-      <c r="U8" s="56" t="str" cm="1">
+      <c r="U8" s="32" t="str" cm="1">
         <f t="array" ref="U8">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="46">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B9" s="40" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C9" s="47" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D9" s="48">
+        <v>46172</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="50">
+        <v>1062539643</v>
+      </c>
+      <c r="G9" s="50">
+        <v>5</v>
+      </c>
+      <c r="H9" s="50">
+        <v>5</v>
+      </c>
+      <c r="I9" s="50">
+        <v>5</v>
+      </c>
+      <c r="J9" s="50">
+        <v>5</v>
+      </c>
+      <c r="K9" s="50">
+        <v>4</v>
+      </c>
+      <c r="L9" s="50">
+        <v>4</v>
+      </c>
+      <c r="M9" s="50">
+        <v>5</v>
+      </c>
+      <c r="N9" s="50">
+        <v>4</v>
+      </c>
+      <c r="O9" s="50">
+        <v>4</v>
+      </c>
+      <c r="P9" s="50">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="50">
+        <v>3</v>
+      </c>
+      <c r="R9" s="50">
+        <v>4</v>
+      </c>
+      <c r="S9" s="50">
+        <v>5</v>
+      </c>
+      <c r="T9" s="51">
+        <f t="shared" ref="T9:T10" si="2">IFERROR(AVERAGE(G9:S9),"-")</f>
+        <v>4.4615384615384617</v>
+      </c>
+      <c r="U9" s="52" t="str" cm="1">
+        <f t="array" ref="U9">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="46">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>5</v>
+      </c>
+      <c r="B10" s="40" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C10" s="47" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>mayo</v>
+      </c>
+      <c r="D10" s="48">
+        <v>46172</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="50">
+        <v>1067947255</v>
+      </c>
+      <c r="G10" s="50">
+        <v>5</v>
+      </c>
+      <c r="H10" s="50">
+        <v>4</v>
+      </c>
+      <c r="I10" s="50">
+        <v>5</v>
+      </c>
+      <c r="J10" s="50">
+        <v>5</v>
+      </c>
+      <c r="K10" s="50">
+        <v>4</v>
+      </c>
+      <c r="L10" s="50">
+        <v>4</v>
+      </c>
+      <c r="M10" s="50">
+        <v>5</v>
+      </c>
+      <c r="N10" s="50">
+        <v>5</v>
+      </c>
+      <c r="O10" s="50">
+        <v>5</v>
+      </c>
+      <c r="P10" s="50">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="50">
+        <v>3</v>
+      </c>
+      <c r="R10" s="50">
+        <v>4</v>
+      </c>
+      <c r="S10" s="50">
+        <v>5</v>
+      </c>
+      <c r="T10" s="51">
+        <f t="shared" si="2"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U10" s="52" t="str" cm="1">
+        <f t="array" ref="U10">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30218"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF750810-FD4A-4BBB-A0B0-D75513CE40C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0355B1-EA86-4A6D-95AA-B6A76239C942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="152">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -694,6 +694,15 @@
   <si>
     <t>Sarah Brieva Rivero</t>
   </si>
+  <si>
+    <t>Juan Pablo Peña Espitia</t>
+  </si>
+  <si>
+    <t>Jose Alejandro Torres</t>
+  </si>
+  <si>
+    <t>Juan Sebastian Vargas Villamizar</t>
+  </si>
 </sst>
 </file>
 
@@ -825,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -942,8 +951,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -953,12 +980,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3081,7 +3102,7 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -3284,7 +3305,7 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -3487,7 +3508,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -3890,7 +3911,7 @@
                         <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>27</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -4058,7 +4079,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -4226,7 +4247,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -4837,7 +4858,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5045,7 +5066,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -5383,7 +5404,7 @@
                         <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>27</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -5551,7 +5572,7 @@
                         <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -5724,7 +5745,7 @@
                         <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -5897,7 +5918,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -6572,7 +6593,7 @@
                   <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6758,7 +6779,7 @@
                         <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -6931,7 +6952,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -7104,7 +7125,7 @@
                         <c:v>21</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -7277,7 +7298,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -7450,7 +7471,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>0</c:v>
+                        <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>0</c:v>
@@ -12156,8 +12177,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O102" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
-  <autoFilter ref="A2:O102" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O116" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
+  <autoFilter ref="A2:O116" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O102">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
@@ -12195,8 +12216,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O56" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A2:O56" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O66" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A2:O66" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O56">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
@@ -12233,8 +12254,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U10" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A2:U10" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U13" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U13" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
@@ -12557,14 +12578,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12594,7 +12615,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12631,7 +12652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12668,7 +12689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12705,7 +12726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12742,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12779,33 +12800,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C7" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A7)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D7" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A7)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A7)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -12816,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
@@ -12853,7 +12874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -12890,7 +12911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -12927,7 +12948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -12964,7 +12985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -13001,7 +13022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -13056,26 +13077,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O116"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" customWidth="1"/>
+    <col min="2" max="2" width="5.6328125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.90625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.36328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.453125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -13092,7 +13113,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13139,7 +13160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13191,7 +13212,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13243,7 +13264,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13295,7 +13316,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13347,7 +13368,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13399,7 +13420,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13451,7 +13472,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13503,7 +13524,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13555,7 +13576,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13607,7 +13628,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13659,7 +13680,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13711,7 +13732,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13763,7 +13784,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13815,7 +13836,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13867,7 +13888,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13919,7 +13940,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13971,7 +13992,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14023,7 +14044,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14075,7 +14096,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14127,7 +14148,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14179,7 +14200,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14231,7 +14252,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14283,7 +14304,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14335,7 +14356,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14387,7 +14408,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14439,7 +14460,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14491,7 +14512,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14543,7 +14564,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14595,7 +14616,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14647,7 +14668,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14699,7 +14720,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14751,7 +14772,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14803,7 +14824,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14855,7 +14876,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14907,7 +14928,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14959,7 +14980,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15011,7 +15032,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15063,7 +15084,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15115,7 +15136,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15167,7 +15188,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15219,7 +15240,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15271,7 +15292,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15323,7 +15344,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15375,7 +15396,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15427,7 +15448,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15479,7 +15500,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15531,7 +15552,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15583,7 +15604,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15635,7 +15656,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15687,7 +15708,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15739,7 +15760,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15791,7 +15812,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15843,7 +15864,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15895,7 +15916,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15947,7 +15968,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15999,7 +16020,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16051,7 +16072,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16103,7 +16124,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16155,7 +16176,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16207,7 +16228,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16259,7 +16280,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16311,7 +16332,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16363,7 +16384,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16415,7 +16436,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16467,7 +16488,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16519,7 +16540,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16571,7 +16592,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16623,7 +16644,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16675,7 +16696,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16727,7 +16748,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16779,7 +16800,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16831,7 +16852,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16883,7 +16904,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16935,7 +16956,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16987,7 +17008,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17039,7 +17060,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17091,7 +17112,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17143,7 +17164,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17195,7 +17216,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17247,7 +17268,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17299,7 +17320,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17351,7 +17372,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17403,7 +17424,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17455,7 +17476,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17507,7 +17528,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17559,7 +17580,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17611,7 +17632,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17663,7 +17684,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17715,7 +17736,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17767,7 +17788,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17819,7 +17840,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17871,7 +17892,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17923,7 +17944,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17975,7 +17996,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18027,7 +18048,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18079,7 +18100,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18131,7 +18152,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18183,7 +18204,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18235,7 +18256,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18287,7 +18308,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18336,6 +18357,734 @@
       </c>
       <c r="O102" s="18" t="str" cm="1">
         <f t="array" ref="O102">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A103" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B103" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C103" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D103" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E103" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="F103" s="46">
+        <v>1068443767</v>
+      </c>
+      <c r="G103" s="47">
+        <v>5</v>
+      </c>
+      <c r="H103" s="47">
+        <v>5</v>
+      </c>
+      <c r="I103" s="47">
+        <v>3</v>
+      </c>
+      <c r="J103" s="47">
+        <v>3</v>
+      </c>
+      <c r="K103" s="47">
+        <v>1</v>
+      </c>
+      <c r="L103" s="47">
+        <v>1</v>
+      </c>
+      <c r="M103" s="47">
+        <v>5</v>
+      </c>
+      <c r="N103" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G103:M103),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O103" s="43" t="str" cm="1">
+        <f t="array" ref="O103">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A104" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B104" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C104" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D104" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E104" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="F104" s="46">
+        <v>1062540875</v>
+      </c>
+      <c r="G104" s="47">
+        <v>5</v>
+      </c>
+      <c r="H104" s="47">
+        <v>5</v>
+      </c>
+      <c r="I104" s="47">
+        <v>4</v>
+      </c>
+      <c r="J104" s="47">
+        <v>4</v>
+      </c>
+      <c r="K104" s="47">
+        <v>3</v>
+      </c>
+      <c r="L104" s="47">
+        <v>3</v>
+      </c>
+      <c r="M104" s="47">
+        <v>5</v>
+      </c>
+      <c r="N104" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G104:M104),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O104" s="43" t="str" cm="1">
+        <f t="array" ref="O104">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A105" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B105" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C105" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D105" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E105" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="F105" s="46">
+        <v>1068442748</v>
+      </c>
+      <c r="G105" s="47">
+        <v>5</v>
+      </c>
+      <c r="H105" s="47">
+        <v>2</v>
+      </c>
+      <c r="I105" s="47">
+        <v>2</v>
+      </c>
+      <c r="J105" s="47">
+        <v>1</v>
+      </c>
+      <c r="K105" s="47">
+        <v>1</v>
+      </c>
+      <c r="L105" s="47">
+        <v>1</v>
+      </c>
+      <c r="M105" s="47">
+        <v>1</v>
+      </c>
+      <c r="N105" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G105:M105),"-")</f>
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O105" s="43" t="str" cm="1">
+        <f t="array" ref="O105">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A106" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B106" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C106" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D106" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E106" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="F106" s="46">
+        <v>1233348383</v>
+      </c>
+      <c r="G106" s="47">
+        <v>5</v>
+      </c>
+      <c r="H106" s="47">
+        <v>5</v>
+      </c>
+      <c r="I106" s="47">
+        <v>4</v>
+      </c>
+      <c r="J106" s="47">
+        <v>4</v>
+      </c>
+      <c r="K106" s="47">
+        <v>3</v>
+      </c>
+      <c r="L106" s="47">
+        <v>3</v>
+      </c>
+      <c r="M106" s="47">
+        <v>5</v>
+      </c>
+      <c r="N106" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G106:M106),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O106" s="43" t="str" cm="1">
+        <f t="array" ref="O106">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A107" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B107" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C107" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D107" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E107" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F107" s="46">
+        <v>1037236492</v>
+      </c>
+      <c r="G107" s="47">
+        <v>5</v>
+      </c>
+      <c r="H107" s="47">
+        <v>5</v>
+      </c>
+      <c r="I107" s="47">
+        <v>5</v>
+      </c>
+      <c r="J107" s="47">
+        <v>4</v>
+      </c>
+      <c r="K107" s="47">
+        <v>4</v>
+      </c>
+      <c r="L107" s="47">
+        <v>4</v>
+      </c>
+      <c r="M107" s="47">
+        <v>5</v>
+      </c>
+      <c r="N107" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G107:M107),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O107" s="43" t="str" cm="1">
+        <f t="array" ref="O107">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B108" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C108" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D108" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E108" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="F108" s="46">
+        <v>1003405136</v>
+      </c>
+      <c r="G108" s="47">
+        <v>5</v>
+      </c>
+      <c r="H108" s="47">
+        <v>5</v>
+      </c>
+      <c r="I108" s="47">
+        <v>5</v>
+      </c>
+      <c r="J108" s="47">
+        <v>4</v>
+      </c>
+      <c r="K108" s="47">
+        <v>4</v>
+      </c>
+      <c r="L108" s="47">
+        <v>3</v>
+      </c>
+      <c r="M108" s="47">
+        <v>5</v>
+      </c>
+      <c r="N108" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G108:M108),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O108" s="43" t="str" cm="1">
+        <f t="array" ref="O108">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B109" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C109" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D109" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E109" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="F109" s="46">
+        <v>1103755851</v>
+      </c>
+      <c r="G109" s="47">
+        <v>5</v>
+      </c>
+      <c r="H109" s="47">
+        <v>5</v>
+      </c>
+      <c r="I109" s="47">
+        <v>5</v>
+      </c>
+      <c r="J109" s="47">
+        <v>4</v>
+      </c>
+      <c r="K109" s="47">
+        <v>4</v>
+      </c>
+      <c r="L109" s="47">
+        <v>4</v>
+      </c>
+      <c r="M109" s="47">
+        <v>5</v>
+      </c>
+      <c r="N109" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G109:M109),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O109" s="43" t="str" cm="1">
+        <f t="array" ref="O109">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A110" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B110" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C110" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D110" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E110" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F110" s="46">
+        <v>50906315</v>
+      </c>
+      <c r="G110" s="47">
+        <v>5</v>
+      </c>
+      <c r="H110" s="47">
+        <v>4</v>
+      </c>
+      <c r="I110" s="47">
+        <v>4</v>
+      </c>
+      <c r="J110" s="47">
+        <v>2</v>
+      </c>
+      <c r="K110" s="47">
+        <v>2</v>
+      </c>
+      <c r="L110" s="47">
+        <v>2</v>
+      </c>
+      <c r="M110" s="47">
+        <v>2</v>
+      </c>
+      <c r="N110" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G110:M110),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O110" s="43" t="str" cm="1">
+        <f t="array" ref="O110">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A111" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B111" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C111" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D111" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E111" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="F111" s="46">
+        <v>1003047136</v>
+      </c>
+      <c r="G111" s="47">
+        <v>5</v>
+      </c>
+      <c r="H111" s="47">
+        <v>5</v>
+      </c>
+      <c r="I111" s="47">
+        <v>4</v>
+      </c>
+      <c r="J111" s="47">
+        <v>3</v>
+      </c>
+      <c r="K111" s="47">
+        <v>3</v>
+      </c>
+      <c r="L111" s="47">
+        <v>3</v>
+      </c>
+      <c r="M111" s="47">
+        <v>1</v>
+      </c>
+      <c r="N111" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G111:M111),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O111" s="43" t="str" cm="1">
+        <f t="array" ref="O111">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A112" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B112" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C112" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D112" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E112" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F112" s="46">
+        <v>1233040347</v>
+      </c>
+      <c r="G112" s="47">
+        <v>5</v>
+      </c>
+      <c r="H112" s="47">
+        <v>4</v>
+      </c>
+      <c r="I112" s="47">
+        <v>4</v>
+      </c>
+      <c r="J112" s="47">
+        <v>4</v>
+      </c>
+      <c r="K112" s="47">
+        <v>3</v>
+      </c>
+      <c r="L112" s="47">
+        <v>3</v>
+      </c>
+      <c r="M112" s="47">
+        <v>3</v>
+      </c>
+      <c r="N112" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G112:M112),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O112" s="43" t="str" cm="1">
+        <f t="array" ref="O112">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A113" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B113" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C113" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D113" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E113" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F113" s="46">
+        <v>1068440514</v>
+      </c>
+      <c r="G113" s="47">
+        <v>5</v>
+      </c>
+      <c r="H113" s="47">
+        <v>3</v>
+      </c>
+      <c r="I113" s="47">
+        <v>3</v>
+      </c>
+      <c r="J113" s="47">
+        <v>2</v>
+      </c>
+      <c r="K113" s="47">
+        <v>2</v>
+      </c>
+      <c r="L113" s="47">
+        <v>2</v>
+      </c>
+      <c r="M113" s="47">
+        <v>3</v>
+      </c>
+      <c r="N113" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G113:M113),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O113" s="43" t="str" cm="1">
+        <f t="array" ref="O113">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A114" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B114" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C114" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D114" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E114" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="F114" s="46">
+        <v>1065443120</v>
+      </c>
+      <c r="G114" s="47">
+        <v>5</v>
+      </c>
+      <c r="H114" s="47">
+        <v>5</v>
+      </c>
+      <c r="I114" s="47">
+        <v>5</v>
+      </c>
+      <c r="J114" s="47">
+        <v>5</v>
+      </c>
+      <c r="K114" s="47">
+        <v>4</v>
+      </c>
+      <c r="L114" s="47">
+        <v>4</v>
+      </c>
+      <c r="M114" s="47">
+        <v>5</v>
+      </c>
+      <c r="N114" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G114:M114),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O114" s="43" t="str" cm="1">
+        <f t="array" ref="O114">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A115" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B115" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C115" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D115" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E115" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="F115" s="46">
+        <v>1001897545</v>
+      </c>
+      <c r="G115" s="47">
+        <v>5</v>
+      </c>
+      <c r="H115" s="47">
+        <v>5</v>
+      </c>
+      <c r="I115" s="47">
+        <v>5</v>
+      </c>
+      <c r="J115" s="47">
+        <v>5</v>
+      </c>
+      <c r="K115" s="47">
+        <v>5</v>
+      </c>
+      <c r="L115" s="47">
+        <v>5</v>
+      </c>
+      <c r="M115" s="47">
+        <v>5</v>
+      </c>
+      <c r="N115" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G115:M115),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O115" s="43" t="str" cm="1">
+        <f t="array" ref="O115">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A116" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B116" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C116" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D116" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E116" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="F116" s="46">
+        <v>1091978602</v>
+      </c>
+      <c r="G116" s="47">
+        <v>5</v>
+      </c>
+      <c r="H116" s="47">
+        <v>4</v>
+      </c>
+      <c r="I116" s="47">
+        <v>3</v>
+      </c>
+      <c r="J116" s="47">
+        <v>2</v>
+      </c>
+      <c r="K116" s="47">
+        <v>2</v>
+      </c>
+      <c r="L116" s="47">
+        <v>2</v>
+      </c>
+      <c r="M116" s="47">
+        <v>3</v>
+      </c>
+      <c r="N116" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G116:M116),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O116" s="43" t="str" cm="1">
+        <f t="array" ref="O116">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -18363,29 +19112,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" customWidth="1"/>
+    <col min="5" max="5" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" customWidth="1"/>
+    <col min="11" max="11" width="7.90625" customWidth="1"/>
+    <col min="12" max="12" width="6.36328125" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" customWidth="1"/>
+    <col min="14" max="14" width="7.08984375" customWidth="1"/>
+    <col min="15" max="15" width="15.6328125" customWidth="1"/>
+    <col min="16" max="16" width="15.36328125" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>58</v>
@@ -18403,7 +19152,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -18450,7 +19199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -18502,7 +19251,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -18554,7 +19303,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18606,7 +19355,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18658,7 +19407,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18710,7 +19459,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18762,7 +19511,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18814,7 +19563,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18866,7 +19615,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -18918,7 +19667,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -18970,7 +19719,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19022,7 +19771,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19074,7 +19823,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19126,7 +19875,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19178,7 +19927,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19230,7 +19979,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19282,7 +20031,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19334,7 +20083,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19386,7 +20135,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19438,7 +20187,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19490,7 +20239,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19542,7 +20291,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19594,7 +20343,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19646,7 +20395,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19698,7 +20447,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19750,7 +20499,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19802,7 +20551,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19854,7 +20603,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19906,7 +20655,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -19958,7 +20707,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20010,7 +20759,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20062,7 +20811,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20114,7 +20863,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20166,1095 +20915,1615 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="41">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B36" s="42" t="str">
+      <c r="B36" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C36" s="42" t="str">
+      <c r="C36" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="3">
         <v>46172</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="1">
         <v>8203609</v>
       </c>
-      <c r="G36" s="41">
-        <v>5</v>
-      </c>
-      <c r="H36" s="41">
-        <v>4</v>
-      </c>
-      <c r="I36" s="41">
-        <v>5</v>
-      </c>
-      <c r="J36" s="41">
-        <v>3</v>
-      </c>
-      <c r="K36" s="41">
-        <v>4</v>
-      </c>
-      <c r="L36" s="41">
-        <v>5</v>
-      </c>
-      <c r="M36" s="41">
+      <c r="G36" s="1">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1">
+        <v>4</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1">
+        <v>4</v>
+      </c>
+      <c r="L36" s="1">
+        <v>5</v>
+      </c>
+      <c r="M36" s="1">
         <v>4</v>
       </c>
       <c r="N36" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G36:M36),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O36" s="43" t="str" cm="1">
+      <c r="O36" s="18" t="str" cm="1">
         <f t="array" ref="O36">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="41">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B37" s="42" t="str">
+      <c r="B37" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C37" s="42" t="str">
+      <c r="C37" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="3">
         <v>46172</v>
       </c>
-      <c r="E37" s="45" t="s">
+      <c r="E37" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="1">
         <v>1001481017</v>
       </c>
-      <c r="G37" s="41">
-        <v>4</v>
-      </c>
-      <c r="H37" s="41">
-        <v>3</v>
-      </c>
-      <c r="I37" s="41">
+      <c r="G37" s="1">
+        <v>4</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1">
         <v>2</v>
       </c>
-      <c r="J37" s="41">
-        <v>3</v>
-      </c>
-      <c r="K37" s="41">
-        <v>4</v>
-      </c>
-      <c r="L37" s="41">
-        <v>4</v>
-      </c>
-      <c r="M37" s="41">
+      <c r="J37" s="1">
+        <v>3</v>
+      </c>
+      <c r="K37" s="1">
+        <v>4</v>
+      </c>
+      <c r="L37" s="1">
+        <v>4</v>
+      </c>
+      <c r="M37" s="1">
         <v>2</v>
       </c>
       <c r="N37" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G37:M37),"-")</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O37" s="43" t="str" cm="1">
+      <c r="O37" s="18" t="str" cm="1">
         <f t="array" ref="O37">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="41">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B38" s="42" t="str">
+      <c r="B38" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C38" s="42" t="str">
+      <c r="C38" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="3">
         <v>46172</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F38" s="41">
+      <c r="F38" s="1">
         <v>1003027198</v>
       </c>
-      <c r="G38" s="41">
-        <v>5</v>
-      </c>
-      <c r="H38" s="41">
-        <v>4</v>
-      </c>
-      <c r="I38" s="41">
-        <v>3</v>
-      </c>
-      <c r="J38" s="41">
-        <v>5</v>
-      </c>
-      <c r="K38" s="41">
-        <v>4</v>
-      </c>
-      <c r="L38" s="41">
-        <v>5</v>
-      </c>
-      <c r="M38" s="41">
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1">
+        <v>4</v>
+      </c>
+      <c r="I38" s="1">
+        <v>3</v>
+      </c>
+      <c r="J38" s="1">
+        <v>5</v>
+      </c>
+      <c r="K38" s="1">
+        <v>4</v>
+      </c>
+      <c r="L38" s="1">
+        <v>5</v>
+      </c>
+      <c r="M38" s="1">
         <v>2</v>
       </c>
       <c r="N38" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G38:M38),"-")</f>
         <v>4</v>
       </c>
-      <c r="O38" s="43" t="str" cm="1">
+      <c r="O38" s="18" t="str" cm="1">
         <f t="array" ref="O38">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="41">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B39" s="42" t="str">
+      <c r="B39" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C39" s="42" t="str">
+      <c r="C39" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D39" s="44">
+      <c r="D39" s="3">
         <v>46172</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="1">
         <v>1003435656</v>
       </c>
-      <c r="G39" s="41">
-        <v>4</v>
-      </c>
-      <c r="H39" s="41">
-        <v>4</v>
-      </c>
-      <c r="I39" s="41">
-        <v>3</v>
-      </c>
-      <c r="J39" s="41">
-        <v>3</v>
-      </c>
-      <c r="K39" s="41">
-        <v>3</v>
-      </c>
-      <c r="L39" s="41">
-        <v>5</v>
-      </c>
-      <c r="M39" s="41">
+      <c r="G39" s="1">
+        <v>4</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39" s="1">
+        <v>3</v>
+      </c>
+      <c r="J39" s="1">
+        <v>3</v>
+      </c>
+      <c r="K39" s="1">
+        <v>3</v>
+      </c>
+      <c r="L39" s="1">
+        <v>5</v>
+      </c>
+      <c r="M39" s="1">
         <v>2</v>
       </c>
       <c r="N39" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G39:M39),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O39" s="43" t="str" cm="1">
+      <c r="O39" s="18" t="str" cm="1">
         <f t="array" ref="O39">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="41">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B40" s="42" t="str">
+      <c r="B40" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C40" s="42" t="str">
+      <c r="C40" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D40" s="44">
+      <c r="D40" s="3">
         <v>46172</v>
       </c>
-      <c r="E40" s="45" t="s">
+      <c r="E40" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="41">
+      <c r="F40" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G40" s="41">
-        <v>5</v>
-      </c>
-      <c r="H40" s="41">
-        <v>4</v>
-      </c>
-      <c r="I40" s="41">
-        <v>5</v>
-      </c>
-      <c r="J40" s="41">
-        <v>4</v>
-      </c>
-      <c r="K40" s="41">
-        <v>4</v>
-      </c>
-      <c r="L40" s="41">
-        <v>5</v>
-      </c>
-      <c r="M40" s="41">
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>4</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" s="1">
+        <v>4</v>
+      </c>
+      <c r="L40" s="1">
+        <v>5</v>
+      </c>
+      <c r="M40" s="1">
         <v>4</v>
       </c>
       <c r="N40" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G40:M40),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O40" s="43" t="str" cm="1">
+      <c r="O40" s="18" t="str" cm="1">
         <f t="array" ref="O40">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="41">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B41" s="42" t="str">
+      <c r="B41" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C41" s="42" t="str">
+      <c r="C41" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D41" s="44">
+      <c r="D41" s="3">
         <v>46172</v>
       </c>
-      <c r="E41" s="45" t="s">
+      <c r="E41" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="41">
+      <c r="F41" s="1">
         <v>1029722943</v>
       </c>
-      <c r="G41" s="41">
-        <v>5</v>
-      </c>
-      <c r="H41" s="41">
-        <v>4</v>
-      </c>
-      <c r="I41" s="41">
-        <v>4</v>
-      </c>
-      <c r="J41" s="41">
-        <v>4</v>
-      </c>
-      <c r="K41" s="41">
-        <v>4</v>
-      </c>
-      <c r="L41" s="41">
-        <v>5</v>
-      </c>
-      <c r="M41" s="41">
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>4</v>
+      </c>
+      <c r="I41" s="1">
+        <v>4</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1">
+        <v>4</v>
+      </c>
+      <c r="L41" s="1">
+        <v>5</v>
+      </c>
+      <c r="M41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G41:M41),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O41" s="43" t="str" cm="1">
+      <c r="O41" s="18" t="str" cm="1">
         <f t="array" ref="O41">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="41">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B42" s="42" t="str">
+      <c r="B42" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C42" s="42" t="str">
+      <c r="C42" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D42" s="44">
+      <c r="D42" s="3">
         <v>46172</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F42" s="41">
+      <c r="F42" s="1">
         <v>1062444411</v>
       </c>
-      <c r="G42" s="41">
-        <v>5</v>
-      </c>
-      <c r="H42" s="41">
-        <v>5</v>
-      </c>
-      <c r="I42" s="41">
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>5</v>
+      </c>
+      <c r="I42" s="1">
         <v>2</v>
       </c>
-      <c r="J42" s="41">
-        <v>4</v>
-      </c>
-      <c r="K42" s="41">
-        <v>4</v>
-      </c>
-      <c r="L42" s="41">
-        <v>5</v>
-      </c>
-      <c r="M42" s="41">
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="1">
+        <v>4</v>
+      </c>
+      <c r="L42" s="1">
+        <v>5</v>
+      </c>
+      <c r="M42" s="1">
         <v>2</v>
       </c>
       <c r="N42" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G42:M42),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O42" s="43" t="str" cm="1">
+      <c r="O42" s="18" t="str" cm="1">
         <f t="array" ref="O42">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="41">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B43" s="42" t="str">
+      <c r="B43" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C43" s="42" t="str">
+      <c r="C43" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D43" s="44">
+      <c r="D43" s="3">
         <v>46172</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G43" s="41">
-        <v>4</v>
-      </c>
-      <c r="H43" s="41">
-        <v>4</v>
-      </c>
-      <c r="I43" s="41">
+      <c r="G43" s="1">
+        <v>4</v>
+      </c>
+      <c r="H43" s="1">
+        <v>4</v>
+      </c>
+      <c r="I43" s="1">
         <v>2</v>
       </c>
-      <c r="J43" s="41">
-        <v>3</v>
-      </c>
-      <c r="K43" s="41">
-        <v>3</v>
-      </c>
-      <c r="L43" s="41">
-        <v>3</v>
-      </c>
-      <c r="M43" s="41">
+      <c r="J43" s="1">
+        <v>3</v>
+      </c>
+      <c r="K43" s="1">
+        <v>3</v>
+      </c>
+      <c r="L43" s="1">
+        <v>3</v>
+      </c>
+      <c r="M43" s="1">
         <v>2</v>
       </c>
       <c r="N43" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G43:M43),"-")</f>
         <v>3</v>
       </c>
-      <c r="O43" s="43" t="str" cm="1">
+      <c r="O43" s="18" t="str" cm="1">
         <f t="array" ref="O43">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="41">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B44" s="42" t="str">
+      <c r="B44" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C44" s="42" t="str">
+      <c r="C44" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="3">
         <v>46172</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="41">
+      <c r="F44" s="1">
         <v>1062980565</v>
       </c>
-      <c r="G44" s="41">
-        <v>5</v>
-      </c>
-      <c r="H44" s="41">
-        <v>5</v>
-      </c>
-      <c r="I44" s="41">
-        <v>4</v>
-      </c>
-      <c r="J44" s="41">
-        <v>5</v>
-      </c>
-      <c r="K44" s="41">
-        <v>4</v>
-      </c>
-      <c r="L44" s="41">
-        <v>5</v>
-      </c>
-      <c r="M44" s="41">
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>5</v>
+      </c>
+      <c r="I44" s="1">
+        <v>4</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5</v>
+      </c>
+      <c r="K44" s="1">
+        <v>4</v>
+      </c>
+      <c r="L44" s="1">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1">
         <v>5</v>
       </c>
       <c r="N44" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G44:M44),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O44" s="43" t="str" cm="1">
+      <c r="O44" s="18" t="str" cm="1">
         <f t="array" ref="O44">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="41">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B45" s="42" t="str">
+      <c r="B45" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C45" s="42" t="str">
+      <c r="C45" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D45" s="44">
+      <c r="D45" s="3">
         <v>46172</v>
       </c>
-      <c r="E45" s="45" t="s">
+      <c r="E45" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="1">
         <v>1062981643</v>
       </c>
-      <c r="G45" s="41">
-        <v>4</v>
-      </c>
-      <c r="H45" s="41">
-        <v>5</v>
-      </c>
-      <c r="I45" s="41">
+      <c r="G45" s="1">
+        <v>4</v>
+      </c>
+      <c r="H45" s="1">
+        <v>5</v>
+      </c>
+      <c r="I45" s="1">
         <v>2</v>
       </c>
-      <c r="J45" s="41">
-        <v>3</v>
-      </c>
-      <c r="K45" s="41">
-        <v>3</v>
-      </c>
-      <c r="L45" s="41">
-        <v>4</v>
-      </c>
-      <c r="M45" s="41">
+      <c r="J45" s="1">
+        <v>3</v>
+      </c>
+      <c r="K45" s="1">
+        <v>3</v>
+      </c>
+      <c r="L45" s="1">
+        <v>4</v>
+      </c>
+      <c r="M45" s="1">
         <v>3</v>
       </c>
       <c r="N45" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G45:M45),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O45" s="43" t="str" cm="1">
+      <c r="O45" s="18" t="str" cm="1">
         <f t="array" ref="O45">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="41">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B46" s="42" t="str">
+      <c r="B46" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C46" s="42" t="str">
+      <c r="C46" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D46" s="44">
+      <c r="D46" s="3">
         <v>46172</v>
       </c>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F46" s="41">
+      <c r="F46" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G46" s="41">
-        <v>4</v>
-      </c>
-      <c r="H46" s="41">
-        <v>4</v>
-      </c>
-      <c r="I46" s="41">
-        <v>4</v>
-      </c>
-      <c r="J46" s="41">
-        <v>4</v>
-      </c>
-      <c r="K46" s="41">
-        <v>4</v>
-      </c>
-      <c r="L46" s="41">
-        <v>5</v>
-      </c>
-      <c r="M46" s="41">
+      <c r="G46" s="1">
+        <v>4</v>
+      </c>
+      <c r="H46" s="1">
+        <v>4</v>
+      </c>
+      <c r="I46" s="1">
+        <v>4</v>
+      </c>
+      <c r="J46" s="1">
+        <v>4</v>
+      </c>
+      <c r="K46" s="1">
+        <v>4</v>
+      </c>
+      <c r="L46" s="1">
+        <v>5</v>
+      </c>
+      <c r="M46" s="1">
         <v>1</v>
       </c>
       <c r="N46" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G46:M46),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O46" s="43" t="str" cm="1">
+      <c r="O46" s="18" t="str" cm="1">
         <f t="array" ref="O46">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="41">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B47" s="42" t="str">
+      <c r="B47" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C47" s="42" t="str">
+      <c r="C47" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D47" s="44">
+      <c r="D47" s="3">
         <v>46172</v>
       </c>
-      <c r="E47" s="45" t="s">
+      <c r="E47" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="41">
+      <c r="F47" s="1">
         <v>1067945529</v>
       </c>
-      <c r="G47" s="41">
-        <v>4</v>
-      </c>
-      <c r="H47" s="41">
-        <v>4</v>
-      </c>
-      <c r="I47" s="41">
-        <v>4</v>
-      </c>
-      <c r="J47" s="41">
-        <v>4</v>
-      </c>
-      <c r="K47" s="41">
-        <v>4</v>
-      </c>
-      <c r="L47" s="41">
-        <v>4</v>
-      </c>
-      <c r="M47" s="41">
+      <c r="G47" s="1">
+        <v>4</v>
+      </c>
+      <c r="H47" s="1">
+        <v>4</v>
+      </c>
+      <c r="I47" s="1">
+        <v>4</v>
+      </c>
+      <c r="J47" s="1">
+        <v>4</v>
+      </c>
+      <c r="K47" s="1">
+        <v>4</v>
+      </c>
+      <c r="L47" s="1">
+        <v>4</v>
+      </c>
+      <c r="M47" s="1">
         <v>1</v>
       </c>
       <c r="N47" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G47:M47),"-")</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O47" s="43" t="str" cm="1">
+      <c r="O47" s="18" t="str" cm="1">
         <f t="array" ref="O47">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="41">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B48" s="42" t="str">
+      <c r="B48" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C48" s="42" t="str">
+      <c r="C48" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D48" s="44">
+      <c r="D48" s="3">
         <v>46172</v>
       </c>
-      <c r="E48" s="45" t="s">
+      <c r="E48" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F48" s="1">
         <v>1067955099</v>
       </c>
-      <c r="G48" s="41">
-        <v>5</v>
-      </c>
-      <c r="H48" s="41">
-        <v>5</v>
-      </c>
-      <c r="I48" s="41">
-        <v>3</v>
-      </c>
-      <c r="J48" s="41">
-        <v>4</v>
-      </c>
-      <c r="K48" s="41">
-        <v>4</v>
-      </c>
-      <c r="L48" s="41">
-        <v>5</v>
-      </c>
-      <c r="M48" s="41">
+      <c r="G48" s="1">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1">
+        <v>5</v>
+      </c>
+      <c r="I48" s="1">
+        <v>3</v>
+      </c>
+      <c r="J48" s="1">
+        <v>4</v>
+      </c>
+      <c r="K48" s="1">
+        <v>4</v>
+      </c>
+      <c r="L48" s="1">
+        <v>5</v>
+      </c>
+      <c r="M48" s="1">
         <v>3</v>
       </c>
       <c r="N48" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G48:M48),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O48" s="43" t="str" cm="1">
+      <c r="O48" s="18" t="str" cm="1">
         <f t="array" ref="O48">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="41">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B49" s="42" t="str">
+      <c r="B49" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C49" s="42" t="str">
+      <c r="C49" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D49" s="44">
+      <c r="D49" s="3">
         <v>46172</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F49" s="41">
+      <c r="F49" s="1">
         <v>1067956606</v>
       </c>
-      <c r="G49" s="41">
+      <c r="G49" s="1">
         <v>0</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="1">
         <v>0</v>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="1">
         <v>0</v>
       </c>
-      <c r="J49" s="41">
+      <c r="J49" s="1">
         <v>0</v>
       </c>
-      <c r="K49" s="41">
+      <c r="K49" s="1">
         <v>0</v>
       </c>
-      <c r="L49" s="41">
+      <c r="L49" s="1">
         <v>0</v>
       </c>
-      <c r="M49" s="41">
+      <c r="M49" s="1">
         <v>0</v>
       </c>
       <c r="N49" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G49:M49),"-")</f>
         <v>0</v>
       </c>
-      <c r="O49" s="43" t="str" cm="1">
+      <c r="O49" s="18" t="str" cm="1">
         <f t="array" ref="O49">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="41">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B50" s="42" t="str">
+      <c r="B50" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C50" s="42" t="str">
+      <c r="C50" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D50" s="44">
+      <c r="D50" s="3">
         <v>46172</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="F50" s="41">
+      <c r="F50" s="1">
         <v>1068439668</v>
       </c>
-      <c r="G50" s="41">
-        <v>5</v>
-      </c>
-      <c r="H50" s="41">
-        <v>5</v>
-      </c>
-      <c r="I50" s="41">
-        <v>4</v>
-      </c>
-      <c r="J50" s="41">
-        <v>5</v>
-      </c>
-      <c r="K50" s="41">
-        <v>4</v>
-      </c>
-      <c r="L50" s="41">
-        <v>5</v>
-      </c>
-      <c r="M50" s="41">
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1">
+        <v>5</v>
+      </c>
+      <c r="I50" s="1">
+        <v>4</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="1">
+        <v>4</v>
+      </c>
+      <c r="L50" s="1">
+        <v>5</v>
+      </c>
+      <c r="M50" s="1">
         <v>5</v>
       </c>
       <c r="N50" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G50:M50),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O50" s="43" t="str" cm="1">
+      <c r="O50" s="18" t="str" cm="1">
         <f t="array" ref="O50">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="41">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B51" s="42" t="str">
+      <c r="B51" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C51" s="42" t="str">
+      <c r="C51" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D51" s="44">
+      <c r="D51" s="3">
         <v>46172</v>
       </c>
-      <c r="E51" s="45" t="s">
+      <c r="E51" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F51" s="41">
+      <c r="F51" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G51" s="41">
-        <v>5</v>
-      </c>
-      <c r="H51" s="41">
-        <v>4</v>
-      </c>
-      <c r="I51" s="41">
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4</v>
+      </c>
+      <c r="I51" s="1">
         <v>2</v>
       </c>
-      <c r="J51" s="41">
-        <v>4</v>
-      </c>
-      <c r="K51" s="41">
-        <v>3</v>
-      </c>
-      <c r="L51" s="41">
-        <v>5</v>
-      </c>
-      <c r="M51" s="41">
+      <c r="J51" s="1">
+        <v>4</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3</v>
+      </c>
+      <c r="L51" s="1">
+        <v>5</v>
+      </c>
+      <c r="M51" s="1">
         <v>2</v>
       </c>
       <c r="N51" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G51:M51),"-")</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O51" s="43" t="str" cm="1">
+      <c r="O51" s="18" t="str" cm="1">
         <f t="array" ref="O51">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="41">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B52" s="42" t="str">
+      <c r="B52" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C52" s="42" t="str">
+      <c r="C52" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D52" s="44">
+      <c r="D52" s="3">
         <v>46172</v>
       </c>
-      <c r="E52" s="45" t="s">
+      <c r="E52" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="1">
         <v>1137975856</v>
       </c>
-      <c r="G52" s="41">
-        <v>4</v>
-      </c>
-      <c r="H52" s="41">
-        <v>4</v>
-      </c>
-      <c r="I52" s="41">
-        <v>4</v>
-      </c>
-      <c r="J52" s="41">
-        <v>5</v>
-      </c>
-      <c r="K52" s="41">
-        <v>4</v>
-      </c>
-      <c r="L52" s="41">
-        <v>5</v>
-      </c>
-      <c r="M52" s="41">
+      <c r="G52" s="1">
+        <v>4</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1">
+        <v>4</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
+        <v>4</v>
+      </c>
+      <c r="L52" s="1">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1">
         <v>4</v>
       </c>
       <c r="N52" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G52:M52),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O52" s="43" t="str" cm="1">
+      <c r="O52" s="18" t="str" cm="1">
         <f t="array" ref="O52">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="41">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B53" s="42" t="str">
+      <c r="B53" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C53" s="42" t="str">
+      <c r="C53" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D53" s="44">
+      <c r="D53" s="3">
         <v>46172</v>
       </c>
-      <c r="E53" s="45" t="s">
+      <c r="E53" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F53" s="41">
+      <c r="F53" s="1">
         <v>1138032406</v>
       </c>
-      <c r="G53" s="41">
-        <v>5</v>
-      </c>
-      <c r="H53" s="41">
-        <v>5</v>
-      </c>
-      <c r="I53" s="41">
-        <v>3</v>
-      </c>
-      <c r="J53" s="41">
-        <v>4</v>
-      </c>
-      <c r="K53" s="41">
-        <v>3</v>
-      </c>
-      <c r="L53" s="41">
-        <v>5</v>
-      </c>
-      <c r="M53" s="41">
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1">
+        <v>5</v>
+      </c>
+      <c r="I53" s="1">
+        <v>3</v>
+      </c>
+      <c r="J53" s="1">
+        <v>4</v>
+      </c>
+      <c r="K53" s="1">
+        <v>3</v>
+      </c>
+      <c r="L53" s="1">
+        <v>5</v>
+      </c>
+      <c r="M53" s="1">
         <v>2</v>
       </c>
       <c r="N53" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G53:M53),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O53" s="43" t="str" cm="1">
+      <c r="O53" s="18" t="str" cm="1">
         <f t="array" ref="O53">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="41">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B54" s="42" t="str">
+      <c r="B54" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C54" s="42" t="str">
+      <c r="C54" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D54" s="44">
+      <c r="D54" s="3">
         <v>46172</v>
       </c>
-      <c r="E54" s="45" t="s">
+      <c r="E54" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F54" s="41">
+      <c r="F54" s="1">
         <v>1138032417</v>
       </c>
-      <c r="G54" s="41">
-        <v>5</v>
-      </c>
-      <c r="H54" s="41">
-        <v>4</v>
-      </c>
-      <c r="I54" s="41">
-        <v>4</v>
-      </c>
-      <c r="J54" s="41">
-        <v>4</v>
-      </c>
-      <c r="K54" s="41">
-        <v>3</v>
-      </c>
-      <c r="L54" s="41">
-        <v>5</v>
-      </c>
-      <c r="M54" s="41">
+      <c r="G54" s="1">
+        <v>5</v>
+      </c>
+      <c r="H54" s="1">
+        <v>4</v>
+      </c>
+      <c r="I54" s="1">
+        <v>4</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4</v>
+      </c>
+      <c r="K54" s="1">
+        <v>3</v>
+      </c>
+      <c r="L54" s="1">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1">
         <v>4</v>
       </c>
       <c r="N54" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G54:M54),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O54" s="43" t="str" cm="1">
+      <c r="O54" s="18" t="str" cm="1">
         <f t="array" ref="O54">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="41">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B55" s="42" t="str">
+      <c r="B55" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C55" s="42" t="str">
+      <c r="C55" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D55" s="44">
+      <c r="D55" s="3">
         <v>46172</v>
       </c>
-      <c r="E55" s="45" t="s">
+      <c r="E55" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="1">
         <v>1138032549</v>
       </c>
-      <c r="G55" s="41">
-        <v>5</v>
-      </c>
-      <c r="H55" s="41">
-        <v>5</v>
-      </c>
-      <c r="I55" s="41">
-        <v>3</v>
-      </c>
-      <c r="J55" s="41">
-        <v>4</v>
-      </c>
-      <c r="K55" s="41">
-        <v>5</v>
-      </c>
-      <c r="L55" s="41">
-        <v>5</v>
-      </c>
-      <c r="M55" s="41">
+      <c r="G55" s="1">
+        <v>5</v>
+      </c>
+      <c r="H55" s="1">
+        <v>5</v>
+      </c>
+      <c r="I55" s="1">
+        <v>3</v>
+      </c>
+      <c r="J55" s="1">
+        <v>4</v>
+      </c>
+      <c r="K55" s="1">
+        <v>5</v>
+      </c>
+      <c r="L55" s="1">
+        <v>5</v>
+      </c>
+      <c r="M55" s="1">
         <v>5</v>
       </c>
       <c r="N55" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G55:M55),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O55" s="43" t="str" cm="1">
+      <c r="O55" s="18" t="str" cm="1">
         <f t="array" ref="O55">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="41">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B56" s="42" t="str">
+      <c r="B56" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C56" s="42" t="str">
+      <c r="C56" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D56" s="44">
+      <c r="D56" s="3">
         <v>46172</v>
       </c>
-      <c r="E56" s="45" t="s">
+      <c r="E56" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="41">
+      <c r="F56" s="1">
         <v>1140444971</v>
       </c>
-      <c r="G56" s="41">
-        <v>5</v>
-      </c>
-      <c r="H56" s="41">
-        <v>5</v>
-      </c>
-      <c r="I56" s="41">
-        <v>4</v>
-      </c>
-      <c r="J56" s="41">
-        <v>5</v>
-      </c>
-      <c r="K56" s="41">
-        <v>3</v>
-      </c>
-      <c r="L56" s="41">
-        <v>5</v>
-      </c>
-      <c r="M56" s="41">
+      <c r="G56" s="1">
+        <v>5</v>
+      </c>
+      <c r="H56" s="1">
+        <v>5</v>
+      </c>
+      <c r="I56" s="1">
+        <v>4</v>
+      </c>
+      <c r="J56" s="1">
+        <v>5</v>
+      </c>
+      <c r="K56" s="1">
+        <v>3</v>
+      </c>
+      <c r="L56" s="1">
+        <v>5</v>
+      </c>
+      <c r="M56" s="1">
         <v>2</v>
       </c>
       <c r="N56" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G56:M56),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O56" s="43" t="str" cm="1">
+      <c r="O56" s="18" t="str" cm="1">
         <f t="array" ref="O56">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B57" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C57" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D57" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57" s="47">
+        <v>1062981643</v>
+      </c>
+      <c r="G57" s="47">
+        <v>5</v>
+      </c>
+      <c r="H57" s="47">
+        <v>5</v>
+      </c>
+      <c r="I57" s="47">
+        <v>2</v>
+      </c>
+      <c r="J57" s="47">
+        <v>3</v>
+      </c>
+      <c r="K57" s="47">
+        <v>3</v>
+      </c>
+      <c r="L57" s="47">
+        <v>5</v>
+      </c>
+      <c r="M57" s="47">
+        <v>3</v>
+      </c>
+      <c r="N57" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G57:M57),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O57" s="49" t="str" cm="1">
+        <f t="array" ref="O57">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B58" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C58" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D58" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F58" s="47">
+        <v>1027663882</v>
+      </c>
+      <c r="G58" s="47">
+        <v>5</v>
+      </c>
+      <c r="H58" s="47">
+        <v>5</v>
+      </c>
+      <c r="I58" s="47">
+        <v>5</v>
+      </c>
+      <c r="J58" s="47">
+        <v>4</v>
+      </c>
+      <c r="K58" s="47">
+        <v>4</v>
+      </c>
+      <c r="L58" s="47">
+        <v>5</v>
+      </c>
+      <c r="M58" s="47">
+        <v>5</v>
+      </c>
+      <c r="N58" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G58:M58),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O58" s="49" t="str" cm="1">
+        <f t="array" ref="O58">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B59" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C59" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D59" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="F59" s="47">
+        <v>1138032549</v>
+      </c>
+      <c r="G59" s="47">
+        <v>5</v>
+      </c>
+      <c r="H59" s="47">
+        <v>5</v>
+      </c>
+      <c r="I59" s="47">
+        <v>5</v>
+      </c>
+      <c r="J59" s="47">
+        <v>4</v>
+      </c>
+      <c r="K59" s="47">
+        <v>4</v>
+      </c>
+      <c r="L59" s="47">
+        <v>5</v>
+      </c>
+      <c r="M59" s="47">
+        <v>5</v>
+      </c>
+      <c r="N59" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G59:M59),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O59" s="49" t="str" cm="1">
+        <f t="array" ref="O59">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A60" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B60" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C60" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D60" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="F60" s="47">
+        <v>1067859838</v>
+      </c>
+      <c r="G60" s="47">
+        <v>4</v>
+      </c>
+      <c r="H60" s="47">
+        <v>4</v>
+      </c>
+      <c r="I60" s="47">
+        <v>4</v>
+      </c>
+      <c r="J60" s="47">
+        <v>4</v>
+      </c>
+      <c r="K60" s="47">
+        <v>4</v>
+      </c>
+      <c r="L60" s="47">
+        <v>5</v>
+      </c>
+      <c r="M60" s="47">
+        <v>1</v>
+      </c>
+      <c r="N60" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G60:M60),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O60" s="49" t="str" cm="1">
+        <f t="array" ref="O60">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B61" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C61" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D61" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" s="47">
+        <v>1073817245</v>
+      </c>
+      <c r="G61" s="47">
+        <v>5</v>
+      </c>
+      <c r="H61" s="47">
+        <v>5</v>
+      </c>
+      <c r="I61" s="47">
+        <v>3</v>
+      </c>
+      <c r="J61" s="47">
+        <v>4</v>
+      </c>
+      <c r="K61" s="47">
+        <v>3</v>
+      </c>
+      <c r="L61" s="47">
+        <v>5</v>
+      </c>
+      <c r="M61" s="47">
+        <v>2</v>
+      </c>
+      <c r="N61" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G61:M61),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O61" s="49" t="str" cm="1">
+        <f t="array" ref="O61">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B62" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C62" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D62" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E62" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="47">
+        <v>1140444971</v>
+      </c>
+      <c r="G62" s="47">
+        <v>5</v>
+      </c>
+      <c r="H62" s="47">
+        <v>5</v>
+      </c>
+      <c r="I62" s="47">
+        <v>5</v>
+      </c>
+      <c r="J62" s="47">
+        <v>5</v>
+      </c>
+      <c r="K62" s="47">
+        <v>4</v>
+      </c>
+      <c r="L62" s="47">
+        <v>5</v>
+      </c>
+      <c r="M62" s="47">
+        <v>4</v>
+      </c>
+      <c r="N62" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G62:M62),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O62" s="49" t="str" cm="1">
+        <f t="array" ref="O62">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B63" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C63" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D63" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F63" s="47">
+        <v>1067945529</v>
+      </c>
+      <c r="G63" s="47">
+        <v>4</v>
+      </c>
+      <c r="H63" s="47">
+        <v>4</v>
+      </c>
+      <c r="I63" s="47">
+        <v>3</v>
+      </c>
+      <c r="J63" s="47">
+        <v>4</v>
+      </c>
+      <c r="K63" s="47">
+        <v>4</v>
+      </c>
+      <c r="L63" s="47">
+        <v>4</v>
+      </c>
+      <c r="M63" s="47">
+        <v>1</v>
+      </c>
+      <c r="N63" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G63:M63),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O63" s="49" t="str" cm="1">
+        <f t="array" ref="O63">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B64" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C64" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D64" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F64" s="47">
+        <v>1137975856</v>
+      </c>
+      <c r="G64" s="47">
+        <v>4</v>
+      </c>
+      <c r="H64" s="47">
+        <v>4</v>
+      </c>
+      <c r="I64" s="47">
+        <v>4</v>
+      </c>
+      <c r="J64" s="47">
+        <v>4</v>
+      </c>
+      <c r="K64" s="47">
+        <v>4</v>
+      </c>
+      <c r="L64" s="47">
+        <v>5</v>
+      </c>
+      <c r="M64" s="47">
+        <v>4</v>
+      </c>
+      <c r="N64" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G64:M64),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O64" s="49" t="str" cm="1">
+        <f t="array" ref="O64">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B65" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C65" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D65" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E65" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="F65" s="47">
+        <v>8203609</v>
+      </c>
+      <c r="G65" s="47">
+        <v>5</v>
+      </c>
+      <c r="H65" s="47">
+        <v>4</v>
+      </c>
+      <c r="I65" s="47">
+        <v>5</v>
+      </c>
+      <c r="J65" s="47">
+        <v>3</v>
+      </c>
+      <c r="K65" s="47">
+        <v>4</v>
+      </c>
+      <c r="L65" s="47">
+        <v>5</v>
+      </c>
+      <c r="M65" s="47">
+        <v>4</v>
+      </c>
+      <c r="N65" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G65:M65),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O65" s="49" t="str" cm="1">
+        <f t="array" ref="O65">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" s="47">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B66" s="48" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C66" s="48" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D66" s="44">
+        <v>46199</v>
+      </c>
+      <c r="E66" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F66" s="47">
+        <v>1062438398</v>
+      </c>
+      <c r="G66" s="47">
+        <v>4</v>
+      </c>
+      <c r="H66" s="47">
+        <v>4</v>
+      </c>
+      <c r="I66" s="47">
+        <v>3</v>
+      </c>
+      <c r="J66" s="47">
+        <v>3</v>
+      </c>
+      <c r="K66" s="47">
+        <v>2</v>
+      </c>
+      <c r="L66" s="47">
+        <v>4</v>
+      </c>
+      <c r="M66" s="47">
+        <v>2</v>
+      </c>
+      <c r="N66" s="42">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G66:M66),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O66" s="49" t="str" cm="1">
+        <f t="array" ref="O66">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -21282,32 +22551,32 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.36328125" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.90625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.36328125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.90625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.54296875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.453125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.36328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="18.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="E1" s="28" t="s">
         <v>59</v>
       </c>
@@ -21328,7 +22597,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="42" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -21393,7 +22662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -21463,7 +22732,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -21533,7 +22802,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -21603,7 +22872,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -21673,7 +22942,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -21743,7 +23012,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -21813,143 +23082,353 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="46">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B9" s="40" t="str">
+      <c r="B9" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C9" s="47" t="str">
+      <c r="C9" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="21">
         <v>46172</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="23">
         <v>1062539643</v>
       </c>
-      <c r="G9" s="50">
-        <v>5</v>
-      </c>
-      <c r="H9" s="50">
-        <v>5</v>
-      </c>
-      <c r="I9" s="50">
-        <v>5</v>
-      </c>
-      <c r="J9" s="50">
-        <v>5</v>
-      </c>
-      <c r="K9" s="50">
-        <v>4</v>
-      </c>
-      <c r="L9" s="50">
-        <v>4</v>
-      </c>
-      <c r="M9" s="50">
-        <v>5</v>
-      </c>
-      <c r="N9" s="50">
-        <v>4</v>
-      </c>
-      <c r="O9" s="50">
-        <v>4</v>
-      </c>
-      <c r="P9" s="50">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="50">
-        <v>3</v>
-      </c>
-      <c r="R9" s="50">
-        <v>4</v>
-      </c>
-      <c r="S9" s="50">
-        <v>5</v>
-      </c>
-      <c r="T9" s="51">
+      <c r="G9" s="23">
+        <v>5</v>
+      </c>
+      <c r="H9" s="23">
+        <v>5</v>
+      </c>
+      <c r="I9" s="23">
+        <v>5</v>
+      </c>
+      <c r="J9" s="23">
+        <v>5</v>
+      </c>
+      <c r="K9" s="23">
+        <v>4</v>
+      </c>
+      <c r="L9" s="23">
+        <v>4</v>
+      </c>
+      <c r="M9" s="23">
+        <v>5</v>
+      </c>
+      <c r="N9" s="23">
+        <v>4</v>
+      </c>
+      <c r="O9" s="23">
+        <v>4</v>
+      </c>
+      <c r="P9" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="23">
+        <v>3</v>
+      </c>
+      <c r="R9" s="23">
+        <v>4</v>
+      </c>
+      <c r="S9" s="23">
+        <v>5</v>
+      </c>
+      <c r="T9" s="24">
         <f t="shared" ref="T9:T10" si="2">IFERROR(AVERAGE(G9:S9),"-")</f>
         <v>4.4615384615384617</v>
       </c>
-      <c r="U9" s="52" t="str" cm="1">
+      <c r="U9" s="32" t="str" cm="1">
         <f t="array" ref="U9">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="46">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
       </c>
-      <c r="B10" s="40" t="str">
+      <c r="B10" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C10" s="47" t="str">
+      <c r="C10" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>mayo</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="21">
         <v>46172</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="23">
         <v>1067947255</v>
       </c>
-      <c r="G10" s="50">
-        <v>5</v>
-      </c>
-      <c r="H10" s="50">
-        <v>4</v>
-      </c>
-      <c r="I10" s="50">
-        <v>5</v>
-      </c>
-      <c r="J10" s="50">
-        <v>5</v>
-      </c>
-      <c r="K10" s="50">
-        <v>4</v>
-      </c>
-      <c r="L10" s="50">
-        <v>4</v>
-      </c>
-      <c r="M10" s="50">
-        <v>5</v>
-      </c>
-      <c r="N10" s="50">
-        <v>5</v>
-      </c>
-      <c r="O10" s="50">
-        <v>5</v>
-      </c>
-      <c r="P10" s="50">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="50">
-        <v>3</v>
-      </c>
-      <c r="R10" s="50">
-        <v>4</v>
-      </c>
-      <c r="S10" s="50">
-        <v>5</v>
-      </c>
-      <c r="T10" s="51">
+      <c r="G10" s="23">
+        <v>5</v>
+      </c>
+      <c r="H10" s="23">
+        <v>4</v>
+      </c>
+      <c r="I10" s="23">
+        <v>5</v>
+      </c>
+      <c r="J10" s="23">
+        <v>5</v>
+      </c>
+      <c r="K10" s="23">
+        <v>4</v>
+      </c>
+      <c r="L10" s="23">
+        <v>4</v>
+      </c>
+      <c r="M10" s="23">
+        <v>5</v>
+      </c>
+      <c r="N10" s="23">
+        <v>5</v>
+      </c>
+      <c r="O10" s="23">
+        <v>5</v>
+      </c>
+      <c r="P10" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>3</v>
+      </c>
+      <c r="R10" s="23">
+        <v>4</v>
+      </c>
+      <c r="S10" s="23">
+        <v>5</v>
+      </c>
+      <c r="T10" s="24">
         <f t="shared" si="2"/>
         <v>4.5384615384615383</v>
       </c>
-      <c r="U10" s="52" t="str" cm="1">
+      <c r="U10" s="32" t="str" cm="1">
         <f t="array" ref="U10">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B11" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C11" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D11" s="52">
+        <v>46203</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="54">
+        <v>1062980565</v>
+      </c>
+      <c r="G11" s="54">
+        <v>5</v>
+      </c>
+      <c r="H11" s="54">
+        <v>5</v>
+      </c>
+      <c r="I11" s="54">
+        <v>5</v>
+      </c>
+      <c r="J11" s="54">
+        <v>5</v>
+      </c>
+      <c r="K11" s="54">
+        <v>4</v>
+      </c>
+      <c r="L11" s="54">
+        <v>3</v>
+      </c>
+      <c r="M11" s="54">
+        <v>5</v>
+      </c>
+      <c r="N11" s="54">
+        <v>4</v>
+      </c>
+      <c r="O11" s="54">
+        <v>4</v>
+      </c>
+      <c r="P11" s="54">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="54">
+        <v>2</v>
+      </c>
+      <c r="R11" s="54">
+        <v>4</v>
+      </c>
+      <c r="S11" s="54">
+        <v>5</v>
+      </c>
+      <c r="T11" s="55">
+        <f t="shared" ref="T11:T13" si="3">IFERROR(AVERAGE(G11:S11),"-")</f>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U11" s="56" t="str" cm="1">
+        <f t="array" ref="U11">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B12" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C12" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D12" s="52">
+        <v>46203</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="54">
+        <v>1062539643</v>
+      </c>
+      <c r="G12" s="54">
+        <v>5</v>
+      </c>
+      <c r="H12" s="54">
+        <v>5</v>
+      </c>
+      <c r="I12" s="54">
+        <v>5</v>
+      </c>
+      <c r="J12" s="54">
+        <v>5</v>
+      </c>
+      <c r="K12" s="54">
+        <v>4</v>
+      </c>
+      <c r="L12" s="54">
+        <v>4</v>
+      </c>
+      <c r="M12" s="54">
+        <v>5</v>
+      </c>
+      <c r="N12" s="54">
+        <v>4</v>
+      </c>
+      <c r="O12" s="54">
+        <v>5</v>
+      </c>
+      <c r="P12" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="54">
+        <v>3</v>
+      </c>
+      <c r="R12" s="54">
+        <v>4</v>
+      </c>
+      <c r="S12" s="54">
+        <v>5</v>
+      </c>
+      <c r="T12" s="55">
+        <f t="shared" si="3"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U12" s="56" t="str" cm="1">
+        <f t="array" ref="U12">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="50">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B13" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C13" s="51" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D13" s="52">
+        <v>46203</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="54">
+        <v>1068439668</v>
+      </c>
+      <c r="G13" s="54">
+        <v>5</v>
+      </c>
+      <c r="H13" s="54">
+        <v>5</v>
+      </c>
+      <c r="I13" s="54">
+        <v>5</v>
+      </c>
+      <c r="J13" s="54">
+        <v>5</v>
+      </c>
+      <c r="K13" s="54">
+        <v>4</v>
+      </c>
+      <c r="L13" s="54">
+        <v>3</v>
+      </c>
+      <c r="M13" s="54">
+        <v>5</v>
+      </c>
+      <c r="N13" s="54">
+        <v>4</v>
+      </c>
+      <c r="O13" s="54">
+        <v>5</v>
+      </c>
+      <c r="P13" s="54">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="54">
+        <v>2</v>
+      </c>
+      <c r="R13" s="54">
+        <v>4</v>
+      </c>
+      <c r="S13" s="54">
+        <v>5</v>
+      </c>
+      <c r="T13" s="55">
+        <f t="shared" si="3"/>
+        <v>4.384615384615385</v>
+      </c>
+      <c r="U13" s="56" t="str" cm="1">
+        <f t="array" ref="U13">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -21973,15 +23452,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
@@ -21995,7 +23474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="12" t="s">
         <v>98</v>
@@ -22007,7 +23486,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="12" t="s">
         <v>98</v>
@@ -22019,7 +23498,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="26"/>
       <c r="B5" s="12" t="s">
         <v>98</v>
@@ -22031,7 +23510,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="26"/>
       <c r="B6" s="12" t="s">
         <v>98</v>
@@ -22043,7 +23522,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="12" t="s">
         <v>98</v>
@@ -22055,7 +23534,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="12" t="s">
         <v>98</v>
@@ -22067,7 +23546,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="26"/>
       <c r="B9" s="12" t="s">
         <v>98</v>
@@ -22079,7 +23558,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="26"/>
       <c r="B10" s="12" t="s">
         <v>98</v>
@@ -22091,7 +23570,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="12" t="s">
         <v>98</v>
@@ -22103,7 +23582,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="12" t="s">
         <v>98</v>
@@ -22115,7 +23594,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="26"/>
       <c r="B13" s="12" t="s">
         <v>98</v>
@@ -22127,7 +23606,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="26"/>
       <c r="B14" s="12" t="s">
         <v>98</v>
@@ -22139,7 +23618,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="12" t="s">
         <v>98</v>
@@ -22151,7 +23630,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="12" t="s">
         <v>98</v>
@@ -22163,733 +23642,733 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="26"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="27"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="26"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="27"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="38"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="26"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="38"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="26"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="38"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="38"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="38"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="26"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="38"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="26"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="38"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="38"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="38"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="26"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="27"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="26"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="38"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="26"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="38"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="26"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="38"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="26"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="38"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="26"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="38"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="26"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="38"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="26"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="38"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="26"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="38"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="26"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="38"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="26"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="38"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="26"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="38"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="26"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="38"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="26"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="38"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="26"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="38"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="26"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="38"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="26"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="38"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="26"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="38"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="26"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="38"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="26"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="38"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="26"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="38"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="26"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="38"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="26"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="38"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="26"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="38"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="26"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="38"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="26"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="38"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="26"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="38"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="26"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="38"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="26"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
       <c r="D58" s="38"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="26"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="38"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="26"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="38"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="26"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
       <c r="D61" s="38"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="26"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
       <c r="D62" s="38"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="26"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
       <c r="D63" s="38"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="26"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
       <c r="D64" s="38"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="26"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="38"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="26"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="38"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="26"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="38"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="26"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
       <c r="D68" s="38"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="26"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
       <c r="D69" s="38"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="26"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="38"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="26"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="38"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="26"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
       <c r="D72" s="38"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="26"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="38"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="26"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="38"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="26"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="38"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="26"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="38"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="26"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="38"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="26"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="38"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="26"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="D79" s="38"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="26"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="38"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="26"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="38"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="26"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="38"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="26"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="38"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="26"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="38"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="26"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="38"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="26"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="38"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="26"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="38"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="26"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="38"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="26"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="D89" s="38"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="26"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="D90" s="38"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="26"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="D91" s="38"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="26"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="38"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="26"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="38"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="26"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="38"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="26"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="D95" s="38"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="26"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="38"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="26"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="38"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="26"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="38"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="26"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="D99" s="38"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="26"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="38"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="26"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="38"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="26"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="D102" s="38"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="26"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="38"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="26"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="D104" s="38"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="26"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
       <c r="D105" s="38"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="26"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="38"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="26"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="D107" s="38"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="26"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="38"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="26"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
       <c r="D109" s="38"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="26"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="38"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="26"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="D111" s="38"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="26"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
       <c r="D112" s="38"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="26"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
       <c r="D113" s="38"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="26"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
       <c r="D114" s="38"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="26"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
       <c r="D115" s="38"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="26"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
       <c r="D116" s="38"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="26"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
       <c r="D117" s="38"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="26"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="38"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="26"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="D119" s="38"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="26"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
       <c r="D120" s="38"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="26"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
       <c r="D121" s="38"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="26"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
       <c r="D122" s="38"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="26"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
       <c r="D123" s="38"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="26"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
       <c r="D124" s="38"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="26"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="D125" s="38"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="26"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="38"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="26"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="D127" s="38"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="26"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
       <c r="D128" s="38"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="26"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="38"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="26"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="38"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="26"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="D131" s="38"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="26"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
       <c r="D132" s="38"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="26"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
       <c r="D133" s="38"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="26"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="38"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="26"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="38"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="26"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
       <c r="D136" s="38"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="26"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
       <c r="D137" s="38"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="26"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30218"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0355B1-EA86-4A6D-95AA-B6A76239C942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A388C0-D85C-48C1-B50D-DA8189529E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="158">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -703,6 +703,24 @@
   <si>
     <t>Juan Sebastian Vargas Villamizar</t>
   </si>
+  <si>
+    <t>Gustavo Machado Petro</t>
+  </si>
+  <si>
+    <t>Elisa del toro Martínez</t>
+  </si>
+  <si>
+    <t>Valery Guerrero Medina</t>
+  </si>
+  <si>
+    <t>Juan Sebastian Taborda</t>
+  </si>
+  <si>
+    <t>Isabel Sofia Diaz blanco</t>
+  </si>
+  <si>
+    <t>Reyk Sayk Alemán Acuña</t>
+  </si>
 </sst>
 </file>
 
@@ -834,7 +852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,12 +975,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -975,623 +987,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2581,6 +1990,591 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -3105,7 +3099,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3308,7 +3302,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3511,7 +3505,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -3914,7 +3908,7 @@
                         <c:v>27</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>38</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -4082,7 +4076,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -4861,7 +4855,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -5407,7 +5401,7 @@
                         <c:v>27</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>38</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -5575,7 +5569,7 @@
                         <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>19</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -5748,7 +5742,7 @@
                         <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -5921,7 +5915,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -6596,7 +6590,7 @@
                   <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -6782,7 +6776,7 @@
                         <c:v>14</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>19</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -6955,7 +6949,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -7128,7 +7122,7 @@
                         <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -7474,7 +7468,7 @@
                         <c:v>3</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>0</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -12177,37 +12171,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O116" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56">
-  <autoFilter ref="A2:O116" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O135" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
+  <autoFilter ref="A2:O135" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O135">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="55">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="31">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="30">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="53">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="29">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="42">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="18">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="41">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="17">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12216,36 +12210,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O66" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A2:O66" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O79" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:O79" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O79">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="38">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12254,42 +12248,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U13" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A2:U13" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U19" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
+  <autoFilter ref="A2:U19" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U19">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="61">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="60">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="59">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="45"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="44"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="42">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="41">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12298,17 +12292,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="62"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12578,14 +12572,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031510B-662C-4B68-8770-DE372FF29377}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.6328125" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -12615,7 +12609,7 @@
       </c>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
@@ -12652,7 +12646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
@@ -12689,7 +12683,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
@@ -12726,7 +12720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>38</v>
       </c>
@@ -12763,7 +12757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>39</v>
       </c>
@@ -12800,7 +12794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
@@ -12837,25 +12831,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C8" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A8)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D8" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A8)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
@@ -12863,7 +12857,7 @@
       </c>
       <c r="G8" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A8)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H8" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -12874,7 +12868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>42</v>
       </c>
@@ -12911,7 +12905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>43</v>
       </c>
@@ -12948,7 +12942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>44</v>
       </c>
@@ -12985,7 +12979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -13022,7 +13016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>46</v>
       </c>
@@ -13077,26 +13071,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O135"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" customWidth="1"/>
-    <col min="2" max="2" width="5.6328125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="7.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.36328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.90625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="6.36328125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="6.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E1" s="25" t="s">
         <v>48</v>
       </c>
@@ -13113,7 +13107,7 @@
       <c r="N1" s="33"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -13160,7 +13154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13212,7 +13206,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13264,7 +13258,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13316,7 +13310,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13368,7 +13362,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13420,7 +13414,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13472,7 +13466,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13524,7 +13518,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13576,7 +13570,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13628,7 +13622,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -13680,7 +13674,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13732,7 +13726,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13784,7 +13778,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13836,7 +13830,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13888,7 +13882,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13940,7 +13934,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -13992,7 +13986,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14044,7 +14038,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14096,7 +14090,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14148,7 +14142,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14200,7 +14194,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14252,7 +14246,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14304,7 +14298,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -14356,7 +14350,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14408,7 +14402,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14460,7 +14454,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14512,7 +14506,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14564,7 +14558,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14616,7 +14610,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14668,7 +14662,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14720,7 +14714,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14772,7 +14766,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14824,7 +14818,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14876,7 +14870,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14928,7 +14922,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -14980,7 +14974,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15032,7 +15026,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15084,7 +15078,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15136,7 +15130,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15188,7 +15182,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15240,7 +15234,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15292,7 +15286,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15344,7 +15338,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15396,7 +15390,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -15448,7 +15442,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15500,7 +15494,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15552,7 +15546,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15604,7 +15598,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15656,7 +15650,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15708,7 +15702,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15760,7 +15754,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15812,7 +15806,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15864,7 +15858,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15916,7 +15910,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -15968,7 +15962,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16020,7 +16014,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16072,7 +16066,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16124,7 +16118,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16176,7 +16170,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16228,7 +16222,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16280,7 +16274,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16332,7 +16326,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16384,7 +16378,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16436,7 +16430,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16488,7 +16482,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16540,7 +16534,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16592,7 +16586,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16644,7 +16638,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16696,7 +16690,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16748,7 +16742,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16800,7 +16794,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16852,7 +16846,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16904,7 +16898,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -16956,7 +16950,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17008,7 +17002,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -17060,7 +17054,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17112,7 +17106,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17164,7 +17158,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17216,7 +17210,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17268,7 +17262,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17320,7 +17314,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17372,7 +17366,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17424,7 +17418,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17476,7 +17470,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17528,7 +17522,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17580,7 +17574,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17632,7 +17626,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17684,7 +17678,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17736,7 +17730,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17788,7 +17782,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17840,7 +17834,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17892,7 +17886,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17944,7 +17938,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -17996,7 +17990,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18048,7 +18042,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18100,7 +18094,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18152,7 +18146,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18204,7 +18198,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18256,7 +18250,7 @@
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18308,7 +18302,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -18360,731 +18354,1719 @@
         <v>-</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A103" s="40">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B103" s="41" t="str">
+      <c r="B103" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C103" s="41" t="str">
+      <c r="C103" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D103" s="44">
+      <c r="D103" s="3">
         <v>46199</v>
       </c>
-      <c r="E103" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="F103" s="46">
-        <v>1068443767</v>
-      </c>
-      <c r="G103" s="47">
-        <v>5</v>
-      </c>
-      <c r="H103" s="47">
-        <v>5</v>
-      </c>
-      <c r="I103" s="47">
-        <v>3</v>
-      </c>
-      <c r="J103" s="47">
-        <v>3</v>
-      </c>
-      <c r="K103" s="47">
-        <v>1</v>
-      </c>
-      <c r="L103" s="47">
-        <v>1</v>
-      </c>
-      <c r="M103" s="47">
-        <v>5</v>
-      </c>
-      <c r="N103" s="42">
+      <c r="E103" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F103" s="1">
+        <v>50906315</v>
+      </c>
+      <c r="G103" s="1">
+        <v>5</v>
+      </c>
+      <c r="H103" s="1">
+        <v>4</v>
+      </c>
+      <c r="I103" s="1">
+        <v>4</v>
+      </c>
+      <c r="J103" s="1">
+        <v>2</v>
+      </c>
+      <c r="K103" s="1">
+        <v>2</v>
+      </c>
+      <c r="L103" s="1">
+        <v>2</v>
+      </c>
+      <c r="M103" s="1">
+        <v>2</v>
+      </c>
+      <c r="N103" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G103:M103),"-")</f>
-        <v>3.2857142857142856</v>
-      </c>
-      <c r="O103" s="43" t="str" cm="1">
+        <v>3</v>
+      </c>
+      <c r="O103" s="18" t="str" cm="1">
         <f t="array" ref="O103">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A104" s="40">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B104" s="41" t="str">
+      <c r="B104" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C104" s="41" t="str">
+      <c r="C104" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D104" s="44">
+      <c r="D104" s="3">
         <v>46199</v>
       </c>
-      <c r="E104" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="F104" s="46">
-        <v>1062540875</v>
-      </c>
-      <c r="G104" s="47">
-        <v>5</v>
-      </c>
-      <c r="H104" s="47">
-        <v>5</v>
-      </c>
-      <c r="I104" s="47">
-        <v>4</v>
-      </c>
-      <c r="J104" s="47">
-        <v>4</v>
-      </c>
-      <c r="K104" s="47">
-        <v>3</v>
-      </c>
-      <c r="L104" s="47">
-        <v>3</v>
-      </c>
-      <c r="M104" s="47">
-        <v>5</v>
-      </c>
-      <c r="N104" s="42">
+      <c r="E104" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1001897545</v>
+      </c>
+      <c r="G104" s="1">
+        <v>5</v>
+      </c>
+      <c r="H104" s="1">
+        <v>5</v>
+      </c>
+      <c r="I104" s="1">
+        <v>5</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
+        <v>5</v>
+      </c>
+      <c r="L104" s="1">
+        <v>5</v>
+      </c>
+      <c r="M104" s="1">
+        <v>5</v>
+      </c>
+      <c r="N104" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G104:M104),"-")</f>
-        <v>4.1428571428571432</v>
-      </c>
-      <c r="O104" s="43" t="str" cm="1">
+        <v>5</v>
+      </c>
+      <c r="O104" s="18" t="str" cm="1">
         <f t="array" ref="O104">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A105" s="40">
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B105" s="41" t="str">
+      <c r="B105" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C105" s="41" t="str">
+      <c r="C105" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D105" s="44">
+      <c r="D105" s="3">
         <v>46199</v>
       </c>
-      <c r="E105" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="F105" s="46">
-        <v>1068442748</v>
-      </c>
-      <c r="G105" s="47">
-        <v>5</v>
-      </c>
-      <c r="H105" s="47">
-        <v>2</v>
-      </c>
-      <c r="I105" s="47">
-        <v>2</v>
-      </c>
-      <c r="J105" s="47">
+      <c r="E105" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F105" s="1">
+        <v>1003047136</v>
+      </c>
+      <c r="G105" s="1">
+        <v>5</v>
+      </c>
+      <c r="H105" s="1">
+        <v>5</v>
+      </c>
+      <c r="I105" s="1">
+        <v>4</v>
+      </c>
+      <c r="J105" s="1">
+        <v>3</v>
+      </c>
+      <c r="K105" s="1">
+        <v>3</v>
+      </c>
+      <c r="L105" s="1">
+        <v>3</v>
+      </c>
+      <c r="M105" s="1">
         <v>1</v>
       </c>
-      <c r="K105" s="47">
-        <v>1</v>
-      </c>
-      <c r="L105" s="47">
-        <v>1</v>
-      </c>
-      <c r="M105" s="47">
-        <v>1</v>
-      </c>
-      <c r="N105" s="42">
+      <c r="N105" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G105:M105),"-")</f>
-        <v>1.8571428571428572</v>
-      </c>
-      <c r="O105" s="43" t="str" cm="1">
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O105" s="18" t="str" cm="1">
         <f t="array" ref="O105">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A106" s="40">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B106" s="41" t="str">
+      <c r="B106" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C106" s="41" t="str">
+      <c r="C106" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D106" s="44">
+      <c r="D106" s="3">
         <v>46199</v>
       </c>
-      <c r="E106" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="F106" s="46">
-        <v>1233348383</v>
-      </c>
-      <c r="G106" s="47">
-        <v>5</v>
-      </c>
-      <c r="H106" s="47">
-        <v>5</v>
-      </c>
-      <c r="I106" s="47">
-        <v>4</v>
-      </c>
-      <c r="J106" s="47">
-        <v>4</v>
-      </c>
-      <c r="K106" s="47">
-        <v>3</v>
-      </c>
-      <c r="L106" s="47">
-        <v>3</v>
-      </c>
-      <c r="M106" s="47">
-        <v>5</v>
-      </c>
-      <c r="N106" s="42">
+      <c r="E106" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F106" s="1">
+        <v>1003405136</v>
+      </c>
+      <c r="G106" s="1">
+        <v>5</v>
+      </c>
+      <c r="H106" s="1">
+        <v>5</v>
+      </c>
+      <c r="I106" s="1">
+        <v>5</v>
+      </c>
+      <c r="J106" s="1">
+        <v>4</v>
+      </c>
+      <c r="K106" s="1">
+        <v>4</v>
+      </c>
+      <c r="L106" s="1">
+        <v>3</v>
+      </c>
+      <c r="M106" s="1">
+        <v>5</v>
+      </c>
+      <c r="N106" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G106:M106),"-")</f>
-        <v>4.1428571428571432</v>
-      </c>
-      <c r="O106" s="43" t="str" cm="1">
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O106" s="18" t="str" cm="1">
         <f t="array" ref="O106">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A107" s="40">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B107" s="41" t="str">
+      <c r="B107" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C107" s="41" t="str">
+      <c r="C107" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D107" s="44">
+      <c r="D107" s="3">
         <v>46199</v>
       </c>
-      <c r="E107" s="45" t="s">
+      <c r="E107" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F107" s="46">
+      <c r="F107" s="1">
         <v>1037236492</v>
       </c>
-      <c r="G107" s="47">
-        <v>5</v>
-      </c>
-      <c r="H107" s="47">
-        <v>5</v>
-      </c>
-      <c r="I107" s="47">
-        <v>5</v>
-      </c>
-      <c r="J107" s="47">
-        <v>4</v>
-      </c>
-      <c r="K107" s="47">
-        <v>4</v>
-      </c>
-      <c r="L107" s="47">
-        <v>4</v>
-      </c>
-      <c r="M107" s="47">
-        <v>5</v>
-      </c>
-      <c r="N107" s="42">
+      <c r="G107" s="1">
+        <v>5</v>
+      </c>
+      <c r="H107" s="1">
+        <v>5</v>
+      </c>
+      <c r="I107" s="1">
+        <v>5</v>
+      </c>
+      <c r="J107" s="1">
+        <v>4</v>
+      </c>
+      <c r="K107" s="1">
+        <v>4</v>
+      </c>
+      <c r="L107" s="1">
+        <v>4</v>
+      </c>
+      <c r="M107" s="1">
+        <v>5</v>
+      </c>
+      <c r="N107" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G107:M107),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O107" s="43" t="str" cm="1">
+      <c r="O107" s="18" t="str" cm="1">
         <f t="array" ref="O107">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A108" s="40">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B108" s="41" t="str">
+      <c r="B108" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C108" s="41" t="str">
+      <c r="C108" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D108" s="44">
+      <c r="D108" s="3">
         <v>46199</v>
       </c>
-      <c r="E108" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="F108" s="46">
-        <v>1003405136</v>
-      </c>
-      <c r="G108" s="47">
-        <v>5</v>
-      </c>
-      <c r="H108" s="47">
-        <v>5</v>
-      </c>
-      <c r="I108" s="47">
-        <v>5</v>
-      </c>
-      <c r="J108" s="47">
-        <v>4</v>
-      </c>
-      <c r="K108" s="47">
-        <v>4</v>
-      </c>
-      <c r="L108" s="47">
-        <v>3</v>
-      </c>
-      <c r="M108" s="47">
-        <v>5</v>
-      </c>
-      <c r="N108" s="42">
+      <c r="E108" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F108" s="1">
+        <v>1062540875</v>
+      </c>
+      <c r="G108" s="1">
+        <v>5</v>
+      </c>
+      <c r="H108" s="1">
+        <v>5</v>
+      </c>
+      <c r="I108" s="1">
+        <v>4</v>
+      </c>
+      <c r="J108" s="1">
+        <v>4</v>
+      </c>
+      <c r="K108" s="1">
+        <v>3</v>
+      </c>
+      <c r="L108" s="1">
+        <v>3</v>
+      </c>
+      <c r="M108" s="1">
+        <v>5</v>
+      </c>
+      <c r="N108" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G108:M108),"-")</f>
-        <v>4.4285714285714288</v>
-      </c>
-      <c r="O108" s="43" t="str" cm="1">
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O108" s="18" t="str" cm="1">
         <f t="array" ref="O108">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A109" s="40">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B109" s="41" t="str">
+      <c r="B109" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C109" s="41" t="str">
+      <c r="C109" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D109" s="44">
+      <c r="D109" s="3">
         <v>46199</v>
       </c>
-      <c r="E109" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="F109" s="46">
-        <v>1103755851</v>
-      </c>
-      <c r="G109" s="47">
-        <v>5</v>
-      </c>
-      <c r="H109" s="47">
-        <v>5</v>
-      </c>
-      <c r="I109" s="47">
-        <v>5</v>
-      </c>
-      <c r="J109" s="47">
-        <v>4</v>
-      </c>
-      <c r="K109" s="47">
-        <v>4</v>
-      </c>
-      <c r="L109" s="47">
-        <v>4</v>
-      </c>
-      <c r="M109" s="47">
-        <v>5</v>
-      </c>
-      <c r="N109" s="42">
+      <c r="E109" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F109" s="1">
+        <v>1065443120</v>
+      </c>
+      <c r="G109" s="1">
+        <v>5</v>
+      </c>
+      <c r="H109" s="1">
+        <v>5</v>
+      </c>
+      <c r="I109" s="1">
+        <v>5</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
+        <v>4</v>
+      </c>
+      <c r="L109" s="1">
+        <v>4</v>
+      </c>
+      <c r="M109" s="1">
+        <v>5</v>
+      </c>
+      <c r="N109" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G109:M109),"-")</f>
-        <v>4.5714285714285712</v>
-      </c>
-      <c r="O109" s="43" t="str" cm="1">
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O109" s="18" t="str" cm="1">
         <f t="array" ref="O109">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A110" s="40">
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B110" s="41" t="str">
+      <c r="B110" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C110" s="41" t="str">
+      <c r="C110" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D110" s="44">
+      <c r="D110" s="3">
         <v>46199</v>
       </c>
-      <c r="E110" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F110" s="46">
-        <v>50906315</v>
-      </c>
-      <c r="G110" s="47">
-        <v>5</v>
-      </c>
-      <c r="H110" s="47">
-        <v>4</v>
-      </c>
-      <c r="I110" s="47">
-        <v>4</v>
-      </c>
-      <c r="J110" s="47">
+      <c r="E110" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F110" s="1">
+        <v>1068440514</v>
+      </c>
+      <c r="G110" s="1">
+        <v>5</v>
+      </c>
+      <c r="H110" s="1">
+        <v>3</v>
+      </c>
+      <c r="I110" s="1">
+        <v>3</v>
+      </c>
+      <c r="J110" s="1">
         <v>2</v>
       </c>
-      <c r="K110" s="47">
+      <c r="K110" s="1">
         <v>2</v>
       </c>
-      <c r="L110" s="47">
+      <c r="L110" s="1">
         <v>2</v>
       </c>
-      <c r="M110" s="47">
-        <v>2</v>
-      </c>
-      <c r="N110" s="42">
+      <c r="M110" s="1">
+        <v>3</v>
+      </c>
+      <c r="N110" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G110:M110),"-")</f>
-        <v>3</v>
-      </c>
-      <c r="O110" s="43" t="str" cm="1">
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O110" s="18" t="str" cm="1">
         <f t="array" ref="O110">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A111" s="40">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B111" s="41" t="str">
+      <c r="B111" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C111" s="41" t="str">
+      <c r="C111" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D111" s="44">
+      <c r="D111" s="3">
         <v>46199</v>
       </c>
-      <c r="E111" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="F111" s="46">
-        <v>1003047136</v>
-      </c>
-      <c r="G111" s="47">
-        <v>5</v>
-      </c>
-      <c r="H111" s="47">
-        <v>5</v>
-      </c>
-      <c r="I111" s="47">
-        <v>4</v>
-      </c>
-      <c r="J111" s="47">
-        <v>3</v>
-      </c>
-      <c r="K111" s="47">
-        <v>3</v>
-      </c>
-      <c r="L111" s="47">
-        <v>3</v>
-      </c>
-      <c r="M111" s="47">
+      <c r="E111" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F111" s="1">
+        <v>1068442748</v>
+      </c>
+      <c r="G111" s="1">
+        <v>5</v>
+      </c>
+      <c r="H111" s="1">
+        <v>2</v>
+      </c>
+      <c r="I111" s="1">
+        <v>2</v>
+      </c>
+      <c r="J111" s="1">
         <v>1</v>
       </c>
-      <c r="N111" s="42">
+      <c r="K111" s="1">
+        <v>1</v>
+      </c>
+      <c r="L111" s="1">
+        <v>1</v>
+      </c>
+      <c r="M111" s="1">
+        <v>1</v>
+      </c>
+      <c r="N111" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G111:M111),"-")</f>
-        <v>3.4285714285714284</v>
-      </c>
-      <c r="O111" s="43" t="str" cm="1">
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="O111" s="18" t="str" cm="1">
         <f t="array" ref="O111">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A112" s="40">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B112" s="41" t="str">
+      <c r="B112" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C112" s="41" t="str">
+      <c r="C112" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D112" s="44">
+      <c r="D112" s="3">
         <v>46199</v>
       </c>
-      <c r="E112" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F112" s="46">
-        <v>1233040347</v>
-      </c>
-      <c r="G112" s="47">
-        <v>5</v>
-      </c>
-      <c r="H112" s="47">
-        <v>4</v>
-      </c>
-      <c r="I112" s="47">
-        <v>4</v>
-      </c>
-      <c r="J112" s="47">
-        <v>4</v>
-      </c>
-      <c r="K112" s="47">
-        <v>3</v>
-      </c>
-      <c r="L112" s="47">
-        <v>3</v>
-      </c>
-      <c r="M112" s="47">
-        <v>3</v>
-      </c>
-      <c r="N112" s="42">
+      <c r="E112" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1068443767</v>
+      </c>
+      <c r="G112" s="1">
+        <v>5</v>
+      </c>
+      <c r="H112" s="1">
+        <v>5</v>
+      </c>
+      <c r="I112" s="1">
+        <v>3</v>
+      </c>
+      <c r="J112" s="1">
+        <v>3</v>
+      </c>
+      <c r="K112" s="1">
+        <v>1</v>
+      </c>
+      <c r="L112" s="1">
+        <v>1</v>
+      </c>
+      <c r="M112" s="1">
+        <v>5</v>
+      </c>
+      <c r="N112" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G112:M112),"-")</f>
-        <v>3.7142857142857144</v>
-      </c>
-      <c r="O112" s="43" t="str" cm="1">
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O112" s="18" t="str" cm="1">
         <f t="array" ref="O112">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A113" s="40">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A113" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B113" s="41" t="str">
+      <c r="B113" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C113" s="41" t="str">
+      <c r="C113" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D113" s="44">
+      <c r="D113" s="3">
         <v>46199</v>
       </c>
-      <c r="E113" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="F113" s="46">
-        <v>1068440514</v>
-      </c>
-      <c r="G113" s="47">
-        <v>5</v>
-      </c>
-      <c r="H113" s="47">
-        <v>3</v>
-      </c>
-      <c r="I113" s="47">
-        <v>3</v>
-      </c>
-      <c r="J113" s="47">
+      <c r="E113" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F113" s="1">
+        <v>1091978602</v>
+      </c>
+      <c r="G113" s="1">
+        <v>5</v>
+      </c>
+      <c r="H113" s="1">
+        <v>4</v>
+      </c>
+      <c r="I113" s="1">
+        <v>3</v>
+      </c>
+      <c r="J113" s="1">
         <v>2</v>
       </c>
-      <c r="K113" s="47">
+      <c r="K113" s="1">
         <v>2</v>
       </c>
-      <c r="L113" s="47">
+      <c r="L113" s="1">
         <v>2</v>
       </c>
-      <c r="M113" s="47">
-        <v>3</v>
-      </c>
-      <c r="N113" s="42">
+      <c r="M113" s="1">
+        <v>3</v>
+      </c>
+      <c r="N113" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G113:M113),"-")</f>
-        <v>2.8571428571428572</v>
-      </c>
-      <c r="O113" s="43" t="str" cm="1">
+        <v>3</v>
+      </c>
+      <c r="O113" s="18" t="str" cm="1">
         <f t="array" ref="O113">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A114" s="40">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A114" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B114" s="41" t="str">
+      <c r="B114" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C114" s="41" t="str">
+      <c r="C114" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D114" s="44">
+      <c r="D114" s="3">
         <v>46199</v>
       </c>
-      <c r="E114" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="F114" s="46">
-        <v>1065443120</v>
-      </c>
-      <c r="G114" s="47">
-        <v>5</v>
-      </c>
-      <c r="H114" s="47">
-        <v>5</v>
-      </c>
-      <c r="I114" s="47">
-        <v>5</v>
-      </c>
-      <c r="J114" s="47">
-        <v>5</v>
-      </c>
-      <c r="K114" s="47">
-        <v>4</v>
-      </c>
-      <c r="L114" s="47">
-        <v>4</v>
-      </c>
-      <c r="M114" s="47">
-        <v>5</v>
-      </c>
-      <c r="N114" s="42">
+      <c r="E114" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F114" s="1">
+        <v>1103755851</v>
+      </c>
+      <c r="G114" s="1">
+        <v>5</v>
+      </c>
+      <c r="H114" s="1">
+        <v>5</v>
+      </c>
+      <c r="I114" s="1">
+        <v>5</v>
+      </c>
+      <c r="J114" s="1">
+        <v>4</v>
+      </c>
+      <c r="K114" s="1">
+        <v>4</v>
+      </c>
+      <c r="L114" s="1">
+        <v>4</v>
+      </c>
+      <c r="M114" s="1">
+        <v>5</v>
+      </c>
+      <c r="N114" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G114:M114),"-")</f>
-        <v>4.7142857142857144</v>
-      </c>
-      <c r="O114" s="43" t="str" cm="1">
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O114" s="18" t="str" cm="1">
         <f t="array" ref="O114">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>CAMBIA A NIVEL 2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A115" s="40">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A115" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B115" s="41" t="str">
+      <c r="B115" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C115" s="41" t="str">
+      <c r="C115" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D115" s="44">
+      <c r="D115" s="3">
         <v>46199</v>
       </c>
-      <c r="E115" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="F115" s="46">
-        <v>1001897545</v>
-      </c>
-      <c r="G115" s="47">
-        <v>5</v>
-      </c>
-      <c r="H115" s="47">
-        <v>5</v>
-      </c>
-      <c r="I115" s="47">
-        <v>5</v>
-      </c>
-      <c r="J115" s="47">
-        <v>5</v>
-      </c>
-      <c r="K115" s="47">
-        <v>5</v>
-      </c>
-      <c r="L115" s="47">
-        <v>5</v>
-      </c>
-      <c r="M115" s="47">
-        <v>5</v>
-      </c>
-      <c r="N115" s="42">
+      <c r="E115" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F115" s="1">
+        <v>1233040347</v>
+      </c>
+      <c r="G115" s="1">
+        <v>5</v>
+      </c>
+      <c r="H115" s="1">
+        <v>4</v>
+      </c>
+      <c r="I115" s="1">
+        <v>4</v>
+      </c>
+      <c r="J115" s="1">
+        <v>4</v>
+      </c>
+      <c r="K115" s="1">
+        <v>3</v>
+      </c>
+      <c r="L115" s="1">
+        <v>3</v>
+      </c>
+      <c r="M115" s="1">
+        <v>3</v>
+      </c>
+      <c r="N115" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G115:M115),"-")</f>
-        <v>5</v>
-      </c>
-      <c r="O115" s="43" t="str" cm="1">
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O115" s="18" t="str" cm="1">
         <f t="array" ref="O115">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>CAMBIA A NIVEL 2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A116" s="40">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A116" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B116" s="41" t="str">
+      <c r="B116" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C116" s="41" t="str">
+      <c r="C116" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D116" s="44">
+      <c r="D116" s="3">
         <v>46199</v>
       </c>
-      <c r="E116" s="45" t="s">
+      <c r="E116" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F116" s="1">
+        <v>1233348383</v>
+      </c>
+      <c r="G116" s="1">
+        <v>5</v>
+      </c>
+      <c r="H116" s="1">
+        <v>5</v>
+      </c>
+      <c r="I116" s="1">
+        <v>4</v>
+      </c>
+      <c r="J116" s="1">
+        <v>4</v>
+      </c>
+      <c r="K116" s="1">
+        <v>3</v>
+      </c>
+      <c r="L116" s="1">
+        <v>3</v>
+      </c>
+      <c r="M116" s="1">
+        <v>5</v>
+      </c>
+      <c r="N116" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G116:M116),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O116" s="18" t="str" cm="1">
+        <f t="array" ref="O116">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A117" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B117" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C117" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D117" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E117" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="F117" s="44">
+        <v>25800927</v>
+      </c>
+      <c r="G117" s="45">
+        <v>5</v>
+      </c>
+      <c r="H117" s="45">
+        <v>4</v>
+      </c>
+      <c r="I117" s="45">
+        <v>4</v>
+      </c>
+      <c r="J117" s="45">
+        <v>2</v>
+      </c>
+      <c r="K117" s="45">
+        <v>2</v>
+      </c>
+      <c r="L117" s="45">
+        <v>2</v>
+      </c>
+      <c r="M117" s="45">
+        <v>3</v>
+      </c>
+      <c r="N117" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G117:M117),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O117" s="46" t="str" cm="1">
+        <f t="array" ref="O117">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A118" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B118" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C118" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D118" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E118" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="F118" s="44">
+        <v>50906315</v>
+      </c>
+      <c r="G118" s="45">
+        <v>5</v>
+      </c>
+      <c r="H118" s="45">
+        <v>4</v>
+      </c>
+      <c r="I118" s="45">
+        <v>3</v>
+      </c>
+      <c r="J118" s="45">
+        <v>2</v>
+      </c>
+      <c r="K118" s="45">
+        <v>2</v>
+      </c>
+      <c r="L118" s="45">
+        <v>2</v>
+      </c>
+      <c r="M118" s="45">
+        <v>2</v>
+      </c>
+      <c r="N118" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G118:M118),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O118" s="46" t="str" cm="1">
+        <f t="array" ref="O118">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A119" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B119" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C119" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D119" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E119" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="F119" s="44">
+        <v>1016116812</v>
+      </c>
+      <c r="G119" s="45">
+        <v>5</v>
+      </c>
+      <c r="H119" s="45">
+        <v>5</v>
+      </c>
+      <c r="I119" s="45">
+        <v>5</v>
+      </c>
+      <c r="J119" s="45">
+        <v>4</v>
+      </c>
+      <c r="K119" s="45">
+        <v>4</v>
+      </c>
+      <c r="L119" s="45">
+        <v>4</v>
+      </c>
+      <c r="M119" s="45">
+        <v>5</v>
+      </c>
+      <c r="N119" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G119:M119),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O119" s="46" t="str" cm="1">
+        <f t="array" ref="O119">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A120" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B120" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C120" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D120" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E120" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="F120" s="44">
+        <v>1037236492</v>
+      </c>
+      <c r="G120" s="45">
+        <v>5</v>
+      </c>
+      <c r="H120" s="45">
+        <v>5</v>
+      </c>
+      <c r="I120" s="45">
+        <v>5</v>
+      </c>
+      <c r="J120" s="45">
+        <v>4</v>
+      </c>
+      <c r="K120" s="45">
+        <v>5</v>
+      </c>
+      <c r="L120" s="45">
+        <v>4</v>
+      </c>
+      <c r="M120" s="45">
+        <v>5</v>
+      </c>
+      <c r="N120" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G120:M120),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O120" s="46" t="str" cm="1">
+        <f t="array" ref="O120">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A121" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B121" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C121" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D121" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E121" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="F121" s="44">
+        <v>1062535690</v>
+      </c>
+      <c r="G121" s="45">
+        <v>5</v>
+      </c>
+      <c r="H121" s="45">
+        <v>5</v>
+      </c>
+      <c r="I121" s="45">
+        <v>5</v>
+      </c>
+      <c r="J121" s="45">
+        <v>4</v>
+      </c>
+      <c r="K121" s="45">
+        <v>4</v>
+      </c>
+      <c r="L121" s="45">
+        <v>4</v>
+      </c>
+      <c r="M121" s="45">
+        <v>5</v>
+      </c>
+      <c r="N121" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G121:M121),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O121" s="46" t="str" cm="1">
+        <f t="array" ref="O121">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A122" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B122" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C122" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D122" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E122" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F122" s="44">
+        <v>1062540875</v>
+      </c>
+      <c r="G122" s="45">
+        <v>5</v>
+      </c>
+      <c r="H122" s="45">
+        <v>5</v>
+      </c>
+      <c r="I122" s="45">
+        <v>4</v>
+      </c>
+      <c r="J122" s="45">
+        <v>3</v>
+      </c>
+      <c r="K122" s="45">
+        <v>3</v>
+      </c>
+      <c r="L122" s="45">
+        <v>3</v>
+      </c>
+      <c r="M122" s="45">
+        <v>5</v>
+      </c>
+      <c r="N122" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G122:M122),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O122" s="46" t="str" cm="1">
+        <f t="array" ref="O122">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A123" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B123" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C123" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D123" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E123" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F123" s="44">
+        <v>1062979535</v>
+      </c>
+      <c r="G123" s="45">
+        <v>5</v>
+      </c>
+      <c r="H123" s="45">
+        <v>5</v>
+      </c>
+      <c r="I123" s="45">
+        <v>4</v>
+      </c>
+      <c r="J123" s="45">
+        <v>4</v>
+      </c>
+      <c r="K123" s="45">
+        <v>3</v>
+      </c>
+      <c r="L123" s="45">
+        <v>3</v>
+      </c>
+      <c r="M123" s="45">
+        <v>5</v>
+      </c>
+      <c r="N123" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G123:M123),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O123" s="46" t="str" cm="1">
+        <f t="array" ref="O123">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A124" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B124" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C124" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D124" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E124" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F124" s="44">
+        <v>1068442748</v>
+      </c>
+      <c r="G124" s="45">
+        <v>5</v>
+      </c>
+      <c r="H124" s="45">
+        <v>3</v>
+      </c>
+      <c r="I124" s="45">
+        <v>3</v>
+      </c>
+      <c r="J124" s="45">
+        <v>1</v>
+      </c>
+      <c r="K124" s="45">
+        <v>1</v>
+      </c>
+      <c r="L124" s="45">
+        <v>1</v>
+      </c>
+      <c r="M124" s="45">
+        <v>1</v>
+      </c>
+      <c r="N124" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G124:M124),"-")</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="O124" s="46" t="str" cm="1">
+        <f t="array" ref="O124">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A125" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B125" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C125" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D125" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E125" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F125" s="44">
+        <v>1068443767</v>
+      </c>
+      <c r="G125" s="45">
+        <v>5</v>
+      </c>
+      <c r="H125" s="45">
+        <v>5</v>
+      </c>
+      <c r="I125" s="45">
+        <v>4</v>
+      </c>
+      <c r="J125" s="45">
+        <v>4</v>
+      </c>
+      <c r="K125" s="45">
+        <v>2</v>
+      </c>
+      <c r="L125" s="45">
+        <v>2</v>
+      </c>
+      <c r="M125" s="45">
+        <v>5</v>
+      </c>
+      <c r="N125" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G125:M125),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O125" s="46" t="str" cm="1">
+        <f t="array" ref="O125">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A126" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B126" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C126" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D126" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E126" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="F126" s="44">
+        <v>1068445190</v>
+      </c>
+      <c r="G126" s="45">
+        <v>5</v>
+      </c>
+      <c r="H126" s="45">
+        <v>3</v>
+      </c>
+      <c r="I126" s="45">
+        <v>2</v>
+      </c>
+      <c r="J126" s="45">
+        <v>2</v>
+      </c>
+      <c r="K126" s="45">
+        <v>1</v>
+      </c>
+      <c r="L126" s="45">
+        <v>1</v>
+      </c>
+      <c r="M126" s="45">
+        <v>2</v>
+      </c>
+      <c r="N126" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G126:M126),"-")</f>
+        <v>2.2857142857142856</v>
+      </c>
+      <c r="O126" s="46" t="str" cm="1">
+        <f t="array" ref="O126">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A127" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B127" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C127" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D127" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E127" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="F116" s="46">
+      <c r="F127" s="44">
         <v>1091978602</v>
       </c>
-      <c r="G116" s="47">
-        <v>5</v>
-      </c>
-      <c r="H116" s="47">
-        <v>4</v>
-      </c>
-      <c r="I116" s="47">
-        <v>3</v>
-      </c>
-      <c r="J116" s="47">
+      <c r="G127" s="45">
+        <v>5</v>
+      </c>
+      <c r="H127" s="45">
+        <v>5</v>
+      </c>
+      <c r="I127" s="45">
+        <v>4</v>
+      </c>
+      <c r="J127" s="45">
+        <v>3</v>
+      </c>
+      <c r="K127" s="45">
+        <v>3</v>
+      </c>
+      <c r="L127" s="45">
+        <v>3</v>
+      </c>
+      <c r="M127" s="45">
+        <v>5</v>
+      </c>
+      <c r="N127" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G127:M127),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O127" s="46" t="str" cm="1">
+        <f t="array" ref="O127">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A128" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B128" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C128" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D128" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E128" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F128" s="44">
+        <v>1103755851</v>
+      </c>
+      <c r="G128" s="45">
+        <v>5</v>
+      </c>
+      <c r="H128" s="45">
+        <v>5</v>
+      </c>
+      <c r="I128" s="45">
+        <v>5</v>
+      </c>
+      <c r="J128" s="45">
+        <v>5</v>
+      </c>
+      <c r="K128" s="45">
+        <v>5</v>
+      </c>
+      <c r="L128" s="45">
+        <v>5</v>
+      </c>
+      <c r="M128" s="45">
+        <v>5</v>
+      </c>
+      <c r="N128" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G128:M128),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O128" s="46" t="str" cm="1">
+        <f t="array" ref="O128">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A129" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B129" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C129" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D129" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E129" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="F129" s="44">
+        <v>1233040347</v>
+      </c>
+      <c r="G129" s="45">
+        <v>5</v>
+      </c>
+      <c r="H129" s="45">
+        <v>5</v>
+      </c>
+      <c r="I129" s="45">
+        <v>5</v>
+      </c>
+      <c r="J129" s="45">
+        <v>3</v>
+      </c>
+      <c r="K129" s="45">
+        <v>4</v>
+      </c>
+      <c r="L129" s="45">
+        <v>3</v>
+      </c>
+      <c r="M129" s="45">
+        <v>5</v>
+      </c>
+      <c r="N129" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G129:M129),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O129" s="46" t="str" cm="1">
+        <f t="array" ref="O129">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A130" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B130" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C130" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D130" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E130" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="F130" s="44">
+        <v>34882674</v>
+      </c>
+      <c r="G130" s="45">
+        <v>5</v>
+      </c>
+      <c r="H130" s="45">
+        <v>4</v>
+      </c>
+      <c r="I130" s="45">
+        <v>4</v>
+      </c>
+      <c r="J130" s="45">
         <v>2</v>
       </c>
-      <c r="K116" s="47">
+      <c r="K130" s="45">
         <v>2</v>
       </c>
-      <c r="L116" s="47">
+      <c r="L130" s="45">
         <v>2</v>
       </c>
-      <c r="M116" s="47">
-        <v>3</v>
-      </c>
-      <c r="N116" s="42">
-        <f>IFERROR(AVERAGE('NIVEL 1'!G116:M116),"-")</f>
-        <v>3</v>
-      </c>
-      <c r="O116" s="43" t="str" cm="1">
-        <f t="array" ref="O116">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+      <c r="M130" s="45">
+        <v>5</v>
+      </c>
+      <c r="N130" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G130:M130),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O130" s="46" t="str" cm="1">
+        <f t="array" ref="O130">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A131" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B131" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C131" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D131" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E131" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="F131" s="44">
+        <v>1003047136</v>
+      </c>
+      <c r="G131" s="45">
+        <v>5</v>
+      </c>
+      <c r="H131" s="45">
+        <v>5</v>
+      </c>
+      <c r="I131" s="45">
+        <v>5</v>
+      </c>
+      <c r="J131" s="45">
+        <v>2</v>
+      </c>
+      <c r="K131" s="45">
+        <v>3</v>
+      </c>
+      <c r="L131" s="45">
+        <v>2</v>
+      </c>
+      <c r="M131" s="45">
+        <v>2</v>
+      </c>
+      <c r="N131" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G131:M131),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O131" s="46" t="str" cm="1">
+        <f t="array" ref="O131">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A132" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B132" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C132" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D132" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E132" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="F132" s="44">
+        <v>1025564047</v>
+      </c>
+      <c r="G132" s="45">
+        <v>5</v>
+      </c>
+      <c r="H132" s="45">
+        <v>5</v>
+      </c>
+      <c r="I132" s="45">
+        <v>5</v>
+      </c>
+      <c r="J132" s="45">
+        <v>4</v>
+      </c>
+      <c r="K132" s="45">
+        <v>4</v>
+      </c>
+      <c r="L132" s="45">
+        <v>4</v>
+      </c>
+      <c r="M132" s="45">
+        <v>5</v>
+      </c>
+      <c r="N132" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G132:M132),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O132" s="46" t="str" cm="1">
+        <f t="array" ref="O132">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A133" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B133" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C133" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D133" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E133" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="F133" s="44">
+        <v>1068440514</v>
+      </c>
+      <c r="G133" s="45">
+        <v>5</v>
+      </c>
+      <c r="H133" s="45">
+        <v>2</v>
+      </c>
+      <c r="I133" s="45">
+        <v>2</v>
+      </c>
+      <c r="J133" s="45">
+        <v>2</v>
+      </c>
+      <c r="K133" s="45">
+        <v>2</v>
+      </c>
+      <c r="L133" s="45">
+        <v>2</v>
+      </c>
+      <c r="M133" s="45">
+        <v>4</v>
+      </c>
+      <c r="N133" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G133:M133),"-")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="O133" s="46" t="str" cm="1">
+        <f t="array" ref="O133">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A134" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B134" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C134" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D134" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E134" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="F134" s="44">
+        <v>1138031915</v>
+      </c>
+      <c r="G134" s="45">
+        <v>5</v>
+      </c>
+      <c r="H134" s="45">
+        <v>5</v>
+      </c>
+      <c r="I134" s="45">
+        <v>4</v>
+      </c>
+      <c r="J134" s="45">
+        <v>3</v>
+      </c>
+      <c r="K134" s="45">
+        <v>4</v>
+      </c>
+      <c r="L134" s="45">
+        <v>3</v>
+      </c>
+      <c r="M134" s="45">
+        <v>3</v>
+      </c>
+      <c r="N134" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G134:M134),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O134" s="46" t="str" cm="1">
+        <f t="array" ref="O134">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A135" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B135" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C135" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D135" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E135" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F135" s="44">
+        <v>1138032050</v>
+      </c>
+      <c r="G135" s="45">
+        <v>5</v>
+      </c>
+      <c r="H135" s="45">
+        <v>2</v>
+      </c>
+      <c r="I135" s="45">
+        <v>2</v>
+      </c>
+      <c r="J135" s="45">
+        <v>2</v>
+      </c>
+      <c r="K135" s="45">
+        <v>2</v>
+      </c>
+      <c r="L135" s="45">
+        <v>2</v>
+      </c>
+      <c r="M135" s="45">
+        <v>2</v>
+      </c>
+      <c r="N135" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G135:M135),"-")</f>
+        <v>2.4285714285714284</v>
+      </c>
+      <c r="O135" s="46" t="str" cm="1">
+        <f t="array" ref="O135">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -19112,29 +20094,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O79"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" customWidth="1"/>
-    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6328125" customWidth="1"/>
-    <col min="5" max="5" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.54296875" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" customWidth="1"/>
-    <col min="10" max="10" width="8.36328125" customWidth="1"/>
-    <col min="11" max="11" width="7.90625" customWidth="1"/>
-    <col min="12" max="12" width="6.36328125" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" customWidth="1"/>
-    <col min="14" max="14" width="7.08984375" customWidth="1"/>
-    <col min="15" max="15" width="15.6328125" customWidth="1"/>
-    <col min="16" max="16" width="15.36328125" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C1" s="3"/>
       <c r="E1" s="25" t="s">
         <v>58</v>
@@ -19152,7 +20134,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" ht="31.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -19199,7 +20181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -19251,7 +20233,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="29">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -19303,7 +20285,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19355,7 +20337,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19407,7 +20389,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19459,7 +20441,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19511,7 +20493,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19563,7 +20545,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19615,7 +20597,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -19667,7 +20649,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19719,7 +20701,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19771,7 +20753,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19823,7 +20805,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19875,7 +20857,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19927,7 +20909,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -19979,7 +20961,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20031,7 +21013,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20083,7 +21065,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20135,7 +21117,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20187,7 +21169,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20239,7 +21221,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -20291,7 +21273,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20343,7 +21325,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20395,7 +21377,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20447,7 +21429,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20499,7 +21481,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20551,7 +21533,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20603,7 +21585,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20655,7 +21637,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20707,7 +21689,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20759,7 +21741,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20811,7 +21793,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20863,7 +21845,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -20915,7 +21897,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -20967,7 +21949,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21019,7 +22001,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21071,7 +22053,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21123,7 +22105,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21175,7 +22157,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21227,7 +22209,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21279,7 +22261,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21331,7 +22313,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21383,7 +22365,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21435,7 +22417,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21487,7 +22469,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21539,7 +22521,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21591,7 +22573,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21643,7 +22625,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21695,7 +22677,7 @@
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21747,7 +22729,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21799,7 +22781,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21851,7 +22833,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21903,7 +22885,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -21955,7 +22937,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -22007,523 +22989,1199 @@
         <v>-</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="47">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B57" s="48" t="str">
+      <c r="B57" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C57" s="48" t="str">
+      <c r="C57" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D57" s="44">
+      <c r="D57" s="3">
         <v>46199</v>
       </c>
-      <c r="E57" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="47">
-        <v>1062981643</v>
-      </c>
-      <c r="G57" s="47">
-        <v>5</v>
-      </c>
-      <c r="H57" s="47">
-        <v>5</v>
-      </c>
-      <c r="I57" s="47">
-        <v>2</v>
-      </c>
-      <c r="J57" s="47">
-        <v>3</v>
-      </c>
-      <c r="K57" s="47">
-        <v>3</v>
-      </c>
-      <c r="L57" s="47">
-        <v>5</v>
-      </c>
-      <c r="M57" s="47">
-        <v>3</v>
-      </c>
-      <c r="N57" s="42">
+      <c r="E57" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F57" s="1">
+        <v>8203609</v>
+      </c>
+      <c r="G57" s="1">
+        <v>5</v>
+      </c>
+      <c r="H57" s="1">
+        <v>4</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3</v>
+      </c>
+      <c r="K57" s="1">
+        <v>4</v>
+      </c>
+      <c r="L57" s="1">
+        <v>5</v>
+      </c>
+      <c r="M57" s="1">
+        <v>4</v>
+      </c>
+      <c r="N57" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G57:M57),"-")</f>
-        <v>3.7142857142857144</v>
-      </c>
-      <c r="O57" s="49" t="str" cm="1">
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O57" s="18" t="str" cm="1">
         <f t="array" ref="O57">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="47">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B58" s="48" t="str">
+      <c r="B58" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C58" s="48" t="str">
+      <c r="C58" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D58" s="44">
+      <c r="D58" s="3">
         <v>46199</v>
       </c>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F58" s="47">
+      <c r="F58" s="1">
         <v>1027663882</v>
       </c>
-      <c r="G58" s="47">
-        <v>5</v>
-      </c>
-      <c r="H58" s="47">
-        <v>5</v>
-      </c>
-      <c r="I58" s="47">
-        <v>5</v>
-      </c>
-      <c r="J58" s="47">
-        <v>4</v>
-      </c>
-      <c r="K58" s="47">
-        <v>4</v>
-      </c>
-      <c r="L58" s="47">
-        <v>5</v>
-      </c>
-      <c r="M58" s="47">
-        <v>5</v>
-      </c>
-      <c r="N58" s="42">
+      <c r="G58" s="1">
+        <v>5</v>
+      </c>
+      <c r="H58" s="1">
+        <v>5</v>
+      </c>
+      <c r="I58" s="1">
+        <v>5</v>
+      </c>
+      <c r="J58" s="1">
+        <v>4</v>
+      </c>
+      <c r="K58" s="1">
+        <v>4</v>
+      </c>
+      <c r="L58" s="1">
+        <v>5</v>
+      </c>
+      <c r="M58" s="1">
+        <v>5</v>
+      </c>
+      <c r="N58" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G58:M58),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O58" s="49" t="str" cm="1">
+      <c r="O58" s="18" t="str" cm="1">
         <f t="array" ref="O58">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 3</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="47">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B59" s="48" t="str">
+      <c r="B59" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C59" s="48" t="str">
+      <c r="C59" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D59" s="44">
+      <c r="D59" s="3">
         <v>46199</v>
       </c>
-      <c r="E59" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59" s="47">
-        <v>1138032549</v>
-      </c>
-      <c r="G59" s="47">
-        <v>5</v>
-      </c>
-      <c r="H59" s="47">
-        <v>5</v>
-      </c>
-      <c r="I59" s="47">
-        <v>5</v>
-      </c>
-      <c r="J59" s="47">
-        <v>4</v>
-      </c>
-      <c r="K59" s="47">
-        <v>4</v>
-      </c>
-      <c r="L59" s="47">
-        <v>5</v>
-      </c>
-      <c r="M59" s="47">
-        <v>5</v>
-      </c>
-      <c r="N59" s="42">
+      <c r="E59" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1062438398</v>
+      </c>
+      <c r="G59" s="1">
+        <v>4</v>
+      </c>
+      <c r="H59" s="1">
+        <v>4</v>
+      </c>
+      <c r="I59" s="1">
+        <v>3</v>
+      </c>
+      <c r="J59" s="1">
+        <v>3</v>
+      </c>
+      <c r="K59" s="1">
+        <v>2</v>
+      </c>
+      <c r="L59" s="1">
+        <v>4</v>
+      </c>
+      <c r="M59" s="1">
+        <v>2</v>
+      </c>
+      <c r="N59" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G59:M59),"-")</f>
-        <v>4.7142857142857144</v>
-      </c>
-      <c r="O59" s="49" t="str" cm="1">
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O59" s="18" t="str" cm="1">
         <f t="array" ref="O59">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>CAMBIA A NIVEL 3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="47">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B60" s="48" t="str">
+      <c r="B60" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C60" s="48" t="str">
+      <c r="C60" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D60" s="44">
+      <c r="D60" s="3">
         <v>46199</v>
       </c>
-      <c r="E60" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="F60" s="47">
-        <v>1067859838</v>
-      </c>
-      <c r="G60" s="47">
-        <v>4</v>
-      </c>
-      <c r="H60" s="47">
-        <v>4</v>
-      </c>
-      <c r="I60" s="47">
-        <v>4</v>
-      </c>
-      <c r="J60" s="47">
-        <v>4</v>
-      </c>
-      <c r="K60" s="47">
-        <v>4</v>
-      </c>
-      <c r="L60" s="47">
-        <v>5</v>
-      </c>
-      <c r="M60" s="47">
-        <v>1</v>
-      </c>
-      <c r="N60" s="42">
+      <c r="E60" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1062981643</v>
+      </c>
+      <c r="G60" s="1">
+        <v>5</v>
+      </c>
+      <c r="H60" s="1">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1">
+        <v>2</v>
+      </c>
+      <c r="J60" s="1">
+        <v>3</v>
+      </c>
+      <c r="K60" s="1">
+        <v>3</v>
+      </c>
+      <c r="L60" s="1">
+        <v>5</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3</v>
+      </c>
+      <c r="N60" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G60:M60),"-")</f>
         <v>3.7142857142857144</v>
       </c>
-      <c r="O60" s="49" t="str" cm="1">
+      <c r="O60" s="18" t="str" cm="1">
         <f t="array" ref="O60">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="47">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B61" s="48" t="str">
+      <c r="B61" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C61" s="48" t="str">
+      <c r="C61" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D61" s="44">
+      <c r="D61" s="3">
         <v>46199</v>
       </c>
-      <c r="E61" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" s="47">
-        <v>1073817245</v>
-      </c>
-      <c r="G61" s="47">
-        <v>5</v>
-      </c>
-      <c r="H61" s="47">
-        <v>5</v>
-      </c>
-      <c r="I61" s="47">
-        <v>3</v>
-      </c>
-      <c r="J61" s="47">
-        <v>4</v>
-      </c>
-      <c r="K61" s="47">
-        <v>3</v>
-      </c>
-      <c r="L61" s="47">
-        <v>5</v>
-      </c>
-      <c r="M61" s="47">
-        <v>2</v>
-      </c>
-      <c r="N61" s="42">
+      <c r="E61" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1067859838</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4</v>
+      </c>
+      <c r="H61" s="1">
+        <v>4</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4</v>
+      </c>
+      <c r="L61" s="1">
+        <v>5</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G61:M61),"-")</f>
-        <v>3.8571428571428572</v>
-      </c>
-      <c r="O61" s="49" t="str" cm="1">
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O61" s="18" t="str" cm="1">
         <f t="array" ref="O61">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="47">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B62" s="48" t="str">
+      <c r="B62" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C62" s="48" t="str">
+      <c r="C62" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D62" s="44">
+      <c r="D62" s="3">
         <v>46199</v>
       </c>
-      <c r="E62" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="F62" s="47">
-        <v>1140444971</v>
-      </c>
-      <c r="G62" s="47">
-        <v>5</v>
-      </c>
-      <c r="H62" s="47">
-        <v>5</v>
-      </c>
-      <c r="I62" s="47">
-        <v>5</v>
-      </c>
-      <c r="J62" s="47">
-        <v>5</v>
-      </c>
-      <c r="K62" s="47">
-        <v>4</v>
-      </c>
-      <c r="L62" s="47">
-        <v>5</v>
-      </c>
-      <c r="M62" s="47">
-        <v>4</v>
-      </c>
-      <c r="N62" s="42">
+      <c r="E62" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1067945529</v>
+      </c>
+      <c r="G62" s="1">
+        <v>4</v>
+      </c>
+      <c r="H62" s="1">
+        <v>4</v>
+      </c>
+      <c r="I62" s="1">
+        <v>3</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1">
+        <v>4</v>
+      </c>
+      <c r="L62" s="1">
+        <v>4</v>
+      </c>
+      <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G62:M62),"-")</f>
-        <v>4.7142857142857144</v>
-      </c>
-      <c r="O62" s="49" t="str" cm="1">
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O62" s="18" t="str" cm="1">
         <f t="array" ref="O62">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>CAMBIA A NIVEL 3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="47">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B63" s="48" t="str">
+      <c r="B63" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C63" s="48" t="str">
+      <c r="C63" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D63" s="44">
+      <c r="D63" s="3">
         <v>46199</v>
       </c>
-      <c r="E63" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F63" s="47">
-        <v>1067945529</v>
-      </c>
-      <c r="G63" s="47">
-        <v>4</v>
-      </c>
-      <c r="H63" s="47">
-        <v>4</v>
-      </c>
-      <c r="I63" s="47">
-        <v>3</v>
-      </c>
-      <c r="J63" s="47">
-        <v>4</v>
-      </c>
-      <c r="K63" s="47">
-        <v>4</v>
-      </c>
-      <c r="L63" s="47">
-        <v>4</v>
-      </c>
-      <c r="M63" s="47">
-        <v>1</v>
-      </c>
-      <c r="N63" s="42">
+      <c r="E63" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1073817245</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" s="1">
+        <v>5</v>
+      </c>
+      <c r="I63" s="1">
+        <v>3</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1">
+        <v>3</v>
+      </c>
+      <c r="L63" s="1">
+        <v>5</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+      <c r="N63" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G63:M63),"-")</f>
-        <v>3.4285714285714284</v>
-      </c>
-      <c r="O63" s="49" t="str" cm="1">
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O63" s="18" t="str" cm="1">
         <f t="array" ref="O63">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="47">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B64" s="48" t="str">
+      <c r="B64" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C64" s="48" t="str">
+      <c r="C64" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D64" s="44">
+      <c r="D64" s="3">
         <v>46199</v>
       </c>
-      <c r="E64" s="45" t="s">
+      <c r="E64" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F64" s="47">
+      <c r="F64" s="1">
         <v>1137975856</v>
       </c>
-      <c r="G64" s="47">
-        <v>4</v>
-      </c>
-      <c r="H64" s="47">
-        <v>4</v>
-      </c>
-      <c r="I64" s="47">
-        <v>4</v>
-      </c>
-      <c r="J64" s="47">
-        <v>4</v>
-      </c>
-      <c r="K64" s="47">
-        <v>4</v>
-      </c>
-      <c r="L64" s="47">
-        <v>5</v>
-      </c>
-      <c r="M64" s="47">
-        <v>4</v>
-      </c>
-      <c r="N64" s="42">
+      <c r="G64" s="1">
+        <v>4</v>
+      </c>
+      <c r="H64" s="1">
+        <v>4</v>
+      </c>
+      <c r="I64" s="1">
+        <v>4</v>
+      </c>
+      <c r="J64" s="1">
+        <v>4</v>
+      </c>
+      <c r="K64" s="1">
+        <v>4</v>
+      </c>
+      <c r="L64" s="1">
+        <v>5</v>
+      </c>
+      <c r="M64" s="1">
+        <v>4</v>
+      </c>
+      <c r="N64" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G64:M64),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O64" s="49" t="str" cm="1">
+      <c r="O64" s="18" t="str" cm="1">
         <f t="array" ref="O64">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="47">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B65" s="48" t="str">
+      <c r="B65" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C65" s="48" t="str">
+      <c r="C65" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D65" s="44">
+      <c r="D65" s="3">
         <v>46199</v>
       </c>
-      <c r="E65" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="F65" s="47">
-        <v>8203609</v>
-      </c>
-      <c r="G65" s="47">
-        <v>5</v>
-      </c>
-      <c r="H65" s="47">
-        <v>4</v>
-      </c>
-      <c r="I65" s="47">
-        <v>5</v>
-      </c>
-      <c r="J65" s="47">
-        <v>3</v>
-      </c>
-      <c r="K65" s="47">
-        <v>4</v>
-      </c>
-      <c r="L65" s="47">
-        <v>5</v>
-      </c>
-      <c r="M65" s="47">
-        <v>4</v>
-      </c>
-      <c r="N65" s="42">
+      <c r="E65" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1138032549</v>
+      </c>
+      <c r="G65" s="1">
+        <v>5</v>
+      </c>
+      <c r="H65" s="1">
+        <v>5</v>
+      </c>
+      <c r="I65" s="1">
+        <v>5</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4</v>
+      </c>
+      <c r="K65" s="1">
+        <v>4</v>
+      </c>
+      <c r="L65" s="1">
+        <v>5</v>
+      </c>
+      <c r="M65" s="1">
+        <v>5</v>
+      </c>
+      <c r="N65" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G65:M65),"-")</f>
-        <v>4.2857142857142856</v>
-      </c>
-      <c r="O65" s="49" t="str" cm="1">
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O65" s="18" t="str" cm="1">
         <f t="array" ref="O65">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="47">
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B66" s="48" t="str">
+      <c r="B66" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C66" s="48" t="str">
+      <c r="C66" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D66" s="44">
+      <c r="D66" s="3">
         <v>46199</v>
       </c>
-      <c r="E66" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="F66" s="47">
-        <v>1062438398</v>
-      </c>
-      <c r="G66" s="47">
-        <v>4</v>
-      </c>
-      <c r="H66" s="47">
-        <v>4</v>
-      </c>
-      <c r="I66" s="47">
-        <v>3</v>
-      </c>
-      <c r="J66" s="47">
-        <v>3</v>
-      </c>
-      <c r="K66" s="47">
+      <c r="E66" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1140444971</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5</v>
+      </c>
+      <c r="H66" s="1">
+        <v>5</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
+        <v>4</v>
+      </c>
+      <c r="L66" s="1">
+        <v>5</v>
+      </c>
+      <c r="M66" s="1">
+        <v>4</v>
+      </c>
+      <c r="N66" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G66:M66),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O66" s="18" t="str" cm="1">
+        <f t="array" ref="O66">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B67" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C67" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D67" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E67" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="F67" s="45">
+        <v>8203609</v>
+      </c>
+      <c r="G67" s="45">
+        <v>5</v>
+      </c>
+      <c r="H67" s="45">
+        <v>4</v>
+      </c>
+      <c r="I67" s="45">
+        <v>5</v>
+      </c>
+      <c r="J67" s="45">
+        <v>3</v>
+      </c>
+      <c r="K67" s="45">
+        <v>4</v>
+      </c>
+      <c r="L67" s="45">
+        <v>5</v>
+      </c>
+      <c r="M67" s="45">
+        <v>5</v>
+      </c>
+      <c r="N67" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G67:M67),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O67" s="48" t="str" cm="1">
+        <f t="array" ref="O67">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B68" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C68" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D68" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E68" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F68" s="45">
+        <v>1001897545</v>
+      </c>
+      <c r="G68" s="45">
+        <v>5</v>
+      </c>
+      <c r="H68" s="45">
+        <v>4</v>
+      </c>
+      <c r="I68" s="45">
+        <v>3</v>
+      </c>
+      <c r="J68" s="45">
+        <v>4</v>
+      </c>
+      <c r="K68" s="45">
+        <v>4</v>
+      </c>
+      <c r="L68" s="45">
+        <v>5</v>
+      </c>
+      <c r="M68" s="45">
+        <v>3</v>
+      </c>
+      <c r="N68" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G68:M68),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O68" s="48" t="str" cm="1">
+        <f t="array" ref="O68">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B69" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C69" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D69" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E69" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="45">
+        <v>1029722943</v>
+      </c>
+      <c r="G69" s="45">
+        <v>5</v>
+      </c>
+      <c r="H69" s="45">
+        <v>4</v>
+      </c>
+      <c r="I69" s="45">
+        <v>3</v>
+      </c>
+      <c r="J69" s="45">
+        <v>4</v>
+      </c>
+      <c r="K69" s="45">
+        <v>4</v>
+      </c>
+      <c r="L69" s="45">
+        <v>5</v>
+      </c>
+      <c r="M69" s="45">
+        <v>5</v>
+      </c>
+      <c r="N69" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G69:M69),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O69" s="48" t="str" cm="1">
+        <f t="array" ref="O69">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B70" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C70" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D70" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E70" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="45">
+        <v>1062544508</v>
+      </c>
+      <c r="G70" s="45">
+        <v>4</v>
+      </c>
+      <c r="H70" s="45">
+        <v>4</v>
+      </c>
+      <c r="I70" s="45">
         <v>2</v>
       </c>
-      <c r="L66" s="47">
-        <v>4</v>
-      </c>
-      <c r="M66" s="47">
+      <c r="J70" s="45">
+        <v>3</v>
+      </c>
+      <c r="K70" s="45">
+        <v>3</v>
+      </c>
+      <c r="L70" s="45">
+        <v>3</v>
+      </c>
+      <c r="M70" s="45">
         <v>2</v>
       </c>
-      <c r="N66" s="42">
-        <f>IFERROR(AVERAGE('NIVEL 2'!G66:M66),"-")</f>
+      <c r="N70" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G70:M70),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O70" s="48" t="str" cm="1">
+        <f t="array" ref="O70">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B71" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C71" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D71" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="45">
+        <v>1062981643</v>
+      </c>
+      <c r="G71" s="45">
+        <v>5</v>
+      </c>
+      <c r="H71" s="45">
+        <v>5</v>
+      </c>
+      <c r="I71" s="45">
+        <v>3</v>
+      </c>
+      <c r="J71" s="45">
+        <v>4</v>
+      </c>
+      <c r="K71" s="45">
+        <v>3</v>
+      </c>
+      <c r="L71" s="45">
+        <v>5</v>
+      </c>
+      <c r="M71" s="45">
+        <v>3</v>
+      </c>
+      <c r="N71" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G71:M71),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O71" s="48" t="str" cm="1">
+        <f t="array" ref="O71">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B72" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C72" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D72" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="F72" s="45">
+        <v>1065443120</v>
+      </c>
+      <c r="G72" s="45">
+        <v>4</v>
+      </c>
+      <c r="H72" s="45">
+        <v>4</v>
+      </c>
+      <c r="I72" s="45">
+        <v>2</v>
+      </c>
+      <c r="J72" s="45">
+        <v>3</v>
+      </c>
+      <c r="K72" s="45">
+        <v>3</v>
+      </c>
+      <c r="L72" s="45">
+        <v>4</v>
+      </c>
+      <c r="M72" s="45">
+        <v>2</v>
+      </c>
+      <c r="N72" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G72:M72),"-")</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O66" s="49" t="str" cm="1">
-        <f t="array" ref="O66">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+      <c r="O72" s="48" t="str" cm="1">
+        <f t="array" ref="O72">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B73" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C73" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D73" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E73" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="45">
+        <v>1067859838</v>
+      </c>
+      <c r="G73" s="45">
+        <v>5</v>
+      </c>
+      <c r="H73" s="45">
+        <v>4</v>
+      </c>
+      <c r="I73" s="45">
+        <v>5</v>
+      </c>
+      <c r="J73" s="45">
+        <v>5</v>
+      </c>
+      <c r="K73" s="45">
+        <v>5</v>
+      </c>
+      <c r="L73" s="45">
+        <v>5</v>
+      </c>
+      <c r="M73" s="45">
+        <v>1</v>
+      </c>
+      <c r="N73" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G73:M73),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O73" s="48" t="str" cm="1">
+        <f t="array" ref="O73">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B74" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C74" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D74" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E74" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" s="45">
+        <v>1067945529</v>
+      </c>
+      <c r="G74" s="45">
+        <v>5</v>
+      </c>
+      <c r="H74" s="45">
+        <v>4</v>
+      </c>
+      <c r="I74" s="45">
+        <v>4</v>
+      </c>
+      <c r="J74" s="45">
+        <v>5</v>
+      </c>
+      <c r="K74" s="45">
+        <v>5</v>
+      </c>
+      <c r="L74" s="45">
+        <v>5</v>
+      </c>
+      <c r="M74" s="45">
+        <v>1</v>
+      </c>
+      <c r="N74" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G74:M74),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O74" s="48" t="str" cm="1">
+        <f t="array" ref="O74">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B75" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C75" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D75" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E75" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="45">
+        <v>1073817245</v>
+      </c>
+      <c r="G75" s="45">
+        <v>5</v>
+      </c>
+      <c r="H75" s="45">
+        <v>5</v>
+      </c>
+      <c r="I75" s="45">
+        <v>4</v>
+      </c>
+      <c r="J75" s="45">
+        <v>4</v>
+      </c>
+      <c r="K75" s="45">
+        <v>3</v>
+      </c>
+      <c r="L75" s="45">
+        <v>5</v>
+      </c>
+      <c r="M75" s="45">
+        <v>2</v>
+      </c>
+      <c r="N75" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G75:M75),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O75" s="48" t="str" cm="1">
+        <f t="array" ref="O75">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B76" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C76" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D76" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="45">
+        <v>1104382840</v>
+      </c>
+      <c r="G76" s="45">
+        <v>5</v>
+      </c>
+      <c r="H76" s="45">
+        <v>4</v>
+      </c>
+      <c r="I76" s="45">
+        <v>3</v>
+      </c>
+      <c r="J76" s="45">
+        <v>3</v>
+      </c>
+      <c r="K76" s="45">
+        <v>4</v>
+      </c>
+      <c r="L76" s="45">
+        <v>5</v>
+      </c>
+      <c r="M76" s="45">
+        <v>1</v>
+      </c>
+      <c r="N76" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G76:M76),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O76" s="48" t="str" cm="1">
+        <f t="array" ref="O76">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B77" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C77" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D77" s="42">
+        <v>46234</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="F77" s="45">
+        <v>1137975856</v>
+      </c>
+      <c r="G77" s="45">
+        <v>5</v>
+      </c>
+      <c r="H77" s="45">
+        <v>4</v>
+      </c>
+      <c r="I77" s="45">
+        <v>4</v>
+      </c>
+      <c r="J77" s="45">
+        <v>5</v>
+      </c>
+      <c r="K77" s="45">
+        <v>5</v>
+      </c>
+      <c r="L77" s="45">
+        <v>4</v>
+      </c>
+      <c r="M77" s="45">
+        <v>5</v>
+      </c>
+      <c r="N77" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G77:M77),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O77" s="48" t="str" cm="1">
+        <f t="array" ref="O77">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B78" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C78" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D78" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E78" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="45">
+        <v>1138032406</v>
+      </c>
+      <c r="G78" s="45">
+        <v>5</v>
+      </c>
+      <c r="H78" s="45">
+        <v>5</v>
+      </c>
+      <c r="I78" s="45">
+        <v>5</v>
+      </c>
+      <c r="J78" s="45">
+        <v>4</v>
+      </c>
+      <c r="K78" s="45">
+        <v>3</v>
+      </c>
+      <c r="L78" s="45">
+        <v>5</v>
+      </c>
+      <c r="M78" s="45">
+        <v>2</v>
+      </c>
+      <c r="N78" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G78:M78),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O78" s="48" t="str" cm="1">
+        <f t="array" ref="O78">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B79" s="47" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C79" s="47" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D79" s="42">
+        <v>46233</v>
+      </c>
+      <c r="E79" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="45">
+        <v>1138032417</v>
+      </c>
+      <c r="G79" s="45">
+        <v>5</v>
+      </c>
+      <c r="H79" s="45">
+        <v>4</v>
+      </c>
+      <c r="I79" s="45">
+        <v>4</v>
+      </c>
+      <c r="J79" s="45">
+        <v>4</v>
+      </c>
+      <c r="K79" s="45">
+        <v>3</v>
+      </c>
+      <c r="L79" s="45">
+        <v>5</v>
+      </c>
+      <c r="M79" s="45">
+        <v>4</v>
+      </c>
+      <c r="N79" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G79:M79),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O79" s="48" t="str" cm="1">
+        <f t="array" ref="O79">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -22551,32 +24209,32 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.36328125" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.36328125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.90625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.36328125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.90625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.36328125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="5.54296875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.453125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.36328125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6328125" customWidth="1"/>
-    <col min="21" max="21" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
+    <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E1" s="28" t="s">
         <v>59</v>
       </c>
@@ -22597,7 +24255,7 @@
       <c r="R1" s="31"/>
       <c r="S1" s="31"/>
     </row>
-    <row r="2" spans="1:21" ht="42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>61</v>
       </c>
@@ -22662,7 +24320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -22732,7 +24390,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>1</v>
@@ -22794,7 +24452,7 @@
         <v>5</v>
       </c>
       <c r="T4" s="24">
-        <f t="shared" ref="T4:T5" si="0">IFERROR(AVERAGE(G4:S4),"-")</f>
+        <f>IFERROR(AVERAGE(G4:S4),"-")</f>
         <v>4.9230769230769234</v>
       </c>
       <c r="U4" s="32" t="str" cm="1">
@@ -22802,7 +24460,7 @@
         <v>CAMBIA A EQUIPO</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>2</v>
@@ -22864,7 +24522,7 @@
         <v>4</v>
       </c>
       <c r="T5" s="24">
-        <f t="shared" si="0"/>
+        <f>IFERROR(AVERAGE(G5:S5),"-")</f>
         <v>4.0769230769230766</v>
       </c>
       <c r="U5" s="32" t="str" cm="1">
@@ -22872,7 +24530,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>3</v>
@@ -22942,7 +24600,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -23004,7 +24662,7 @@
         <v>5</v>
       </c>
       <c r="T7" s="24">
-        <f t="shared" ref="T7:T8" si="1">IFERROR(AVERAGE(G7:S7),"-")</f>
+        <f>IFERROR(AVERAGE(G7:S7),"-")</f>
         <v>4.3076923076923075</v>
       </c>
       <c r="U7" s="32" t="str" cm="1">
@@ -23012,7 +24670,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>4</v>
@@ -23074,7 +24732,7 @@
         <v>5</v>
       </c>
       <c r="T8" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="T8:T19" si="0">IFERROR(AVERAGE(G8:S8),"-")</f>
         <v>4.384615384615385</v>
       </c>
       <c r="U8" s="32" t="str" cm="1">
@@ -23082,7 +24740,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -23144,7 +24802,7 @@
         <v>5</v>
       </c>
       <c r="T9" s="24">
-        <f t="shared" ref="T9:T10" si="2">IFERROR(AVERAGE(G9:S9),"-")</f>
+        <f t="shared" si="0"/>
         <v>4.4615384615384617</v>
       </c>
       <c r="U9" s="32" t="str" cm="1">
@@ -23152,7 +24810,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>5</v>
@@ -23214,7 +24872,7 @@
         <v>5</v>
       </c>
       <c r="T10" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4.5384615384615383</v>
       </c>
       <c r="U10" s="32" t="str" cm="1">
@@ -23222,213 +24880,633 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="50">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B11" s="41" t="str">
+      <c r="B11" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C11" s="51" t="str">
+      <c r="C11" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="21">
         <v>46203</v>
       </c>
-      <c r="E11" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="54">
-        <v>1062980565</v>
-      </c>
-      <c r="G11" s="54">
-        <v>5</v>
-      </c>
-      <c r="H11" s="54">
-        <v>5</v>
-      </c>
-      <c r="I11" s="54">
-        <v>5</v>
-      </c>
-      <c r="J11" s="54">
-        <v>5</v>
-      </c>
-      <c r="K11" s="54">
-        <v>4</v>
-      </c>
-      <c r="L11" s="54">
-        <v>3</v>
-      </c>
-      <c r="M11" s="54">
-        <v>5</v>
-      </c>
-      <c r="N11" s="54">
-        <v>4</v>
-      </c>
-      <c r="O11" s="54">
-        <v>4</v>
-      </c>
-      <c r="P11" s="54">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="54">
-        <v>2</v>
-      </c>
-      <c r="R11" s="54">
-        <v>4</v>
-      </c>
-      <c r="S11" s="54">
-        <v>5</v>
-      </c>
-      <c r="T11" s="55">
-        <f t="shared" ref="T11:T13" si="3">IFERROR(AVERAGE(G11:S11),"-")</f>
-        <v>4.2307692307692308</v>
-      </c>
-      <c r="U11" s="56" t="str" cm="1">
+      <c r="E11" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="23">
+        <v>1062539643</v>
+      </c>
+      <c r="G11" s="23">
+        <v>5</v>
+      </c>
+      <c r="H11" s="23">
+        <v>5</v>
+      </c>
+      <c r="I11" s="23">
+        <v>5</v>
+      </c>
+      <c r="J11" s="23">
+        <v>5</v>
+      </c>
+      <c r="K11" s="23">
+        <v>4</v>
+      </c>
+      <c r="L11" s="23">
+        <v>4</v>
+      </c>
+      <c r="M11" s="23">
+        <v>5</v>
+      </c>
+      <c r="N11" s="23">
+        <v>4</v>
+      </c>
+      <c r="O11" s="23">
+        <v>5</v>
+      </c>
+      <c r="P11" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="23">
+        <v>3</v>
+      </c>
+      <c r="R11" s="23">
+        <v>4</v>
+      </c>
+      <c r="S11" s="23">
+        <v>5</v>
+      </c>
+      <c r="T11" s="24">
+        <f t="shared" si="0"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U11" s="32" t="str" cm="1">
         <f t="array" ref="U11">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="50">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B12" s="41" t="str">
+      <c r="B12" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C12" s="51" t="str">
+      <c r="C12" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="21">
         <v>46203</v>
       </c>
-      <c r="E12" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="54">
-        <v>1062539643</v>
-      </c>
-      <c r="G12" s="54">
-        <v>5</v>
-      </c>
-      <c r="H12" s="54">
-        <v>5</v>
-      </c>
-      <c r="I12" s="54">
-        <v>5</v>
-      </c>
-      <c r="J12" s="54">
-        <v>5</v>
-      </c>
-      <c r="K12" s="54">
-        <v>4</v>
-      </c>
-      <c r="L12" s="54">
-        <v>4</v>
-      </c>
-      <c r="M12" s="54">
-        <v>5</v>
-      </c>
-      <c r="N12" s="54">
-        <v>4</v>
-      </c>
-      <c r="O12" s="54">
-        <v>5</v>
-      </c>
-      <c r="P12" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="54">
-        <v>3</v>
-      </c>
-      <c r="R12" s="54">
-        <v>4</v>
-      </c>
-      <c r="S12" s="54">
-        <v>5</v>
-      </c>
-      <c r="T12" s="55">
-        <f t="shared" si="3"/>
-        <v>4.5384615384615383</v>
-      </c>
-      <c r="U12" s="56" t="str" cm="1">
+      <c r="E12" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1062980565</v>
+      </c>
+      <c r="G12" s="23">
+        <v>5</v>
+      </c>
+      <c r="H12" s="23">
+        <v>5</v>
+      </c>
+      <c r="I12" s="23">
+        <v>5</v>
+      </c>
+      <c r="J12" s="23">
+        <v>5</v>
+      </c>
+      <c r="K12" s="23">
+        <v>4</v>
+      </c>
+      <c r="L12" s="23">
+        <v>3</v>
+      </c>
+      <c r="M12" s="23">
+        <v>5</v>
+      </c>
+      <c r="N12" s="23">
+        <v>4</v>
+      </c>
+      <c r="O12" s="23">
+        <v>4</v>
+      </c>
+      <c r="P12" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="23">
+        <v>2</v>
+      </c>
+      <c r="R12" s="23">
+        <v>4</v>
+      </c>
+      <c r="S12" s="23">
+        <v>5</v>
+      </c>
+      <c r="T12" s="24">
+        <f t="shared" si="0"/>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U12" s="32" t="str" cm="1">
         <f t="array" ref="U12">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="50">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="36">
         <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
         <v>6</v>
       </c>
-      <c r="B13" s="41" t="str">
+      <c r="B13" s="12" t="str">
         <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
         <v>NIVEL 3</v>
       </c>
-      <c r="C13" s="51" t="str">
+      <c r="C13" s="37" t="str">
         <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>junio</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="21">
         <v>46203</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="23">
         <v>1068439668</v>
       </c>
-      <c r="G13" s="54">
-        <v>5</v>
-      </c>
-      <c r="H13" s="54">
-        <v>5</v>
-      </c>
-      <c r="I13" s="54">
-        <v>5</v>
-      </c>
-      <c r="J13" s="54">
-        <v>5</v>
-      </c>
-      <c r="K13" s="54">
-        <v>4</v>
-      </c>
-      <c r="L13" s="54">
-        <v>3</v>
-      </c>
-      <c r="M13" s="54">
-        <v>5</v>
-      </c>
-      <c r="N13" s="54">
-        <v>4</v>
-      </c>
-      <c r="O13" s="54">
-        <v>5</v>
-      </c>
-      <c r="P13" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="54">
+      <c r="G13" s="23">
+        <v>5</v>
+      </c>
+      <c r="H13" s="23">
+        <v>5</v>
+      </c>
+      <c r="I13" s="23">
+        <v>5</v>
+      </c>
+      <c r="J13" s="23">
+        <v>5</v>
+      </c>
+      <c r="K13" s="23">
+        <v>4</v>
+      </c>
+      <c r="L13" s="23">
+        <v>3</v>
+      </c>
+      <c r="M13" s="23">
+        <v>5</v>
+      </c>
+      <c r="N13" s="23">
+        <v>4</v>
+      </c>
+      <c r="O13" s="23">
+        <v>5</v>
+      </c>
+      <c r="P13" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="23">
         <v>2</v>
       </c>
-      <c r="R13" s="54">
-        <v>4</v>
-      </c>
-      <c r="S13" s="54">
-        <v>5</v>
-      </c>
-      <c r="T13" s="55">
-        <f t="shared" si="3"/>
+      <c r="R13" s="23">
+        <v>4</v>
+      </c>
+      <c r="S13" s="23">
+        <v>5</v>
+      </c>
+      <c r="T13" s="24">
+        <f t="shared" si="0"/>
         <v>4.384615384615385</v>
       </c>
-      <c r="U13" s="56" t="str" cm="1">
+      <c r="U13" s="32" t="str" cm="1">
         <f t="array" ref="U13">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B14" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C14" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D14" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="23">
+        <v>1027663882</v>
+      </c>
+      <c r="G14" s="23">
+        <v>4</v>
+      </c>
+      <c r="H14" s="23">
+        <v>4</v>
+      </c>
+      <c r="I14" s="23">
+        <v>5</v>
+      </c>
+      <c r="J14" s="23">
+        <v>4</v>
+      </c>
+      <c r="K14" s="23">
+        <v>4</v>
+      </c>
+      <c r="L14" s="23">
+        <v>3</v>
+      </c>
+      <c r="M14" s="23">
+        <v>5</v>
+      </c>
+      <c r="N14" s="23">
+        <v>4</v>
+      </c>
+      <c r="O14" s="23">
+        <v>4</v>
+      </c>
+      <c r="P14" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>3</v>
+      </c>
+      <c r="R14" s="23">
+        <v>5</v>
+      </c>
+      <c r="S14" s="23">
+        <v>5</v>
+      </c>
+      <c r="T14" s="24">
+        <f t="shared" si="0"/>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U14" s="32" t="str" cm="1">
+        <f t="array" ref="U14">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B15" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C15" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D15" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="23">
+        <v>1062539643</v>
+      </c>
+      <c r="G15" s="23">
+        <v>5</v>
+      </c>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
+      <c r="I15" s="23">
+        <v>5</v>
+      </c>
+      <c r="J15" s="23">
+        <v>5</v>
+      </c>
+      <c r="K15" s="23">
+        <v>4</v>
+      </c>
+      <c r="L15" s="23">
+        <v>4</v>
+      </c>
+      <c r="M15" s="23">
+        <v>5</v>
+      </c>
+      <c r="N15" s="23">
+        <v>4</v>
+      </c>
+      <c r="O15" s="23">
+        <v>5</v>
+      </c>
+      <c r="P15" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="23">
+        <v>3</v>
+      </c>
+      <c r="R15" s="23">
+        <v>4</v>
+      </c>
+      <c r="S15" s="23">
+        <v>5</v>
+      </c>
+      <c r="T15" s="24">
+        <f t="shared" si="0"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U15" s="32" t="str" cm="1">
+        <f t="array" ref="U15">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B16" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C16" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D16" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="23">
+        <v>1062980565</v>
+      </c>
+      <c r="G16" s="23">
+        <v>5</v>
+      </c>
+      <c r="H16" s="23">
+        <v>5</v>
+      </c>
+      <c r="I16" s="23">
+        <v>5</v>
+      </c>
+      <c r="J16" s="23">
+        <v>5</v>
+      </c>
+      <c r="K16" s="23">
+        <v>4</v>
+      </c>
+      <c r="L16" s="23">
+        <v>3</v>
+      </c>
+      <c r="M16" s="23">
+        <v>5</v>
+      </c>
+      <c r="N16" s="23">
+        <v>4</v>
+      </c>
+      <c r="O16" s="23">
+        <v>4</v>
+      </c>
+      <c r="P16" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="23">
+        <v>2</v>
+      </c>
+      <c r="R16" s="23">
+        <v>4</v>
+      </c>
+      <c r="S16" s="23">
+        <v>5</v>
+      </c>
+      <c r="T16" s="24">
+        <f t="shared" si="0"/>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U16" s="32" t="str" cm="1">
+        <f t="array" ref="U16">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B17" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C17" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D17" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="23">
+        <v>1068439668</v>
+      </c>
+      <c r="G17" s="23">
+        <v>5</v>
+      </c>
+      <c r="H17" s="23">
+        <v>5</v>
+      </c>
+      <c r="I17" s="23">
+        <v>5</v>
+      </c>
+      <c r="J17" s="23">
+        <v>5</v>
+      </c>
+      <c r="K17" s="23">
+        <v>4</v>
+      </c>
+      <c r="L17" s="23">
+        <v>3</v>
+      </c>
+      <c r="M17" s="23">
+        <v>5</v>
+      </c>
+      <c r="N17" s="23">
+        <v>4</v>
+      </c>
+      <c r="O17" s="23">
+        <v>5</v>
+      </c>
+      <c r="P17" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>2</v>
+      </c>
+      <c r="R17" s="23">
+        <v>4</v>
+      </c>
+      <c r="S17" s="23">
+        <v>5</v>
+      </c>
+      <c r="T17" s="24">
+        <f t="shared" si="0"/>
+        <v>4.384615384615385</v>
+      </c>
+      <c r="U17" s="32" t="str" cm="1">
+        <f t="array" ref="U17">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B18" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C18" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D18" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="23">
+        <v>1138032549</v>
+      </c>
+      <c r="G18" s="23">
+        <v>4</v>
+      </c>
+      <c r="H18" s="23">
+        <v>4</v>
+      </c>
+      <c r="I18" s="23">
+        <v>5</v>
+      </c>
+      <c r="J18" s="23">
+        <v>3</v>
+      </c>
+      <c r="K18" s="23">
+        <v>4</v>
+      </c>
+      <c r="L18" s="23">
+        <v>2</v>
+      </c>
+      <c r="M18" s="23">
+        <v>5</v>
+      </c>
+      <c r="N18" s="23">
+        <v>4</v>
+      </c>
+      <c r="O18" s="23">
+        <v>4</v>
+      </c>
+      <c r="P18" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="23">
+        <v>2</v>
+      </c>
+      <c r="R18" s="23">
+        <v>4</v>
+      </c>
+      <c r="S18" s="23">
+        <v>5</v>
+      </c>
+      <c r="T18" s="24">
+        <f t="shared" si="0"/>
+        <v>3.8461538461538463</v>
+      </c>
+      <c r="U18" s="32" t="str" cm="1">
+        <f t="array" ref="U18">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>7</v>
+      </c>
+      <c r="B19" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C19" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>julio</v>
+      </c>
+      <c r="D19" s="21">
+        <v>46233</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="23">
+        <v>1140444971</v>
+      </c>
+      <c r="G19" s="23">
+        <v>5</v>
+      </c>
+      <c r="H19" s="23">
+        <v>2</v>
+      </c>
+      <c r="I19" s="23">
+        <v>5</v>
+      </c>
+      <c r="J19" s="23">
+        <v>4</v>
+      </c>
+      <c r="K19" s="23">
+        <v>4</v>
+      </c>
+      <c r="L19" s="23">
+        <v>2</v>
+      </c>
+      <c r="M19" s="23">
+        <v>5</v>
+      </c>
+      <c r="N19" s="23">
+        <v>4</v>
+      </c>
+      <c r="O19" s="23">
+        <v>5</v>
+      </c>
+      <c r="P19" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="23">
+        <v>2</v>
+      </c>
+      <c r="R19" s="23">
+        <v>3</v>
+      </c>
+      <c r="S19" s="23">
+        <v>5</v>
+      </c>
+      <c r="T19" s="24">
+        <f t="shared" si="0"/>
+        <v>3.9230769230769229</v>
+      </c>
+      <c r="U19" s="32" t="str" cm="1">
+        <f t="array" ref="U19">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -23437,9 +25515,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="T4:T5" formulaRange="1"/>
-  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -23452,15 +25527,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:D138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
@@ -23474,7 +25549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="26"/>
       <c r="B3" s="12" t="s">
         <v>98</v>
@@ -23486,7 +25561,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="12" t="s">
         <v>98</v>
@@ -23498,7 +25573,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="26"/>
       <c r="B5" s="12" t="s">
         <v>98</v>
@@ -23510,7 +25585,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="26"/>
       <c r="B6" s="12" t="s">
         <v>98</v>
@@ -23522,7 +25597,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="26"/>
       <c r="B7" s="12" t="s">
         <v>98</v>
@@ -23534,7 +25609,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="12" t="s">
         <v>98</v>
@@ -23546,7 +25621,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="26"/>
       <c r="B9" s="12" t="s">
         <v>98</v>
@@ -23558,7 +25633,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="26"/>
       <c r="B10" s="12" t="s">
         <v>98</v>
@@ -23570,7 +25645,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="26"/>
       <c r="B11" s="12" t="s">
         <v>98</v>
@@ -23582,7 +25657,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="26"/>
       <c r="B12" s="12" t="s">
         <v>98</v>
@@ -23594,7 +25669,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="26"/>
       <c r="B13" s="12" t="s">
         <v>98</v>
@@ -23606,7 +25681,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="26"/>
       <c r="B14" s="12" t="s">
         <v>98</v>
@@ -23618,7 +25693,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
       <c r="B15" s="12" t="s">
         <v>98</v>
@@ -23630,7 +25705,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="12" t="s">
         <v>98</v>
@@ -23642,733 +25717,733 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="27"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="27"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="38"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="26"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="38"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="26"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="38"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="26"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="38"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="38"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="38"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="38"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="26"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="38"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="26"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="38"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="26"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="38"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="26"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="27"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="26"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="38"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="26"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="38"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="26"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="38"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="26"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="38"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="26"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="38"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="26"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="26"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="38"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="26"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="38"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="26"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="38"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="26"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="38"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="26"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="38"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="26"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="38"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="26"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="38"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="26"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="38"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="26"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="38"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="26"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="38"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="26"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="38"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="26"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="38"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="26"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="38"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="26"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="38"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
       <c r="D50" s="38"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="38"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="26"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="38"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="26"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="38"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="26"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="38"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="26"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="38"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="26"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
       <c r="D56" s="38"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="26"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
       <c r="D57" s="38"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="26"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
       <c r="D58" s="38"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="26"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="38"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="26"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="38"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="26"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
       <c r="D61" s="38"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="26"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
       <c r="D62" s="38"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="26"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
       <c r="D63" s="38"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="26"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
       <c r="D64" s="38"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="26"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="38"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="26"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="38"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="26"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="38"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="26"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
       <c r="D68" s="38"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="26"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
       <c r="D69" s="38"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="26"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="38"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="26"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="38"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="26"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
       <c r="D72" s="38"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="26"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="38"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="26"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
       <c r="D74" s="38"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="26"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
       <c r="D75" s="38"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="26"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
       <c r="D76" s="38"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="26"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="38"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="26"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="38"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="26"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
       <c r="D79" s="38"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="26"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="38"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="26"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="38"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="38"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="26"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="38"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="26"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
       <c r="D84" s="38"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="26"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
       <c r="D85" s="38"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="26"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
       <c r="D86" s="38"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="26"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="38"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="26"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="38"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
       <c r="D89" s="38"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="26"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
       <c r="D90" s="38"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="26"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
       <c r="D91" s="38"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="26"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="38"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="26"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="38"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="26"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
       <c r="D94" s="38"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
       <c r="D95" s="38"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="26"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="38"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="26"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="38"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="26"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="38"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="26"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
       <c r="D99" s="38"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="26"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="38"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="26"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="38"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="26"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="D102" s="38"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="26"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="38"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="26"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
       <c r="D104" s="38"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="26"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
       <c r="D105" s="38"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="26"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="38"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="26"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="D107" s="38"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
       <c r="D108" s="38"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="26"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
       <c r="D109" s="38"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="26"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="38"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="26"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
       <c r="D111" s="38"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="26"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
       <c r="D112" s="38"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="26"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
       <c r="D113" s="38"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="26"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
       <c r="D114" s="38"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="26"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
       <c r="D115" s="38"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="26"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
       <c r="D116" s="38"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="26"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
       <c r="D117" s="38"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="26"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
       <c r="D118" s="38"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="26"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
       <c r="D119" s="38"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="26"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
       <c r="D120" s="38"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="26"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
       <c r="D121" s="38"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="26"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
       <c r="D122" s="38"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="26"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
       <c r="D123" s="38"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="26"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
       <c r="D124" s="38"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="26"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="D125" s="38"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="26"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
       <c r="D126" s="38"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="26"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
       <c r="D127" s="38"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="26"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
       <c r="D128" s="38"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="26"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="38"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="26"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="38"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="26"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="D131" s="38"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="26"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
       <c r="D132" s="38"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="26"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
       <c r="D133" s="38"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="26"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="38"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="26"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="38"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="26"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
       <c r="D136" s="38"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="26"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
       <c r="D137" s="38"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="26"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>

--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A388C0-D85C-48C1-B50D-DA8189529E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720FB67B-2E78-4416-98AF-2D4278C6B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE" sheetId="5" r:id="rId1"/>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -69,6 +69,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -90,7 +92,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -99,7 +101,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +110,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -139,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="173">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -721,6 +723,51 @@
   <si>
     <t>Reyk Sayk Alemán Acuña</t>
   </si>
+  <si>
+    <t>Angel Coneo</t>
+  </si>
+  <si>
+    <t>Violeta Oviedo</t>
+  </si>
+  <si>
+    <t>Helena Torres Buelvas</t>
+  </si>
+  <si>
+    <t>Esteban Marzola Martinez</t>
+  </si>
+  <si>
+    <t>Thael sofia pastrana vasco</t>
+  </si>
+  <si>
+    <t>Sebastian Jiménez Rivillas</t>
+  </si>
+  <si>
+    <t>MARIA ANGEL AYAZO ZABALA</t>
+  </si>
+  <si>
+    <t>Luis Fernando Ricardo Macea</t>
+  </si>
+  <si>
+    <t>Catalina chica</t>
+  </si>
+  <si>
+    <t>Alvaro Jose Perez</t>
+  </si>
+  <si>
+    <t>MARIA ALEJANDRA BURGOS</t>
+  </si>
+  <si>
+    <t>Cathrin Anned Mejia Lopez</t>
+  </si>
+  <si>
+    <t>Kiana Karolina Sanchez López</t>
+  </si>
+  <si>
+    <t>Lorena Marcela Marin Urrea</t>
+  </si>
+  <si>
+    <t>Nahia Lopez Lopez</t>
+  </si>
 </sst>
 </file>
 
@@ -852,7 +899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -969,879 +1016,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor theme="0" tint="-0.14999847407452621"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2575,6 +1754,428 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -2837,6 +2438,425 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3096,13 +3116,13 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3305,7 +3325,7 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3508,7 +3528,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3905,13 +3925,13 @@
                         <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>27</c:v>
+                        <c:v>29</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>38</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>49</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4079,7 +4099,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4247,7 +4267,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -4858,7 +4878,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5066,7 +5086,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5398,13 +5418,13 @@
                         <c:v>48</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>27</c:v>
+                        <c:v>29</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>38</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>49</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -5566,13 +5586,13 @@
                         <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>14</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>19</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -5745,7 +5765,7 @@
                         <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>18</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -5918,7 +5938,7 @@
                         <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -6587,13 +6607,13 @@
                   <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6773,13 +6793,13 @@
                         <c:v>25</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>14</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>19</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -6952,7 +6972,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7125,7 +7145,7 @@
                         <c:v>13</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>18</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7298,7 +7318,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -7471,7 +7491,7 @@
                         <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>0</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>0</c:v>
@@ -12127,7 +12147,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -12140,29 +12160,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="54">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="53">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="52">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="51">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="50">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="49">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="48">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="47">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12171,37 +12191,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O135" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A2:O135" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O161" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74" tableBorderDxfId="73">
+  <autoFilter ref="A2:O161" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O135">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="31">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="72">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="71">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="29">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="70">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="60"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="59">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="17">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="58">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12210,36 +12230,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O79" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A2:O79" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O97" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+  <autoFilter ref="A2:O97" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O79">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="44">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="43">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="12">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="42">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12248,42 +12268,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U19" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62">
-  <autoFilter ref="A2:U19" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U26" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
+  <autoFilter ref="A2:U26" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U19">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="61">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="60">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="45"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="41">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12292,17 +12312,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12800,11 +12820,11 @@
       </c>
       <c r="B7" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A7)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
@@ -12874,27 +12894,27 @@
       </c>
       <c r="B9" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C9" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D9" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F9" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A9)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H9" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -13071,10 +13091,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O135"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" style="10" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
@@ -19083,990 +19103,2339 @@
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A117" s="40">
+      <c r="A117" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B117" s="41" t="str">
+      <c r="B117" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C117" s="41" t="str">
+      <c r="C117" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D117" s="42">
+      <c r="D117" s="3">
         <v>46233</v>
       </c>
-      <c r="E117" s="43" t="s">
+      <c r="E117" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="F117" s="44">
+      <c r="F117" s="1">
         <v>25800927</v>
       </c>
-      <c r="G117" s="45">
-        <v>5</v>
-      </c>
-      <c r="H117" s="45">
-        <v>4</v>
-      </c>
-      <c r="I117" s="45">
-        <v>4</v>
-      </c>
-      <c r="J117" s="45">
+      <c r="G117" s="1">
+        <v>5</v>
+      </c>
+      <c r="H117" s="1">
+        <v>4</v>
+      </c>
+      <c r="I117" s="1">
+        <v>4</v>
+      </c>
+      <c r="J117" s="1">
         <v>2</v>
       </c>
-      <c r="K117" s="45">
+      <c r="K117" s="1">
         <v>2</v>
       </c>
-      <c r="L117" s="45">
+      <c r="L117" s="1">
         <v>2</v>
       </c>
-      <c r="M117" s="45">
+      <c r="M117" s="1">
         <v>3</v>
       </c>
       <c r="N117" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G117:M117),"-")</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O117" s="46" t="str" cm="1">
+      <c r="O117" s="18" t="str" cm="1">
         <f t="array" ref="O117">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A118" s="40">
+      <c r="A118" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B118" s="41" t="str">
+      <c r="B118" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C118" s="41" t="str">
+      <c r="C118" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D118" s="42">
+      <c r="D118" s="3">
         <v>46233</v>
       </c>
-      <c r="E118" s="43" t="s">
+      <c r="E118" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F118" s="44">
+      <c r="F118" s="1">
         <v>50906315</v>
       </c>
-      <c r="G118" s="45">
-        <v>5</v>
-      </c>
-      <c r="H118" s="45">
-        <v>4</v>
-      </c>
-      <c r="I118" s="45">
-        <v>3</v>
-      </c>
-      <c r="J118" s="45">
+      <c r="G118" s="1">
+        <v>5</v>
+      </c>
+      <c r="H118" s="1">
+        <v>4</v>
+      </c>
+      <c r="I118" s="1">
+        <v>3</v>
+      </c>
+      <c r="J118" s="1">
         <v>2</v>
       </c>
-      <c r="K118" s="45">
+      <c r="K118" s="1">
         <v>2</v>
       </c>
-      <c r="L118" s="45">
+      <c r="L118" s="1">
         <v>2</v>
       </c>
-      <c r="M118" s="45">
+      <c r="M118" s="1">
         <v>2</v>
       </c>
       <c r="N118" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G118:M118),"-")</f>
         <v>2.8571428571428572</v>
       </c>
-      <c r="O118" s="46" t="str" cm="1">
+      <c r="O118" s="18" t="str" cm="1">
         <f t="array" ref="O118">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A119" s="40">
+      <c r="A119" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B119" s="41" t="str">
+      <c r="B119" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C119" s="41" t="str">
+      <c r="C119" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D119" s="42">
+      <c r="D119" s="3">
         <v>46233</v>
       </c>
-      <c r="E119" s="43" t="s">
+      <c r="E119" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F119" s="44">
+      <c r="F119" s="1">
         <v>1016116812</v>
       </c>
-      <c r="G119" s="45">
-        <v>5</v>
-      </c>
-      <c r="H119" s="45">
-        <v>5</v>
-      </c>
-      <c r="I119" s="45">
-        <v>5</v>
-      </c>
-      <c r="J119" s="45">
-        <v>4</v>
-      </c>
-      <c r="K119" s="45">
-        <v>4</v>
-      </c>
-      <c r="L119" s="45">
-        <v>4</v>
-      </c>
-      <c r="M119" s="45">
+      <c r="G119" s="1">
+        <v>5</v>
+      </c>
+      <c r="H119" s="1">
+        <v>5</v>
+      </c>
+      <c r="I119" s="1">
+        <v>5</v>
+      </c>
+      <c r="J119" s="1">
+        <v>4</v>
+      </c>
+      <c r="K119" s="1">
+        <v>4</v>
+      </c>
+      <c r="L119" s="1">
+        <v>4</v>
+      </c>
+      <c r="M119" s="1">
         <v>5</v>
       </c>
       <c r="N119" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G119:M119),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O119" s="46" t="str" cm="1">
+      <c r="O119" s="18" t="str" cm="1">
         <f t="array" ref="O119">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A120" s="40">
+      <c r="A120" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B120" s="41" t="str">
+      <c r="B120" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C120" s="41" t="str">
+      <c r="C120" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D120" s="42">
+      <c r="D120" s="3">
         <v>46233</v>
       </c>
-      <c r="E120" s="43" t="s">
+      <c r="E120" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="44">
+      <c r="F120" s="1">
         <v>1037236492</v>
       </c>
-      <c r="G120" s="45">
-        <v>5</v>
-      </c>
-      <c r="H120" s="45">
-        <v>5</v>
-      </c>
-      <c r="I120" s="45">
-        <v>5</v>
-      </c>
-      <c r="J120" s="45">
-        <v>4</v>
-      </c>
-      <c r="K120" s="45">
-        <v>5</v>
-      </c>
-      <c r="L120" s="45">
-        <v>4</v>
-      </c>
-      <c r="M120" s="45">
+      <c r="G120" s="1">
+        <v>5</v>
+      </c>
+      <c r="H120" s="1">
+        <v>5</v>
+      </c>
+      <c r="I120" s="1">
+        <v>5</v>
+      </c>
+      <c r="J120" s="1">
+        <v>4</v>
+      </c>
+      <c r="K120" s="1">
+        <v>5</v>
+      </c>
+      <c r="L120" s="1">
+        <v>4</v>
+      </c>
+      <c r="M120" s="1">
         <v>5</v>
       </c>
       <c r="N120" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G120:M120),"-")</f>
         <v>4.7142857142857144</v>
       </c>
-      <c r="O120" s="46" t="str" cm="1">
+      <c r="O120" s="18" t="str" cm="1">
         <f t="array" ref="O120">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A121" s="40">
+      <c r="A121" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B121" s="41" t="str">
+      <c r="B121" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C121" s="41" t="str">
+      <c r="C121" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D121" s="42">
+      <c r="D121" s="3">
         <v>46233</v>
       </c>
-      <c r="E121" s="43" t="s">
+      <c r="E121" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F121" s="44">
+      <c r="F121" s="1">
         <v>1062535690</v>
       </c>
-      <c r="G121" s="45">
-        <v>5</v>
-      </c>
-      <c r="H121" s="45">
-        <v>5</v>
-      </c>
-      <c r="I121" s="45">
-        <v>5</v>
-      </c>
-      <c r="J121" s="45">
-        <v>4</v>
-      </c>
-      <c r="K121" s="45">
-        <v>4</v>
-      </c>
-      <c r="L121" s="45">
-        <v>4</v>
-      </c>
-      <c r="M121" s="45">
+      <c r="G121" s="1">
+        <v>5</v>
+      </c>
+      <c r="H121" s="1">
+        <v>5</v>
+      </c>
+      <c r="I121" s="1">
+        <v>5</v>
+      </c>
+      <c r="J121" s="1">
+        <v>4</v>
+      </c>
+      <c r="K121" s="1">
+        <v>4</v>
+      </c>
+      <c r="L121" s="1">
+        <v>4</v>
+      </c>
+      <c r="M121" s="1">
         <v>5</v>
       </c>
       <c r="N121" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G121:M121),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O121" s="46" t="str" cm="1">
+      <c r="O121" s="18" t="str" cm="1">
         <f t="array" ref="O121">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A122" s="40">
+      <c r="A122" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B122" s="41" t="str">
+      <c r="B122" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C122" s="41" t="str">
+      <c r="C122" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D122" s="42">
+      <c r="D122" s="3">
         <v>46233</v>
       </c>
-      <c r="E122" s="43" t="s">
+      <c r="E122" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F122" s="44">
+      <c r="F122" s="1">
         <v>1062540875</v>
       </c>
-      <c r="G122" s="45">
-        <v>5</v>
-      </c>
-      <c r="H122" s="45">
-        <v>5</v>
-      </c>
-      <c r="I122" s="45">
-        <v>4</v>
-      </c>
-      <c r="J122" s="45">
-        <v>3</v>
-      </c>
-      <c r="K122" s="45">
-        <v>3</v>
-      </c>
-      <c r="L122" s="45">
-        <v>3</v>
-      </c>
-      <c r="M122" s="45">
+      <c r="G122" s="1">
+        <v>5</v>
+      </c>
+      <c r="H122" s="1">
+        <v>5</v>
+      </c>
+      <c r="I122" s="1">
+        <v>4</v>
+      </c>
+      <c r="J122" s="1">
+        <v>3</v>
+      </c>
+      <c r="K122" s="1">
+        <v>3</v>
+      </c>
+      <c r="L122" s="1">
+        <v>3</v>
+      </c>
+      <c r="M122" s="1">
         <v>5</v>
       </c>
       <c r="N122" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G122:M122),"-")</f>
         <v>4</v>
       </c>
-      <c r="O122" s="46" t="str" cm="1">
+      <c r="O122" s="18" t="str" cm="1">
         <f t="array" ref="O122">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A123" s="40">
+      <c r="A123" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B123" s="41" t="str">
+      <c r="B123" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C123" s="41" t="str">
+      <c r="C123" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D123" s="42">
+      <c r="D123" s="3">
         <v>46233</v>
       </c>
-      <c r="E123" s="43" t="s">
+      <c r="E123" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F123" s="44">
+      <c r="F123" s="1">
         <v>1062979535</v>
       </c>
-      <c r="G123" s="45">
-        <v>5</v>
-      </c>
-      <c r="H123" s="45">
-        <v>5</v>
-      </c>
-      <c r="I123" s="45">
-        <v>4</v>
-      </c>
-      <c r="J123" s="45">
-        <v>4</v>
-      </c>
-      <c r="K123" s="45">
-        <v>3</v>
-      </c>
-      <c r="L123" s="45">
-        <v>3</v>
-      </c>
-      <c r="M123" s="45">
+      <c r="G123" s="1">
+        <v>5</v>
+      </c>
+      <c r="H123" s="1">
+        <v>5</v>
+      </c>
+      <c r="I123" s="1">
+        <v>4</v>
+      </c>
+      <c r="J123" s="1">
+        <v>4</v>
+      </c>
+      <c r="K123" s="1">
+        <v>3</v>
+      </c>
+      <c r="L123" s="1">
+        <v>3</v>
+      </c>
+      <c r="M123" s="1">
         <v>5</v>
       </c>
       <c r="N123" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G123:M123),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O123" s="46" t="str" cm="1">
+      <c r="O123" s="18" t="str" cm="1">
         <f t="array" ref="O123">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A124" s="40">
+      <c r="A124" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B124" s="41" t="str">
+      <c r="B124" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C124" s="41" t="str">
+      <c r="C124" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D124" s="42">
+      <c r="D124" s="3">
         <v>46233</v>
       </c>
-      <c r="E124" s="43" t="s">
+      <c r="E124" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F124" s="44">
+      <c r="F124" s="1">
         <v>1068442748</v>
       </c>
-      <c r="G124" s="45">
-        <v>5</v>
-      </c>
-      <c r="H124" s="45">
-        <v>3</v>
-      </c>
-      <c r="I124" s="45">
-        <v>3</v>
-      </c>
-      <c r="J124" s="45">
+      <c r="G124" s="1">
+        <v>5</v>
+      </c>
+      <c r="H124" s="1">
+        <v>3</v>
+      </c>
+      <c r="I124" s="1">
+        <v>3</v>
+      </c>
+      <c r="J124" s="1">
         <v>1</v>
       </c>
-      <c r="K124" s="45">
+      <c r="K124" s="1">
         <v>1</v>
       </c>
-      <c r="L124" s="45">
+      <c r="L124" s="1">
         <v>1</v>
       </c>
-      <c r="M124" s="45">
+      <c r="M124" s="1">
         <v>1</v>
       </c>
       <c r="N124" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G124:M124),"-")</f>
         <v>2.1428571428571428</v>
       </c>
-      <c r="O124" s="46" t="str" cm="1">
+      <c r="O124" s="18" t="str" cm="1">
         <f t="array" ref="O124">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A125" s="40">
+      <c r="A125" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B125" s="41" t="str">
+      <c r="B125" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C125" s="41" t="str">
+      <c r="C125" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D125" s="42">
+      <c r="D125" s="3">
         <v>46233</v>
       </c>
-      <c r="E125" s="43" t="s">
+      <c r="E125" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F125" s="44">
+      <c r="F125" s="1">
         <v>1068443767</v>
       </c>
-      <c r="G125" s="45">
-        <v>5</v>
-      </c>
-      <c r="H125" s="45">
-        <v>5</v>
-      </c>
-      <c r="I125" s="45">
-        <v>4</v>
-      </c>
-      <c r="J125" s="45">
-        <v>4</v>
-      </c>
-      <c r="K125" s="45">
+      <c r="G125" s="1">
+        <v>5</v>
+      </c>
+      <c r="H125" s="1">
+        <v>5</v>
+      </c>
+      <c r="I125" s="1">
+        <v>4</v>
+      </c>
+      <c r="J125" s="1">
+        <v>4</v>
+      </c>
+      <c r="K125" s="1">
         <v>2</v>
       </c>
-      <c r="L125" s="45">
+      <c r="L125" s="1">
         <v>2</v>
       </c>
-      <c r="M125" s="45">
+      <c r="M125" s="1">
         <v>5</v>
       </c>
       <c r="N125" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G125:M125),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O125" s="46" t="str" cm="1">
+      <c r="O125" s="18" t="str" cm="1">
         <f t="array" ref="O125">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A126" s="40">
+      <c r="A126" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B126" s="41" t="str">
+      <c r="B126" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C126" s="41" t="str">
+      <c r="C126" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D126" s="42">
+      <c r="D126" s="3">
         <v>46233</v>
       </c>
-      <c r="E126" s="43" t="s">
+      <c r="E126" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F126" s="44">
+      <c r="F126" s="1">
         <v>1068445190</v>
       </c>
-      <c r="G126" s="45">
-        <v>5</v>
-      </c>
-      <c r="H126" s="45">
-        <v>3</v>
-      </c>
-      <c r="I126" s="45">
+      <c r="G126" s="1">
+        <v>5</v>
+      </c>
+      <c r="H126" s="1">
+        <v>3</v>
+      </c>
+      <c r="I126" s="1">
         <v>2</v>
       </c>
-      <c r="J126" s="45">
+      <c r="J126" s="1">
         <v>2</v>
       </c>
-      <c r="K126" s="45">
+      <c r="K126" s="1">
         <v>1</v>
       </c>
-      <c r="L126" s="45">
+      <c r="L126" s="1">
         <v>1</v>
       </c>
-      <c r="M126" s="45">
+      <c r="M126" s="1">
         <v>2</v>
       </c>
       <c r="N126" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G126:M126),"-")</f>
         <v>2.2857142857142856</v>
       </c>
-      <c r="O126" s="46" t="str" cm="1">
+      <c r="O126" s="18" t="str" cm="1">
         <f t="array" ref="O126">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A127" s="40">
+      <c r="A127" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B127" s="41" t="str">
+      <c r="B127" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C127" s="41" t="str">
+      <c r="C127" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D127" s="42">
+      <c r="D127" s="3">
         <v>46233</v>
       </c>
-      <c r="E127" s="43" t="s">
+      <c r="E127" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F127" s="44">
+      <c r="F127" s="1">
         <v>1091978602</v>
       </c>
-      <c r="G127" s="45">
-        <v>5</v>
-      </c>
-      <c r="H127" s="45">
-        <v>5</v>
-      </c>
-      <c r="I127" s="45">
-        <v>4</v>
-      </c>
-      <c r="J127" s="45">
-        <v>3</v>
-      </c>
-      <c r="K127" s="45">
-        <v>3</v>
-      </c>
-      <c r="L127" s="45">
-        <v>3</v>
-      </c>
-      <c r="M127" s="45">
+      <c r="G127" s="1">
+        <v>5</v>
+      </c>
+      <c r="H127" s="1">
+        <v>5</v>
+      </c>
+      <c r="I127" s="1">
+        <v>4</v>
+      </c>
+      <c r="J127" s="1">
+        <v>3</v>
+      </c>
+      <c r="K127" s="1">
+        <v>3</v>
+      </c>
+      <c r="L127" s="1">
+        <v>3</v>
+      </c>
+      <c r="M127" s="1">
         <v>5</v>
       </c>
       <c r="N127" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G127:M127),"-")</f>
         <v>4</v>
       </c>
-      <c r="O127" s="46" t="str" cm="1">
+      <c r="O127" s="18" t="str" cm="1">
         <f t="array" ref="O127">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A128" s="40">
+      <c r="A128" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B128" s="41" t="str">
+      <c r="B128" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C128" s="41" t="str">
+      <c r="C128" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D128" s="42">
+      <c r="D128" s="3">
         <v>46233</v>
       </c>
-      <c r="E128" s="43" t="s">
+      <c r="E128" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="F128" s="44">
+      <c r="F128" s="1">
         <v>1103755851</v>
       </c>
-      <c r="G128" s="45">
-        <v>5</v>
-      </c>
-      <c r="H128" s="45">
-        <v>5</v>
-      </c>
-      <c r="I128" s="45">
-        <v>5</v>
-      </c>
-      <c r="J128" s="45">
-        <v>5</v>
-      </c>
-      <c r="K128" s="45">
-        <v>5</v>
-      </c>
-      <c r="L128" s="45">
-        <v>5</v>
-      </c>
-      <c r="M128" s="45">
+      <c r="G128" s="1">
+        <v>5</v>
+      </c>
+      <c r="H128" s="1">
+        <v>5</v>
+      </c>
+      <c r="I128" s="1">
+        <v>5</v>
+      </c>
+      <c r="J128" s="1">
+        <v>5</v>
+      </c>
+      <c r="K128" s="1">
+        <v>5</v>
+      </c>
+      <c r="L128" s="1">
+        <v>5</v>
+      </c>
+      <c r="M128" s="1">
         <v>5</v>
       </c>
       <c r="N128" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G128:M128),"-")</f>
         <v>5</v>
       </c>
-      <c r="O128" s="46" t="str" cm="1">
+      <c r="O128" s="18" t="str" cm="1">
         <f t="array" ref="O128">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>CAMBIA A NIVEL 2</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A129" s="40">
+      <c r="A129" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B129" s="41" t="str">
+      <c r="B129" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C129" s="41" t="str">
+      <c r="C129" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D129" s="42">
+      <c r="D129" s="3">
         <v>46233</v>
       </c>
-      <c r="E129" s="43" t="s">
+      <c r="E129" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F129" s="44">
+      <c r="F129" s="1">
         <v>1233040347</v>
       </c>
-      <c r="G129" s="45">
-        <v>5</v>
-      </c>
-      <c r="H129" s="45">
-        <v>5</v>
-      </c>
-      <c r="I129" s="45">
-        <v>5</v>
-      </c>
-      <c r="J129" s="45">
-        <v>3</v>
-      </c>
-      <c r="K129" s="45">
-        <v>4</v>
-      </c>
-      <c r="L129" s="45">
-        <v>3</v>
-      </c>
-      <c r="M129" s="45">
+      <c r="G129" s="1">
+        <v>5</v>
+      </c>
+      <c r="H129" s="1">
+        <v>5</v>
+      </c>
+      <c r="I129" s="1">
+        <v>5</v>
+      </c>
+      <c r="J129" s="1">
+        <v>3</v>
+      </c>
+      <c r="K129" s="1">
+        <v>4</v>
+      </c>
+      <c r="L129" s="1">
+        <v>3</v>
+      </c>
+      <c r="M129" s="1">
         <v>5</v>
       </c>
       <c r="N129" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G129:M129),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O129" s="46" t="str" cm="1">
+      <c r="O129" s="18" t="str" cm="1">
         <f t="array" ref="O129">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A130" s="40">
+      <c r="A130" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B130" s="41" t="str">
+      <c r="B130" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C130" s="41" t="str">
+      <c r="C130" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D130" s="42">
+      <c r="D130" s="3">
         <v>46234</v>
       </c>
-      <c r="E130" s="43" t="s">
+      <c r="E130" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F130" s="44">
+      <c r="F130" s="1">
         <v>34882674</v>
       </c>
-      <c r="G130" s="45">
-        <v>5</v>
-      </c>
-      <c r="H130" s="45">
-        <v>4</v>
-      </c>
-      <c r="I130" s="45">
-        <v>4</v>
-      </c>
-      <c r="J130" s="45">
+      <c r="G130" s="1">
+        <v>5</v>
+      </c>
+      <c r="H130" s="1">
+        <v>4</v>
+      </c>
+      <c r="I130" s="1">
+        <v>4</v>
+      </c>
+      <c r="J130" s="1">
         <v>2</v>
       </c>
-      <c r="K130" s="45">
+      <c r="K130" s="1">
         <v>2</v>
       </c>
-      <c r="L130" s="45">
+      <c r="L130" s="1">
         <v>2</v>
       </c>
-      <c r="M130" s="45">
+      <c r="M130" s="1">
         <v>5</v>
       </c>
       <c r="N130" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G130:M130),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O130" s="46" t="str" cm="1">
+      <c r="O130" s="18" t="str" cm="1">
         <f t="array" ref="O130">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A131" s="40">
+      <c r="A131" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B131" s="41" t="str">
+      <c r="B131" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C131" s="41" t="str">
+      <c r="C131" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D131" s="42">
+      <c r="D131" s="3">
         <v>46234</v>
       </c>
-      <c r="E131" s="43" t="s">
+      <c r="E131" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F131" s="44">
+      <c r="F131" s="1">
         <v>1003047136</v>
       </c>
-      <c r="G131" s="45">
-        <v>5</v>
-      </c>
-      <c r="H131" s="45">
-        <v>5</v>
-      </c>
-      <c r="I131" s="45">
-        <v>5</v>
-      </c>
-      <c r="J131" s="45">
+      <c r="G131" s="1">
+        <v>5</v>
+      </c>
+      <c r="H131" s="1">
+        <v>5</v>
+      </c>
+      <c r="I131" s="1">
+        <v>5</v>
+      </c>
+      <c r="J131" s="1">
         <v>2</v>
       </c>
-      <c r="K131" s="45">
-        <v>3</v>
-      </c>
-      <c r="L131" s="45">
+      <c r="K131" s="1">
+        <v>3</v>
+      </c>
+      <c r="L131" s="1">
         <v>2</v>
       </c>
-      <c r="M131" s="45">
+      <c r="M131" s="1">
         <v>2</v>
       </c>
       <c r="N131" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G131:M131),"-")</f>
         <v>3.4285714285714284</v>
       </c>
-      <c r="O131" s="46" t="str" cm="1">
+      <c r="O131" s="18" t="str" cm="1">
         <f t="array" ref="O131">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A132" s="40">
+      <c r="A132" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B132" s="41" t="str">
+      <c r="B132" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C132" s="41" t="str">
+      <c r="C132" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D132" s="42">
+      <c r="D132" s="3">
         <v>46234</v>
       </c>
-      <c r="E132" s="43" t="s">
+      <c r="E132" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F132" s="44">
+      <c r="F132" s="1">
         <v>1025564047</v>
       </c>
-      <c r="G132" s="45">
-        <v>5</v>
-      </c>
-      <c r="H132" s="45">
-        <v>5</v>
-      </c>
-      <c r="I132" s="45">
-        <v>5</v>
-      </c>
-      <c r="J132" s="45">
-        <v>4</v>
-      </c>
-      <c r="K132" s="45">
-        <v>4</v>
-      </c>
-      <c r="L132" s="45">
-        <v>4</v>
-      </c>
-      <c r="M132" s="45">
+      <c r="G132" s="1">
+        <v>5</v>
+      </c>
+      <c r="H132" s="1">
+        <v>5</v>
+      </c>
+      <c r="I132" s="1">
+        <v>5</v>
+      </c>
+      <c r="J132" s="1">
+        <v>4</v>
+      </c>
+      <c r="K132" s="1">
+        <v>4</v>
+      </c>
+      <c r="L132" s="1">
+        <v>4</v>
+      </c>
+      <c r="M132" s="1">
         <v>5</v>
       </c>
       <c r="N132" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G132:M132),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O132" s="46" t="str" cm="1">
+      <c r="O132" s="18" t="str" cm="1">
         <f t="array" ref="O132">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A133" s="40">
+      <c r="A133" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B133" s="41" t="str">
+      <c r="B133" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C133" s="41" t="str">
+      <c r="C133" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D133" s="42">
+      <c r="D133" s="3">
         <v>46234</v>
       </c>
-      <c r="E133" s="43" t="s">
+      <c r="E133" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="F133" s="44">
+      <c r="F133" s="1">
         <v>1068440514</v>
       </c>
-      <c r="G133" s="45">
-        <v>5</v>
-      </c>
-      <c r="H133" s="45">
+      <c r="G133" s="1">
+        <v>5</v>
+      </c>
+      <c r="H133" s="1">
         <v>2</v>
       </c>
-      <c r="I133" s="45">
+      <c r="I133" s="1">
         <v>2</v>
       </c>
-      <c r="J133" s="45">
+      <c r="J133" s="1">
         <v>2</v>
       </c>
-      <c r="K133" s="45">
+      <c r="K133" s="1">
         <v>2</v>
       </c>
-      <c r="L133" s="45">
+      <c r="L133" s="1">
         <v>2</v>
       </c>
-      <c r="M133" s="45">
+      <c r="M133" s="1">
         <v>4</v>
       </c>
       <c r="N133" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G133:M133),"-")</f>
         <v>2.7142857142857144</v>
       </c>
-      <c r="O133" s="46" t="str" cm="1">
+      <c r="O133" s="18" t="str" cm="1">
         <f t="array" ref="O133">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A134" s="40">
+      <c r="A134" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B134" s="41" t="str">
+      <c r="B134" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C134" s="41" t="str">
+      <c r="C134" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D134" s="42">
+      <c r="D134" s="3">
         <v>46234</v>
       </c>
-      <c r="E134" s="43" t="s">
+      <c r="E134" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F134" s="44">
+      <c r="F134" s="1">
         <v>1138031915</v>
       </c>
-      <c r="G134" s="45">
-        <v>5</v>
-      </c>
-      <c r="H134" s="45">
-        <v>5</v>
-      </c>
-      <c r="I134" s="45">
-        <v>4</v>
-      </c>
-      <c r="J134" s="45">
-        <v>3</v>
-      </c>
-      <c r="K134" s="45">
-        <v>4</v>
-      </c>
-      <c r="L134" s="45">
-        <v>3</v>
-      </c>
-      <c r="M134" s="45">
+      <c r="G134" s="1">
+        <v>5</v>
+      </c>
+      <c r="H134" s="1">
+        <v>5</v>
+      </c>
+      <c r="I134" s="1">
+        <v>4</v>
+      </c>
+      <c r="J134" s="1">
+        <v>3</v>
+      </c>
+      <c r="K134" s="1">
+        <v>4</v>
+      </c>
+      <c r="L134" s="1">
+        <v>3</v>
+      </c>
+      <c r="M134" s="1">
         <v>3</v>
       </c>
       <c r="N134" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G134:M134),"-")</f>
         <v>3.8571428571428572</v>
       </c>
-      <c r="O134" s="46" t="str" cm="1">
+      <c r="O134" s="18" t="str" cm="1">
         <f t="array" ref="O134">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A135" s="40">
+      <c r="A135" s="29">
         <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B135" s="41" t="str">
+      <c r="B135" s="12" t="str">
         <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
         <v>NIVEL 1</v>
       </c>
-      <c r="C135" s="41" t="str">
+      <c r="C135" s="12" t="str">
         <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D135" s="42">
+      <c r="D135" s="3">
         <v>46234</v>
       </c>
-      <c r="E135" s="43" t="s">
+      <c r="E135" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F135" s="44">
+      <c r="F135" s="1">
         <v>1138032050</v>
       </c>
-      <c r="G135" s="45">
-        <v>5</v>
-      </c>
-      <c r="H135" s="45">
+      <c r="G135" s="1">
+        <v>5</v>
+      </c>
+      <c r="H135" s="1">
         <v>2</v>
       </c>
-      <c r="I135" s="45">
+      <c r="I135" s="1">
         <v>2</v>
       </c>
-      <c r="J135" s="45">
+      <c r="J135" s="1">
         <v>2</v>
       </c>
-      <c r="K135" s="45">
+      <c r="K135" s="1">
         <v>2</v>
       </c>
-      <c r="L135" s="45">
+      <c r="L135" s="1">
         <v>2</v>
       </c>
-      <c r="M135" s="45">
+      <c r="M135" s="1">
         <v>2</v>
       </c>
       <c r="N135" s="19">
         <f>IFERROR(AVERAGE('NIVEL 1'!G135:M135),"-")</f>
         <v>2.4285714285714284</v>
       </c>
-      <c r="O135" s="46" t="str" cm="1">
+      <c r="O135" s="18" t="str" cm="1">
         <f t="array" ref="O135">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A136" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B136" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C136" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D136" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G136" s="1">
+        <v>5</v>
+      </c>
+      <c r="H136" s="1">
+        <v>5</v>
+      </c>
+      <c r="I136" s="1">
+        <v>4</v>
+      </c>
+      <c r="J136" s="1">
+        <v>3</v>
+      </c>
+      <c r="K136" s="1">
+        <v>3</v>
+      </c>
+      <c r="L136" s="1">
+        <v>3</v>
+      </c>
+      <c r="M136" s="1">
+        <v>4</v>
+      </c>
+      <c r="N136" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G136:M136),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O136" s="18" t="str" cm="1">
+        <f t="array" ref="O136">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A137" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B137" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C137" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D137" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F137" s="1">
+        <v>1035017030</v>
+      </c>
+      <c r="G137" s="1">
+        <v>5</v>
+      </c>
+      <c r="H137" s="1">
+        <v>5</v>
+      </c>
+      <c r="I137" s="1">
+        <v>5</v>
+      </c>
+      <c r="J137" s="1">
+        <v>4</v>
+      </c>
+      <c r="K137" s="1">
+        <v>4</v>
+      </c>
+      <c r="L137" s="1">
+        <v>4</v>
+      </c>
+      <c r="M137" s="1">
+        <v>5</v>
+      </c>
+      <c r="N137" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G137:M137),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O137" s="18" t="str" cm="1">
+        <f t="array" ref="O137">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A138" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B138" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C138" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D138" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E138" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F138" s="1">
+        <v>1068442748</v>
+      </c>
+      <c r="G138" s="1">
+        <v>5</v>
+      </c>
+      <c r="H138" s="1">
+        <v>2</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="1">
+        <v>2</v>
+      </c>
+      <c r="L138" s="1">
+        <v>1</v>
+      </c>
+      <c r="M138" s="1">
+        <v>1</v>
+      </c>
+      <c r="N138" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G138:M138),"-")</f>
+        <v>2</v>
+      </c>
+      <c r="O138" s="18" t="str" cm="1">
+        <f t="array" ref="O138">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A139" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B139" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C139" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D139" s="3">
+        <v>46199</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F139" s="1">
+        <v>1233348383</v>
+      </c>
+      <c r="G139" s="1">
+        <v>5</v>
+      </c>
+      <c r="H139" s="1">
+        <v>5</v>
+      </c>
+      <c r="I139" s="1">
+        <v>4</v>
+      </c>
+      <c r="J139" s="1">
+        <v>4</v>
+      </c>
+      <c r="K139" s="1">
+        <v>4</v>
+      </c>
+      <c r="L139" s="1">
+        <v>3</v>
+      </c>
+      <c r="M139" s="1">
+        <v>5</v>
+      </c>
+      <c r="N139" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G139:M139),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O139" s="18" t="str" cm="1">
+        <f t="array" ref="O139">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A140" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>6</v>
+      </c>
+      <c r="B140" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C140" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>junio</v>
+      </c>
+      <c r="D140" s="3">
+        <v>46199</v>
+      </c>
+      <c r="E140" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F140" s="1">
+        <v>1003405136</v>
+      </c>
+      <c r="G140" s="1">
+        <v>5</v>
+      </c>
+      <c r="H140" s="1">
+        <v>5</v>
+      </c>
+      <c r="I140" s="1">
+        <v>5</v>
+      </c>
+      <c r="J140" s="1">
+        <v>4</v>
+      </c>
+      <c r="K140" s="1">
+        <v>4</v>
+      </c>
+      <c r="L140" s="1">
+        <v>3</v>
+      </c>
+      <c r="M140" s="1">
+        <v>5</v>
+      </c>
+      <c r="N140" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G140:M140),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O140" s="18" t="str" cm="1">
+        <f t="array" ref="O140">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A141" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B141" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C141" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D141" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F141" s="1">
+        <v>1025564047</v>
+      </c>
+      <c r="G141" s="1">
+        <v>5</v>
+      </c>
+      <c r="H141" s="1">
+        <v>5</v>
+      </c>
+      <c r="I141" s="1">
+        <v>5</v>
+      </c>
+      <c r="J141" s="1">
+        <v>4</v>
+      </c>
+      <c r="K141" s="1">
+        <v>4</v>
+      </c>
+      <c r="L141" s="1">
+        <v>4</v>
+      </c>
+      <c r="M141" s="1">
+        <v>5</v>
+      </c>
+      <c r="N141" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G141:M141),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O141" s="18" t="str" cm="1">
+        <f t="array" ref="O141">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A142" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B142" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C142" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D142" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1003047136</v>
+      </c>
+      <c r="G142" s="1">
+        <v>5</v>
+      </c>
+      <c r="H142" s="1">
+        <v>5</v>
+      </c>
+      <c r="I142" s="1">
+        <v>5</v>
+      </c>
+      <c r="J142" s="1">
+        <v>3</v>
+      </c>
+      <c r="K142" s="1">
+        <v>3</v>
+      </c>
+      <c r="L142" s="1">
+        <v>2</v>
+      </c>
+      <c r="M142" s="1">
+        <v>2</v>
+      </c>
+      <c r="N142" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G142:M142),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O142" s="18" t="str" cm="1">
+        <f t="array" ref="O142">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A143" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B143" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C143" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D143" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F143" s="1">
+        <v>1233040347</v>
+      </c>
+      <c r="G143" s="1">
+        <v>5</v>
+      </c>
+      <c r="H143" s="1">
+        <v>5</v>
+      </c>
+      <c r="I143" s="1">
+        <v>5</v>
+      </c>
+      <c r="J143" s="1">
+        <v>4</v>
+      </c>
+      <c r="K143" s="1">
+        <v>4</v>
+      </c>
+      <c r="L143" s="1">
+        <v>4</v>
+      </c>
+      <c r="M143" s="1">
+        <v>5</v>
+      </c>
+      <c r="N143" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G143:M143),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O143" s="18" t="str" cm="1">
+        <f t="array" ref="O143">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A144" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B144" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C144" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D144" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F144" s="1">
+        <v>1138031915</v>
+      </c>
+      <c r="G144" s="1">
+        <v>5</v>
+      </c>
+      <c r="H144" s="1">
+        <v>5</v>
+      </c>
+      <c r="I144" s="1">
+        <v>4</v>
+      </c>
+      <c r="J144" s="1">
+        <v>3</v>
+      </c>
+      <c r="K144" s="1">
+        <v>4</v>
+      </c>
+      <c r="L144" s="1">
+        <v>2</v>
+      </c>
+      <c r="M144" s="1">
+        <v>5</v>
+      </c>
+      <c r="N144" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G144:M144),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O144" s="18" t="str" cm="1">
+        <f t="array" ref="O144">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A145" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B145" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C145" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D145" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F145" s="1">
+        <v>1091978602</v>
+      </c>
+      <c r="G145" s="1">
+        <v>5</v>
+      </c>
+      <c r="H145" s="1">
+        <v>5</v>
+      </c>
+      <c r="I145" s="1">
+        <v>5</v>
+      </c>
+      <c r="J145" s="1">
+        <v>4</v>
+      </c>
+      <c r="K145" s="1">
+        <v>4</v>
+      </c>
+      <c r="L145" s="1">
+        <v>3</v>
+      </c>
+      <c r="M145" s="1">
+        <v>5</v>
+      </c>
+      <c r="N145" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G145:M145),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O145" s="18" t="str" cm="1">
+        <f t="array" ref="O145">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A146" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B146" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C146" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D146" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F146" s="1">
+        <v>1062983530</v>
+      </c>
+      <c r="G146" s="1">
+        <v>5</v>
+      </c>
+      <c r="H146" s="1">
+        <v>5</v>
+      </c>
+      <c r="I146" s="1">
+        <v>5</v>
+      </c>
+      <c r="J146" s="1">
+        <v>4</v>
+      </c>
+      <c r="K146" s="1">
+        <v>4</v>
+      </c>
+      <c r="L146" s="1">
+        <v>4</v>
+      </c>
+      <c r="M146" s="1">
+        <v>5</v>
+      </c>
+      <c r="N146" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G146:M146),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O146" s="18" t="str" cm="1">
+        <f t="array" ref="O146">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A147" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B147" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C147" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D147" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F147" s="1">
+        <v>1068444855</v>
+      </c>
+      <c r="G147" s="1">
+        <v>5</v>
+      </c>
+      <c r="H147" s="1">
+        <v>3</v>
+      </c>
+      <c r="I147" s="1">
+        <v>3</v>
+      </c>
+      <c r="J147" s="1">
+        <v>3</v>
+      </c>
+      <c r="K147" s="1">
+        <v>2</v>
+      </c>
+      <c r="L147" s="1">
+        <v>2</v>
+      </c>
+      <c r="M147" s="1">
+        <v>3</v>
+      </c>
+      <c r="N147" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G147:M147),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O147" s="18" t="str" cm="1">
+        <f t="array" ref="O147">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A148" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B148" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C148" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D148" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E148" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F148" s="1">
+        <v>1068445190</v>
+      </c>
+      <c r="G148" s="1">
+        <v>5</v>
+      </c>
+      <c r="H148" s="1">
+        <v>3</v>
+      </c>
+      <c r="I148" s="1">
+        <v>3</v>
+      </c>
+      <c r="J148" s="1">
+        <v>3</v>
+      </c>
+      <c r="K148" s="1">
+        <v>2</v>
+      </c>
+      <c r="L148" s="1">
+        <v>2</v>
+      </c>
+      <c r="M148" s="1">
+        <v>2</v>
+      </c>
+      <c r="N148" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G148:M148),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O148" s="18" t="str" cm="1">
+        <f t="array" ref="O148">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A149" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B149" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C149" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D149" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1016116812</v>
+      </c>
+      <c r="G149" s="1">
+        <v>5</v>
+      </c>
+      <c r="H149" s="1">
+        <v>5</v>
+      </c>
+      <c r="I149" s="1">
+        <v>5</v>
+      </c>
+      <c r="J149" s="1">
+        <v>4</v>
+      </c>
+      <c r="K149" s="1">
+        <v>4</v>
+      </c>
+      <c r="L149" s="1">
+        <v>4</v>
+      </c>
+      <c r="M149" s="1">
+        <v>5</v>
+      </c>
+      <c r="N149" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G149:M149),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O149" s="18" t="str" cm="1">
+        <f t="array" ref="O149">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A150" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B150" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C150" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D150" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E150" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1062445950</v>
+      </c>
+      <c r="G150" s="1">
+        <v>5</v>
+      </c>
+      <c r="H150" s="1">
+        <v>5</v>
+      </c>
+      <c r="I150" s="1">
+        <v>5</v>
+      </c>
+      <c r="J150" s="1">
+        <v>5</v>
+      </c>
+      <c r="K150" s="1">
+        <v>5</v>
+      </c>
+      <c r="L150" s="1">
+        <v>5</v>
+      </c>
+      <c r="M150" s="1">
+        <v>5</v>
+      </c>
+      <c r="N150" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G150:M150),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O150" s="18" t="str" cm="1">
+        <f t="array" ref="O150">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A151" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B151" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C151" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D151" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E151" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1062535690</v>
+      </c>
+      <c r="G151" s="1">
+        <v>5</v>
+      </c>
+      <c r="H151" s="1">
+        <v>5</v>
+      </c>
+      <c r="I151" s="1">
+        <v>5</v>
+      </c>
+      <c r="J151" s="1">
+        <v>5</v>
+      </c>
+      <c r="K151" s="1">
+        <v>5</v>
+      </c>
+      <c r="L151" s="1">
+        <v>5</v>
+      </c>
+      <c r="M151" s="1">
+        <v>5</v>
+      </c>
+      <c r="N151" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G151:M151),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O151" s="18" t="str" cm="1">
+        <f t="array" ref="O151">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A152" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B152" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C152" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D152" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E152" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F152" s="1">
+        <v>1138032050</v>
+      </c>
+      <c r="G152" s="1">
+        <v>5</v>
+      </c>
+      <c r="H152" s="1">
+        <v>4</v>
+      </c>
+      <c r="I152" s="1">
+        <v>3</v>
+      </c>
+      <c r="J152" s="1">
+        <v>3</v>
+      </c>
+      <c r="K152" s="1">
+        <v>2</v>
+      </c>
+      <c r="L152" s="1">
+        <v>2</v>
+      </c>
+      <c r="M152" s="1">
+        <v>3</v>
+      </c>
+      <c r="N152" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G152:M152),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O152" s="18" t="str" cm="1">
+        <f t="array" ref="O152">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A153" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B153" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C153" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D153" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1038128197</v>
+      </c>
+      <c r="G153" s="1">
+        <v>5</v>
+      </c>
+      <c r="H153" s="1">
+        <v>5</v>
+      </c>
+      <c r="I153" s="1">
+        <v>4</v>
+      </c>
+      <c r="J153" s="1">
+        <v>5</v>
+      </c>
+      <c r="K153" s="1">
+        <v>4</v>
+      </c>
+      <c r="L153" s="1">
+        <v>4</v>
+      </c>
+      <c r="M153" s="1">
+        <v>5</v>
+      </c>
+      <c r="N153" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G153:M153),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O153" s="18" t="str" cm="1">
+        <f t="array" ref="O153">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A154" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B154" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C154" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D154" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E154" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1062967980</v>
+      </c>
+      <c r="G154" s="1">
+        <v>5</v>
+      </c>
+      <c r="H154" s="1">
+        <v>3</v>
+      </c>
+      <c r="I154" s="1">
+        <v>3</v>
+      </c>
+      <c r="J154" s="1">
+        <v>3</v>
+      </c>
+      <c r="K154" s="1">
+        <v>2</v>
+      </c>
+      <c r="L154" s="1">
+        <v>2</v>
+      </c>
+      <c r="M154" s="1">
+        <v>3</v>
+      </c>
+      <c r="N154" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G154:M154),"-")</f>
+        <v>3</v>
+      </c>
+      <c r="O154" s="18" t="str" cm="1">
+        <f t="array" ref="O154">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A155" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B155" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C155" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D155" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1062440681</v>
+      </c>
+      <c r="G155" s="1">
+        <v>5</v>
+      </c>
+      <c r="H155" s="1">
+        <v>5</v>
+      </c>
+      <c r="I155" s="1">
+        <v>5</v>
+      </c>
+      <c r="J155" s="1">
+        <v>5</v>
+      </c>
+      <c r="K155" s="1">
+        <v>5</v>
+      </c>
+      <c r="L155" s="1">
+        <v>5</v>
+      </c>
+      <c r="M155" s="1">
+        <v>5</v>
+      </c>
+      <c r="N155" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G155:M155),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O155" s="18" t="str" cm="1">
+        <f t="array" ref="O155">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A156" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B156" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C156" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D156" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1017126695</v>
+      </c>
+      <c r="G156" s="1">
+        <v>5</v>
+      </c>
+      <c r="H156" s="1">
+        <v>5</v>
+      </c>
+      <c r="I156" s="1">
+        <v>5</v>
+      </c>
+      <c r="J156" s="1">
+        <v>5</v>
+      </c>
+      <c r="K156" s="1">
+        <v>5</v>
+      </c>
+      <c r="L156" s="1">
+        <v>5</v>
+      </c>
+      <c r="M156" s="1">
+        <v>5</v>
+      </c>
+      <c r="N156" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G156:M156),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O156" s="18" t="str" cm="1">
+        <f t="array" ref="O156">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A157" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B157" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C157" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D157" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1003357893</v>
+      </c>
+      <c r="G157" s="1">
+        <v>5</v>
+      </c>
+      <c r="H157" s="1">
+        <v>5</v>
+      </c>
+      <c r="I157" s="1">
+        <v>4</v>
+      </c>
+      <c r="J157" s="1">
+        <v>4</v>
+      </c>
+      <c r="K157" s="1">
+        <v>4</v>
+      </c>
+      <c r="L157" s="1">
+        <v>3</v>
+      </c>
+      <c r="M157" s="1">
+        <v>5</v>
+      </c>
+      <c r="N157" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G157:M157),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O157" s="18" t="str" cm="1">
+        <f t="array" ref="O157">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B158" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C158" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D158" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E158" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1064988851</v>
+      </c>
+      <c r="G158" s="1">
+        <v>5</v>
+      </c>
+      <c r="H158" s="1">
+        <v>5</v>
+      </c>
+      <c r="I158" s="1">
+        <v>3</v>
+      </c>
+      <c r="J158" s="1">
+        <v>3</v>
+      </c>
+      <c r="K158" s="1">
+        <v>3</v>
+      </c>
+      <c r="L158" s="1">
+        <v>2</v>
+      </c>
+      <c r="M158" s="1">
+        <v>5</v>
+      </c>
+      <c r="N158" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G158:M158),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O158" s="18" t="str" cm="1">
+        <f t="array" ref="O158">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A159" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B159" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C159" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D159" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F159" s="1">
+        <v>1065006937</v>
+      </c>
+      <c r="G159" s="1">
+        <v>5</v>
+      </c>
+      <c r="H159" s="1">
+        <v>3</v>
+      </c>
+      <c r="I159" s="1">
+        <v>2</v>
+      </c>
+      <c r="J159" s="1">
+        <v>3</v>
+      </c>
+      <c r="K159" s="1">
+        <v>2</v>
+      </c>
+      <c r="L159" s="1">
+        <v>2</v>
+      </c>
+      <c r="M159" s="1">
+        <v>3</v>
+      </c>
+      <c r="N159" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G159:M159),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O159" s="18" t="str" cm="1">
+        <f t="array" ref="O159">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A160" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B160" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C160" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D160" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F160" s="1">
+        <v>1003393498</v>
+      </c>
+      <c r="G160" s="1">
+        <v>5</v>
+      </c>
+      <c r="H160" s="1">
+        <v>4</v>
+      </c>
+      <c r="I160" s="1">
+        <v>3</v>
+      </c>
+      <c r="J160" s="1">
+        <v>2</v>
+      </c>
+      <c r="K160" s="1">
+        <v>2</v>
+      </c>
+      <c r="L160" s="1">
+        <v>2</v>
+      </c>
+      <c r="M160" s="1">
+        <v>5</v>
+      </c>
+      <c r="N160" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G160:M160),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O160" s="18" t="str" cm="1">
+        <f t="array" ref="O160">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A161" s="29">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B161" s="12" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C161" s="12" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D161" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F161" s="1">
+        <v>25800927</v>
+      </c>
+      <c r="G161" s="1">
+        <v>5</v>
+      </c>
+      <c r="H161" s="1">
+        <v>3</v>
+      </c>
+      <c r="I161" s="1">
+        <v>3</v>
+      </c>
+      <c r="J161" s="1">
+        <v>2</v>
+      </c>
+      <c r="K161" s="1">
+        <v>2</v>
+      </c>
+      <c r="L161" s="1">
+        <v>2</v>
+      </c>
+      <c r="M161" s="1">
+        <v>3</v>
+      </c>
+      <c r="N161" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G161:M161),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O161" s="18" t="str" cm="1">
+        <f t="array" ref="O161">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -20094,7 +21463,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -20111,7 +21480,7 @@
     <col min="12" max="12" width="6.33203125" customWidth="1"/>
     <col min="13" max="13" width="9.5546875" customWidth="1"/>
     <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="15" max="15" width="15.5546875" customWidth="1"/>
     <col min="16" max="16" width="15.33203125" customWidth="1"/>
     <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -23510,678 +24879,1614 @@
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="45">
+      <c r="A67" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B67" s="47" t="str">
+      <c r="B67" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C67" s="47" t="str">
+      <c r="C67" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D67" s="42">
+      <c r="D67" s="3">
         <v>46233</v>
       </c>
-      <c r="E67" s="43" t="s">
+      <c r="E67" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F67" s="45">
+      <c r="F67" s="1">
         <v>8203609</v>
       </c>
-      <c r="G67" s="45">
-        <v>5</v>
-      </c>
-      <c r="H67" s="45">
-        <v>4</v>
-      </c>
-      <c r="I67" s="45">
-        <v>5</v>
-      </c>
-      <c r="J67" s="45">
-        <v>3</v>
-      </c>
-      <c r="K67" s="45">
-        <v>4</v>
-      </c>
-      <c r="L67" s="45">
-        <v>5</v>
-      </c>
-      <c r="M67" s="45">
+      <c r="G67" s="1">
+        <v>5</v>
+      </c>
+      <c r="H67" s="1">
+        <v>4</v>
+      </c>
+      <c r="I67" s="1">
+        <v>5</v>
+      </c>
+      <c r="J67" s="1">
+        <v>3</v>
+      </c>
+      <c r="K67" s="1">
+        <v>4</v>
+      </c>
+      <c r="L67" s="1">
+        <v>5</v>
+      </c>
+      <c r="M67" s="1">
         <v>5</v>
       </c>
       <c r="N67" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G67:M67),"-")</f>
         <v>4.4285714285714288</v>
       </c>
-      <c r="O67" s="48" t="str" cm="1">
+      <c r="O67" s="18" t="str" cm="1">
         <f t="array" ref="O67">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="45">
+      <c r="A68" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B68" s="47" t="str">
+      <c r="B68" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C68" s="47" t="str">
+      <c r="C68" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D68" s="42">
+      <c r="D68" s="3">
         <v>46233</v>
       </c>
-      <c r="E68" s="43" t="s">
+      <c r="E68" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F68" s="45">
+      <c r="F68" s="1">
         <v>1001897545</v>
       </c>
-      <c r="G68" s="45">
-        <v>5</v>
-      </c>
-      <c r="H68" s="45">
-        <v>4</v>
-      </c>
-      <c r="I68" s="45">
-        <v>3</v>
-      </c>
-      <c r="J68" s="45">
-        <v>4</v>
-      </c>
-      <c r="K68" s="45">
-        <v>4</v>
-      </c>
-      <c r="L68" s="45">
-        <v>5</v>
-      </c>
-      <c r="M68" s="45">
+      <c r="G68" s="1">
+        <v>5</v>
+      </c>
+      <c r="H68" s="1">
+        <v>4</v>
+      </c>
+      <c r="I68" s="1">
+        <v>3</v>
+      </c>
+      <c r="J68" s="1">
+        <v>4</v>
+      </c>
+      <c r="K68" s="1">
+        <v>4</v>
+      </c>
+      <c r="L68" s="1">
+        <v>5</v>
+      </c>
+      <c r="M68" s="1">
         <v>3</v>
       </c>
       <c r="N68" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G68:M68),"-")</f>
         <v>4</v>
       </c>
-      <c r="O68" s="48" t="str" cm="1">
+      <c r="O68" s="18" t="str" cm="1">
         <f t="array" ref="O68">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="45">
+      <c r="A69" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B69" s="47" t="str">
+      <c r="B69" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C69" s="47" t="str">
+      <c r="C69" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D69" s="42">
+      <c r="D69" s="3">
         <v>46233</v>
       </c>
-      <c r="E69" s="43" t="s">
+      <c r="E69" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F69" s="45">
+      <c r="F69" s="1">
         <v>1029722943</v>
       </c>
-      <c r="G69" s="45">
-        <v>5</v>
-      </c>
-      <c r="H69" s="45">
-        <v>4</v>
-      </c>
-      <c r="I69" s="45">
-        <v>3</v>
-      </c>
-      <c r="J69" s="45">
-        <v>4</v>
-      </c>
-      <c r="K69" s="45">
-        <v>4</v>
-      </c>
-      <c r="L69" s="45">
-        <v>5</v>
-      </c>
-      <c r="M69" s="45">
+      <c r="G69" s="1">
+        <v>5</v>
+      </c>
+      <c r="H69" s="1">
+        <v>4</v>
+      </c>
+      <c r="I69" s="1">
+        <v>3</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1">
+        <v>4</v>
+      </c>
+      <c r="L69" s="1">
+        <v>5</v>
+      </c>
+      <c r="M69" s="1">
         <v>5</v>
       </c>
       <c r="N69" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G69:M69),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O69" s="48" t="str" cm="1">
+      <c r="O69" s="18" t="str" cm="1">
         <f t="array" ref="O69">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="45">
+      <c r="A70" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B70" s="47" t="str">
+      <c r="B70" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C70" s="47" t="str">
+      <c r="C70" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D70" s="42">
+      <c r="D70" s="3">
         <v>46233</v>
       </c>
-      <c r="E70" s="43" t="s">
+      <c r="E70" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F70" s="45">
+      <c r="F70" s="1">
         <v>1062544508</v>
       </c>
-      <c r="G70" s="45">
-        <v>4</v>
-      </c>
-      <c r="H70" s="45">
-        <v>4</v>
-      </c>
-      <c r="I70" s="45">
+      <c r="G70" s="1">
+        <v>4</v>
+      </c>
+      <c r="H70" s="1">
+        <v>4</v>
+      </c>
+      <c r="I70" s="1">
         <v>2</v>
       </c>
-      <c r="J70" s="45">
-        <v>3</v>
-      </c>
-      <c r="K70" s="45">
-        <v>3</v>
-      </c>
-      <c r="L70" s="45">
-        <v>3</v>
-      </c>
-      <c r="M70" s="45">
+      <c r="J70" s="1">
+        <v>3</v>
+      </c>
+      <c r="K70" s="1">
+        <v>3</v>
+      </c>
+      <c r="L70" s="1">
+        <v>3</v>
+      </c>
+      <c r="M70" s="1">
         <v>2</v>
       </c>
       <c r="N70" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G70:M70),"-")</f>
         <v>3</v>
       </c>
-      <c r="O70" s="48" t="str" cm="1">
+      <c r="O70" s="18" t="str" cm="1">
         <f t="array" ref="O70">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="45">
+      <c r="A71" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B71" s="47" t="str">
+      <c r="B71" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C71" s="47" t="str">
+      <c r="C71" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D71" s="42">
+      <c r="D71" s="3">
         <v>46233</v>
       </c>
-      <c r="E71" s="43" t="s">
+      <c r="E71" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F71" s="45">
+      <c r="F71" s="1">
         <v>1062981643</v>
       </c>
-      <c r="G71" s="45">
-        <v>5</v>
-      </c>
-      <c r="H71" s="45">
-        <v>5</v>
-      </c>
-      <c r="I71" s="45">
-        <v>3</v>
-      </c>
-      <c r="J71" s="45">
-        <v>4</v>
-      </c>
-      <c r="K71" s="45">
-        <v>3</v>
-      </c>
-      <c r="L71" s="45">
-        <v>5</v>
-      </c>
-      <c r="M71" s="45">
+      <c r="G71" s="1">
+        <v>5</v>
+      </c>
+      <c r="H71" s="1">
+        <v>5</v>
+      </c>
+      <c r="I71" s="1">
+        <v>3</v>
+      </c>
+      <c r="J71" s="1">
+        <v>4</v>
+      </c>
+      <c r="K71" s="1">
+        <v>3</v>
+      </c>
+      <c r="L71" s="1">
+        <v>5</v>
+      </c>
+      <c r="M71" s="1">
         <v>3</v>
       </c>
       <c r="N71" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G71:M71),"-")</f>
         <v>4</v>
       </c>
-      <c r="O71" s="48" t="str" cm="1">
+      <c r="O71" s="18" t="str" cm="1">
         <f t="array" ref="O71">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="45">
+      <c r="A72" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B72" s="47" t="str">
+      <c r="B72" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C72" s="47" t="str">
+      <c r="C72" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D72" s="42">
+      <c r="D72" s="3">
         <v>46233</v>
       </c>
-      <c r="E72" s="43" t="s">
+      <c r="E72" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="F72" s="45">
+      <c r="F72" s="1">
         <v>1065443120</v>
       </c>
-      <c r="G72" s="45">
-        <v>4</v>
-      </c>
-      <c r="H72" s="45">
-        <v>4</v>
-      </c>
-      <c r="I72" s="45">
+      <c r="G72" s="1">
+        <v>4</v>
+      </c>
+      <c r="H72" s="1">
+        <v>4</v>
+      </c>
+      <c r="I72" s="1">
         <v>2</v>
       </c>
-      <c r="J72" s="45">
-        <v>3</v>
-      </c>
-      <c r="K72" s="45">
-        <v>3</v>
-      </c>
-      <c r="L72" s="45">
-        <v>4</v>
-      </c>
-      <c r="M72" s="45">
+      <c r="J72" s="1">
+        <v>3</v>
+      </c>
+      <c r="K72" s="1">
+        <v>3</v>
+      </c>
+      <c r="L72" s="1">
+        <v>4</v>
+      </c>
+      <c r="M72" s="1">
         <v>2</v>
       </c>
       <c r="N72" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G72:M72),"-")</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="O72" s="48" t="str" cm="1">
+      <c r="O72" s="18" t="str" cm="1">
         <f t="array" ref="O72">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="45">
+      <c r="A73" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B73" s="47" t="str">
+      <c r="B73" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C73" s="47" t="str">
+      <c r="C73" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D73" s="42">
+      <c r="D73" s="3">
         <v>46233</v>
       </c>
-      <c r="E73" s="43" t="s">
+      <c r="E73" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F73" s="45">
+      <c r="F73" s="1">
         <v>1067859838</v>
       </c>
-      <c r="G73" s="45">
-        <v>5</v>
-      </c>
-      <c r="H73" s="45">
-        <v>4</v>
-      </c>
-      <c r="I73" s="45">
-        <v>5</v>
-      </c>
-      <c r="J73" s="45">
-        <v>5</v>
-      </c>
-      <c r="K73" s="45">
-        <v>5</v>
-      </c>
-      <c r="L73" s="45">
-        <v>5</v>
-      </c>
-      <c r="M73" s="45">
+      <c r="G73" s="1">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1">
+        <v>4</v>
+      </c>
+      <c r="I73" s="1">
+        <v>5</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>5</v>
+      </c>
+      <c r="L73" s="1">
+        <v>5</v>
+      </c>
+      <c r="M73" s="1">
         <v>1</v>
       </c>
       <c r="N73" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G73:M73),"-")</f>
         <v>4.2857142857142856</v>
       </c>
-      <c r="O73" s="48" t="str" cm="1">
+      <c r="O73" s="18" t="str" cm="1">
         <f t="array" ref="O73">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="45">
+      <c r="A74" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B74" s="47" t="str">
+      <c r="B74" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C74" s="47" t="str">
+      <c r="C74" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D74" s="42">
+      <c r="D74" s="3">
         <v>46233</v>
       </c>
-      <c r="E74" s="43" t="s">
+      <c r="E74" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F74" s="45">
+      <c r="F74" s="1">
         <v>1067945529</v>
       </c>
-      <c r="G74" s="45">
-        <v>5</v>
-      </c>
-      <c r="H74" s="45">
-        <v>4</v>
-      </c>
-      <c r="I74" s="45">
-        <v>4</v>
-      </c>
-      <c r="J74" s="45">
-        <v>5</v>
-      </c>
-      <c r="K74" s="45">
-        <v>5</v>
-      </c>
-      <c r="L74" s="45">
-        <v>5</v>
-      </c>
-      <c r="M74" s="45">
+      <c r="G74" s="1">
+        <v>5</v>
+      </c>
+      <c r="H74" s="1">
+        <v>4</v>
+      </c>
+      <c r="I74" s="1">
+        <v>4</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
+        <v>5</v>
+      </c>
+      <c r="L74" s="1">
+        <v>5</v>
+      </c>
+      <c r="M74" s="1">
         <v>1</v>
       </c>
       <c r="N74" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G74:M74),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O74" s="48" t="str" cm="1">
+      <c r="O74" s="18" t="str" cm="1">
         <f t="array" ref="O74">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="45">
+      <c r="A75" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B75" s="47" t="str">
+      <c r="B75" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C75" s="47" t="str">
+      <c r="C75" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D75" s="42">
+      <c r="D75" s="3">
         <v>46233</v>
       </c>
-      <c r="E75" s="43" t="s">
+      <c r="E75" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F75" s="45">
+      <c r="F75" s="1">
         <v>1073817245</v>
       </c>
-      <c r="G75" s="45">
-        <v>5</v>
-      </c>
-      <c r="H75" s="45">
-        <v>5</v>
-      </c>
-      <c r="I75" s="45">
-        <v>4</v>
-      </c>
-      <c r="J75" s="45">
-        <v>4</v>
-      </c>
-      <c r="K75" s="45">
-        <v>3</v>
-      </c>
-      <c r="L75" s="45">
-        <v>5</v>
-      </c>
-      <c r="M75" s="45">
+      <c r="G75" s="1">
+        <v>5</v>
+      </c>
+      <c r="H75" s="1">
+        <v>5</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4</v>
+      </c>
+      <c r="K75" s="1">
+        <v>3</v>
+      </c>
+      <c r="L75" s="1">
+        <v>5</v>
+      </c>
+      <c r="M75" s="1">
         <v>2</v>
       </c>
       <c r="N75" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G75:M75),"-")</f>
         <v>4</v>
       </c>
-      <c r="O75" s="48" t="str" cm="1">
+      <c r="O75" s="18" t="str" cm="1">
         <f t="array" ref="O75">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="45">
+      <c r="A76" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B76" s="47" t="str">
+      <c r="B76" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C76" s="47" t="str">
+      <c r="C76" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D76" s="42">
+      <c r="D76" s="3">
         <v>46234</v>
       </c>
-      <c r="E76" s="43" t="s">
+      <c r="E76" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="F76" s="45">
+      <c r="F76" s="1">
         <v>1104382840</v>
       </c>
-      <c r="G76" s="45">
-        <v>5</v>
-      </c>
-      <c r="H76" s="45">
-        <v>4</v>
-      </c>
-      <c r="I76" s="45">
-        <v>3</v>
-      </c>
-      <c r="J76" s="45">
-        <v>3</v>
-      </c>
-      <c r="K76" s="45">
-        <v>4</v>
-      </c>
-      <c r="L76" s="45">
-        <v>5</v>
-      </c>
-      <c r="M76" s="45">
+      <c r="G76" s="1">
+        <v>5</v>
+      </c>
+      <c r="H76" s="1">
+        <v>4</v>
+      </c>
+      <c r="I76" s="1">
+        <v>3</v>
+      </c>
+      <c r="J76" s="1">
+        <v>3</v>
+      </c>
+      <c r="K76" s="1">
+        <v>4</v>
+      </c>
+      <c r="L76" s="1">
+        <v>5</v>
+      </c>
+      <c r="M76" s="1">
         <v>1</v>
       </c>
       <c r="N76" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G76:M76),"-")</f>
         <v>3.5714285714285716</v>
       </c>
-      <c r="O76" s="48" t="str" cm="1">
+      <c r="O76" s="18" t="str" cm="1">
         <f t="array" ref="O76">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="45">
+      <c r="A77" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B77" s="47" t="str">
+      <c r="B77" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C77" s="47" t="str">
+      <c r="C77" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D77" s="42">
+      <c r="D77" s="3">
         <v>46234</v>
       </c>
-      <c r="E77" s="43" t="s">
+      <c r="E77" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F77" s="45">
+      <c r="F77" s="1">
         <v>1137975856</v>
       </c>
-      <c r="G77" s="45">
-        <v>5</v>
-      </c>
-      <c r="H77" s="45">
-        <v>4</v>
-      </c>
-      <c r="I77" s="45">
-        <v>4</v>
-      </c>
-      <c r="J77" s="45">
-        <v>5</v>
-      </c>
-      <c r="K77" s="45">
-        <v>5</v>
-      </c>
-      <c r="L77" s="45">
-        <v>4</v>
-      </c>
-      <c r="M77" s="45">
+      <c r="G77" s="1">
+        <v>5</v>
+      </c>
+      <c r="H77" s="1">
+        <v>4</v>
+      </c>
+      <c r="I77" s="1">
+        <v>4</v>
+      </c>
+      <c r="J77" s="1">
+        <v>5</v>
+      </c>
+      <c r="K77" s="1">
+        <v>5</v>
+      </c>
+      <c r="L77" s="1">
+        <v>4</v>
+      </c>
+      <c r="M77" s="1">
         <v>5</v>
       </c>
       <c r="N77" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G77:M77),"-")</f>
         <v>4.5714285714285712</v>
       </c>
-      <c r="O77" s="48" t="str" cm="1">
+      <c r="O77" s="18" t="str" cm="1">
         <f t="array" ref="O77">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="45">
+      <c r="A78" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B78" s="47" t="str">
+      <c r="B78" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C78" s="47" t="str">
+      <c r="C78" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D78" s="42">
+      <c r="D78" s="3">
         <v>46233</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F78" s="45">
+      <c r="F78" s="1">
         <v>1138032406</v>
       </c>
-      <c r="G78" s="45">
-        <v>5</v>
-      </c>
-      <c r="H78" s="45">
-        <v>5</v>
-      </c>
-      <c r="I78" s="45">
-        <v>5</v>
-      </c>
-      <c r="J78" s="45">
-        <v>4</v>
-      </c>
-      <c r="K78" s="45">
-        <v>3</v>
-      </c>
-      <c r="L78" s="45">
-        <v>5</v>
-      </c>
-      <c r="M78" s="45">
+      <c r="G78" s="1">
+        <v>5</v>
+      </c>
+      <c r="H78" s="1">
+        <v>5</v>
+      </c>
+      <c r="I78" s="1">
+        <v>5</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4</v>
+      </c>
+      <c r="K78" s="1">
+        <v>3</v>
+      </c>
+      <c r="L78" s="1">
+        <v>5</v>
+      </c>
+      <c r="M78" s="1">
         <v>2</v>
       </c>
       <c r="N78" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G78:M78),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O78" s="48" t="str" cm="1">
+      <c r="O78" s="18" t="str" cm="1">
         <f t="array" ref="O78">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="45">
+      <c r="A79" s="1">
         <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
         <v>7</v>
       </c>
-      <c r="B79" s="47" t="str">
+      <c r="B79" s="12" t="str">
         <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
         <v>NIVEL 2</v>
       </c>
-      <c r="C79" s="47" t="str">
+      <c r="C79" s="12" t="str">
         <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
         <v>julio</v>
       </c>
-      <c r="D79" s="42">
+      <c r="D79" s="3">
         <v>46233</v>
       </c>
-      <c r="E79" s="43" t="s">
+      <c r="E79" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="45">
+      <c r="F79" s="1">
         <v>1138032417</v>
       </c>
-      <c r="G79" s="45">
-        <v>5</v>
-      </c>
-      <c r="H79" s="45">
-        <v>4</v>
-      </c>
-      <c r="I79" s="45">
-        <v>4</v>
-      </c>
-      <c r="J79" s="45">
-        <v>4</v>
-      </c>
-      <c r="K79" s="45">
-        <v>3</v>
-      </c>
-      <c r="L79" s="45">
-        <v>5</v>
-      </c>
-      <c r="M79" s="45">
+      <c r="G79" s="1">
+        <v>5</v>
+      </c>
+      <c r="H79" s="1">
+        <v>4</v>
+      </c>
+      <c r="I79" s="1">
+        <v>4</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4</v>
+      </c>
+      <c r="K79" s="1">
+        <v>3</v>
+      </c>
+      <c r="L79" s="1">
+        <v>5</v>
+      </c>
+      <c r="M79" s="1">
         <v>4</v>
       </c>
       <c r="N79" s="19">
         <f>IFERROR(AVERAGE('NIVEL 2'!G79:M79),"-")</f>
         <v>4.1428571428571432</v>
       </c>
-      <c r="O79" s="48" t="str" cm="1">
+      <c r="O79" s="18" t="str" cm="1">
         <f t="array" ref="O79">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B80" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C80" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D80" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1062981643</v>
+      </c>
+      <c r="G80" s="1">
+        <v>5</v>
+      </c>
+      <c r="H80" s="1">
+        <v>5</v>
+      </c>
+      <c r="I80" s="1">
+        <v>3</v>
+      </c>
+      <c r="J80" s="1">
+        <v>4</v>
+      </c>
+      <c r="K80" s="1">
+        <v>3</v>
+      </c>
+      <c r="L80" s="1">
+        <v>5</v>
+      </c>
+      <c r="M80" s="1">
+        <v>3</v>
+      </c>
+      <c r="N80" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G80:M80),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O80" s="18" t="str" cm="1">
+        <f t="array" ref="O80">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B81" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C81" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D81" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1029722943</v>
+      </c>
+      <c r="G81" s="1">
+        <v>5</v>
+      </c>
+      <c r="H81" s="1">
+        <v>5</v>
+      </c>
+      <c r="I81" s="1">
+        <v>3</v>
+      </c>
+      <c r="J81" s="1">
+        <v>4</v>
+      </c>
+      <c r="K81" s="1">
+        <v>4</v>
+      </c>
+      <c r="L81" s="1">
+        <v>5</v>
+      </c>
+      <c r="M81" s="1">
+        <v>5</v>
+      </c>
+      <c r="N81" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G81:M81),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O81" s="18" t="str" cm="1">
+        <f t="array" ref="O81">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B82" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C82" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D82" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1067955099</v>
+      </c>
+      <c r="G82" s="1">
+        <v>5</v>
+      </c>
+      <c r="H82" s="1">
+        <v>5</v>
+      </c>
+      <c r="I82" s="1">
+        <v>3</v>
+      </c>
+      <c r="J82" s="1">
+        <v>4</v>
+      </c>
+      <c r="K82" s="1">
+        <v>4</v>
+      </c>
+      <c r="L82" s="1">
+        <v>5</v>
+      </c>
+      <c r="M82" s="1">
+        <v>2</v>
+      </c>
+      <c r="N82" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G82:M82),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O82" s="18" t="str" cm="1">
+        <f t="array" ref="O82">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B83" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C83" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D83" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1142930859</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4</v>
+      </c>
+      <c r="H83" s="1">
+        <v>5</v>
+      </c>
+      <c r="I83" s="1">
+        <v>4</v>
+      </c>
+      <c r="J83" s="1">
+        <v>4</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4</v>
+      </c>
+      <c r="L83" s="1">
+        <v>4</v>
+      </c>
+      <c r="M83" s="1">
+        <v>5</v>
+      </c>
+      <c r="N83" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G83:M83),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O83" s="18" t="str" cm="1">
+        <f t="array" ref="O83">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B84" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C84" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D84" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1138032417</v>
+      </c>
+      <c r="G84" s="1">
+        <v>5</v>
+      </c>
+      <c r="H84" s="1">
+        <v>5</v>
+      </c>
+      <c r="I84" s="1">
+        <v>4</v>
+      </c>
+      <c r="J84" s="1">
+        <v>4</v>
+      </c>
+      <c r="K84" s="1">
+        <v>3</v>
+      </c>
+      <c r="L84" s="1">
+        <v>5</v>
+      </c>
+      <c r="M84" s="1">
+        <v>4</v>
+      </c>
+      <c r="N84" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G84:M84),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O84" s="18" t="str" cm="1">
+        <f t="array" ref="O84">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B85" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C85" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D85" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1067859838</v>
+      </c>
+      <c r="G85" s="1">
+        <v>5</v>
+      </c>
+      <c r="H85" s="1">
+        <v>5</v>
+      </c>
+      <c r="I85" s="1">
+        <v>5</v>
+      </c>
+      <c r="J85" s="1">
+        <v>5</v>
+      </c>
+      <c r="K85" s="1">
+        <v>5</v>
+      </c>
+      <c r="L85" s="1">
+        <v>5</v>
+      </c>
+      <c r="M85" s="1">
+        <v>2</v>
+      </c>
+      <c r="N85" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G85:M85),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O85" s="18" t="str" cm="1">
+        <f t="array" ref="O85">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B86" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C86" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D86" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1073817245</v>
+      </c>
+      <c r="G86" s="1">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1">
+        <v>5</v>
+      </c>
+      <c r="I86" s="1">
+        <v>5</v>
+      </c>
+      <c r="J86" s="1">
+        <v>4</v>
+      </c>
+      <c r="K86" s="1">
+        <v>3</v>
+      </c>
+      <c r="L86" s="1">
+        <v>5</v>
+      </c>
+      <c r="M86" s="1">
+        <v>2</v>
+      </c>
+      <c r="N86" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G86:M86),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O86" s="18" t="str" cm="1">
+        <f t="array" ref="O86">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B87" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C87" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46264</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1067945529</v>
+      </c>
+      <c r="G87" s="1">
+        <v>5</v>
+      </c>
+      <c r="H87" s="1">
+        <v>5</v>
+      </c>
+      <c r="I87" s="1">
+        <v>4</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
+        <v>5</v>
+      </c>
+      <c r="L87" s="1">
+        <v>5</v>
+      </c>
+      <c r="M87" s="1">
+        <v>1</v>
+      </c>
+      <c r="N87" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G87:M87),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O87" s="18" t="str" cm="1">
+        <f t="array" ref="O87">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B88" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C88" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D88" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1137975856</v>
+      </c>
+      <c r="G88" s="1">
+        <v>5</v>
+      </c>
+      <c r="H88" s="1">
+        <v>5</v>
+      </c>
+      <c r="I88" s="1">
+        <v>4</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
+        <v>5</v>
+      </c>
+      <c r="L88" s="1">
+        <v>4</v>
+      </c>
+      <c r="M88" s="1">
+        <v>5</v>
+      </c>
+      <c r="N88" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G88:M88),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O88" s="18" t="str" cm="1">
+        <f t="array" ref="O88">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B89" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C89" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D89" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1138031920</v>
+      </c>
+      <c r="G89" s="1">
+        <v>5</v>
+      </c>
+      <c r="H89" s="1">
+        <v>5</v>
+      </c>
+      <c r="I89" s="1">
+        <v>3</v>
+      </c>
+      <c r="J89" s="1">
+        <v>3</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4</v>
+      </c>
+      <c r="L89" s="1">
+        <v>4</v>
+      </c>
+      <c r="M89" s="1">
+        <v>3</v>
+      </c>
+      <c r="N89" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G89:M89),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O89" s="18" t="str" cm="1">
+        <f t="array" ref="O89">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B90" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C90" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D90" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" s="1">
+        <v>8203609</v>
+      </c>
+      <c r="G90" s="1">
+        <v>5</v>
+      </c>
+      <c r="H90" s="1">
+        <v>5</v>
+      </c>
+      <c r="I90" s="1">
+        <v>5</v>
+      </c>
+      <c r="J90" s="1">
+        <v>4</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4</v>
+      </c>
+      <c r="L90" s="1">
+        <v>5</v>
+      </c>
+      <c r="M90" s="1">
+        <v>5</v>
+      </c>
+      <c r="N90" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G90:M90),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O90" s="18" t="str" cm="1">
+        <f t="array" ref="O90">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B91" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C91" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D91" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1062438398</v>
+      </c>
+      <c r="G91" s="1">
+        <v>5</v>
+      </c>
+      <c r="H91" s="1">
+        <v>5</v>
+      </c>
+      <c r="I91" s="1">
+        <v>4</v>
+      </c>
+      <c r="J91" s="1">
+        <v>3</v>
+      </c>
+      <c r="K91" s="1">
+        <v>4</v>
+      </c>
+      <c r="L91" s="1">
+        <v>5</v>
+      </c>
+      <c r="M91" s="1">
+        <v>3</v>
+      </c>
+      <c r="N91" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G91:M91),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O91" s="18" t="str" cm="1">
+        <f t="array" ref="O91">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B92" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C92" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D92" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1065443120</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4</v>
+      </c>
+      <c r="H92" s="1">
+        <v>4</v>
+      </c>
+      <c r="I92" s="1">
+        <v>3</v>
+      </c>
+      <c r="J92" s="1">
+        <v>3</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4</v>
+      </c>
+      <c r="L92" s="1">
+        <v>4</v>
+      </c>
+      <c r="M92" s="1">
+        <v>2</v>
+      </c>
+      <c r="N92" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G92:M92),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O92" s="18" t="str" cm="1">
+        <f t="array" ref="O92">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B93" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C93" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D93" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1001897545</v>
+      </c>
+      <c r="G93" s="1">
+        <v>5</v>
+      </c>
+      <c r="H93" s="1">
+        <v>5</v>
+      </c>
+      <c r="I93" s="1">
+        <v>3</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
+        <v>5</v>
+      </c>
+      <c r="L93" s="1">
+        <v>5</v>
+      </c>
+      <c r="M93" s="1">
+        <v>3</v>
+      </c>
+      <c r="N93" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G93:M93),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O93" s="18" t="str" cm="1">
+        <f t="array" ref="O93">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B94" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C94" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D94" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F94" s="1">
+        <v>1104382840</v>
+      </c>
+      <c r="G94" s="1">
+        <v>5</v>
+      </c>
+      <c r="H94" s="1">
+        <v>5</v>
+      </c>
+      <c r="I94" s="1">
+        <v>3</v>
+      </c>
+      <c r="J94" s="1">
+        <v>4</v>
+      </c>
+      <c r="K94" s="1">
+        <v>5</v>
+      </c>
+      <c r="L94" s="1">
+        <v>5</v>
+      </c>
+      <c r="M94" s="1">
+        <v>2</v>
+      </c>
+      <c r="N94" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G94:M94),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O94" s="18" t="str" cm="1">
+        <f t="array" ref="O94">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B95" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C95" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D95" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1037236492</v>
+      </c>
+      <c r="G95" s="1">
+        <v>4</v>
+      </c>
+      <c r="H95" s="1">
+        <v>3</v>
+      </c>
+      <c r="I95" s="1">
+        <v>3</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2</v>
+      </c>
+      <c r="K95" s="1">
+        <v>5</v>
+      </c>
+      <c r="L95" s="1">
+        <v>4</v>
+      </c>
+      <c r="M95" s="1">
+        <v>2</v>
+      </c>
+      <c r="N95" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G95:M95),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O95" s="18" t="str" cm="1">
+        <f t="array" ref="O95">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B96" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C96" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D96" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F96" s="1">
+        <v>1103755851</v>
+      </c>
+      <c r="G96" s="1">
+        <v>4</v>
+      </c>
+      <c r="H96" s="1">
+        <v>4</v>
+      </c>
+      <c r="I96" s="1">
+        <v>3</v>
+      </c>
+      <c r="J96" s="1">
+        <v>3</v>
+      </c>
+      <c r="K96" s="1">
+        <v>2</v>
+      </c>
+      <c r="L96" s="1">
+        <v>3</v>
+      </c>
+      <c r="M96" s="1">
+        <v>1</v>
+      </c>
+      <c r="N96" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G96:M96),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O96" s="18" t="str" cm="1">
+        <f t="array" ref="O96">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B97" s="12" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C97" s="12" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D97" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1068433055</v>
+      </c>
+      <c r="G97" s="1">
+        <v>4</v>
+      </c>
+      <c r="H97" s="1">
+        <v>4</v>
+      </c>
+      <c r="I97" s="1">
+        <v>4</v>
+      </c>
+      <c r="J97" s="1">
+        <v>3</v>
+      </c>
+      <c r="K97" s="1">
+        <v>3</v>
+      </c>
+      <c r="L97" s="1">
+        <v>3</v>
+      </c>
+      <c r="M97" s="1">
+        <v>2</v>
+      </c>
+      <c r="N97" s="19">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G97:M97),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O97" s="18" t="str" cm="1">
+        <f t="array" ref="O97">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -24209,7 +26514,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -24226,10 +26531,10 @@
     <col min="12" max="12" width="6.33203125" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.5546875" style="2" customWidth="1"/>
     <col min="14" max="14" width="7.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.21875" style="2" customWidth="1"/>
     <col min="16" max="17" width="5.5546875" style="2" customWidth="1"/>
     <col min="18" max="18" width="6.44140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.21875" style="1" customWidth="1"/>
     <col min="20" max="20" width="5.6640625" customWidth="1"/>
     <col min="21" max="21" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -25507,6 +27812,496 @@
       </c>
       <c r="U19" s="32" t="str" cm="1">
         <f t="array" ref="U19">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B20" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C20" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D20" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1027663882</v>
+      </c>
+      <c r="G20" s="23">
+        <v>5</v>
+      </c>
+      <c r="H20" s="23">
+        <v>4</v>
+      </c>
+      <c r="I20" s="23">
+        <v>5</v>
+      </c>
+      <c r="J20" s="23">
+        <v>5</v>
+      </c>
+      <c r="K20" s="23">
+        <v>4</v>
+      </c>
+      <c r="L20" s="23">
+        <v>3</v>
+      </c>
+      <c r="M20" s="23">
+        <v>5</v>
+      </c>
+      <c r="N20" s="23">
+        <v>5</v>
+      </c>
+      <c r="O20" s="23">
+        <v>5</v>
+      </c>
+      <c r="P20" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="23">
+        <v>3</v>
+      </c>
+      <c r="R20" s="23">
+        <v>5</v>
+      </c>
+      <c r="S20" s="23">
+        <v>5</v>
+      </c>
+      <c r="T20" s="24">
+        <f t="shared" ref="T20:T26" si="1">IFERROR(AVERAGE(G20:S20),"-")</f>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U20" s="32" t="str" cm="1">
+        <f t="array" ref="U20">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B21" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C21" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D21" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="23">
+        <v>1062980565</v>
+      </c>
+      <c r="G21" s="23">
+        <v>5</v>
+      </c>
+      <c r="H21" s="23">
+        <v>5</v>
+      </c>
+      <c r="I21" s="23">
+        <v>5</v>
+      </c>
+      <c r="J21" s="23">
+        <v>5</v>
+      </c>
+      <c r="K21" s="23">
+        <v>4</v>
+      </c>
+      <c r="L21" s="23">
+        <v>3</v>
+      </c>
+      <c r="M21" s="23">
+        <v>5</v>
+      </c>
+      <c r="N21" s="23">
+        <v>4</v>
+      </c>
+      <c r="O21" s="23">
+        <v>4</v>
+      </c>
+      <c r="P21" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>3</v>
+      </c>
+      <c r="R21" s="23">
+        <v>4</v>
+      </c>
+      <c r="S21" s="23">
+        <v>5</v>
+      </c>
+      <c r="T21" s="24">
+        <f t="shared" si="1"/>
+        <v>4.3076923076923075</v>
+      </c>
+      <c r="U21" s="32" t="str" cm="1">
+        <f t="array" ref="U21">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B22" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C22" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D22" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="23">
+        <v>1062539643</v>
+      </c>
+      <c r="G22" s="23">
+        <v>5</v>
+      </c>
+      <c r="H22" s="23">
+        <v>5</v>
+      </c>
+      <c r="I22" s="23">
+        <v>5</v>
+      </c>
+      <c r="J22" s="23">
+        <v>5</v>
+      </c>
+      <c r="K22" s="23">
+        <v>4</v>
+      </c>
+      <c r="L22" s="23">
+        <v>4</v>
+      </c>
+      <c r="M22" s="23">
+        <v>5</v>
+      </c>
+      <c r="N22" s="23">
+        <v>4</v>
+      </c>
+      <c r="O22" s="23">
+        <v>5</v>
+      </c>
+      <c r="P22" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="23">
+        <v>4</v>
+      </c>
+      <c r="R22" s="23">
+        <v>5</v>
+      </c>
+      <c r="S22" s="23">
+        <v>5</v>
+      </c>
+      <c r="T22" s="24">
+        <f t="shared" si="1"/>
+        <v>4.6923076923076925</v>
+      </c>
+      <c r="U22" s="32" t="str" cm="1">
+        <f t="array" ref="U22">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B23" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C23" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D23" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="23">
+        <v>1138032549</v>
+      </c>
+      <c r="G23" s="23">
+        <v>5</v>
+      </c>
+      <c r="H23" s="23">
+        <v>4</v>
+      </c>
+      <c r="I23" s="23">
+        <v>5</v>
+      </c>
+      <c r="J23" s="23">
+        <v>4</v>
+      </c>
+      <c r="K23" s="23">
+        <v>4</v>
+      </c>
+      <c r="L23" s="23">
+        <v>3</v>
+      </c>
+      <c r="M23" s="23">
+        <v>5</v>
+      </c>
+      <c r="N23" s="23">
+        <v>4</v>
+      </c>
+      <c r="O23" s="23">
+        <v>4</v>
+      </c>
+      <c r="P23" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="23">
+        <v>2</v>
+      </c>
+      <c r="R23" s="23">
+        <v>4</v>
+      </c>
+      <c r="S23" s="23">
+        <v>5</v>
+      </c>
+      <c r="T23" s="24">
+        <f t="shared" si="1"/>
+        <v>4.1538461538461542</v>
+      </c>
+      <c r="U23" s="32" t="str" cm="1">
+        <f t="array" ref="U23">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B24" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C24" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D24" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24" s="23">
+        <v>1007822238</v>
+      </c>
+      <c r="G24" s="23">
+        <v>5</v>
+      </c>
+      <c r="H24" s="23">
+        <v>3</v>
+      </c>
+      <c r="I24" s="23">
+        <v>5</v>
+      </c>
+      <c r="J24" s="23">
+        <v>5</v>
+      </c>
+      <c r="K24" s="23">
+        <v>4</v>
+      </c>
+      <c r="L24" s="23">
+        <v>3</v>
+      </c>
+      <c r="M24" s="23">
+        <v>5</v>
+      </c>
+      <c r="N24" s="23">
+        <v>5</v>
+      </c>
+      <c r="O24" s="23">
+        <v>5</v>
+      </c>
+      <c r="P24" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="23">
+        <v>3</v>
+      </c>
+      <c r="R24" s="23">
+        <v>3</v>
+      </c>
+      <c r="S24" s="23">
+        <v>5</v>
+      </c>
+      <c r="T24" s="24">
+        <f t="shared" si="1"/>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U24" s="32" t="str" cm="1">
+        <f t="array" ref="U24">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B25" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C25" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D25" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="23">
+        <v>1068439668</v>
+      </c>
+      <c r="G25" s="23">
+        <v>5</v>
+      </c>
+      <c r="H25" s="23">
+        <v>5</v>
+      </c>
+      <c r="I25" s="23">
+        <v>5</v>
+      </c>
+      <c r="J25" s="23">
+        <v>5</v>
+      </c>
+      <c r="K25" s="23">
+        <v>4</v>
+      </c>
+      <c r="L25" s="23">
+        <v>3</v>
+      </c>
+      <c r="M25" s="23">
+        <v>5</v>
+      </c>
+      <c r="N25" s="23">
+        <v>4</v>
+      </c>
+      <c r="O25" s="23">
+        <v>5</v>
+      </c>
+      <c r="P25" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>3</v>
+      </c>
+      <c r="R25" s="23">
+        <v>4</v>
+      </c>
+      <c r="S25" s="23">
+        <v>5</v>
+      </c>
+      <c r="T25" s="24">
+        <f t="shared" si="1"/>
+        <v>4.4615384615384617</v>
+      </c>
+      <c r="U25" s="32" t="str" cm="1">
+        <f t="array" ref="U25">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="36">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>8</v>
+      </c>
+      <c r="B26" s="12" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C26" s="37" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>agosto</v>
+      </c>
+      <c r="D26" s="21">
+        <v>46265</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="23">
+        <v>1140444971</v>
+      </c>
+      <c r="G26" s="23">
+        <v>5</v>
+      </c>
+      <c r="H26" s="23">
+        <v>2</v>
+      </c>
+      <c r="I26" s="23">
+        <v>5</v>
+      </c>
+      <c r="J26" s="23">
+        <v>4</v>
+      </c>
+      <c r="K26" s="23">
+        <v>4</v>
+      </c>
+      <c r="L26" s="23">
+        <v>2</v>
+      </c>
+      <c r="M26" s="23">
+        <v>5</v>
+      </c>
+      <c r="N26" s="23">
+        <v>3</v>
+      </c>
+      <c r="O26" s="23">
+        <v>5</v>
+      </c>
+      <c r="P26" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="23">
+        <v>3</v>
+      </c>
+      <c r="R26" s="23">
+        <v>3</v>
+      </c>
+      <c r="S26" s="23">
+        <v>5</v>
+      </c>
+      <c r="T26" s="24">
+        <f t="shared" si="1"/>
+        <v>3.9230769230769229</v>
+      </c>
+      <c r="U26" s="32" t="str" cm="1">
+        <f t="array" ref="U26">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
